--- a/Twitter_Donnees.xlsx
+++ b/Twitter_Donnees.xlsx
@@ -8,20 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\charl\Documents\Bourse\mon-projet-react\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6393950D-6617-4FE8-A824-3155912406E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{50C78A13-E74B-42B6-931D-157788115683}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{681F2475-BFBB-46A2-8C8E-FDF2C3BE0A13}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{34B28D09-7900-43B1-B012-2781D0CCA81A}"/>
   </bookViews>
   <sheets>
-    <sheet name="Donnees" sheetId="1" r:id="rId1"/>
+    <sheet name="Donnees_Export" sheetId="1" r:id="rId1"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId2"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Donnees!$A$2:$G$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Donnees_Export!$A$2:$D$11</definedName>
     <definedName name="cours">[1]Cours!$A$2:$H$3000</definedName>
-    <definedName name="_xlnm.Criteria" localSheetId="0">Donnees!$O$1</definedName>
+    <definedName name="_xlnm.Criteria" localSheetId="0">Donnees_Export!$L$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,15 +47,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="119">
   <si>
     <t>Colonne1</t>
   </si>
   <si>
     <t>Code</t>
-  </si>
-  <si>
-    <t>Marché</t>
   </si>
   <si>
     <t>Valeur</t>
@@ -64,19 +61,10 @@
     <t>Cours</t>
   </si>
   <si>
-    <t>RECO</t>
-  </si>
-  <si>
-    <t>Différence</t>
-  </si>
-  <si>
     <t>Les valeurs qui montent 📈 avec des volumes 👍:</t>
   </si>
   <si>
     <t>ATE</t>
-  </si>
-  <si>
-    <t>SRD</t>
   </si>
   <si>
     <t>ALTEN</t>
@@ -89,9 +77,6 @@
   </si>
   <si>
     <t>SRP</t>
-  </si>
-  <si>
-    <t>B</t>
   </si>
   <si>
     <t>SRP GROUP</t>
@@ -131,9 +116,6 @@
   </si>
   <si>
     <t>REMY COINTREAU</t>
-  </si>
-  <si>
-    <t>Moyenne</t>
   </si>
   <si>
     <t>nb &gt; 0</t>
@@ -214,16 +196,10 @@
     <t>ALTOO</t>
   </si>
   <si>
-    <t>EG</t>
-  </si>
-  <si>
     <t>TOOSLA</t>
   </si>
   <si>
     <t>AVT</t>
-  </si>
-  <si>
-    <t>C</t>
   </si>
   <si>
     <t>AVENIR TELECOM</t>
@@ -283,6 +259,60 @@
     <t>Les valeurs de confiance pour le LT👍:</t>
   </si>
   <si>
+    <t>ELIS</t>
+  </si>
+  <si>
+    <t>CARM</t>
+  </si>
+  <si>
+    <t>CARMILA</t>
+  </si>
+  <si>
+    <t>IDL</t>
+  </si>
+  <si>
+    <t>ID LOGISTICS</t>
+  </si>
+  <si>
+    <t>COV</t>
+  </si>
+  <si>
+    <t>COVIVIO</t>
+  </si>
+  <si>
+    <t>TFI</t>
+  </si>
+  <si>
+    <t>TF1</t>
+  </si>
+  <si>
+    <t>ICAD</t>
+  </si>
+  <si>
+    <t>ICADE</t>
+  </si>
+  <si>
+    <t>ADP</t>
+  </si>
+  <si>
+    <t>GFC</t>
+  </si>
+  <si>
+    <t>GECINA</t>
+  </si>
+  <si>
+    <t>ELIOR</t>
+  </si>
+  <si>
+    <t>ELIOR GROUP</t>
+  </si>
+  <si>
+    <t>BOL</t>
+  </si>
+  <si>
+    <t>BOLLORE</t>
+  </si>
+  <si>
     <t>15-janv</t>
   </si>
   <si>
@@ -322,10 +352,49 @@
     <t xml:space="preserve">Etoiles </t>
   </si>
   <si>
-    <t>Décote</t>
+    <t>RF</t>
   </si>
   <si>
-    <t>Colonne2</t>
+    <t>EURAZÉO</t>
+  </si>
+  <si>
+    <t>CEN</t>
+  </si>
+  <si>
+    <t>CRIT</t>
+  </si>
+  <si>
+    <t>QDT</t>
+  </si>
+  <si>
+    <t>QUADIENT</t>
+  </si>
+  <si>
+    <t>ARG</t>
+  </si>
+  <si>
+    <t>ARGAN</t>
+  </si>
+  <si>
+    <t>BSD</t>
+  </si>
+  <si>
+    <t>BOURSE DIRECT</t>
+  </si>
+  <si>
+    <t>DEC</t>
+  </si>
+  <si>
+    <t>JCDECAUX</t>
+  </si>
+  <si>
+    <t>RI</t>
+  </si>
+  <si>
+    <t>PERNOD RICARD</t>
+  </si>
+  <si>
+    <t>Décote</t>
   </si>
   <si>
     <t>Etoiles Small</t>
@@ -345,7 +414,7 @@
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$€-1]_-;\-* #,##0.00\ [$€-1]_-;_-* &quot;-&quot;??\ [$€-1]_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="000000"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -388,24 +457,18 @@
     </font>
     <font>
       <b/>
-      <sz val="8"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -450,12 +513,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="41"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -467,19 +524,10 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="23">
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="9" tint="0.39997558519241921"/>
-      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -495,63 +543,9 @@
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right/>
       <top style="thin">
         <color theme="9" tint="0.39997558519241921"/>
-      </top>
-      <bottom style="thin">
-        <color theme="9" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
       </top>
       <bottom style="thin">
         <color theme="9" tint="0.39997558519241921"/>
@@ -583,73 +577,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFA9D08E"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFA9D08E"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color theme="9" tint="0.39997558519241921"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color theme="9" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color theme="9" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -657,21 +584,6 @@
       </top>
       <bottom style="thin">
         <color theme="9" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color theme="9" tint="0.39997558519241921"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -688,6 +600,190 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFA9D08E"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFA9D08E"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFA9D08E"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFA9D08E"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFA9D08E"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFA9D08E"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFA9D08E"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="double">
+        <color theme="9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFA9D08E"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFA9D08E"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFA9D08E"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFA9D08E"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFA9D08E"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFA9D08E"/>
+      </right>
+      <top style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFA9D08E"/>
+      </right>
+      <top style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFA9D08E"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -695,19 +791,8 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="16" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -717,545 +802,134 @@
     <xf numFmtId="49" fontId="5" fillId="6" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="5" fillId="7" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="7" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="10" fontId="6" fillId="8" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="6" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="5" fillId="6" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="10" fontId="8" fillId="8" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="7" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="10" fontId="8" fillId="8" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="5" fillId="6" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="3" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="5" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="10" fontId="8" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="10" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="10" fontId="8" fillId="8" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="10" fontId="8" fillId="8" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="2" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="10" fontId="6" fillId="8" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="5" fillId="7" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="5" fillId="7" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="5" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="10" fontId="8" fillId="8" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="5" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="2" fontId="5" fillId="7" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="5" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="5" fillId="7" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="7" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="16" fontId="2" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="5" fillId="7" borderId="19" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="5" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="2" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="5" fillId="9" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="16" fontId="2" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="5" fillId="9" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="2" xr:uid="{062D14FD-4985-41AC-AE72-1AFF66235744}"/>
-    <cellStyle name="Normal 4" xfId="3" xr:uid="{60CACC79-7377-43F4-B63F-223BD43DCC6D}"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{CCF4ECE8-666D-4EC4-B0DE-85DFF0D56AEE}"/>
+    <cellStyle name="Normal 4" xfId="3" xr:uid="{0F2DDFE9-8BF8-49EF-A975-453BE6D4E763}"/>
     <cellStyle name="Pourcentage" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="171">
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
+  <dxfs count="106">
     <dxf>
       <font>
         <b/>
         <i val="0"/>
         <condense val="0"/>
         <extend val="0"/>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color auto="1"/>
+        <color indexed="12"/>
       </font>
     </dxf>
     <dxf>
@@ -1382,6 +1056,413 @@
         <condense val="0"/>
         <extend val="0"/>
         <color indexed="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
       </font>
     </dxf>
     <dxf>
@@ -1807,1906 +1888,6 @@
         <color indexed="18"/>
       </font>
     </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="000000"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="000000"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor indexed="9"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="000000"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor indexed="31"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="9"/>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="000000"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="000000"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor indexed="31"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color rgb="FFA9D08E"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFA9D08E"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFA9D08E"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFA9D08E"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="9"/>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="000000"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor indexed="9"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="000000"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor indexed="9"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color rgb="FFA9D08E"/>
-        </left>
-        <top style="thin">
-          <color rgb="FFA9D08E"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFA9D08E"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="9"/>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="000000"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor indexed="9"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="000000"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor indexed="9"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color rgb="FFA9D08E"/>
-        </left>
-        <top style="thin">
-          <color rgb="FFA9D08E"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFA9D08E"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="9"/>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="000000"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="000000"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor indexed="9"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="000000"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor indexed="9"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color rgb="FFA9D08E"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFA9D08E"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFA9D08E"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFA9D08E"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="9"/>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="000000"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="000000"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor indexed="9"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="000000"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor indexed="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="000000"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor indexed="9"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color rgb="FFA9D08E"/>
-        </left>
-        <top style="thin">
-          <color rgb="FFA9D08E"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFA9D08E"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="9"/>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -19569,132 +17750,6 @@
     </sheetDataSet>
   </externalBook>
 </externalLink>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{98FFFADB-5119-4692-B07C-41B5A45AB3F9}" name="Hausses288" displayName="Hausses288" ref="A29:G40" totalsRowCount="1" headerRowDxfId="170" tableBorderDxfId="169">
-  <autoFilter ref="A29:G39" xr:uid="{00000000-0009-0000-0100-000057000000}"/>
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{F1FEB98B-A1DD-4D9C-90CC-4506B36C48F9}" name="Position" dataDxfId="168" totalsRowDxfId="167"/>
-    <tableColumn id="2" xr3:uid="{9052776D-2949-4793-84CA-CFFC81F439A8}" name="Code" dataDxfId="166" totalsRowDxfId="165" dataCellStyle="Normal 2"/>
-    <tableColumn id="3" xr3:uid="{491EB7F3-13DE-42DB-B5E0-ACA21365AF0F}" name="Marché" dataDxfId="164" totalsRowDxfId="163" dataCellStyle="Normal 2"/>
-    <tableColumn id="4" xr3:uid="{DB63CB45-0C99-4382-B5CE-5ED2157829B1}" name="Valeur" dataDxfId="162" totalsRowDxfId="161" dataCellStyle="Normal 2"/>
-    <tableColumn id="5" xr3:uid="{6B115E43-B030-410F-AF1A-5C4604597C9C}" name="Colonne3" dataDxfId="160" dataCellStyle="Normal 2"/>
-    <tableColumn id="6" xr3:uid="{F546DAB9-8EDC-4C7D-A777-794FE69C8973}" name="RECO" totalsRowLabel="Moyenne" dataDxfId="159" totalsRowDxfId="158" dataCellStyle="Normal 2">
-      <calculatedColumnFormula>IFERROR(((VLOOKUP(B30,cours,7,FALSE))),"")</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="7" xr3:uid="{9B04D924-ED03-4F83-9C67-C20A4E272A87}" name="Différence" totalsRowFunction="custom" dataDxfId="157" totalsRowDxfId="156" dataCellStyle="Normal 4">
-      <calculatedColumnFormula>(F30/E30-1)</calculatedColumnFormula>
-      <totalsRowFormula>AVERAGE(G30:G39)</totalsRowFormula>
-    </tableColumn>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{45A266A2-0DFF-411C-A98B-07E482CA5960}" name="Hausses389" displayName="Hausses389" ref="A42:G53" totalsRowShown="0" headerRowDxfId="155" tableBorderDxfId="154">
-  <autoFilter ref="A42:G53" xr:uid="{00000000-0009-0000-0100-000058000000}"/>
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{DFAB3AF1-973F-414E-A6A4-267976139BEF}" name="Position" dataDxfId="153"/>
-    <tableColumn id="2" xr3:uid="{BA66AEF0-3F0A-4B13-8682-0C35EF00CCD6}" name="Code" dataDxfId="152" dataCellStyle="Normal 2"/>
-    <tableColumn id="3" xr3:uid="{DD2F6E1A-23D5-408F-8D88-11A5276E3005}" name="Marché" dataDxfId="151" dataCellStyle="Normal 2"/>
-    <tableColumn id="4" xr3:uid="{2732C3CA-76D0-4C66-AC9B-D2C835B2A117}" name="Valeur" dataDxfId="150" dataCellStyle="Normal 2"/>
-    <tableColumn id="5" xr3:uid="{73C18B83-B917-44C5-9962-6F308DEA3E74}" name="Colonne8" dataDxfId="149" dataCellStyle="Normal 2"/>
-    <tableColumn id="6" xr3:uid="{D076B95E-D9D2-4CFE-A5E8-AC7799997FF5}" name="RECO" dataDxfId="148" dataCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{928F6055-DBE1-444D-A806-7C2EFBE10692}" name="Différence" dataDxfId="147" dataCellStyle="Normal 4"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{AEDF3F1E-6CBE-41A5-9DA8-D1E1B0CAB3BD}" name="Decotes92" displayName="Decotes92" ref="A81:G92" totalsRowShown="0">
-  <autoFilter ref="A81:G92" xr:uid="{00000000-0009-0000-0100-00005B000000}"/>
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{9D746D70-B069-4D1E-9E27-06E937C1DF7C}" name="Colonne1" dataDxfId="146"/>
-    <tableColumn id="2" xr3:uid="{F22EC7B7-4867-4058-A022-AFF12D1B4AF4}" name="Décote" dataDxfId="145"/>
-    <tableColumn id="3" xr3:uid="{1AEC7F5E-4ED7-4D44-BB6C-FEB8F13A1314}" name="Colonne2" dataDxfId="144"/>
-    <tableColumn id="4" xr3:uid="{62393306-8CD3-462C-9FA4-3A31D970E059}" name="Valeur" dataDxfId="143"/>
-    <tableColumn id="5" xr3:uid="{2ADFF112-9C16-400C-B5D7-8AC977B121AE}" name="Colonne3" dataDxfId="142"/>
-    <tableColumn id="6" xr3:uid="{5C06834F-BD2B-467B-88EA-6D75624C5E8D}" name="RECO" dataDxfId="141" dataCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{210D9B93-814E-40CD-9122-61F974260CC7}" name="Différence" dataDxfId="140" dataCellStyle="Normal 4"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{817F1B9E-9349-4B4D-84C6-19363342E56C}" name="Hausses186225165" displayName="Hausses186225165" ref="A1:G12" totalsRowShown="0" headerRowDxfId="139" tableBorderDxfId="138">
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{4A80B7BB-DD5F-4208-B94A-ACDB5D71BE3D}" name="Colonne1" dataDxfId="137"/>
-    <tableColumn id="2" xr3:uid="{70A95DBB-8F46-407F-89D7-B527ED3A4D8D}" name="Code" dataDxfId="136" dataCellStyle="Normal 2"/>
-    <tableColumn id="3" xr3:uid="{5DB73F28-4E0E-4F2F-9EE1-9ADB77A10D3B}" name="Marché" dataDxfId="135" dataCellStyle="Normal 2"/>
-    <tableColumn id="4" xr3:uid="{FFD5CD1D-BA2D-4D06-9218-F05E552C5C8D}" name="Valeur" dataDxfId="134" dataCellStyle="Normal 2"/>
-    <tableColumn id="5" xr3:uid="{E8AA8DD2-EF9E-4669-8A42-72347A45B226}" name="Cours" dataDxfId="133" dataCellStyle="Normal 2"/>
-    <tableColumn id="6" xr3:uid="{5E9117C5-0FD5-451C-9C49-9772C6046481}" name="RECO" dataDxfId="132" dataCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{81555918-09A6-4334-8A12-826B36B4377C}" name="Différence" dataDxfId="131" dataCellStyle="Normal 4"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{8CF17551-22CF-4E8A-810B-1096D4BFDD72}" name="Baisses187226166" displayName="Baisses187226166" ref="A15:E27" totalsRowShown="0" headerRowDxfId="130" tableBorderDxfId="129">
-  <autoFilter ref="A15:E27" xr:uid="{00000000-0009-0000-0100-0000A5000000}"/>
-  <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{54C55259-5A7C-4298-A0AB-A144303F6A00}" name="Position" dataDxfId="128"/>
-    <tableColumn id="2" xr3:uid="{6A3733BB-8AD6-4C9D-B768-785F2A7152F7}" name="Code" dataDxfId="127" dataCellStyle="Normal 2"/>
-    <tableColumn id="3" xr3:uid="{3D26DFFC-F92F-44E2-9C31-9C254E785F5D}" name="Marché" dataDxfId="126" dataCellStyle="Normal 2"/>
-    <tableColumn id="4" xr3:uid="{C3655C0F-987C-4F15-B068-D66D25AA9511}" name="Valeur" dataDxfId="125" dataCellStyle="Normal 2"/>
-    <tableColumn id="5" xr3:uid="{BBCF84A1-4EB9-44F2-93D1-C51ECD229F3C}" name="Colonne1" dataDxfId="124" dataCellStyle="Normal 2"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{405CF69C-933B-48FA-8F1C-CDF017F8A5CA}" name="Hausses490229167" displayName="Hausses490229167" ref="A55:E66" totalsRowShown="0" headerRowDxfId="123" tableBorderDxfId="122">
-  <autoFilter ref="A55:E66" xr:uid="{00000000-0009-0000-0100-0000A6000000}"/>
-  <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{C9ACD5BA-6D6A-4307-8793-BABD5F603576}" name="Position" dataDxfId="121"/>
-    <tableColumn id="2" xr3:uid="{ACE159F4-725E-4218-9D0C-2EEF341C077B}" name="Code" dataDxfId="120"/>
-    <tableColumn id="3" xr3:uid="{761473C0-9C35-4030-A932-72C1F547AB48}" name="Marché" dataDxfId="119"/>
-    <tableColumn id="4" xr3:uid="{3C54B3DC-805F-4246-A8F3-35250C282D93}" name="Valeur" dataDxfId="118"/>
-    <tableColumn id="5" xr3:uid="{104A9296-A5B0-4DD0-8CBD-B36D29F6DD75}" name="15-janv" dataDxfId="117"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{AF93C0CB-C847-46C4-A180-3FFC5314031E}" name="Baisses291230168" displayName="Baisses291230168" ref="A68:E78" totalsRowShown="0" headerRowDxfId="116">
-  <autoFilter ref="A68:E78" xr:uid="{00000000-0009-0000-0100-0000A7000000}"/>
-  <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{B718F261-33C3-4FB5-AB71-41C1EE6288DA}" name="Position" dataDxfId="115"/>
-    <tableColumn id="2" xr3:uid="{1DDB60C3-E6C0-4E0C-BFD7-78C9CBF25958}" name="Code" dataDxfId="114" dataCellStyle="Normal 2"/>
-    <tableColumn id="3" xr3:uid="{A597C481-4B51-4B04-9544-93DBFFCC3449}" name="Marché" dataDxfId="113" dataCellStyle="Normal 2"/>
-    <tableColumn id="4" xr3:uid="{8171BA73-B860-4378-A77B-0202CF346B94}" name="Valeur" dataDxfId="112" dataCellStyle="Normal 2"/>
-    <tableColumn id="5" xr3:uid="{AD6C05C1-5862-4196-A8E6-775C4B7D1D2B}" name="Colonne1" dataDxfId="111" dataCellStyle="Normal 2"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{301315EF-F318-4BE8-A7BE-6150A1201850}" name="Etoiles93232169" displayName="Etoiles93232169" ref="A95:G106" totalsRowShown="0">
-  <autoFilter ref="A95:G106" xr:uid="{00000000-0009-0000-0100-0000A8000000}"/>
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{96D70AE3-B41A-4101-B944-1412C83DD25D}" name="Colonne1"/>
-    <tableColumn id="2" xr3:uid="{74475B3C-40BB-47B9-821C-039972863E6C}" name="Etoiles Small" dataDxfId="110"/>
-    <tableColumn id="3" xr3:uid="{42D9D0A4-227D-4FD9-B295-F9270A2711DF}" name="Colonne2" dataDxfId="109"/>
-    <tableColumn id="4" xr3:uid="{13CBD6B1-56E5-4A1C-810E-A82A3385A0E2}" name="Colonne3" dataDxfId="108"/>
-    <tableColumn id="5" xr3:uid="{BA3E8F16-6EAB-4949-8BAC-A3D72090901D}" name="17-juil" dataDxfId="107"/>
-    <tableColumn id="6" xr3:uid="{DFE0B644-B9DB-4B93-95B9-0E53D6DDD8A4}" name="RECO" dataDxfId="106" dataCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{C4194020-A08A-43E4-88FF-2F06994DE07F}" name="Différence" dataDxfId="105" dataCellStyle="Normal 4"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -19958,3029 +18013,1601 @@
 </a:theme>
 </file>
 
-<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
-<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="438" row="2">
-    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </wetp:taskpane>
-  <wetp:taskpane dockstate="right" visibility="0" width="438" row="3">
-    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-  </wetp:taskpane>
-  <wetp:taskpane dockstate="right" visibility="0" width="525" row="2">
-    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
-  </wetp:taskpane>
-  <wetp:taskpane dockstate="right" visibility="0" width="613" row="3">
-    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
-  </wetp:taskpane>
-  <wetp:taskpane dockstate="right" visibility="0" width="613" row="1">
-    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
-  </wetp:taskpane>
-  <wetp:taskpane dockstate="right" visibility="0" width="613" row="1">
-    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
-  </wetp:taskpane>
-</wetp:taskpanes>
-</file>
-
-<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
-<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{27694297-9725-4637-AA53-12676573BE75}">
-  <we:reference id="wa104168603" version="1.0.0.6" store="fr-FR" storeType="OMEX"/>
-  <we:alternateReferences>
-    <we:reference id="WA104168603" version="1.0.0.6" store="WA104168603" storeType="OMEX"/>
-  </we:alternateReferences>
-  <we:properties>
-    <we:property name="savedSettings" value="{&quot;state&quot;:{&quot;seed&quot;:61630,&quot;currentseed&quot;:null,&quot;powerbi&quot;:{&quot;datasetId&quot;:null,&quot;tableName&quot;:null,&quot;datasetName&quot;:null},&quot;powerBILoaded&quot;:false,&quot;VisualizationName&quot;:&quot;Measure trend (all measures)&quot;,&quot;category&quot;:&quot;Category&quot;,&quot;aggregate&quot;:&quot;Avg&quot;,&quot;measure&quot;:&quot;TableRows&quot;,&quot;minDate&quot;:null,&quot;toolbarVisible&quot;:true},&quot;date&quot;:&quot;Sun, 15 Dec 2019 18:17:27 GMT&quot;,&quot;appVersion&quot;:&quot;1.140.6206.22452, 28-12-2016 12:28:24&quot;}"/>
-  </we:properties>
-  <we:bindings/>
-  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-  <we:extLst>
-    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{D87F86FE-615C-45B5-9D79-34F1136793EB}">
-      <we:containsCustomFunctions/>
-    </a:ext>
-  </we:extLst>
-</we:webextension>
-</file>
-
-<file path=xl/webextensions/webextension2.xml><?xml version="1.0" encoding="utf-8"?>
-<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{E9C4EC33-3172-4E64-9A5C-6CA5E22C122F}">
-  <we:reference id="wa104381504" version="1.0.0.0" store="en-US" storeType="OMEX"/>
-  <we:alternateReferences>
-    <we:reference id="wa104381504" version="1.0.0.0" store="wa104381504" storeType="OMEX"/>
-  </we:alternateReferences>
-  <we:properties/>
-  <we:bindings/>
-  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-  <we:extLst>
-    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{D87F86FE-615C-45B5-9D79-34F1136793EB}">
-      <we:containsCustomFunctions/>
-    </a:ext>
-  </we:extLst>
-</we:webextension>
-</file>
-
-<file path=xl/webextensions/webextension3.xml><?xml version="1.0" encoding="utf-8"?>
-<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{2F985317-8844-4FF0-A513-A8200FCBA999}">
-  <we:reference id="wa200005502" version="1.0.0.11" store="fr-FR" storeType="OMEX"/>
-  <we:alternateReferences>
-    <we:reference id="WA200005502" version="1.0.0.11" store="WA200005502" storeType="OMEX"/>
-  </we:alternateReferences>
-  <we:properties>
-    <we:property name="docId" value="&quot;Bn5xycuUiCYpO_ssBGfGU&quot;"/>
-  </we:properties>
-  <we:bindings/>
-  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-  <we:extLst>
-    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{D87F86FE-615C-45B5-9D79-34F1136793EB}">
-      <we:containsCustomFunctions/>
-    </a:ext>
-    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{7C84B067-C214-45C3-A712-C9D94CD141B2}">
-      <we:customFunctionIdList>
-        <we:customFunctionIds>_xldudf_GPT</we:customFunctionIds>
-        <we:customFunctionIds>_xldudf_GPT_LIST</we:customFunctionIds>
-        <we:customFunctionIds>_xldudf_GPT_HLIST</we:customFunctionIds>
-        <we:customFunctionIds>_xldudf_GPT_CLASSIFY</we:customFunctionIds>
-        <we:customFunctionIds>_xldudf_GPT_TRANSLATE</we:customFunctionIds>
-        <we:customFunctionIds>_xldudf_GPT_EXTRACT</we:customFunctionIds>
-        <we:customFunctionIds>_xldudf_GPT_TAG</we:customFunctionIds>
-        <we:customFunctionIds>_xldudf_GPT_CONVERT</we:customFunctionIds>
-        <we:customFunctionIds>_xldudf_GPT_FORMAT</we:customFunctionIds>
-        <we:customFunctionIds>_xldudf_GPT_SUMMARIZE</we:customFunctionIds>
-        <we:customFunctionIds>_xldudf_GPT_TABLE</we:customFunctionIds>
-        <we:customFunctionIds>_xldudf_GPT_FILL</we:customFunctionIds>
-        <we:customFunctionIds>_xldudf_GPT_SPLIT</we:customFunctionIds>
-        <we:customFunctionIds>_xldudf_GPT_HSPLIT</we:customFunctionIds>
-        <we:customFunctionIds>_xldudf_GPT_EDIT</we:customFunctionIds>
-        <we:customFunctionIds>_xldudf_GPT_MATCH</we:customFunctionIds>
-        <we:customFunctionIds>_xldudf_GPT_VISION</we:customFunctionIds>
-      </we:customFunctionIdList>
-    </a:ext>
-  </we:extLst>
-</we:webextension>
-</file>
-
-<file path=xl/webextensions/webextension4.xml><?xml version="1.0" encoding="utf-8"?>
-<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{CB5AB138-7CE9-40B5-9DEC-7AE53947ACF3}">
-  <we:reference id="wa200005669" version="2.0.0.0" store="en-US" storeType="OMEX"/>
-  <we:alternateReferences>
-    <we:reference id="wa200005669" version="2.0.0.0" store="" storeType="OMEX"/>
-  </we:alternateReferences>
-  <we:properties/>
-  <we:bindings/>
-  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</we:webextension>
-</file>
-
-<file path=xl/webextensions/webextension5.xml><?xml version="1.0" encoding="utf-8"?>
-<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{FDB29EDE-E958-4DA0-B998-0E0FE327A19A}">
-  <we:reference id="WA200009404" version="1.0.0.8" store="Omex" storeType="OMEX"/>
-  <we:alternateReferences>
-    <we:reference id="WA200009404" version="1.0.0.8" store="WA200009404" storeType="OMEX"/>
-  </we:alternateReferences>
-  <we:properties>
-    <we:property name="claude.fileId" value="&quot;2be0ef09-03b9-4d7e-af03-0136b99d7f8d&quot;"/>
-  </we:properties>
-  <we:bindings/>
-  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</we:webextension>
-</file>
-
-<file path=xl/webextensions/webextension6.xml><?xml version="1.0" encoding="utf-8"?>
-<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{ED2E914B-AEAC-4FC6-9608-D163F48C135E}">
-  <we:reference id="wa200007447" version="1.1.6.7" store="fr-FR" storeType="OMEX"/>
-  <we:alternateReferences>
-    <we:reference id="wa200007447" version="1.1.6.7" store="wa200007447" storeType="OMEX"/>
-  </we:alternateReferences>
-  <we:properties/>
-  <we:bindings/>
-  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-  <we:extLst>
-    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{D87F86FE-615C-45B5-9D79-34F1136793EB}">
-      <we:containsCustomFunctions/>
-    </a:ext>
-    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{7C84B067-C214-45C3-A712-C9D94CD141B2}">
-      <we:customFunctionIdList>
-        <we:customFunctionIds>_xldudf_BOARDFLARE_EXEC</we:customFunctionIds>
-      </we:customFunctionIdList>
-    </a:ext>
-  </we:extLst>
-</we:webextension>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54D12E2B-B639-4E4D-8EAF-C5301C366D95}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AEB6014-3865-43FC-80C0-F593C28B822B}">
   <sheetPr codeName="Feuil2"/>
-  <dimension ref="A1:V111"/>
+  <dimension ref="A1:S111"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="13.07421875" style="15" customWidth="1"/>
-    <col min="3" max="3" width="10.4609375" customWidth="1"/>
-    <col min="4" max="4" width="27.07421875" customWidth="1"/>
-    <col min="5" max="5" width="12.69140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.07421875" style="15"/>
-    <col min="9" max="9" width="6.3046875" style="7" customWidth="1"/>
-    <col min="11" max="11" width="6.765625" customWidth="1"/>
+    <col min="2" max="2" width="13.07421875" style="6" customWidth="1"/>
+    <col min="3" max="3" width="27.07421875" customWidth="1"/>
+    <col min="4" max="4" width="12.69140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.07421875" style="6"/>
+    <col min="6" max="6" width="6.3046875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="6.765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="M1" s="3"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
+      <c r="P1" s="5"/>
+      <c r="Q1" s="5"/>
+      <c r="R1" s="5"/>
+      <c r="S1" s="5"/>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="A2" s="31">
+        <v>1</v>
+      </c>
+      <c r="B2" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="C2" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="D2" s="34">
+        <v>79.8</v>
+      </c>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="9"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="A3" s="35">
+        <v>2</v>
+      </c>
+      <c r="B3" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="P1" s="8"/>
-      <c r="Q1" s="9"/>
-      <c r="R1" s="9"/>
-      <c r="S1" s="10"/>
-      <c r="T1" s="10"/>
-      <c r="U1" s="10"/>
-      <c r="V1" s="10"/>
+      <c r="C3" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="34">
+        <v>195.6</v>
+      </c>
+      <c r="E3" s="2"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="9"/>
+      <c r="N3" s="10"/>
     </row>
-    <row r="2" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="11">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="A4" s="31">
+        <v>3</v>
+      </c>
+      <c r="B4" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="34">
+        <v>0.8</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="9"/>
+      <c r="N4" s="10"/>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="A5" s="35">
+        <v>4</v>
+      </c>
+      <c r="B5" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="34">
+        <v>6.2050000000000001</v>
+      </c>
+      <c r="E5" s="2"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="9"/>
+      <c r="N5" s="10"/>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="A6" s="31">
+        <v>5</v>
+      </c>
+      <c r="B6" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="34">
+        <v>28.79</v>
+      </c>
+      <c r="E6" s="2"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="9"/>
+      <c r="N6" s="10"/>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="A7" s="35">
+        <v>6</v>
+      </c>
+      <c r="B7" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="34">
+        <v>0.2</v>
+      </c>
+      <c r="E7" s="2"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="9"/>
+      <c r="N7" s="10"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="A8" s="31">
+        <v>7</v>
+      </c>
+      <c r="B8" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="34">
+        <v>42.66</v>
+      </c>
+      <c r="E8" s="2"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="9"/>
+      <c r="N8" s="10"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="A9" s="35">
+        <v>8</v>
+      </c>
+      <c r="B9" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="34">
+        <v>63</v>
+      </c>
+      <c r="E9" s="2"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="9"/>
+      <c r="N9" s="10"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="A10" s="31">
+        <v>9</v>
+      </c>
+      <c r="B10" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="34">
+        <v>0.23300000000000001</v>
+      </c>
+      <c r="E10" s="2"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="9"/>
+      <c r="N10" s="10"/>
+    </row>
+    <row r="11" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A11" s="35">
+        <v>10</v>
+      </c>
+      <c r="B11" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="34">
+        <v>49.02</v>
+      </c>
+      <c r="E11" s="2"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="9"/>
+      <c r="N11" s="10"/>
+    </row>
+    <row r="12" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="40"/>
+      <c r="B12" s="41"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="56"/>
+      <c r="E12" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="F12" s="13" t="e">
+        <v>#REF!</v>
+      </c>
+      <c r="G12" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="H12" s="15" t="e">
+        <v>#REF!</v>
+      </c>
+      <c r="I12" s="9"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="E13" s="2"/>
+      <c r="F13"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="E14" s="2"/>
+      <c r="F14"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="A15" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="C15" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15" s="57" t="s">
+        <v>0</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="A16" s="31">
+        <v>1</v>
+      </c>
+      <c r="B16" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" s="58">
+        <v>19.399999999999999</v>
+      </c>
+      <c r="E16" s="16"/>
+      <c r="F16"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A17" s="35">
+        <v>2</v>
+      </c>
+      <c r="B17" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" s="58">
+        <v>6.33</v>
+      </c>
+      <c r="E17" s="2"/>
+      <c r="F17"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A18" s="31">
+        <v>3</v>
+      </c>
+      <c r="B18" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="D18" s="58">
+        <v>0.154</v>
+      </c>
+      <c r="E18" s="2"/>
+      <c r="F18" s="7"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A19" s="35">
+        <v>4</v>
+      </c>
+      <c r="B19" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="D19" s="58">
+        <v>42.895000000000003</v>
+      </c>
+      <c r="E19" s="2"/>
+      <c r="F19"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A20" s="31">
+        <v>5</v>
+      </c>
+      <c r="B20" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="C20" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="D20" s="58">
+        <v>75.400000000000006</v>
+      </c>
+      <c r="E20" s="2"/>
+      <c r="F20" s="7"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A21" s="35">
+        <v>6</v>
+      </c>
+      <c r="B21" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="C21" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="D21" s="58">
+        <v>12.75</v>
+      </c>
+      <c r="E21" s="2"/>
+      <c r="F21"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A22" s="31">
+        <v>7</v>
+      </c>
+      <c r="B22" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="D22" s="58">
+        <v>34.93</v>
+      </c>
+      <c r="E22" s="2"/>
+      <c r="F22"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A23" s="35">
         <v>8</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="B23" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23" s="33" t="s">
+        <v>41</v>
+      </c>
+      <c r="D23" s="58">
+        <v>0.16800000000000001</v>
+      </c>
+      <c r="E23" s="2"/>
+      <c r="F23"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A24" s="31">
         <v>9</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="B24" s="32" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="D24" s="58">
+        <v>8.56</v>
+      </c>
+      <c r="E24" s="2"/>
+      <c r="F24"/>
+    </row>
+    <row r="25" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="35">
         <v>10</v>
       </c>
-      <c r="E2" s="12">
+      <c r="B25" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="C25" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="D25" s="58">
+        <v>6.76</v>
+      </c>
+      <c r="E25" s="2"/>
+      <c r="F25"/>
+    </row>
+    <row r="26" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="31"/>
+      <c r="B26" s="32"/>
+      <c r="C26" s="59"/>
+      <c r="D26" s="58"/>
+      <c r="E26" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="F26" s="13" t="e">
+        <v>#REF!</v>
+      </c>
+      <c r="G26" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="H26" s="15" t="e">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A27" s="60"/>
+      <c r="B27" s="61"/>
+      <c r="C27" s="62"/>
+      <c r="D27" s="63"/>
+      <c r="E27" s="2"/>
+      <c r="F27"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="E28" s="2"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A29" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C29" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="D29" s="30" t="s">
+        <v>46</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F29"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A30" s="31">
+        <v>1</v>
+      </c>
+      <c r="B30" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="C30" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="D30" s="34">
+        <v>2E-3</v>
+      </c>
+      <c r="E30"/>
+      <c r="F30"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A31" s="35">
+        <v>2</v>
+      </c>
+      <c r="B31" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="C31" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="D31" s="34">
+        <v>9.2999999999999999E-2</v>
+      </c>
+      <c r="E31"/>
+      <c r="F31"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A32" s="31">
+        <v>3</v>
+      </c>
+      <c r="B32" s="32" t="s">
+        <v>52</v>
+      </c>
+      <c r="C32" s="33" t="s">
+        <v>53</v>
+      </c>
+      <c r="D32" s="34">
+        <v>0.28299999999999997</v>
+      </c>
+      <c r="E32"/>
+      <c r="F32"/>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A33" s="35">
+        <v>4</v>
+      </c>
+      <c r="B33" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="C33" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="D33" s="34">
+        <v>3.9</v>
+      </c>
+      <c r="E33"/>
+      <c r="F33"/>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A34" s="31">
+        <v>5</v>
+      </c>
+      <c r="B34" s="32" t="s">
+        <v>56</v>
+      </c>
+      <c r="C34" s="33" t="s">
+        <v>57</v>
+      </c>
+      <c r="D34" s="34">
+        <v>1.18</v>
+      </c>
+      <c r="E34"/>
+      <c r="F34"/>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A35" s="35">
+        <v>6</v>
+      </c>
+      <c r="B35" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="C35" s="33" t="s">
+        <v>59</v>
+      </c>
+      <c r="D35" s="34">
+        <v>0.72799999999999998</v>
+      </c>
+      <c r="E35"/>
+      <c r="F35"/>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A36" s="31">
+        <v>7</v>
+      </c>
+      <c r="B36" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="C36" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="D36" s="34">
+        <v>1.21</v>
+      </c>
+      <c r="E36"/>
+      <c r="F36"/>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A37" s="35">
+        <v>8</v>
+      </c>
+      <c r="B37" s="32" t="s">
+        <v>62</v>
+      </c>
+      <c r="C37" s="33" t="s">
+        <v>63</v>
+      </c>
+      <c r="D37" s="34">
+        <v>8</v>
+      </c>
+      <c r="E37"/>
+      <c r="F37"/>
+      <c r="M37" s="17"/>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A38" s="31">
+        <v>9</v>
+      </c>
+      <c r="B38" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="C38" s="33" t="s">
+        <v>65</v>
+      </c>
+      <c r="D38" s="34">
+        <v>17.75</v>
+      </c>
+      <c r="E38"/>
+      <c r="F38"/>
+      <c r="M38" s="17"/>
+    </row>
+    <row r="39" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A39" s="35">
+        <v>10</v>
+      </c>
+      <c r="B39" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="C39" s="33" t="s">
+        <v>67</v>
+      </c>
+      <c r="D39" s="34">
+        <v>2.04</v>
+      </c>
+      <c r="E39"/>
+      <c r="F39"/>
+    </row>
+    <row r="40" spans="1:13" ht="15" thickTop="1" x14ac:dyDescent="0.4">
+      <c r="A40" s="36"/>
+      <c r="B40" s="37"/>
+      <c r="C40" s="38"/>
+      <c r="D40" s="39"/>
+      <c r="E40" t="e">
+        <v>#REF!</v>
+      </c>
+      <c r="F40"/>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="B41" s="18"/>
+      <c r="C41" s="19"/>
+      <c r="E41"/>
+      <c r="F41"/>
+      <c r="H41" s="15"/>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A42" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="B42" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C42" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="D42" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F42"/>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A43" s="31">
+        <v>1</v>
+      </c>
+      <c r="B43" s="32" t="s">
+        <v>70</v>
+      </c>
+      <c r="C43" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D43" s="34">
+        <v>26.06</v>
+      </c>
+      <c r="E43"/>
+      <c r="F43"/>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A44" s="35">
+        <v>2</v>
+      </c>
+      <c r="B44" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="C44" s="33" t="s">
+        <v>72</v>
+      </c>
+      <c r="D44" s="34">
+        <v>16.64</v>
+      </c>
+      <c r="E44"/>
+      <c r="F44"/>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A45" s="31">
+        <v>3</v>
+      </c>
+      <c r="B45" s="32" t="s">
+        <v>73</v>
+      </c>
+      <c r="C45" s="33" t="s">
+        <v>74</v>
+      </c>
+      <c r="D45" s="34">
+        <v>364</v>
+      </c>
+      <c r="E45"/>
+      <c r="F45"/>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A46" s="35">
+        <v>4</v>
+      </c>
+      <c r="B46" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="C46" s="33" t="s">
+        <v>76</v>
+      </c>
+      <c r="D46" s="34">
+        <v>54.25</v>
+      </c>
+      <c r="E46"/>
+      <c r="F46"/>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A47" s="31">
+        <v>5</v>
+      </c>
+      <c r="B47" s="32" t="s">
+        <v>77</v>
+      </c>
+      <c r="C47" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="D47" s="34">
+        <v>7.12</v>
+      </c>
+      <c r="E47"/>
+      <c r="F47"/>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A48" s="35">
+        <v>6</v>
+      </c>
+      <c r="B48" s="32" t="s">
+        <v>79</v>
+      </c>
+      <c r="C48" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="D48" s="34">
+        <v>19.63</v>
+      </c>
+      <c r="E48"/>
+      <c r="F48"/>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A49" s="31">
+        <v>7</v>
+      </c>
+      <c r="B49" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="C49" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="D49" s="34">
+        <v>112.2</v>
+      </c>
+      <c r="E49"/>
+      <c r="F49"/>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A50" s="35">
+        <v>8</v>
+      </c>
+      <c r="B50" s="32" t="s">
+        <v>82</v>
+      </c>
+      <c r="C50" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="D50" s="34">
+        <v>75.75</v>
+      </c>
+      <c r="E50"/>
+      <c r="F50"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A51" s="31">
+        <v>9</v>
+      </c>
+      <c r="B51" s="32" t="s">
+        <v>84</v>
+      </c>
+      <c r="C51" s="33" t="s">
+        <v>85</v>
+      </c>
+      <c r="D51" s="34">
+        <v>2.1520000000000001</v>
+      </c>
+      <c r="E51"/>
+      <c r="F51"/>
+    </row>
+    <row r="52" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A52" s="35">
+        <v>10</v>
+      </c>
+      <c r="B52" s="32" t="s">
+        <v>86</v>
+      </c>
+      <c r="C52" s="33" t="s">
+        <v>87</v>
+      </c>
+      <c r="D52" s="34">
+        <v>4.0780000000000003</v>
+      </c>
+      <c r="E52"/>
+      <c r="F52"/>
+    </row>
+    <row r="53" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A53" s="40"/>
+      <c r="B53" s="41"/>
+      <c r="C53" s="42"/>
+      <c r="D53" s="43"/>
+      <c r="E53" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="F53" s="13" t="e">
+        <v>#REF!</v>
+      </c>
+      <c r="G53" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="H53" s="15" t="e">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B54" s="4"/>
+      <c r="C54" s="19"/>
+      <c r="E54" s="2"/>
+      <c r="F54"/>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A55" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="B55" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C55" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="D55" s="64" t="s">
+        <v>88</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A56" s="31">
+        <v>1</v>
+      </c>
+      <c r="B56" s="49" t="s">
+        <v>5</v>
+      </c>
+      <c r="C56" s="49" t="s">
+        <v>6</v>
+      </c>
+      <c r="D56" s="65">
         <v>79.8</v>
       </c>
-      <c r="F2" s="13">
-        <f t="shared" ref="F2:F11" si="0">IFERROR(((VLOOKUP(B2,cours,7,FALSE))),"")</f>
-        <v>79.8</v>
-      </c>
-      <c r="G2" s="14">
-        <f t="shared" ref="G2:G11" si="1">(F2/E2-1)</f>
+      <c r="E56" s="2"/>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A57" s="35">
+        <v>2</v>
+      </c>
+      <c r="B57" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="52" t="s">
+        <v>8</v>
+      </c>
+      <c r="D57" s="65">
+        <v>195.6</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57"/>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A58" s="31">
+        <v>3</v>
+      </c>
+      <c r="B58" s="49" t="s">
+        <v>15</v>
+      </c>
+      <c r="C58" s="49" t="s">
+        <v>16</v>
+      </c>
+      <c r="D58" s="65">
+        <v>42.66</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58"/>
+      <c r="H58" s="20"/>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A59" s="35">
+        <v>4</v>
+      </c>
+      <c r="B59" s="52" t="s">
+        <v>90</v>
+      </c>
+      <c r="C59" s="52" t="s">
+        <v>91</v>
+      </c>
+      <c r="D59" s="65">
+        <v>59.65</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59"/>
+      <c r="H59" s="20"/>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A60" s="31">
+        <v>5</v>
+      </c>
+      <c r="B60" s="49" t="s">
+        <v>17</v>
+      </c>
+      <c r="C60" s="49" t="s">
+        <v>18</v>
+      </c>
+      <c r="D60" s="65">
+        <v>63</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60"/>
+      <c r="H60" s="20"/>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A61" s="35">
+        <v>6</v>
+      </c>
+      <c r="B61" s="52" t="s">
+        <v>92</v>
+      </c>
+      <c r="C61" s="52" t="s">
+        <v>93</v>
+      </c>
+      <c r="D61" s="65">
+        <v>75.83</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61"/>
+      <c r="H61" s="20"/>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A62" s="31">
+        <v>7</v>
+      </c>
+      <c r="B62" s="49" t="s">
+        <v>11</v>
+      </c>
+      <c r="C62" s="49" t="s">
+        <v>11</v>
+      </c>
+      <c r="D62" s="65">
+        <v>6.2050000000000001</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62"/>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A63" s="35">
+        <v>8</v>
+      </c>
+      <c r="B63" s="52" t="s">
+        <v>94</v>
+      </c>
+      <c r="C63" s="52" t="s">
+        <v>95</v>
+      </c>
+      <c r="D63" s="65">
+        <v>95.02</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63"/>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A64" s="31">
+        <v>9</v>
+      </c>
+      <c r="B64" s="49" t="s">
+        <v>96</v>
+      </c>
+      <c r="C64" s="49" t="s">
+        <v>97</v>
+      </c>
+      <c r="D64" s="65">
+        <v>107.1</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64"/>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A65" s="35">
+        <v>10</v>
+      </c>
+      <c r="B65" s="52" t="s">
+        <v>98</v>
+      </c>
+      <c r="C65" s="52" t="s">
+        <v>99</v>
+      </c>
+      <c r="D65" s="65">
+        <v>8.125</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65"/>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A66" s="40"/>
+      <c r="B66" s="41"/>
+      <c r="C66" s="42"/>
+      <c r="D66" s="66"/>
+      <c r="E66" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="F66" s="2" t="e">
+        <v>#REF!</v>
+      </c>
+      <c r="G66" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="H66" s="15" t="e">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B67" s="4"/>
+      <c r="C67" s="19"/>
+      <c r="E67" s="2"/>
+      <c r="F67"/>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A68" s="44" t="s">
+        <v>25</v>
+      </c>
+      <c r="B68" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="C68" s="46" t="s">
+        <v>2</v>
+      </c>
+      <c r="D68" s="68" t="s">
         <v>0</v>
       </c>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="17"/>
-      <c r="L2" s="18"/>
-      <c r="T2" s="10"/>
-      <c r="U2" s="10"/>
-      <c r="V2" s="10"/>
+      <c r="E68" s="1" t="s">
+        <v>100</v>
+      </c>
     </row>
-    <row r="3" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="19">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A69" s="48">
+        <v>1</v>
+      </c>
+      <c r="B69" s="49" t="s">
+        <v>15</v>
+      </c>
+      <c r="C69" s="49" t="s">
+        <v>16</v>
+      </c>
+      <c r="D69" s="69">
+        <v>42.66</v>
+      </c>
+      <c r="E69" s="2"/>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A70" s="51">
         <v>2</v>
       </c>
-      <c r="B3" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="9" t="s">
+      <c r="B70" s="52" t="s">
+        <v>94</v>
+      </c>
+      <c r="C70" s="52" t="s">
+        <v>95</v>
+      </c>
+      <c r="D70" s="69">
+        <v>95.02</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70"/>
+      <c r="G70" s="19"/>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A71" s="48">
+        <v>3</v>
+      </c>
+      <c r="B71" s="49" t="s">
+        <v>101</v>
+      </c>
+      <c r="C71" s="49" t="s">
+        <v>102</v>
+      </c>
+      <c r="D71" s="69">
+        <v>46.2</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71"/>
+      <c r="G71" s="19"/>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A72" s="51">
+        <v>4</v>
+      </c>
+      <c r="B72" s="52" t="s">
+        <v>103</v>
+      </c>
+      <c r="C72" s="52" t="s">
+        <v>104</v>
+      </c>
+      <c r="D72" s="69">
+        <v>55.6</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72"/>
+      <c r="G72" s="22"/>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A73" s="48">
+        <v>5</v>
+      </c>
+      <c r="B73" s="49" t="s">
+        <v>105</v>
+      </c>
+      <c r="C73" s="49" t="s">
+        <v>106</v>
+      </c>
+      <c r="D73" s="69">
+        <v>13.46</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73"/>
+      <c r="G73" s="22"/>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A74" s="51">
+        <v>6</v>
+      </c>
+      <c r="B74" s="52" t="s">
+        <v>107</v>
+      </c>
+      <c r="C74" s="52" t="s">
+        <v>108</v>
+      </c>
+      <c r="D74" s="69">
+        <v>76.5</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74"/>
+      <c r="G74" s="22"/>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A75" s="48">
+        <v>7</v>
+      </c>
+      <c r="B75" s="49" t="s">
+        <v>109</v>
+      </c>
+      <c r="C75" s="49" t="s">
+        <v>110</v>
+      </c>
+      <c r="D75" s="69">
+        <v>5.44</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" s="17"/>
+      <c r="G75" s="22"/>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A76" s="51">
+        <v>8</v>
+      </c>
+      <c r="B76" s="52" t="s">
+        <v>111</v>
+      </c>
+      <c r="C76" s="52" t="s">
+        <v>112</v>
+      </c>
+      <c r="D76" s="69">
+        <v>22.42</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76"/>
+      <c r="G76" s="19"/>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A77" s="48">
         <v>9</v>
       </c>
-      <c r="D3" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="12">
-        <v>195.6</v>
-      </c>
-      <c r="F3" s="13">
-        <f t="shared" si="0"/>
-        <v>195.6</v>
-      </c>
-      <c r="G3" s="14">
-        <f t="shared" si="1"/>
+      <c r="B77" s="49" t="s">
+        <v>92</v>
+      </c>
+      <c r="C77" s="49" t="s">
+        <v>93</v>
+      </c>
+      <c r="D77" s="69">
+        <v>75.83</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77"/>
+      <c r="G77" s="19"/>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A78" s="70">
+        <v>10</v>
+      </c>
+      <c r="B78" s="71" t="s">
+        <v>113</v>
+      </c>
+      <c r="C78" s="71" t="s">
+        <v>114</v>
+      </c>
+      <c r="D78" s="72">
+        <v>68.28</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78"/>
+      <c r="G78" s="19"/>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="E79" s="2"/>
+      <c r="F79"/>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="E80" s="2"/>
+      <c r="F80"/>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A81" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="H3" s="7"/>
-      <c r="I3" s="16"/>
-      <c r="J3" s="16"/>
-      <c r="K3" s="17"/>
-      <c r="L3" s="18"/>
-      <c r="Q3" s="20"/>
+      <c r="B81" s="45" t="s">
+        <v>115</v>
+      </c>
+      <c r="C81" s="46" t="s">
+        <v>2</v>
+      </c>
+      <c r="D81" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="E81" s="15" t="e">
+        <v>#REF!</v>
+      </c>
+      <c r="F81"/>
     </row>
-    <row r="4" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="11">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A82" s="48">
+        <v>1</v>
+      </c>
+      <c r="B82" s="49"/>
+      <c r="C82" s="49"/>
+      <c r="D82" s="50"/>
+      <c r="E82"/>
+      <c r="F82"/>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A83" s="51">
+        <v>2</v>
+      </c>
+      <c r="B83" s="52"/>
+      <c r="C83" s="52"/>
+      <c r="D83" s="50"/>
+      <c r="E83"/>
+      <c r="F83"/>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A84" s="48">
         <v>3</v>
       </c>
-      <c r="B4" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="12">
-        <v>0.8</v>
-      </c>
-      <c r="F4" s="13">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="G4" s="14">
-        <f t="shared" si="1"/>
+      <c r="B84" s="49"/>
+      <c r="C84" s="49"/>
+      <c r="D84" s="50"/>
+      <c r="E84"/>
+      <c r="F84"/>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A85" s="51">
+        <v>4</v>
+      </c>
+      <c r="B85" s="52"/>
+      <c r="C85" s="52"/>
+      <c r="D85" s="50"/>
+      <c r="E85"/>
+      <c r="F85"/>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A86" s="48">
+        <v>5</v>
+      </c>
+      <c r="B86" s="49"/>
+      <c r="C86" s="49"/>
+      <c r="D86" s="50"/>
+      <c r="E86"/>
+      <c r="F86"/>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A87" s="51">
+        <v>6</v>
+      </c>
+      <c r="B87" s="52"/>
+      <c r="C87" s="52"/>
+      <c r="D87" s="50"/>
+      <c r="E87"/>
+      <c r="F87"/>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A88" s="48">
+        <v>7</v>
+      </c>
+      <c r="B88" s="49"/>
+      <c r="C88" s="49"/>
+      <c r="D88" s="50"/>
+      <c r="E88"/>
+      <c r="F88"/>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A89" s="51">
+        <v>8</v>
+      </c>
+      <c r="B89" s="52"/>
+      <c r="C89" s="52"/>
+      <c r="D89" s="50"/>
+      <c r="E89"/>
+      <c r="F89"/>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A90" s="48">
+        <v>9</v>
+      </c>
+      <c r="B90" s="49"/>
+      <c r="C90" s="49"/>
+      <c r="D90" s="50"/>
+      <c r="E90"/>
+      <c r="F90"/>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A91" s="51">
+        <v>10</v>
+      </c>
+      <c r="B91" s="52"/>
+      <c r="C91" s="52"/>
+      <c r="D91" s="50"/>
+      <c r="E91"/>
+      <c r="F91"/>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A92" s="53"/>
+      <c r="B92" s="54"/>
+      <c r="C92" s="20"/>
+      <c r="D92" s="55"/>
+      <c r="E92"/>
+      <c r="F92"/>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="E93" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="F93" s="2" t="e">
+        <v>#REF!</v>
+      </c>
+      <c r="G93" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="H93" s="15" t="e">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="E94" s="21"/>
+      <c r="G94" s="21"/>
+      <c r="H94" s="15"/>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A95" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="H4" s="7"/>
-      <c r="I4" s="16"/>
-      <c r="J4" s="16"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="18"/>
-      <c r="Q4" s="20"/>
+      <c r="B95" s="45" t="s">
+        <v>116</v>
+      </c>
+      <c r="C95" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="D95" s="47" t="s">
+        <v>117</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F95" s="24"/>
+      <c r="G95" s="25"/>
+      <c r="I95" s="26"/>
     </row>
-    <row r="5" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="19">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A96" s="48">
+        <v>1</v>
+      </c>
+      <c r="B96" s="49"/>
+      <c r="C96" s="49"/>
+      <c r="D96" s="34"/>
+      <c r="E96" s="2"/>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A97" s="51">
+        <v>2</v>
+      </c>
+      <c r="B97" s="52"/>
+      <c r="C97" s="52"/>
+      <c r="D97" s="34"/>
+      <c r="E97" s="2"/>
+      <c r="F97"/>
+      <c r="G97" s="17"/>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A98" s="48">
+        <v>3</v>
+      </c>
+      <c r="B98" s="49"/>
+      <c r="C98" s="49"/>
+      <c r="D98" s="34"/>
+      <c r="E98" s="2"/>
+      <c r="F98"/>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A99" s="51">
         <v>4</v>
       </c>
-      <c r="B5" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="9" t="s">
+      <c r="B99" s="52"/>
+      <c r="C99" s="52"/>
+      <c r="D99" s="34"/>
+      <c r="E99" s="2"/>
+      <c r="F99"/>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A100" s="48">
+        <v>5</v>
+      </c>
+      <c r="B100" s="49"/>
+      <c r="C100" s="49"/>
+      <c r="D100" s="34"/>
+      <c r="E100" s="2"/>
+      <c r="F100"/>
+      <c r="I100" s="26"/>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A101" s="51">
+        <v>6</v>
+      </c>
+      <c r="B101" s="52"/>
+      <c r="C101" s="52"/>
+      <c r="D101" s="34"/>
+      <c r="E101" s="2"/>
+      <c r="F101"/>
+      <c r="I101" s="26"/>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A102" s="48">
+        <v>7</v>
+      </c>
+      <c r="B102" s="49"/>
+      <c r="C102" s="49"/>
+      <c r="D102" s="34"/>
+      <c r="E102" s="2"/>
+      <c r="F102"/>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A103" s="51">
+        <v>8</v>
+      </c>
+      <c r="B103" s="52"/>
+      <c r="C103" s="52"/>
+      <c r="D103" s="34"/>
+      <c r="E103" s="2"/>
+      <c r="F103"/>
+      <c r="G103" s="17"/>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A104" s="48">
         <v>9</v>
       </c>
-      <c r="D5" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="12">
-        <v>6.2050000000000001</v>
-      </c>
-      <c r="F5" s="13">
-        <f t="shared" si="0"/>
-        <v>6.2050000000000001</v>
-      </c>
-      <c r="G5" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H5" s="7"/>
-      <c r="I5" s="16"/>
-      <c r="J5" s="16"/>
-      <c r="K5" s="17"/>
-      <c r="L5" s="18"/>
-      <c r="Q5" s="20"/>
+      <c r="B104" s="49"/>
+      <c r="C104" s="49"/>
+      <c r="D104" s="34"/>
+      <c r="E104" s="2"/>
+      <c r="F104"/>
+      <c r="H104" s="17"/>
     </row>
-    <row r="6" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="11">
-        <v>5</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="12">
-        <v>28.79</v>
-      </c>
-      <c r="F6" s="13">
-        <f t="shared" si="0"/>
-        <v>28.79</v>
-      </c>
-      <c r="G6" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H6" s="7"/>
-      <c r="I6" s="16"/>
-      <c r="J6" s="16"/>
-      <c r="K6" s="17"/>
-      <c r="L6" s="18"/>
-      <c r="Q6" s="20"/>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A105" s="51">
+        <v>10</v>
+      </c>
+      <c r="B105" s="52"/>
+      <c r="C105" s="52"/>
+      <c r="D105" s="34"/>
+      <c r="E105" s="2"/>
+      <c r="F105"/>
     </row>
-    <row r="7" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="19">
-        <v>6</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" s="12">
-        <v>0.2</v>
-      </c>
-      <c r="F7" s="13">
-        <f t="shared" si="0"/>
-        <v>0.2</v>
-      </c>
-      <c r="G7" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H7" s="7"/>
-      <c r="I7" s="16"/>
-      <c r="J7" s="16"/>
-      <c r="K7" s="17"/>
-      <c r="L7" s="18"/>
-      <c r="Q7" s="20"/>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A106" s="53"/>
+      <c r="B106" s="54"/>
+      <c r="C106" s="20"/>
+      <c r="D106" s="55"/>
+      <c r="E106" s="2"/>
+      <c r="F106"/>
     </row>
-    <row r="8" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="11">
-        <v>7</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="12">
-        <v>42.66</v>
-      </c>
-      <c r="F8" s="13">
-        <f t="shared" si="0"/>
-        <v>42.66</v>
-      </c>
-      <c r="G8" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H8" s="7"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="17"/>
-      <c r="L8" s="18"/>
-      <c r="Q8" s="20"/>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="B107" s="23"/>
+      <c r="C107" s="19"/>
+      <c r="D107" s="19"/>
+      <c r="E107" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="F107" s="2" t="e">
+        <v>#REF!</v>
+      </c>
+      <c r="G107" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="H107" s="2" t="e">
+        <v>#REF!</v>
+      </c>
     </row>
-    <row r="9" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="19">
-        <v>8</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="10" t="s">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="C108" s="19"/>
+      <c r="E108"/>
+      <c r="F108"/>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="C109" s="22"/>
+      <c r="E109" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="12">
-        <v>63</v>
-      </c>
-      <c r="F9" s="13">
-        <f t="shared" si="0"/>
-        <v>63</v>
-      </c>
-      <c r="G9" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H9" s="7"/>
-      <c r="I9" s="16"/>
-      <c r="J9" s="16"/>
-      <c r="K9" s="17"/>
-      <c r="L9" s="18"/>
-      <c r="Q9" s="20"/>
+      <c r="F109" s="2" t="e">
+        <v>#REF!</v>
+      </c>
+      <c r="G109" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="H109" s="2" t="e">
+        <v>#REF!</v>
+      </c>
     </row>
-    <row r="10" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="11">
-        <v>9</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10" s="12">
-        <v>0.23300000000000001</v>
-      </c>
-      <c r="F10" s="13">
-        <f t="shared" si="0"/>
-        <v>0.23300000000000001</v>
-      </c>
-      <c r="G10" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H10" s="7"/>
-      <c r="I10" s="16"/>
-      <c r="J10" s="16"/>
-      <c r="K10" s="17"/>
-      <c r="L10" s="18"/>
-      <c r="Q10" s="20"/>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="C110" s="22"/>
+      <c r="E110"/>
+      <c r="F110"/>
     </row>
-    <row r="11" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="19">
-        <v>10</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="E11" s="12">
-        <v>49.02</v>
-      </c>
-      <c r="F11" s="13">
-        <f t="shared" si="0"/>
-        <v>49.02</v>
-      </c>
-      <c r="G11" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H11" s="7"/>
-      <c r="I11" s="21"/>
-      <c r="J11" s="21"/>
-      <c r="K11" s="17"/>
-      <c r="L11" s="18"/>
-      <c r="Q11" s="20"/>
-    </row>
-    <row r="12" spans="1:22" ht="15.9" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="19"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="22"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="G12" s="25">
-        <f>AVERAGE(G2:G11)</f>
-        <v>0</v>
-      </c>
-      <c r="H12" s="26" t="s">
-        <v>29</v>
-      </c>
-      <c r="I12" s="27">
-        <f>COUNTIF(G2:G11,"&gt;0")</f>
-        <v>0</v>
-      </c>
-      <c r="J12" s="28" t="s">
-        <v>30</v>
-      </c>
-      <c r="K12" s="29">
-        <f>COUNTIF(G2:G11,"&lt;0")</f>
-        <v>0</v>
-      </c>
-      <c r="L12" s="18"/>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.4">
-      <c r="F13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13"/>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.4">
-      <c r="F14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14"/>
-    </row>
-    <row r="15" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="11">
-        <v>1</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="E16" s="12">
-        <v>19.399999999999999</v>
-      </c>
-      <c r="F16" s="13">
-        <f t="shared" ref="F16:F25" si="2">IFERROR(((VLOOKUP(B16,cours,7,FALSE))),"")</f>
-        <v>19.399999999999999</v>
-      </c>
-      <c r="G16" s="14">
-        <f t="shared" ref="G16:G25" si="3">(F16/E16-1)</f>
-        <v>0</v>
-      </c>
-      <c r="H16" s="30"/>
-      <c r="I16"/>
-    </row>
-    <row r="17" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="19">
-        <v>2</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="E17" s="12">
-        <v>6.33</v>
-      </c>
-      <c r="F17" s="13">
-        <f t="shared" si="2"/>
-        <v>6.33</v>
-      </c>
-      <c r="G17" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H17" s="7"/>
-      <c r="I17"/>
-    </row>
-    <row r="18" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="11">
-        <v>3</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="E18" s="12">
-        <v>0.154</v>
-      </c>
-      <c r="F18" s="13">
-        <f t="shared" si="2"/>
-        <v>0.154</v>
-      </c>
-      <c r="G18" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H18" s="7"/>
-      <c r="I18" s="16"/>
-    </row>
-    <row r="19" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="19">
-        <v>4</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="E19" s="12">
-        <v>42.895000000000003</v>
-      </c>
-      <c r="F19" s="13">
-        <f t="shared" si="2"/>
-        <v>42.895000000000003</v>
-      </c>
-      <c r="G19" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H19" s="7"/>
-      <c r="I19"/>
-    </row>
-    <row r="20" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="11">
-        <v>5</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="E20" s="12">
-        <v>75.400000000000006</v>
-      </c>
-      <c r="F20" s="13">
-        <f t="shared" si="2"/>
-        <v>75.400000000000006</v>
-      </c>
-      <c r="G20" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H20" s="7"/>
-      <c r="I20" s="16"/>
-    </row>
-    <row r="21" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="19">
-        <v>6</v>
-      </c>
-      <c r="B21" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="D21" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E21" s="12">
-        <v>12.75</v>
-      </c>
-      <c r="F21" s="13">
-        <f t="shared" si="2"/>
-        <v>12.75</v>
-      </c>
-      <c r="G21" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H21" s="7"/>
-      <c r="I21"/>
-    </row>
-    <row r="22" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="11">
-        <v>7</v>
-      </c>
-      <c r="B22" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="D22" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="E22" s="12">
-        <v>34.93</v>
-      </c>
-      <c r="F22" s="13">
-        <f t="shared" si="2"/>
-        <v>34.93</v>
-      </c>
-      <c r="G22" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H22" s="7"/>
-      <c r="I22"/>
-    </row>
-    <row r="23" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="19">
-        <v>8</v>
-      </c>
-      <c r="B23" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D23" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="E23" s="12">
-        <v>0.16800000000000001</v>
-      </c>
-      <c r="F23" s="13">
-        <f t="shared" si="2"/>
-        <v>0.16800000000000001</v>
-      </c>
-      <c r="G23" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H23" s="7"/>
-      <c r="I23"/>
-    </row>
-    <row r="24" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A24" s="11">
-        <v>9</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="E24" s="12">
-        <v>8.56</v>
-      </c>
-      <c r="F24" s="13">
-        <f t="shared" si="2"/>
-        <v>8.56</v>
-      </c>
-      <c r="G24" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H24" s="7"/>
-      <c r="I24"/>
-    </row>
-    <row r="25" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="19">
-        <v>10</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="E25" s="12">
-        <v>6.76</v>
-      </c>
-      <c r="F25" s="13">
-        <f t="shared" si="2"/>
-        <v>6.76</v>
-      </c>
-      <c r="G25" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H25" s="7"/>
-      <c r="I25"/>
-    </row>
-    <row r="26" spans="1:11" ht="15.9" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="19"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="22"/>
-      <c r="D26" s="23"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="G26" s="32">
-        <f>AVERAGE(G16:G25)</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="26" t="s">
-        <v>29</v>
-      </c>
-      <c r="I26" s="27">
-        <f>COUNTIF(G16:G25,"&gt;0")</f>
-        <v>0</v>
-      </c>
-      <c r="J26" s="28" t="s">
-        <v>30</v>
-      </c>
-      <c r="K26" s="29">
-        <f>COUNTIF(G16:G25,"&lt;0")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A27" s="19"/>
-      <c r="B27" s="33"/>
-      <c r="C27" s="34"/>
-      <c r="D27" s="35"/>
-      <c r="F27" s="7"/>
-      <c r="H27" s="7"/>
-      <c r="I27"/>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="F28" s="7"/>
-      <c r="H28" s="7"/>
-    </row>
-    <row r="29" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G29" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="H29" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="I29"/>
-    </row>
-    <row r="30" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="11">
-        <v>1</v>
-      </c>
-      <c r="B30" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="D30" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="E30" s="12">
-        <v>2E-3</v>
-      </c>
-      <c r="F30" s="13">
-        <f t="shared" ref="F30:F39" si="4">IFERROR(((VLOOKUP(B30,cours,7,FALSE))),"")</f>
-        <v>2E-3</v>
-      </c>
-      <c r="G30" s="14">
-        <f t="shared" ref="G30:G39" si="5">(F30/E30-1)</f>
-        <v>0</v>
-      </c>
-      <c r="H30"/>
-      <c r="I30"/>
-    </row>
-    <row r="31" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="19">
-        <v>2</v>
-      </c>
-      <c r="B31" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="C31" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="D31" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="E31" s="12">
-        <v>9.2999999999999999E-2</v>
-      </c>
-      <c r="F31" s="13">
-        <f t="shared" si="4"/>
-        <v>9.2999999999999999E-2</v>
-      </c>
-      <c r="G31" s="14">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="H31"/>
-      <c r="I31"/>
-    </row>
-    <row r="32" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A32" s="11">
-        <v>3</v>
-      </c>
-      <c r="B32" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="D32" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="E32" s="12">
-        <v>0.28299999999999997</v>
-      </c>
-      <c r="F32" s="13">
-        <f t="shared" si="4"/>
-        <v>0.28299999999999997</v>
-      </c>
-      <c r="G32" s="14">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="H32"/>
-      <c r="I32"/>
-    </row>
-    <row r="33" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="19">
-        <v>4</v>
-      </c>
-      <c r="B33" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="C33" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="D33" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="E33" s="12">
-        <v>3.9</v>
-      </c>
-      <c r="F33" s="13">
-        <f t="shared" si="4"/>
-        <v>3.9</v>
-      </c>
-      <c r="G33" s="14">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="H33"/>
-      <c r="I33"/>
-    </row>
-    <row r="34" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="11">
-        <v>5</v>
-      </c>
-      <c r="B34" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C34" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="D34" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="E34" s="12">
-        <v>1.18</v>
-      </c>
-      <c r="F34" s="13">
-        <f t="shared" si="4"/>
-        <v>1.18</v>
-      </c>
-      <c r="G34" s="14">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="H34"/>
-      <c r="I34"/>
-    </row>
-    <row r="35" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A35" s="19">
-        <v>6</v>
-      </c>
-      <c r="B35" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="C35" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="D35" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="E35" s="12">
-        <v>0.72799999999999998</v>
-      </c>
-      <c r="F35" s="13">
-        <f t="shared" si="4"/>
-        <v>0.72799999999999998</v>
-      </c>
-      <c r="G35" s="14">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="H35"/>
-      <c r="I35"/>
-    </row>
-    <row r="36" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="11">
-        <v>7</v>
-      </c>
-      <c r="B36" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="C36" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="D36" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="E36" s="12">
-        <v>1.21</v>
-      </c>
-      <c r="F36" s="13">
-        <f t="shared" si="4"/>
-        <v>1.21</v>
-      </c>
-      <c r="G36" s="14">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="H36"/>
-      <c r="I36"/>
-    </row>
-    <row r="37" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A37" s="19">
-        <v>8</v>
-      </c>
-      <c r="B37" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C37" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="D37" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="E37" s="12">
-        <v>8</v>
-      </c>
-      <c r="F37" s="13">
-        <f t="shared" si="4"/>
-        <v>8</v>
-      </c>
-      <c r="G37" s="14">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="H37"/>
-      <c r="I37"/>
-      <c r="P37" s="36"/>
-    </row>
-    <row r="38" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="11">
-        <v>9</v>
-      </c>
-      <c r="B38" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="C38" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="D38" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="E38" s="12">
-        <v>17.75</v>
-      </c>
-      <c r="F38" s="13">
-        <f t="shared" si="4"/>
-        <v>17.75</v>
-      </c>
-      <c r="G38" s="14">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="H38"/>
-      <c r="I38"/>
-      <c r="P38" s="36"/>
-    </row>
-    <row r="39" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A39" s="19">
-        <v>10</v>
-      </c>
-      <c r="B39" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="C39" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="D39" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="E39" s="12">
-        <v>2.04</v>
-      </c>
-      <c r="F39" s="13">
-        <f t="shared" si="4"/>
-        <v>2.04</v>
-      </c>
-      <c r="G39" s="14">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="H39"/>
-      <c r="I39"/>
-    </row>
-    <row r="40" spans="1:16" ht="15.45" x14ac:dyDescent="0.4">
-      <c r="A40" s="19"/>
-      <c r="B40" s="37"/>
-      <c r="C40" s="22"/>
-      <c r="D40" s="23"/>
-      <c r="F40" s="38" t="s">
-        <v>28</v>
-      </c>
-      <c r="G40" s="39">
-        <f>AVERAGE(G30:G39)</f>
-        <v>0</v>
-      </c>
-      <c r="H40">
-        <f>COUNTIF(G30:G39,"&lt;0")</f>
-        <v>0</v>
-      </c>
-      <c r="I40"/>
-    </row>
-    <row r="41" spans="1:16" ht="15.45" x14ac:dyDescent="0.4">
-      <c r="B41" s="37"/>
-      <c r="C41" s="40"/>
-      <c r="D41" s="41"/>
-      <c r="F41" s="42"/>
-      <c r="G41" s="43"/>
-      <c r="H41"/>
-      <c r="I41"/>
-      <c r="K41" s="29"/>
-    </row>
-    <row r="42" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A42" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="F42" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G42" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="I42"/>
-    </row>
-    <row r="43" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A43" s="11">
-        <v>1</v>
-      </c>
-      <c r="B43" s="9"/>
-      <c r="C43" s="9"/>
-      <c r="D43" s="10"/>
-      <c r="E43" s="12"/>
-      <c r="F43" s="13" t="str">
-        <f t="shared" ref="F43:F52" si="6">IFERROR(((VLOOKUP(B43,cours,7,FALSE))),"")</f>
-        <v/>
-      </c>
-      <c r="G43" s="14" t="e">
-        <f t="shared" ref="G43:G52" si="7">(F43/E43-1)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H43"/>
-      <c r="I43"/>
-    </row>
-    <row r="44" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A44" s="19">
-        <v>2</v>
-      </c>
-      <c r="B44" s="9"/>
-      <c r="C44" s="9"/>
-      <c r="D44" s="10"/>
-      <c r="E44" s="12"/>
-      <c r="F44" s="13" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="G44" s="14" t="e">
-        <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H44"/>
-      <c r="I44"/>
-    </row>
-    <row r="45" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A45" s="11">
-        <v>3</v>
-      </c>
-      <c r="B45" s="9"/>
-      <c r="C45" s="9"/>
-      <c r="D45" s="10"/>
-      <c r="E45" s="12"/>
-      <c r="F45" s="13" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="G45" s="14" t="e">
-        <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H45"/>
-      <c r="I45"/>
-    </row>
-    <row r="46" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A46" s="19">
-        <v>4</v>
-      </c>
-      <c r="B46" s="9"/>
-      <c r="C46" s="9"/>
-      <c r="D46" s="10"/>
-      <c r="E46" s="12"/>
-      <c r="F46" s="13" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="G46" s="14" t="e">
-        <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H46"/>
-      <c r="I46"/>
-    </row>
-    <row r="47" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A47" s="11">
-        <v>5</v>
-      </c>
-      <c r="B47" s="9"/>
-      <c r="C47" s="9"/>
-      <c r="D47" s="10"/>
-      <c r="E47" s="12"/>
-      <c r="F47" s="13" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="G47" s="14" t="e">
-        <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H47"/>
-      <c r="I47"/>
-    </row>
-    <row r="48" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A48" s="19">
-        <v>6</v>
-      </c>
-      <c r="B48" s="9"/>
-      <c r="C48" s="9"/>
-      <c r="D48" s="10"/>
-      <c r="E48" s="12"/>
-      <c r="F48" s="13" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="G48" s="14" t="e">
-        <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H48"/>
-      <c r="I48"/>
-    </row>
-    <row r="49" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A49" s="11">
-        <v>7</v>
-      </c>
-      <c r="B49" s="9"/>
-      <c r="C49" s="9"/>
-      <c r="D49" s="10"/>
-      <c r="E49" s="12"/>
-      <c r="F49" s="13" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="G49" s="14" t="e">
-        <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H49"/>
-      <c r="I49"/>
-    </row>
-    <row r="50" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A50" s="19">
-        <v>8</v>
-      </c>
-      <c r="B50" s="9"/>
-      <c r="C50" s="9"/>
-      <c r="D50" s="10"/>
-      <c r="E50" s="12"/>
-      <c r="F50" s="13" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="G50" s="14" t="e">
-        <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H50"/>
-      <c r="I50"/>
-    </row>
-    <row r="51" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A51" s="11">
-        <v>9</v>
-      </c>
-      <c r="B51" s="9"/>
-      <c r="C51" s="9"/>
-      <c r="D51" s="10"/>
-      <c r="E51" s="12"/>
-      <c r="F51" s="13" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="G51" s="14" t="e">
-        <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H51"/>
-      <c r="I51"/>
-    </row>
-    <row r="52" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A52" s="19">
-        <v>10</v>
-      </c>
-      <c r="B52" s="9"/>
-      <c r="C52" s="9"/>
-      <c r="D52" s="10"/>
-      <c r="E52" s="12"/>
-      <c r="F52" s="13" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="G52" s="14" t="e">
-        <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H52"/>
-      <c r="I52"/>
-    </row>
-    <row r="53" spans="1:11" ht="15.9" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A53" s="19"/>
-      <c r="B53" s="9"/>
-      <c r="C53" s="22"/>
-      <c r="D53" s="23"/>
-      <c r="F53" s="38" t="s">
-        <v>28</v>
-      </c>
-      <c r="G53" s="44" t="e">
-        <f>AVERAGE(G43:G52)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H53" s="26" t="s">
-        <v>29</v>
-      </c>
-      <c r="I53" s="27">
-        <f>COUNTIF(G43:G52,"&gt;0")</f>
-        <v>0</v>
-      </c>
-      <c r="J53" s="28" t="s">
-        <v>30</v>
-      </c>
-      <c r="K53" s="29">
-        <f>COUNTIF(G43:G52,"&lt;0")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" ht="15.45" x14ac:dyDescent="0.4">
-      <c r="B54" s="9"/>
-      <c r="C54" s="40"/>
-      <c r="D54" s="41"/>
-      <c r="F54" s="42"/>
-      <c r="G54" s="45"/>
-      <c r="H54" s="7"/>
-      <c r="I54"/>
-    </row>
-    <row r="55" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A55" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="F55" s="46" t="s">
-        <v>5</v>
-      </c>
-      <c r="G55" s="47" t="s">
-        <v>6</v>
-      </c>
-      <c r="H55" s="6" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A56" s="11">
-        <v>1</v>
-      </c>
-      <c r="B56" s="48" t="s">
-        <v>8</v>
-      </c>
-      <c r="C56" s="40" t="s">
-        <v>9</v>
-      </c>
-      <c r="D56" s="48" t="s">
-        <v>10</v>
-      </c>
-      <c r="E56" s="49">
-        <v>79.8</v>
-      </c>
-      <c r="F56" s="13">
-        <f t="shared" ref="F56:F65" si="8">IFERROR(((VLOOKUP(B56,cours,7,0))),"")</f>
-        <v>79.8</v>
-      </c>
-      <c r="G56" s="50">
-        <f t="shared" ref="G56:G65" si="9">(F56/E56-1)</f>
-        <v>0</v>
-      </c>
-      <c r="H56" s="7"/>
-    </row>
-    <row r="57" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A57" s="19">
-        <v>2</v>
-      </c>
-      <c r="B57" s="48" t="s">
-        <v>11</v>
-      </c>
-      <c r="C57" s="40" t="s">
-        <v>9</v>
-      </c>
-      <c r="D57" s="48" t="s">
-        <v>12</v>
-      </c>
-      <c r="E57" s="49">
-        <v>195.6</v>
-      </c>
-      <c r="F57" s="13">
-        <f t="shared" si="8"/>
-        <v>195.6</v>
-      </c>
-      <c r="G57" s="50">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H57" s="7"/>
-      <c r="I57"/>
-    </row>
-    <row r="58" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A58" s="11">
-        <v>3</v>
-      </c>
-      <c r="B58" s="48" t="s">
-        <v>20</v>
-      </c>
-      <c r="C58" s="40" t="s">
-        <v>9</v>
-      </c>
-      <c r="D58" s="48" t="s">
-        <v>21</v>
-      </c>
-      <c r="E58" s="49">
-        <v>42.66</v>
-      </c>
-      <c r="F58" s="13">
-        <f t="shared" si="8"/>
-        <v>42.66</v>
-      </c>
-      <c r="G58" s="50">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H58" s="7"/>
-      <c r="I58"/>
-      <c r="K58" s="51"/>
-    </row>
-    <row r="59" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A59" s="19">
-        <v>4</v>
-      </c>
-      <c r="B59" s="48" t="s">
-        <v>80</v>
-      </c>
-      <c r="C59" s="40" t="s">
-        <v>9</v>
-      </c>
-      <c r="D59" s="48" t="s">
-        <v>81</v>
-      </c>
-      <c r="E59" s="49">
-        <v>59.65</v>
-      </c>
-      <c r="F59" s="13">
-        <f t="shared" si="8"/>
-        <v>59.65</v>
-      </c>
-      <c r="G59" s="50">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H59" s="7"/>
-      <c r="I59"/>
-      <c r="K59" s="51"/>
-    </row>
-    <row r="60" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A60" s="11">
-        <v>5</v>
-      </c>
-      <c r="B60" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="C60" s="40" t="s">
-        <v>9</v>
-      </c>
-      <c r="D60" s="48" t="s">
-        <v>23</v>
-      </c>
-      <c r="E60" s="49">
-        <v>63</v>
-      </c>
-      <c r="F60" s="13">
-        <f t="shared" si="8"/>
-        <v>63</v>
-      </c>
-      <c r="G60" s="50">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H60" s="7"/>
-      <c r="I60"/>
-      <c r="K60" s="51"/>
-    </row>
-    <row r="61" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A61" s="19">
-        <v>6</v>
-      </c>
-      <c r="B61" s="48" t="s">
-        <v>82</v>
-      </c>
-      <c r="C61" s="40" t="s">
-        <v>9</v>
-      </c>
-      <c r="D61" s="48" t="s">
-        <v>83</v>
-      </c>
-      <c r="E61" s="49">
-        <v>75.83</v>
-      </c>
-      <c r="F61" s="13">
-        <f t="shared" si="8"/>
-        <v>75.83</v>
-      </c>
-      <c r="G61" s="50">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H61" s="7"/>
-      <c r="I61"/>
-      <c r="K61" s="51"/>
-    </row>
-    <row r="62" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A62" s="11">
-        <v>7</v>
-      </c>
-      <c r="B62" s="48" t="s">
-        <v>16</v>
-      </c>
-      <c r="C62" s="40" t="s">
-        <v>9</v>
-      </c>
-      <c r="D62" s="48" t="s">
-        <v>16</v>
-      </c>
-      <c r="E62" s="49">
-        <v>6.2050000000000001</v>
-      </c>
-      <c r="F62" s="13">
-        <f t="shared" si="8"/>
-        <v>6.2050000000000001</v>
-      </c>
-      <c r="G62" s="50">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H62" s="7"/>
-      <c r="I62"/>
-    </row>
-    <row r="63" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A63" s="19">
-        <v>8</v>
-      </c>
-      <c r="B63" s="48" t="s">
-        <v>84</v>
-      </c>
-      <c r="C63" s="40" t="s">
-        <v>9</v>
-      </c>
-      <c r="D63" s="48" t="s">
-        <v>85</v>
-      </c>
-      <c r="E63" s="49">
-        <v>95.02</v>
-      </c>
-      <c r="F63" s="13">
-        <f t="shared" si="8"/>
-        <v>95.02</v>
-      </c>
-      <c r="G63" s="50">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H63" s="7"/>
-      <c r="I63"/>
-    </row>
-    <row r="64" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A64" s="11">
-        <v>9</v>
-      </c>
-      <c r="B64" s="48" t="s">
-        <v>86</v>
-      </c>
-      <c r="C64" s="40" t="s">
-        <v>9</v>
-      </c>
-      <c r="D64" s="48" t="s">
-        <v>87</v>
-      </c>
-      <c r="E64" s="49">
-        <v>107.1</v>
-      </c>
-      <c r="F64" s="13">
-        <f t="shared" si="8"/>
-        <v>107.1</v>
-      </c>
-      <c r="G64" s="50">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H64" s="7"/>
-      <c r="I64"/>
-    </row>
-    <row r="65" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A65" s="19">
-        <v>10</v>
-      </c>
-      <c r="B65" s="48" t="s">
-        <v>88</v>
-      </c>
-      <c r="C65" s="40" t="s">
-        <v>9</v>
-      </c>
-      <c r="D65" s="48" t="s">
-        <v>89</v>
-      </c>
-      <c r="E65" s="49">
-        <v>8.125</v>
-      </c>
-      <c r="F65" s="13">
-        <f t="shared" si="8"/>
-        <v>8.125</v>
-      </c>
-      <c r="G65" s="50">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H65" s="7"/>
-      <c r="I65"/>
-    </row>
-    <row r="66" spans="1:11" ht="15.45" x14ac:dyDescent="0.4">
-      <c r="A66" s="19"/>
-      <c r="B66" s="9"/>
-      <c r="C66" s="22"/>
-      <c r="D66" s="23"/>
-      <c r="F66" s="52" t="s">
-        <v>28</v>
-      </c>
-      <c r="G66" s="44">
-        <f>AVERAGE(G56:G65)</f>
-        <v>0</v>
-      </c>
-      <c r="H66" s="53" t="s">
-        <v>29</v>
-      </c>
-      <c r="I66" s="7">
-        <f>COUNTIF(G56:G65,"&gt;0")</f>
-        <v>0</v>
-      </c>
-      <c r="J66" s="53" t="s">
-        <v>30</v>
-      </c>
-      <c r="K66" s="29">
-        <f>COUNTIF(G56:G65,"&lt;0")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11" ht="15.45" x14ac:dyDescent="0.4">
-      <c r="B67" s="9"/>
-      <c r="C67" s="40"/>
-      <c r="D67" s="41"/>
-      <c r="F67" s="54"/>
-      <c r="G67" s="45"/>
-      <c r="H67" s="7"/>
-      <c r="I67"/>
-    </row>
-    <row r="68" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A68" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E68" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="F68" s="46" t="s">
-        <v>5</v>
-      </c>
-      <c r="G68" s="47" t="s">
-        <v>6</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A69" s="11">
-        <v>1</v>
-      </c>
-      <c r="B69" s="48"/>
-      <c r="C69" s="40"/>
-      <c r="D69" s="48"/>
-      <c r="E69" s="49"/>
-      <c r="F69" s="13" t="str">
-        <f t="shared" ref="F69" si="10">IFERROR(((VLOOKUP(B69,cours,7,FALSE))),"")</f>
-        <v/>
-      </c>
-      <c r="G69" s="50" t="e">
-        <f t="shared" ref="G69:G78" si="11">(F69/E69-1)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H69" s="7"/>
-    </row>
-    <row r="70" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A70" s="19">
-        <v>2</v>
-      </c>
-      <c r="B70" s="48"/>
-      <c r="C70" s="40"/>
-      <c r="D70" s="48"/>
-      <c r="E70" s="49"/>
-      <c r="F70" s="13" t="str">
-        <f t="shared" ref="F70:F78" si="12">IFERROR(((VLOOKUP(B70,cours,7,0))),"")</f>
-        <v/>
-      </c>
-      <c r="G70" s="50" t="e">
-        <f t="shared" si="11"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H70" s="7"/>
-      <c r="I70"/>
-      <c r="J70" s="41"/>
-    </row>
-    <row r="71" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A71" s="11">
-        <v>3</v>
-      </c>
-      <c r="B71" s="48"/>
-      <c r="C71" s="40"/>
-      <c r="D71" s="48"/>
-      <c r="E71" s="49"/>
-      <c r="F71" s="13" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="G71" s="50" t="e">
-        <f t="shared" si="11"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H71" s="7"/>
-      <c r="I71"/>
-      <c r="J71" s="41"/>
-    </row>
-    <row r="72" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A72" s="19">
-        <v>4</v>
-      </c>
-      <c r="B72" s="48"/>
-      <c r="C72" s="40"/>
-      <c r="D72" s="48"/>
-      <c r="E72" s="49"/>
-      <c r="F72" s="13" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="G72" s="50" t="e">
-        <f t="shared" si="11"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H72" s="7"/>
-      <c r="I72"/>
-      <c r="J72" s="55"/>
-    </row>
-    <row r="73" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A73" s="11">
-        <v>5</v>
-      </c>
-      <c r="B73" s="48"/>
-      <c r="C73" s="40"/>
-      <c r="D73" s="48"/>
-      <c r="E73" s="49"/>
-      <c r="F73" s="13" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="G73" s="50" t="e">
-        <f t="shared" si="11"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H73" s="7"/>
-      <c r="I73"/>
-      <c r="J73" s="55"/>
-    </row>
-    <row r="74" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A74" s="19">
-        <v>6</v>
-      </c>
-      <c r="B74" s="48"/>
-      <c r="C74" s="40"/>
-      <c r="D74" s="48"/>
-      <c r="E74" s="49"/>
-      <c r="F74" s="13" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="G74" s="50" t="e">
-        <f t="shared" si="11"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H74" s="7"/>
-      <c r="I74"/>
-      <c r="J74" s="55"/>
-    </row>
-    <row r="75" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A75" s="11">
-        <v>7</v>
-      </c>
-      <c r="B75" s="48"/>
-      <c r="C75" s="40"/>
-      <c r="D75" s="48"/>
-      <c r="E75" s="49"/>
-      <c r="F75" s="13" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="G75" s="50" t="e">
-        <f t="shared" si="11"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H75" s="7"/>
-      <c r="I75" s="36"/>
-      <c r="J75" s="55"/>
-    </row>
-    <row r="76" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A76" s="19">
-        <v>8</v>
-      </c>
-      <c r="B76" s="48"/>
-      <c r="C76" s="40"/>
-      <c r="D76" s="48"/>
-      <c r="E76" s="49"/>
-      <c r="F76" s="13" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="G76" s="50" t="e">
-        <f t="shared" si="11"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H76" s="7"/>
-      <c r="I76"/>
-      <c r="J76" s="41"/>
-    </row>
-    <row r="77" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A77" s="11">
-        <v>9</v>
-      </c>
-      <c r="B77" s="48"/>
-      <c r="C77" s="40"/>
-      <c r="D77" s="48"/>
-      <c r="E77" s="49"/>
-      <c r="F77" s="13" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="G77" s="50" t="e">
-        <f t="shared" si="11"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H77" s="7"/>
-      <c r="I77"/>
-      <c r="J77" s="41"/>
-    </row>
-    <row r="78" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A78" s="19">
-        <v>10</v>
-      </c>
-      <c r="B78" s="48"/>
-      <c r="C78" s="40"/>
-      <c r="D78" s="48"/>
-      <c r="E78" s="49"/>
-      <c r="F78" s="13" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="G78" s="50" t="e">
-        <f t="shared" si="11"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H78" s="7"/>
-      <c r="I78"/>
-      <c r="J78" s="41"/>
-    </row>
-    <row r="79" spans="1:11" ht="15.45" x14ac:dyDescent="0.4">
-      <c r="F79" s="56" t="s">
-        <v>28</v>
-      </c>
-      <c r="G79" s="44" t="e">
-        <f>AVERAGE(G69:G78)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H79" s="7"/>
-      <c r="I79"/>
-    </row>
-    <row r="80" spans="1:11" ht="15.45" x14ac:dyDescent="0.4">
-      <c r="F80" s="42"/>
-      <c r="G80" s="57"/>
-      <c r="H80" s="7"/>
-      <c r="I80"/>
-    </row>
-    <row r="81" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A81" t="s">
-        <v>0</v>
-      </c>
-      <c r="B81" s="58" t="s">
-        <v>91</v>
-      </c>
-      <c r="C81" t="s">
-        <v>92</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E81" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="F81" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G81" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="H81" s="29">
-        <f>COUNTIF($G$70:$G$79,"&lt;0")</f>
-        <v>0</v>
-      </c>
-      <c r="I81"/>
-    </row>
-    <row r="82" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A82" s="11">
-        <v>1</v>
-      </c>
-      <c r="B82" s="48"/>
-      <c r="C82" s="40"/>
-      <c r="D82" s="48"/>
-      <c r="E82" s="49"/>
-      <c r="F82" s="13" t="str">
-        <f t="shared" ref="F82:F91" si="13">IFERROR(((VLOOKUP(B82,cours,7,0))),"")</f>
-        <v/>
-      </c>
-      <c r="G82" s="50" t="e">
-        <f t="shared" ref="G82:G91" si="14">(F82/E82-1)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H82"/>
-      <c r="I82"/>
-    </row>
-    <row r="83" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A83" s="19">
-        <v>2</v>
-      </c>
-      <c r="B83" s="48"/>
-      <c r="C83" s="40"/>
-      <c r="D83" s="48"/>
-      <c r="E83" s="49"/>
-      <c r="F83" s="13" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="G83" s="50" t="e">
-        <f t="shared" si="14"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H83"/>
-      <c r="I83"/>
-    </row>
-    <row r="84" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A84" s="11">
-        <v>3</v>
-      </c>
-      <c r="B84" s="48"/>
-      <c r="C84" s="40"/>
-      <c r="D84" s="48"/>
-      <c r="E84" s="49"/>
-      <c r="F84" s="13" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="G84" s="50" t="e">
-        <f t="shared" si="14"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H84"/>
-      <c r="I84"/>
-    </row>
-    <row r="85" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A85" s="19">
-        <v>4</v>
-      </c>
-      <c r="B85" s="48"/>
-      <c r="C85" s="59"/>
-      <c r="D85" s="48"/>
-      <c r="E85" s="49"/>
-      <c r="F85" s="13" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="G85" s="50" t="e">
-        <f t="shared" si="14"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H85"/>
-      <c r="I85"/>
-    </row>
-    <row r="86" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A86" s="11">
-        <v>5</v>
-      </c>
-      <c r="B86" s="48"/>
-      <c r="C86" s="59"/>
-      <c r="D86" s="48"/>
-      <c r="E86" s="49"/>
-      <c r="F86" s="13" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="G86" s="50" t="e">
-        <f t="shared" si="14"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H86"/>
-      <c r="I86"/>
-    </row>
-    <row r="87" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A87" s="19">
-        <v>6</v>
-      </c>
-      <c r="B87" s="48"/>
-      <c r="C87" s="59"/>
-      <c r="D87" s="48"/>
-      <c r="E87" s="49"/>
-      <c r="F87" s="13" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="G87" s="50" t="e">
-        <f t="shared" si="14"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H87"/>
-      <c r="I87"/>
-    </row>
-    <row r="88" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A88" s="11">
-        <v>7</v>
-      </c>
-      <c r="B88" s="48"/>
-      <c r="C88" s="40"/>
-      <c r="D88" s="48"/>
-      <c r="E88" s="49"/>
-      <c r="F88" s="13" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="G88" s="50" t="e">
-        <f t="shared" si="14"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H88"/>
-      <c r="I88"/>
-    </row>
-    <row r="89" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A89" s="19">
-        <v>8</v>
-      </c>
-      <c r="B89" s="48"/>
-      <c r="C89" s="59"/>
-      <c r="D89" s="48"/>
-      <c r="E89" s="49"/>
-      <c r="F89" s="13" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="G89" s="50" t="e">
-        <f t="shared" si="14"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H89"/>
-      <c r="I89"/>
-    </row>
-    <row r="90" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A90" s="11">
-        <v>9</v>
-      </c>
-      <c r="B90" s="48"/>
-      <c r="C90" s="40"/>
-      <c r="D90" s="48"/>
-      <c r="E90" s="49"/>
-      <c r="F90" s="13" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="G90" s="50" t="e">
-        <f t="shared" si="14"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H90"/>
-      <c r="I90"/>
-    </row>
-    <row r="91" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A91" s="19">
-        <v>10</v>
-      </c>
-      <c r="B91" s="48"/>
-      <c r="C91" s="40"/>
-      <c r="D91" s="48"/>
-      <c r="E91" s="49"/>
-      <c r="F91" s="13" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="G91" s="50" t="e">
-        <f t="shared" si="14"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H91"/>
-      <c r="I91"/>
-    </row>
-    <row r="92" spans="1:12" ht="15.45" x14ac:dyDescent="0.4">
-      <c r="A92" s="19"/>
-      <c r="B92" s="58"/>
-      <c r="C92" s="40"/>
-      <c r="D92" s="41"/>
-      <c r="E92" s="49"/>
-      <c r="F92" s="56" t="s">
-        <v>28</v>
-      </c>
-      <c r="G92" s="44" t="e">
-        <f>AVERAGE(G82:G91)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H92"/>
-      <c r="I92"/>
-    </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="F93" s="7"/>
-      <c r="H93" s="53" t="s">
-        <v>29</v>
-      </c>
-      <c r="I93" s="7">
-        <f>COUNTIF(G83:G92,"&gt;0")</f>
-        <v>0</v>
-      </c>
-      <c r="J93" s="53" t="s">
-        <v>30</v>
-      </c>
-      <c r="K93" s="29">
-        <f>COUNTIF(G83:G92,"&lt;0")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="F94" s="7"/>
-      <c r="H94" s="53"/>
-      <c r="J94" s="53"/>
-      <c r="K94" s="29"/>
-    </row>
-    <row r="95" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A95" t="s">
-        <v>0</v>
-      </c>
-      <c r="B95" s="58" t="s">
-        <v>93</v>
-      </c>
-      <c r="C95" t="s">
-        <v>92</v>
-      </c>
-      <c r="D95" s="60" t="s">
-        <v>52</v>
-      </c>
-      <c r="E95" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="F95" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G95" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="H95" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="I95" s="61"/>
-      <c r="J95" s="62"/>
-      <c r="L95" s="63"/>
-    </row>
-    <row r="96" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A96" s="11">
-        <v>1</v>
-      </c>
-      <c r="B96" s="48"/>
-      <c r="C96" s="40"/>
-      <c r="D96" s="48"/>
-      <c r="E96" s="12"/>
-      <c r="F96" s="13" t="str">
-        <f t="shared" ref="F96:F105" si="15">IFERROR(((VLOOKUP(B96,cours,7,0))),"")</f>
-        <v/>
-      </c>
-      <c r="G96" s="50" t="e">
-        <f t="shared" ref="G96:G105" si="16">(F96/E96-1)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H96" s="7"/>
-    </row>
-    <row r="97" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A97" s="19">
-        <v>2</v>
-      </c>
-      <c r="B97" s="48"/>
-      <c r="C97" s="40"/>
-      <c r="D97" s="48"/>
-      <c r="E97" s="12"/>
-      <c r="F97" s="13" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="G97" s="50" t="e">
-        <f t="shared" si="16"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H97" s="7"/>
-      <c r="I97"/>
-      <c r="J97" s="36"/>
-    </row>
-    <row r="98" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A98" s="11">
-        <v>3</v>
-      </c>
-      <c r="B98" s="48"/>
-      <c r="C98" s="40"/>
-      <c r="D98" s="48"/>
-      <c r="E98" s="12"/>
-      <c r="F98" s="13" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="G98" s="50" t="e">
-        <f t="shared" si="16"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H98" s="7"/>
-      <c r="I98"/>
-    </row>
-    <row r="99" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A99" s="19">
-        <v>4</v>
-      </c>
-      <c r="B99" s="48"/>
-      <c r="C99" s="40"/>
-      <c r="D99" s="48"/>
-      <c r="E99" s="12"/>
-      <c r="F99" s="13" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="G99" s="50" t="e">
-        <f t="shared" si="16"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H99" s="7"/>
-      <c r="I99"/>
-    </row>
-    <row r="100" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A100" s="11">
-        <v>5</v>
-      </c>
-      <c r="B100" s="48"/>
-      <c r="C100" s="40"/>
-      <c r="D100" s="48"/>
-      <c r="E100" s="12"/>
-      <c r="F100" s="13" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="G100" s="50" t="e">
-        <f t="shared" si="16"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H100" s="7"/>
-      <c r="I100"/>
-      <c r="L100" s="63"/>
-    </row>
-    <row r="101" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A101" s="19">
-        <v>6</v>
-      </c>
-      <c r="B101" s="48"/>
-      <c r="C101" s="40"/>
-      <c r="D101" s="48"/>
-      <c r="E101" s="12"/>
-      <c r="F101" s="13" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="G101" s="50" t="e">
-        <f t="shared" si="16"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H101" s="7"/>
-      <c r="I101"/>
-      <c r="L101" s="63"/>
-    </row>
-    <row r="102" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A102" s="11">
-        <v>7</v>
-      </c>
-      <c r="B102" s="48"/>
-      <c r="C102" s="40"/>
-      <c r="D102" s="48"/>
-      <c r="E102" s="12"/>
-      <c r="F102" s="13" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="G102" s="50" t="e">
-        <f t="shared" si="16"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H102" s="7"/>
-      <c r="I102"/>
-    </row>
-    <row r="103" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A103" s="19">
-        <v>8</v>
-      </c>
-      <c r="B103" s="48"/>
-      <c r="C103" s="40"/>
-      <c r="D103" s="48"/>
-      <c r="E103" s="12"/>
-      <c r="F103" s="13" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="G103" s="50" t="e">
-        <f t="shared" si="16"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H103" s="7"/>
-      <c r="I103"/>
-      <c r="J103" s="36"/>
-    </row>
-    <row r="104" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A104" s="11">
-        <v>9</v>
-      </c>
-      <c r="B104" s="48"/>
-      <c r="C104" s="40"/>
-      <c r="D104" s="48"/>
-      <c r="E104" s="12"/>
-      <c r="F104" s="13" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="G104" s="50" t="e">
-        <f t="shared" si="16"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H104" s="7"/>
-      <c r="I104"/>
-      <c r="K104" s="36"/>
-    </row>
-    <row r="105" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A105" s="19">
-        <v>10</v>
-      </c>
-      <c r="B105" s="48"/>
-      <c r="C105" s="40"/>
-      <c r="D105" s="48"/>
-      <c r="E105" s="12"/>
-      <c r="F105" s="13" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="G105" s="50" t="e">
-        <f t="shared" si="16"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H105" s="7"/>
-      <c r="I105"/>
-    </row>
-    <row r="106" spans="1:12" ht="15.45" x14ac:dyDescent="0.4">
-      <c r="B106" s="58"/>
-      <c r="C106" s="40"/>
-      <c r="D106" s="41"/>
-      <c r="E106" s="49"/>
-      <c r="F106" s="64" t="s">
-        <v>28</v>
-      </c>
-      <c r="G106" s="44" t="e">
-        <f>AVERAGE(G96:G105)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H106" s="7"/>
-      <c r="I106"/>
-    </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="B107" s="58"/>
-      <c r="C107" s="40"/>
-      <c r="D107" s="41"/>
-      <c r="E107" s="41"/>
-      <c r="H107" s="53" t="s">
-        <v>29</v>
-      </c>
-      <c r="I107" s="7">
-        <f>COUNTIF(G97:G106,"&gt;0")</f>
-        <v>0</v>
-      </c>
-      <c r="J107" s="53" t="s">
-        <v>30</v>
-      </c>
-      <c r="K107" s="7">
-        <f>COUNTIF(G97:G106,"&lt;0")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="D108" s="41"/>
-      <c r="H108"/>
-      <c r="I108"/>
-    </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="D109" s="55"/>
-      <c r="H109" s="53" t="s">
-        <v>29</v>
-      </c>
-      <c r="I109" s="7">
-        <f>SUM(I1:I107)</f>
-        <v>0</v>
-      </c>
-      <c r="J109" s="53" t="s">
-        <v>30</v>
-      </c>
-      <c r="K109" s="7">
-        <f>SUM(K1:K107)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="D110" s="55"/>
-      <c r="H110"/>
-      <c r="I110"/>
-    </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="D111" s="55"/>
-      <c r="H111"/>
-      <c r="I111"/>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="C111" s="22"/>
+      <c r="E111"/>
+      <c r="F111"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B56:B65">
-    <cfRule type="expression" dxfId="104" priority="5" stopIfTrue="1">
-      <formula>IF(AO56&gt;0,TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B69:B78">
-    <cfRule type="expression" dxfId="103" priority="3" stopIfTrue="1">
-      <formula>IF(AO69&gt;0,TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B81">
-    <cfRule type="expression" dxfId="102" priority="50" stopIfTrue="1">
-      <formula>IF(AN62&gt;0,TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B82:B91">
-    <cfRule type="expression" dxfId="101" priority="9" stopIfTrue="1">
-      <formula>IF(AL82&gt;0,TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B92">
-    <cfRule type="expression" dxfId="100" priority="46" stopIfTrue="1">
-      <formula>IF(AL91&gt;0,TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B95">
-    <cfRule type="expression" dxfId="99" priority="49" stopIfTrue="1">
-      <formula>IF(AN75&gt;0,TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B96:B105">
-    <cfRule type="expression" dxfId="98" priority="7" stopIfTrue="1">
-      <formula>IF(AO96&gt;0,TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B106">
-    <cfRule type="expression" dxfId="97" priority="47" stopIfTrue="1">
-      <formula>IF(AN104&gt;0,TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B107">
-    <cfRule type="expression" dxfId="96" priority="48" stopIfTrue="1">
-      <formula>IF(AN104&gt;0,TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D56:D65">
-    <cfRule type="expression" dxfId="95" priority="4" stopIfTrue="1">
-      <formula>IF(AQ56&gt;0,TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D69:D78">
-    <cfRule type="expression" dxfId="94" priority="2" stopIfTrue="1">
-      <formula>IF(AQ69&gt;0,TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D82:D91">
-    <cfRule type="expression" dxfId="93" priority="8" stopIfTrue="1">
-      <formula>IF(AN82&gt;0,TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D96:D105">
-    <cfRule type="expression" dxfId="92" priority="6" stopIfTrue="1">
-      <formula>IF(AQ96&gt;0,TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F11 F16:F25">
-    <cfRule type="expression" dxfId="91" priority="19" stopIfTrue="1">
-      <formula>IF(#REF!="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="90" priority="21" stopIfTrue="1">
-      <formula>IF($U200="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="89" priority="22" stopIfTrue="1">
-      <formula>IF($AN1048554="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="88" priority="23" stopIfTrue="1">
-      <formula>IF($T200="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="87" priority="24" stopIfTrue="1">
-      <formula>IF($U200="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="86" priority="20" stopIfTrue="1">
-      <formula>IF($T200="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F30:F39">
-    <cfRule type="expression" dxfId="85" priority="85" stopIfTrue="1">
-      <formula>IF($U230="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="84" priority="84" stopIfTrue="1">
-      <formula>IF($T230="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="83" priority="83" stopIfTrue="1">
-      <formula>IF($AN5="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="82" priority="82" stopIfTrue="1">
-      <formula>IF($U230="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="81" priority="81" stopIfTrue="1">
-      <formula>IF($T230="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="80" priority="80" stopIfTrue="1">
-      <formula>IF(#REF!="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F43:F52">
-    <cfRule type="expression" dxfId="79" priority="86" stopIfTrue="1">
-      <formula>IF(#REF!="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="78" priority="88" stopIfTrue="1">
-      <formula>IF($U242="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="77" priority="89" stopIfTrue="1">
-      <formula>IF($AN17="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="76" priority="90" stopIfTrue="1">
-      <formula>IF($T242="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="75" priority="91" stopIfTrue="1">
-      <formula>IF($U242="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="74" priority="87" stopIfTrue="1">
-      <formula>IF($T242="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F56">
-    <cfRule type="expression" dxfId="73" priority="78" stopIfTrue="1">
-      <formula>IF($T254="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="72" priority="77" stopIfTrue="1">
-      <formula>IF($AN28="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="71" priority="79" stopIfTrue="1">
-      <formula>IF($U254="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F56:F67">
-    <cfRule type="expression" dxfId="70" priority="76" stopIfTrue="1">
-      <formula>IF(#REF!="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F57:F67">
-    <cfRule type="expression" dxfId="69" priority="95" stopIfTrue="1">
-      <formula>IF($U255="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="68" priority="93" stopIfTrue="1">
-      <formula>IF($AK29="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="67" priority="94" stopIfTrue="1">
-      <formula>IF($T255="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F69">
-    <cfRule type="expression" dxfId="66" priority="97" stopIfTrue="1">
-      <formula>IF($U268="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="65" priority="96" stopIfTrue="1">
-      <formula>IF($T268="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="64" priority="98" stopIfTrue="1">
-      <formula>IF($AJ43="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="63" priority="99" stopIfTrue="1">
-      <formula>IF($T268="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="62" priority="100" stopIfTrue="1">
-      <formula>IF($U268="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F69:F78">
-    <cfRule type="expression" dxfId="61" priority="1" stopIfTrue="1">
-      <formula>IF(#REF!="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F70:F78">
-    <cfRule type="expression" dxfId="60" priority="103" stopIfTrue="1">
-      <formula>IF($U267="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="59" priority="102" stopIfTrue="1">
-      <formula>IF($T267="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="58" priority="101" stopIfTrue="1">
-      <formula>IF($AJ42="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F82">
-    <cfRule type="expression" dxfId="57" priority="106" stopIfTrue="1">
-      <formula>IF($U278="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="56" priority="104" stopIfTrue="1">
-      <formula>IF($AJ53="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="55" priority="105" stopIfTrue="1">
-      <formula>IF($T278="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F82:F91">
-    <cfRule type="expression" dxfId="54" priority="65" stopIfTrue="1">
-      <formula>IF(#REF!="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F83:F91">
-    <cfRule type="expression" dxfId="53" priority="68" stopIfTrue="1">
-      <formula>IF($U279="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="52" priority="66" stopIfTrue="1">
-      <formula>IF($AN55="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="51" priority="67" stopIfTrue="1">
-      <formula>IF($T279="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F96:F97">
-    <cfRule type="expression" dxfId="50" priority="74" stopIfTrue="1">
-      <formula>IF($T291="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="49" priority="75" stopIfTrue="1">
-      <formula>IF($U291="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="48" priority="73" stopIfTrue="1">
-      <formula>IF($AN65="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F96:F106">
-    <cfRule type="expression" dxfId="47" priority="69" stopIfTrue="1">
-      <formula>IF(#REF!="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F98:F106">
-    <cfRule type="expression" dxfId="46" priority="70" stopIfTrue="1">
-      <formula>IF($AN68="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="45" priority="71" stopIfTrue="1">
-      <formula>IF($T293="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="44" priority="72" stopIfTrue="1">
-      <formula>IF($U293="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G12 G16:G26 G30:G41">
-    <cfRule type="cellIs" dxfId="43" priority="53" stopIfTrue="1" operator="greaterThanOrEqual">
-      <formula>#REF!</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="52" stopIfTrue="1" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G12 G16:G28">
-    <cfRule type="cellIs" dxfId="41" priority="25" stopIfTrue="1" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G30:G41 G2:G12 G16:G26">
-    <cfRule type="cellIs" dxfId="40" priority="51" operator="greaterThan">
-      <formula>#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G43:G54 G30:G41 G56:G67">
-    <cfRule type="cellIs" dxfId="39" priority="42" stopIfTrue="1" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G43:G54">
-    <cfRule type="cellIs" dxfId="38" priority="30" stopIfTrue="1" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="33" stopIfTrue="1" operator="greaterThanOrEqual">
-      <formula>#REF!</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="36" priority="32" stopIfTrue="1" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="35" priority="31" operator="greaterThan">
-      <formula>#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G53:G54">
-    <cfRule type="cellIs" dxfId="34" priority="16" operator="greaterThan">
-      <formula>#REF!</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="18" stopIfTrue="1" operator="greaterThanOrEqual">
-      <formula>#REF!</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="32" priority="17" stopIfTrue="1" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G56:G67">
-    <cfRule type="cellIs" dxfId="31" priority="45" stopIfTrue="1" operator="greaterThanOrEqual">
-      <formula>#REF!</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="43" operator="greaterThan">
-      <formula>#REF!</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="29" priority="44" stopIfTrue="1" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G69:G80">
-    <cfRule type="cellIs" dxfId="28" priority="29" stopIfTrue="1" operator="greaterThanOrEqual">
-      <formula>#REF!</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="27" operator="greaterThan">
-      <formula>#REF!</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="26" stopIfTrue="1" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="28" stopIfTrue="1" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G82:G92">
-    <cfRule type="cellIs" dxfId="24" priority="40" stopIfTrue="1" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="39" operator="greaterThan">
-      <formula>#REF!</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="41" stopIfTrue="1" operator="greaterThanOrEqual">
-      <formula>#REF!</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="38" stopIfTrue="1" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G96:G106">
-    <cfRule type="cellIs" dxfId="20" priority="37" stopIfTrue="1" operator="greaterThanOrEqual">
-      <formula>#REF!</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="36" stopIfTrue="1" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="35" operator="greaterThan">
-      <formula>#REF!</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="34" stopIfTrue="1" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H81">
-    <cfRule type="cellIs" dxfId="16" priority="15" operator="greaterThan">
-      <formula>$H81</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I12 I53 K53 I66 K66">
-    <cfRule type="cellIs" dxfId="15" priority="59" operator="greaterThan">
-      <formula>$K12</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I26">
-    <cfRule type="cellIs" dxfId="14" priority="10" operator="greaterThan">
-      <formula>$K26</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I75">
-    <cfRule type="cellIs" dxfId="13" priority="60" stopIfTrue="1" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I93:I94">
-    <cfRule type="cellIs" dxfId="12" priority="58" operator="greaterThan">
-      <formula>$K93</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I107">
-    <cfRule type="cellIs" dxfId="11" priority="57" operator="greaterThan">
-      <formula>$K107</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I109">
-    <cfRule type="cellIs" dxfId="10" priority="55" operator="greaterThan">
-      <formula>$K109</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J97">
-    <cfRule type="cellIs" dxfId="9" priority="62" stopIfTrue="1" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J103">
-    <cfRule type="cellIs" dxfId="8" priority="61" stopIfTrue="1" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K12">
-    <cfRule type="cellIs" dxfId="7" priority="13" operator="greaterThan">
-      <formula>$K12</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K26">
-    <cfRule type="cellIs" dxfId="6" priority="12" operator="greaterThan">
-      <formula>$K26</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K41">
-    <cfRule type="cellIs" dxfId="5" priority="11" operator="greaterThan">
-      <formula>$K41</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K93:K94">
-    <cfRule type="cellIs" dxfId="4" priority="14" operator="greaterThan">
-      <formula>$K93</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K104">
-    <cfRule type="cellIs" dxfId="3" priority="63" stopIfTrue="1" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K107">
-    <cfRule type="cellIs" dxfId="2" priority="56" operator="greaterThan">
-      <formula>$I107</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K109">
-    <cfRule type="cellIs" dxfId="1" priority="54" operator="greaterThan">
-      <formula>$I109</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P37:P38">
-    <cfRule type="cellIs" dxfId="0" priority="64" stopIfTrue="1" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
-  <tableParts count="8">
-    <tablePart r:id="rId2"/>
-    <tablePart r:id="rId3"/>
-    <tablePart r:id="rId4"/>
-    <tablePart r:id="rId5"/>
-    <tablePart r:id="rId6"/>
-    <tablePart r:id="rId7"/>
-    <tablePart r:id="rId8"/>
-    <tablePart r:id="rId9"/>
-  </tableParts>
 </worksheet>
 </file>
--- a/Twitter_Donnees.xlsx
+++ b/Twitter_Donnees.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\charl\Documents\Bourse\mon-projet-react\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{118D8851-6342-4430-BABC-769A64FBF7F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9684C68B-FA7C-43C0-AA33-94118EA98BD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{1E491141-9037-4602-B68E-E720201A1995}"/>
   </bookViews>
   <sheets>
     <sheet name="Donnees" sheetId="1" r:id="rId1"/>
+    <sheet name="Suivi" sheetId="2" r:id="rId2"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId2"/>
+    <externalReference r:id="rId3"/>
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Donnees!$A$2:$G$11</definedName>
@@ -47,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="168">
   <si>
     <t>Colonne1</t>
   </si>
@@ -363,6 +364,195 @@
   <si>
     <t>Confiance Small</t>
   </si>
+  <si>
+    <t>EXA</t>
+  </si>
+  <si>
+    <t>EXAIL TECH</t>
+  </si>
+  <si>
+    <t>ATEME</t>
+  </si>
+  <si>
+    <t>EXENS</t>
+  </si>
+  <si>
+    <t>EXOSENS</t>
+  </si>
+  <si>
+    <t>AB</t>
+  </si>
+  <si>
+    <t>AB SCIENCE</t>
+  </si>
+  <si>
+    <t>NXI</t>
+  </si>
+  <si>
+    <t>NEXITY</t>
+  </si>
+  <si>
+    <t>CRI</t>
+  </si>
+  <si>
+    <t>CHARGEURS</t>
+  </si>
+  <si>
+    <t>CVX</t>
+  </si>
+  <si>
+    <t>CARVOLIX</t>
+  </si>
+  <si>
+    <t>S30</t>
+  </si>
+  <si>
+    <t>SOLUTIONS 30</t>
+  </si>
+  <si>
+    <t>CO</t>
+  </si>
+  <si>
+    <t>CASINO GUICHARD</t>
+  </si>
+  <si>
+    <t>SAN</t>
+  </si>
+  <si>
+    <t>SANOFI</t>
+  </si>
+  <si>
+    <t>ANTIN</t>
+  </si>
+  <si>
+    <t>ANTIN INFRA</t>
+  </si>
+  <si>
+    <t>ALDUX</t>
+  </si>
+  <si>
+    <t>ADUX</t>
+  </si>
+  <si>
+    <t>ALATA</t>
+  </si>
+  <si>
+    <t>ATARI</t>
+  </si>
+  <si>
+    <t>ALHAF</t>
+  </si>
+  <si>
+    <t>HAFFNER ENERGY</t>
+  </si>
+  <si>
+    <t>ALDVI</t>
+  </si>
+  <si>
+    <t>ADVICENNE</t>
+  </si>
+  <si>
+    <t>ALMAR</t>
+  </si>
+  <si>
+    <t>MARE NOSTRUM</t>
+  </si>
+  <si>
+    <t>ALWTR</t>
+  </si>
+  <si>
+    <t>WATERA</t>
+  </si>
+  <si>
+    <t>ALESA</t>
+  </si>
+  <si>
+    <t>ECOSLOPS</t>
+  </si>
+  <si>
+    <t>ALBFR</t>
+  </si>
+  <si>
+    <t>SIDETRADE</t>
+  </si>
+  <si>
+    <t>IDL</t>
+  </si>
+  <si>
+    <t>ID LOGISTICS</t>
+  </si>
+  <si>
+    <t>KOF</t>
+  </si>
+  <si>
+    <t>KAUFMAN ET BROAD</t>
+  </si>
+  <si>
+    <t>ENGI</t>
+  </si>
+  <si>
+    <t>ENGIE</t>
+  </si>
+  <si>
+    <t>SW</t>
+  </si>
+  <si>
+    <t>SODEXO</t>
+  </si>
+  <si>
+    <t>RUI</t>
+  </si>
+  <si>
+    <t>RUBIS</t>
+  </si>
+  <si>
+    <t>MAU</t>
+  </si>
+  <si>
+    <t>MAUREL ET PROM</t>
+  </si>
+  <si>
+    <t>BNP</t>
+  </si>
+  <si>
+    <t>BNP PARIBAS</t>
+  </si>
+  <si>
+    <t>SCR</t>
+  </si>
+  <si>
+    <t>SCOR SE</t>
+  </si>
+  <si>
+    <t>SOP</t>
+  </si>
+  <si>
+    <t>SOPRA STERIA GROUP</t>
+  </si>
+  <si>
+    <t>ACA</t>
+  </si>
+  <si>
+    <t>CREDIT AGRICOLE SA</t>
+  </si>
+  <si>
+    <t>VK</t>
+  </si>
+  <si>
+    <t>VALLOUREC</t>
+  </si>
+  <si>
+    <t>PLX</t>
+  </si>
+  <si>
+    <t>PLUXEE</t>
+  </si>
+  <si>
+    <t>LIN</t>
+  </si>
+  <si>
+    <t>LINEDATA</t>
+  </si>
 </sst>
 </file>
 
@@ -500,7 +690,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="39">
+  <borders count="43">
     <border>
       <left/>
       <right/>
@@ -976,6 +1166,44 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="double">
+        <color theme="9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -983,7 +1211,7 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="112">
+  <cellXfs count="133">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1098,9 +1326,8 @@
     <xf numFmtId="16" fontId="2" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="5" fillId="6" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="5" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="5" fillId="7" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1110,7 +1337,7 @@
     <xf numFmtId="10" fontId="6" fillId="8" borderId="23" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="7" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1130,13 +1357,13 @@
     <xf numFmtId="10" fontId="6" fillId="8" borderId="29" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="26" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="5" borderId="26" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="4" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="5" fillId="7" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1155,7 +1382,7 @@
     <xf numFmtId="16" fontId="2" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="31" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1168,14 +1395,14 @@
     <xf numFmtId="10" fontId="6" fillId="8" borderId="33" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1193,17 +1420,17 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="5" borderId="26" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="6" borderId="26" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="26" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
     <xf numFmtId="16" fontId="2" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="5" fillId="10" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="37" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1211,7 +1438,7 @@
     <xf numFmtId="2" fontId="5" fillId="10" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1224,6 +1451,52 @@
     <xf numFmtId="2" fontId="5" fillId="7" borderId="38" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="16" fontId="2" fillId="2" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="5" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="16" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="2" fillId="2" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="7" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="10" fontId="8" fillId="8" borderId="23" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="10" fontId="6" fillId="8" borderId="41" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="16" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="7" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="10" fontId="8" fillId="8" borderId="41" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="5" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="8" fillId="8" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1231,15 +1504,1661 @@
     <cellStyle name="Normal 4" xfId="3" xr:uid="{3F2E2F33-14E3-4A20-86E4-61B290AEBEBF}"/>
     <cellStyle name="Pourcentage" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="106">
+  <dxfs count="120">
     <dxf>
       <font>
         <b/>
         <i val="0"/>
+        <strike val="0"/>
         <condense val="0"/>
         <extend val="0"/>
-        <color indexed="12"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
       </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="000000"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor indexed="9"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="000000"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor indexed="9"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FFA9D08E"/>
+        </left>
+        <top style="thin">
+          <color rgb="FFA9D08E"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFA9D08E"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right/>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="000000"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor indexed="9"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="000000"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor indexed="9"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="9" tint="0.79998168889431442"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FFA9D08E"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFA9D08E"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFA9D08E"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFA9D08E"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="000000"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor indexed="9"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="000000"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor indexed="9"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="9" tint="0.79998168889431442"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FFA9D08E"/>
+        </left>
+        <top style="thin">
+          <color rgb="FFA9D08E"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFA9D08E"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="9"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="000000"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor indexed="9"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="000000"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor indexed="9"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FFA9D08E"/>
+        </left>
+        <top style="thin">
+          <color rgb="FFA9D08E"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFA9D08E"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="9"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="000000"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="9" tint="0.79998168889431442"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="9" tint="0.79998168889431442"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FFA9D08E"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFA9D08E"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFA9D08E"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFA9D08E"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="9"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="000000"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor indexed="9"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="000000"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor indexed="31"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </left>
+        <right style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </right>
+        <top style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="000000"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor indexed="31"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FFA9D08E"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFA9D08E"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFA9D08E"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFA9D08E"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FFA9D08E"/>
+        </left>
+        <top style="thin">
+          <color rgb="FFA9D08E"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFA9D08E"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FFA9D08E"/>
+        </left>
+        <top style="thin">
+          <color rgb="FFA9D08E"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFA9D08E"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FFA9D08E"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFA9D08E"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFA9D08E"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFA9D08E"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="000000"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="000000"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor indexed="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FFA9D08E"/>
+        </left>
+        <top style="thin">
+          <color rgb="FFA9D08E"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFA9D08E"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -1351,122 +3270,6 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -1521,80 +3324,6 @@
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -1987,186 +3716,6 @@
         <i val="0"/>
         <condense val="0"/>
         <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
         <color indexed="18"/>
       </font>
     </dxf>
@@ -18189,6 +19738,100 @@
     </sheetDataSet>
   </externalBook>
 </externalLink>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{92BF0698-33E9-41CD-8155-F073A3C7F328}" name="Hausses28850" displayName="Hausses28850" ref="A29:G40" totalsRowCount="1" tableBorderDxfId="7">
+  <autoFilter ref="A29:G39" xr:uid="{92BF0698-33E9-41CD-8155-F073A3C7F328}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{31577117-E3A9-48F6-9095-51CBF7E790A5}" name="Position" dataDxfId="6" totalsRowDxfId="54"/>
+    <tableColumn id="2" xr3:uid="{9529492B-938B-4650-A138-FE3E4D2F8D9F}" name="Code" dataDxfId="5" totalsRowDxfId="53" dataCellStyle="Normal 2"/>
+    <tableColumn id="3" xr3:uid="{6A2A09B6-4418-45E2-A808-2E2D192DBC80}" name="Marché" dataDxfId="4" totalsRowDxfId="52" dataCellStyle="Normal 2"/>
+    <tableColumn id="4" xr3:uid="{B4A95E53-AE4E-4E9B-9949-B387111DA66B}" name="Valeur" dataDxfId="3" totalsRowDxfId="51" dataCellStyle="Normal 2"/>
+    <tableColumn id="5" xr3:uid="{61B00A1C-E2C0-4967-9CB2-A6FEBD3DEFA5}" name="Colonne3" dataDxfId="2" dataCellStyle="Normal 2"/>
+    <tableColumn id="6" xr3:uid="{221CD27E-9E8F-4666-891A-DC33DCD73C88}" name="RECO" totalsRowLabel="Moyenne" dataDxfId="1" totalsRowDxfId="50" dataCellStyle="Normal 2">
+      <calculatedColumnFormula>IFERROR(((VLOOKUP(B30,cours,7,FALSE))),"")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{5FBE68F3-EF87-430E-B40A-1F5F050674EA}" name="Différence" totalsRowFunction="custom" dataDxfId="0" totalsRowDxfId="49" dataCellStyle="Normal 4">
+      <calculatedColumnFormula>(F30/E30-1)</calculatedColumnFormula>
+      <totalsRowFormula>AVERAGE(G30:G39)</totalsRowFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{05A4E370-A7F6-4B9E-B09B-F1BDB0BAA9EE}" name="Hausses38951" displayName="Hausses38951" ref="A42:G53" totalsRowShown="0" tableBorderDxfId="15">
+  <autoFilter ref="A42:G53" xr:uid="{05A4E370-A7F6-4B9E-B09B-F1BDB0BAA9EE}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{C35FC0B1-B7D8-48D4-A97F-E2B9E64247FA}" name="Position" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{D711042C-88CC-4588-9319-1EB81C098E48}" name="Code" dataDxfId="13" dataCellStyle="Normal 2"/>
+    <tableColumn id="3" xr3:uid="{ED94FDA2-E9D6-4C05-8FF3-89E8F52352D2}" name="Marché" dataDxfId="12" dataCellStyle="Normal 2"/>
+    <tableColumn id="4" xr3:uid="{19E898A0-C11D-4FF0-885B-7E085BFB539B}" name="Valeur" dataDxfId="11" dataCellStyle="Normal 2"/>
+    <tableColumn id="5" xr3:uid="{B7375946-7B1D-442B-93F6-8F0B694E8259}" name="Colonne8" dataDxfId="10" dataCellStyle="Normal 2"/>
+    <tableColumn id="6" xr3:uid="{415F3967-A72B-4C60-86E2-6D79BC720EAB}" name="RECO" dataDxfId="9" dataCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{B3421297-D8C5-4C3F-BFBE-15BBEA19AF14}" name="Différence" dataDxfId="8" dataCellStyle="Normal 4"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{06FBA511-3574-4BC2-81D5-A39781333BAD}" name="Hausses18622516553" displayName="Hausses18622516553" ref="A1:G12" totalsRowShown="0" tableBorderDxfId="23">
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{8FA0EB51-7F08-47E4-AD3D-704567C42E4C}" name="Colonne1" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{38C2CE8A-FDBF-442A-A4C3-2D3DE27F093D}" name="Code" dataDxfId="21" dataCellStyle="Normal 2"/>
+    <tableColumn id="3" xr3:uid="{6364D553-D690-42CD-84F3-F351621C76A3}" name="Marché" dataDxfId="20" dataCellStyle="Normal 2"/>
+    <tableColumn id="4" xr3:uid="{0A618134-D84C-4F93-B913-AFD2D34CBF05}" name="Valeur" dataDxfId="19" dataCellStyle="Normal 2"/>
+    <tableColumn id="5" xr3:uid="{E22894F9-2CC5-4EEE-83F2-605389F3A3B9}" name="Cours" dataDxfId="18" dataCellStyle="Normal 2"/>
+    <tableColumn id="6" xr3:uid="{EA7F434A-4FF5-4378-9B9A-F1EA23A183C5}" name="RECO" dataDxfId="17" dataCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{79724786-FEC0-4408-94CC-084393D6828A}" name="Différence" dataDxfId="16" dataCellStyle="Normal 4"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{750C643D-D0F6-416C-89C9-B92C82B54617}" name="Baisses18722616654" displayName="Baisses18722616654" ref="A15:E27" totalsRowShown="0" headerRowDxfId="24" tableBorderDxfId="30">
+  <autoFilter ref="A15:E27" xr:uid="{750C643D-D0F6-416C-89C9-B92C82B54617}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{FDEC13FC-7587-4CCD-A919-A6A7EF9E4627}" name="Position" dataDxfId="29"/>
+    <tableColumn id="2" xr3:uid="{5C47DDB8-769A-4289-8C97-3B2DEB89F145}" name="Code" dataDxfId="28" dataCellStyle="Normal 2"/>
+    <tableColumn id="3" xr3:uid="{A048A9CB-4718-4341-BFBE-38E84F4742C3}" name="Marché" dataDxfId="27" dataCellStyle="Normal 2"/>
+    <tableColumn id="4" xr3:uid="{9DA6B000-4EDB-436A-8EEB-F4CE41F3FD4C}" name="Valeur" dataDxfId="26" dataCellStyle="Normal 2"/>
+    <tableColumn id="5" xr3:uid="{98E9DFFA-F67C-48AA-A752-6B7243756550}" name="Colonne1" dataDxfId="25" dataCellStyle="Normal 2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{7A387C55-B685-41F1-BD31-E2A325B4748A}" name="Hausses49022916755" displayName="Hausses49022916755" ref="A55:E66" totalsRowShown="0" headerRowDxfId="31" tableBorderDxfId="35">
+  <autoFilter ref="A55:E66" xr:uid="{7A387C55-B685-41F1-BD31-E2A325B4748A}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{CEFA1162-3DFC-4F5B-81BA-3D9B048C669E}" name="Position" dataDxfId="34"/>
+    <tableColumn id="2" xr3:uid="{C50255C7-9870-4400-928F-0FB2A9585AA1}" name="Code" dataDxfId="44"/>
+    <tableColumn id="3" xr3:uid="{0FB6E53A-004C-4A85-BB4F-477FEB795BBD}" name="Marché" dataDxfId="33"/>
+    <tableColumn id="4" xr3:uid="{4376EE77-1AB2-43BE-B36F-B28A248A3107}" name="Valeur" dataDxfId="43"/>
+    <tableColumn id="5" xr3:uid="{E6EE4523-D389-497E-91B8-ADA34A89A0C6}" name="15-janv" dataDxfId="32"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{19001D83-110C-4EF7-AEC9-BF52FFEFE882}" name="Baisses29123016856" displayName="Baisses29123016856" ref="A68:E78" totalsRowShown="0" headerRowDxfId="36" tableBorderDxfId="42">
+  <autoFilter ref="A68:E78" xr:uid="{19001D83-110C-4EF7-AEC9-BF52FFEFE882}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{793125D1-843C-4D99-980F-9F49AE811552}" name="Position" dataDxfId="41"/>
+    <tableColumn id="2" xr3:uid="{6F008CE4-BEE4-4A10-B787-A246C39D18DA}" name="Code" dataDxfId="40" dataCellStyle="Normal 2"/>
+    <tableColumn id="3" xr3:uid="{83A37498-BB21-40D7-A280-41D9C67846E8}" name="Marché" dataDxfId="39" dataCellStyle="Normal 2"/>
+    <tableColumn id="4" xr3:uid="{E5DE8F55-0C31-4DA1-949C-5D5EFDFA4859}" name="Valeur" dataDxfId="38" dataCellStyle="Normal 2"/>
+    <tableColumn id="5" xr3:uid="{0983F889-F48C-4793-9E34-23479C089DA4}" name="Colonne1" dataDxfId="37" dataCellStyle="Normal 2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -18650,16 +20293,16 @@
       <c r="C2" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="54" t="s">
+      <c r="D2" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="55">
+      <c r="E2" s="54">
         <v>0.20200000000000001</v>
       </c>
-      <c r="F2" s="56">
+      <c r="F2" s="55">
         <v>0.20200000000000001</v>
       </c>
-      <c r="G2" s="57">
+      <c r="G2" s="56">
         <v>0</v>
       </c>
       <c r="I2" s="11"/>
@@ -18671,7 +20314,7 @@
       <c r="V2" s="7"/>
     </row>
     <row r="3" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="58">
+      <c r="A3" s="57">
         <v>2</v>
       </c>
       <c r="B3" s="53" t="s">
@@ -18680,16 +20323,16 @@
       <c r="C3" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="54" t="s">
+      <c r="D3" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="55">
+      <c r="E3" s="54">
         <v>123</v>
       </c>
-      <c r="F3" s="56">
+      <c r="F3" s="55">
         <v>123</v>
       </c>
-      <c r="G3" s="57">
+      <c r="G3" s="56">
         <v>0</v>
       </c>
       <c r="H3" s="4"/>
@@ -18709,16 +20352,16 @@
       <c r="C4" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="54" t="s">
+      <c r="D4" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="55">
+      <c r="E4" s="54">
         <v>3.9750000000000001</v>
       </c>
-      <c r="F4" s="56">
+      <c r="F4" s="55">
         <v>3.9750000000000001</v>
       </c>
-      <c r="G4" s="57">
+      <c r="G4" s="56">
         <v>0</v>
       </c>
       <c r="H4" s="4"/>
@@ -18729,7 +20372,7 @@
       <c r="Q4" s="14"/>
     </row>
     <row r="5" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="58">
+      <c r="A5" s="57">
         <v>4</v>
       </c>
       <c r="B5" s="53" t="s">
@@ -18738,16 +20381,16 @@
       <c r="C5" s="53" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="54" t="s">
+      <c r="D5" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="55">
+      <c r="E5" s="54">
         <v>15.04</v>
       </c>
-      <c r="F5" s="56">
+      <c r="F5" s="55">
         <v>15.04</v>
       </c>
-      <c r="G5" s="57">
+      <c r="G5" s="56">
         <v>0</v>
       </c>
       <c r="H5" s="4"/>
@@ -18767,16 +20410,16 @@
       <c r="C6" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="54" t="s">
+      <c r="D6" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="55">
+      <c r="E6" s="54">
         <v>22.96</v>
       </c>
-      <c r="F6" s="56">
+      <c r="F6" s="55">
         <v>22.96</v>
       </c>
-      <c r="G6" s="57">
+      <c r="G6" s="56">
         <v>0</v>
       </c>
       <c r="H6" s="4"/>
@@ -18787,7 +20430,7 @@
       <c r="Q6" s="14"/>
     </row>
     <row r="7" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="58">
+      <c r="A7" s="57">
         <v>6</v>
       </c>
       <c r="B7" s="53" t="s">
@@ -18796,16 +20439,16 @@
       <c r="C7" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="54" t="s">
+      <c r="D7" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="E7" s="55">
+      <c r="E7" s="54">
         <v>6.54</v>
       </c>
-      <c r="F7" s="56">
+      <c r="F7" s="55">
         <v>6.54</v>
       </c>
-      <c r="G7" s="57">
+      <c r="G7" s="56">
         <v>0</v>
       </c>
       <c r="H7" s="4"/>
@@ -18825,16 +20468,16 @@
       <c r="C8" s="53" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="54" t="s">
+      <c r="D8" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="55">
+      <c r="E8" s="54">
         <v>0.23499999999999999</v>
       </c>
-      <c r="F8" s="56">
+      <c r="F8" s="55">
         <v>0.23499999999999999</v>
       </c>
-      <c r="G8" s="57">
+      <c r="G8" s="56">
         <v>0</v>
       </c>
       <c r="H8" s="4"/>
@@ -18845,7 +20488,7 @@
       <c r="Q8" s="14"/>
     </row>
     <row r="9" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="58">
+      <c r="A9" s="57">
         <v>8</v>
       </c>
       <c r="B9" s="53" t="s">
@@ -18854,16 +20497,16 @@
       <c r="C9" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="54" t="s">
+      <c r="D9" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="55">
+      <c r="E9" s="54">
         <v>94</v>
       </c>
-      <c r="F9" s="56">
+      <c r="F9" s="55">
         <v>94</v>
       </c>
-      <c r="G9" s="57">
+      <c r="G9" s="56">
         <v>0</v>
       </c>
       <c r="H9" s="4"/>
@@ -18883,16 +20526,16 @@
       <c r="C10" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="54" t="s">
+      <c r="D10" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="55">
+      <c r="E10" s="54">
         <v>284.49099999999999</v>
       </c>
-      <c r="F10" s="56">
+      <c r="F10" s="55">
         <v>284.49099999999999</v>
       </c>
-      <c r="G10" s="57">
+      <c r="G10" s="56">
         <v>0</v>
       </c>
       <c r="H10" s="4"/>
@@ -18903,7 +20546,7 @@
       <c r="Q10" s="14"/>
     </row>
     <row r="11" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="58">
+      <c r="A11" s="57">
         <v>10</v>
       </c>
       <c r="B11" s="53" t="s">
@@ -18912,16 +20555,16 @@
       <c r="C11" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="54" t="s">
+      <c r="D11" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="E11" s="55">
+      <c r="E11" s="54">
         <v>61.1</v>
       </c>
-      <c r="F11" s="56">
+      <c r="F11" s="55">
         <v>61.1</v>
       </c>
-      <c r="G11" s="57">
+      <c r="G11" s="56">
         <v>0</v>
       </c>
       <c r="H11" s="4"/>
@@ -18932,12 +20575,12 @@
       <c r="Q11" s="14"/>
     </row>
     <row r="12" spans="1:22" ht="15.9" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="68"/>
-      <c r="B12" s="69"/>
-      <c r="C12" s="70"/>
-      <c r="D12" s="71"/>
-      <c r="E12" s="93"/>
-      <c r="F12" s="64" t="s">
+      <c r="A12" s="67"/>
+      <c r="B12" s="68"/>
+      <c r="C12" s="69"/>
+      <c r="D12" s="70"/>
+      <c r="E12" s="92"/>
+      <c r="F12" s="63" t="s">
         <v>28</v>
       </c>
       <c r="G12" s="23">
@@ -18980,7 +20623,7 @@
       <c r="D15" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="E15" s="94" t="s">
+      <c r="E15" s="93" t="s">
         <v>0</v>
       </c>
       <c r="F15" s="1" t="s">
@@ -19003,10 +20646,10 @@
       <c r="C16" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="D16" s="54" t="s">
+      <c r="D16" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="E16" s="95">
+      <c r="E16" s="94">
         <v>30</v>
       </c>
       <c r="F16" s="8">
@@ -19019,7 +20662,7 @@
       <c r="I16"/>
     </row>
     <row r="17" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="58">
+      <c r="A17" s="57">
         <v>2</v>
       </c>
       <c r="B17" s="53" t="s">
@@ -19028,10 +20671,10 @@
       <c r="C17" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="D17" s="54" t="s">
+      <c r="D17" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="E17" s="95">
+      <c r="E17" s="94">
         <v>5.62</v>
       </c>
       <c r="F17" s="8">
@@ -19053,10 +20696,10 @@
       <c r="C18" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="D18" s="54" t="s">
+      <c r="D18" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="E18" s="95">
+      <c r="E18" s="94">
         <v>29.46</v>
       </c>
       <c r="F18" s="8">
@@ -19069,7 +20712,7 @@
       <c r="I18" s="11"/>
     </row>
     <row r="19" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="58">
+      <c r="A19" s="57">
         <v>4</v>
       </c>
       <c r="B19" s="53" t="s">
@@ -19078,10 +20721,10 @@
       <c r="C19" s="53" t="s">
         <v>20</v>
       </c>
-      <c r="D19" s="54" t="s">
+      <c r="D19" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="E19" s="95">
+      <c r="E19" s="94">
         <v>19.100000000000001</v>
       </c>
       <c r="F19" s="8">
@@ -19103,10 +20746,10 @@
       <c r="C20" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="D20" s="54" t="s">
+      <c r="D20" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="E20" s="95">
+      <c r="E20" s="94">
         <v>15.66</v>
       </c>
       <c r="F20" s="8">
@@ -19119,7 +20762,7 @@
       <c r="I20" s="11"/>
     </row>
     <row r="21" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="58">
+      <c r="A21" s="57">
         <v>6</v>
       </c>
       <c r="B21" s="53" t="s">
@@ -19128,10 +20771,10 @@
       <c r="C21" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="D21" s="54" t="s">
+      <c r="D21" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="E21" s="95">
+      <c r="E21" s="94">
         <v>0.152</v>
       </c>
       <c r="F21" s="8">
@@ -19153,10 +20796,10 @@
       <c r="C22" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="D22" s="54" t="s">
+      <c r="D22" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="E22" s="95">
+      <c r="E22" s="94">
         <v>157.19999999999999</v>
       </c>
       <c r="F22" s="8">
@@ -19169,7 +20812,7 @@
       <c r="I22"/>
     </row>
     <row r="23" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="58">
+      <c r="A23" s="57">
         <v>8</v>
       </c>
       <c r="B23" s="53" t="s">
@@ -19178,10 +20821,10 @@
       <c r="C23" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="D23" s="54" t="s">
+      <c r="D23" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="E23" s="95">
+      <c r="E23" s="94">
         <v>24.58</v>
       </c>
       <c r="F23" s="8">
@@ -19203,10 +20846,10 @@
       <c r="C24" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="D24" s="54" t="s">
+      <c r="D24" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="E24" s="95">
+      <c r="E24" s="94">
         <v>16.010000000000002</v>
       </c>
       <c r="F24" s="8">
@@ -19219,7 +20862,7 @@
       <c r="I24"/>
     </row>
     <row r="25" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="58">
+      <c r="A25" s="57">
         <v>10</v>
       </c>
       <c r="B25" s="53" t="s">
@@ -19228,10 +20871,10 @@
       <c r="C25" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="D25" s="54" t="s">
+      <c r="D25" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="E25" s="95">
+      <c r="E25" s="94">
         <v>75.2</v>
       </c>
       <c r="F25" s="8">
@@ -19246,9 +20889,9 @@
     <row r="26" spans="1:11" ht="15.9" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A26" s="52"/>
       <c r="B26" s="53"/>
-      <c r="C26" s="83"/>
-      <c r="D26" s="96"/>
-      <c r="E26" s="95"/>
+      <c r="C26" s="82"/>
+      <c r="D26" s="95"/>
+      <c r="E26" s="94"/>
       <c r="F26" s="22" t="s">
         <v>28</v>
       </c>
@@ -19269,11 +20912,11 @@
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A27" s="97"/>
-      <c r="B27" s="98"/>
-      <c r="C27" s="69"/>
-      <c r="D27" s="99"/>
-      <c r="E27" s="100"/>
+      <c r="A27" s="96"/>
+      <c r="B27" s="97"/>
+      <c r="C27" s="68"/>
+      <c r="D27" s="98"/>
+      <c r="E27" s="99"/>
       <c r="F27" s="4"/>
       <c r="H27" s="4"/>
       <c r="I27"/>
@@ -19319,23 +20962,23 @@
       <c r="C30" s="53" t="s">
         <v>54</v>
       </c>
-      <c r="D30" s="54" t="s">
+      <c r="D30" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="E30" s="55">
+      <c r="E30" s="54">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F30" s="56">
+      <c r="F30" s="55">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G30" s="57">
+      <c r="G30" s="56">
         <v>0</v>
       </c>
       <c r="H30"/>
       <c r="I30"/>
     </row>
     <row r="31" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="58">
+      <c r="A31" s="57">
         <v>2</v>
       </c>
       <c r="B31" s="53" t="s">
@@ -19344,16 +20987,16 @@
       <c r="C31" s="53" t="s">
         <v>54</v>
       </c>
-      <c r="D31" s="54" t="s">
+      <c r="D31" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="E31" s="55">
+      <c r="E31" s="54">
         <v>0.29299999999999998</v>
       </c>
-      <c r="F31" s="56">
+      <c r="F31" s="55">
         <v>0.29299999999999998</v>
       </c>
-      <c r="G31" s="57">
+      <c r="G31" s="56">
         <v>0</v>
       </c>
       <c r="H31"/>
@@ -19369,23 +21012,23 @@
       <c r="C32" s="53" t="s">
         <v>54</v>
       </c>
-      <c r="D32" s="54" t="s">
+      <c r="D32" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="E32" s="55">
+      <c r="E32" s="54">
         <v>26.58</v>
       </c>
-      <c r="F32" s="56">
+      <c r="F32" s="55">
         <v>26.58</v>
       </c>
-      <c r="G32" s="57">
+      <c r="G32" s="56">
         <v>0</v>
       </c>
       <c r="H32"/>
       <c r="I32"/>
     </row>
     <row r="33" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="58">
+      <c r="A33" s="57">
         <v>4</v>
       </c>
       <c r="B33" s="53" t="s">
@@ -19394,16 +21037,16 @@
       <c r="C33" s="53" t="s">
         <v>54</v>
       </c>
-      <c r="D33" s="54" t="s">
+      <c r="D33" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="E33" s="55">
+      <c r="E33" s="54">
         <v>8.26</v>
       </c>
-      <c r="F33" s="56">
+      <c r="F33" s="55">
         <v>8.26</v>
       </c>
-      <c r="G33" s="57">
+      <c r="G33" s="56">
         <v>0</v>
       </c>
       <c r="H33"/>
@@ -19419,23 +21062,23 @@
       <c r="C34" s="53" t="s">
         <v>63</v>
       </c>
-      <c r="D34" s="54" t="s">
+      <c r="D34" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="E34" s="55">
+      <c r="E34" s="54">
         <v>2.76</v>
       </c>
-      <c r="F34" s="56">
+      <c r="F34" s="55">
         <v>2.76</v>
       </c>
-      <c r="G34" s="57">
+      <c r="G34" s="56">
         <v>0</v>
       </c>
       <c r="H34"/>
       <c r="I34"/>
     </row>
     <row r="35" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A35" s="58">
+      <c r="A35" s="57">
         <v>6</v>
       </c>
       <c r="B35" s="53" t="s">
@@ -19444,16 +21087,16 @@
       <c r="C35" s="53" t="s">
         <v>63</v>
       </c>
-      <c r="D35" s="54" t="s">
+      <c r="D35" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="E35" s="55">
+      <c r="E35" s="54">
         <v>2.7949999999999999</v>
       </c>
-      <c r="F35" s="56">
+      <c r="F35" s="55">
         <v>2.7949999999999999</v>
       </c>
-      <c r="G35" s="57">
+      <c r="G35" s="56">
         <v>0</v>
       </c>
       <c r="H35"/>
@@ -19469,23 +21112,23 @@
       <c r="C36" s="53" t="s">
         <v>54</v>
       </c>
-      <c r="D36" s="54" t="s">
+      <c r="D36" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="E36" s="55">
+      <c r="E36" s="54">
         <v>35.799999999999997</v>
       </c>
-      <c r="F36" s="56">
+      <c r="F36" s="55">
         <v>35.799999999999997</v>
       </c>
-      <c r="G36" s="57">
+      <c r="G36" s="56">
         <v>0</v>
       </c>
       <c r="H36"/>
       <c r="I36"/>
     </row>
     <row r="37" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A37" s="58">
+      <c r="A37" s="57">
         <v>8</v>
       </c>
       <c r="B37" s="53" t="s">
@@ -19494,16 +21137,16 @@
       <c r="C37" s="53" t="s">
         <v>54</v>
       </c>
-      <c r="D37" s="54" t="s">
+      <c r="D37" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="E37" s="55">
+      <c r="E37" s="54">
         <v>2.1</v>
       </c>
-      <c r="F37" s="56">
+      <c r="F37" s="55">
         <v>2.1</v>
       </c>
-      <c r="G37" s="57">
+      <c r="G37" s="56">
         <v>0</v>
       </c>
       <c r="H37"/>
@@ -19520,16 +21163,16 @@
       <c r="C38" s="53" t="s">
         <v>54</v>
       </c>
-      <c r="D38" s="54" t="s">
+      <c r="D38" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="E38" s="55">
+      <c r="E38" s="54">
         <v>5.76</v>
       </c>
-      <c r="F38" s="56">
+      <c r="F38" s="55">
         <v>5.76</v>
       </c>
-      <c r="G38" s="57">
+      <c r="G38" s="56">
         <v>0</v>
       </c>
       <c r="H38"/>
@@ -19537,7 +21180,7 @@
       <c r="P38" s="24"/>
     </row>
     <row r="39" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A39" s="58">
+      <c r="A39" s="57">
         <v>10</v>
       </c>
       <c r="B39" s="53" t="s">
@@ -19546,31 +21189,31 @@
       <c r="C39" s="53" t="s">
         <v>54</v>
       </c>
-      <c r="D39" s="54" t="s">
+      <c r="D39" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="E39" s="55">
+      <c r="E39" s="54">
         <v>0.72799999999999998</v>
       </c>
-      <c r="F39" s="56">
+      <c r="F39" s="55">
         <v>0.72799999999999998</v>
       </c>
-      <c r="G39" s="57">
+      <c r="G39" s="56">
         <v>0</v>
       </c>
       <c r="H39"/>
       <c r="I39"/>
     </row>
     <row r="40" spans="1:16" ht="15.9" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="59"/>
-      <c r="B40" s="60"/>
-      <c r="C40" s="61"/>
-      <c r="D40" s="62"/>
-      <c r="E40" s="63"/>
-      <c r="F40" s="64" t="s">
+      <c r="A40" s="58"/>
+      <c r="B40" s="59"/>
+      <c r="C40" s="60"/>
+      <c r="D40" s="61"/>
+      <c r="E40" s="62"/>
+      <c r="F40" s="63" t="s">
         <v>28</v>
       </c>
-      <c r="G40" s="65">
+      <c r="G40" s="64">
         <v>0</v>
       </c>
       <c r="H40">
@@ -19607,7 +21250,7 @@
       <c r="F42" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="G42" s="66" t="s">
+      <c r="G42" s="65" t="s">
         <v>6</v>
       </c>
       <c r="H42" s="3" t="s">
@@ -19621,29 +21264,29 @@
       </c>
       <c r="B43" s="53"/>
       <c r="C43" s="53"/>
-      <c r="D43" s="54"/>
-      <c r="E43" s="55"/>
-      <c r="F43" s="56">
+      <c r="D43" s="15"/>
+      <c r="E43" s="54"/>
+      <c r="F43" s="55">
         <v>15.04</v>
       </c>
-      <c r="G43" s="67">
+      <c r="G43" s="66">
         <v>0</v>
       </c>
       <c r="H43"/>
       <c r="I43"/>
     </row>
     <row r="44" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A44" s="58">
+      <c r="A44" s="57">
         <v>2</v>
       </c>
       <c r="B44" s="53"/>
       <c r="C44" s="53"/>
-      <c r="D44" s="54"/>
-      <c r="E44" s="55"/>
-      <c r="F44" s="56">
+      <c r="D44" s="15"/>
+      <c r="E44" s="54"/>
+      <c r="F44" s="55">
         <v>19.739999999999998</v>
       </c>
-      <c r="G44" s="67">
+      <c r="G44" s="66">
         <v>0</v>
       </c>
       <c r="H44"/>
@@ -19655,29 +21298,29 @@
       </c>
       <c r="B45" s="53"/>
       <c r="C45" s="53"/>
-      <c r="D45" s="54"/>
-      <c r="E45" s="55"/>
-      <c r="F45" s="56">
+      <c r="D45" s="15"/>
+      <c r="E45" s="54"/>
+      <c r="F45" s="55">
         <v>197.3</v>
       </c>
-      <c r="G45" s="67">
+      <c r="G45" s="66">
         <v>0</v>
       </c>
       <c r="H45"/>
       <c r="I45"/>
     </row>
     <row r="46" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A46" s="58">
+      <c r="A46" s="57">
         <v>4</v>
       </c>
       <c r="B46" s="53"/>
       <c r="C46" s="53"/>
-      <c r="D46" s="54"/>
-      <c r="E46" s="55"/>
-      <c r="F46" s="56">
+      <c r="D46" s="15"/>
+      <c r="E46" s="54"/>
+      <c r="F46" s="55">
         <v>33.520000000000003</v>
       </c>
-      <c r="G46" s="67">
+      <c r="G46" s="66">
         <v>0</v>
       </c>
       <c r="H46"/>
@@ -19689,29 +21332,29 @@
       </c>
       <c r="B47" s="53"/>
       <c r="C47" s="53"/>
-      <c r="D47" s="54"/>
-      <c r="E47" s="55"/>
-      <c r="F47" s="56">
+      <c r="D47" s="15"/>
+      <c r="E47" s="54"/>
+      <c r="F47" s="55">
         <v>31.7</v>
       </c>
-      <c r="G47" s="67">
+      <c r="G47" s="66">
         <v>0</v>
       </c>
       <c r="H47"/>
       <c r="I47"/>
     </row>
     <row r="48" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A48" s="58">
+      <c r="A48" s="57">
         <v>6</v>
       </c>
       <c r="B48" s="53"/>
       <c r="C48" s="53"/>
-      <c r="D48" s="54"/>
-      <c r="E48" s="55"/>
-      <c r="F48" s="56">
+      <c r="D48" s="15"/>
+      <c r="E48" s="54"/>
+      <c r="F48" s="55">
         <v>12.1</v>
       </c>
-      <c r="G48" s="67">
+      <c r="G48" s="66">
         <v>0</v>
       </c>
       <c r="H48"/>
@@ -19723,29 +21366,29 @@
       </c>
       <c r="B49" s="53"/>
       <c r="C49" s="53"/>
-      <c r="D49" s="54"/>
-      <c r="E49" s="55"/>
-      <c r="F49" s="56">
+      <c r="D49" s="15"/>
+      <c r="E49" s="54"/>
+      <c r="F49" s="55">
         <v>9.4</v>
       </c>
-      <c r="G49" s="67">
+      <c r="G49" s="66">
         <v>0</v>
       </c>
       <c r="H49"/>
       <c r="I49"/>
     </row>
     <row r="50" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A50" s="58">
+      <c r="A50" s="57">
         <v>8</v>
       </c>
       <c r="B50" s="53"/>
       <c r="C50" s="53"/>
-      <c r="D50" s="54"/>
-      <c r="E50" s="55"/>
-      <c r="F50" s="56">
+      <c r="D50" s="15"/>
+      <c r="E50" s="54"/>
+      <c r="F50" s="55">
         <v>7</v>
       </c>
-      <c r="G50" s="67">
+      <c r="G50" s="66">
         <v>0</v>
       </c>
       <c r="H50"/>
@@ -19757,44 +21400,44 @@
       </c>
       <c r="B51" s="53"/>
       <c r="C51" s="53"/>
-      <c r="D51" s="54"/>
-      <c r="E51" s="55"/>
-      <c r="F51" s="56">
+      <c r="D51" s="15"/>
+      <c r="E51" s="54"/>
+      <c r="F51" s="55">
         <v>5.8419999999999996</v>
       </c>
-      <c r="G51" s="67">
+      <c r="G51" s="66">
         <v>0</v>
       </c>
       <c r="H51"/>
       <c r="I51"/>
     </row>
     <row r="52" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A52" s="58">
+      <c r="A52" s="57">
         <v>10</v>
       </c>
       <c r="B52" s="53"/>
       <c r="C52" s="53"/>
-      <c r="D52" s="54"/>
-      <c r="E52" s="55"/>
-      <c r="F52" s="56">
+      <c r="D52" s="15"/>
+      <c r="E52" s="54"/>
+      <c r="F52" s="55">
         <v>39.5</v>
       </c>
-      <c r="G52" s="67">
+      <c r="G52" s="66">
         <v>0</v>
       </c>
       <c r="H52"/>
       <c r="I52"/>
     </row>
     <row r="53" spans="1:11" ht="15.9" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A53" s="68"/>
-      <c r="B53" s="69"/>
-      <c r="C53" s="70"/>
-      <c r="D53" s="71"/>
-      <c r="E53" s="72"/>
-      <c r="F53" s="73" t="s">
+      <c r="A53" s="67"/>
+      <c r="B53" s="68"/>
+      <c r="C53" s="69"/>
+      <c r="D53" s="70"/>
+      <c r="E53" s="71"/>
+      <c r="F53" s="72" t="s">
         <v>28</v>
       </c>
-      <c r="G53" s="74">
+      <c r="G53" s="73">
         <v>0</v>
       </c>
       <c r="H53" s="17" t="s">
@@ -19832,7 +21475,7 @@
       <c r="D55" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="E55" s="101" t="s">
+      <c r="E55" s="100" t="s">
         <v>77</v>
       </c>
       <c r="F55" s="32" t="s">
@@ -19849,10 +21492,10 @@
       <c r="A56" s="52">
         <v>1</v>
       </c>
-      <c r="B56" s="82"/>
-      <c r="C56" s="83"/>
-      <c r="D56" s="82"/>
-      <c r="E56" s="102"/>
+      <c r="B56" s="81"/>
+      <c r="C56" s="82"/>
+      <c r="D56" s="81"/>
+      <c r="E56" s="101"/>
       <c r="F56" s="8">
         <v>190.7</v>
       </c>
@@ -19862,13 +21505,13 @@
       <c r="H56" s="4"/>
     </row>
     <row r="57" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A57" s="58">
+      <c r="A57" s="57">
         <v>2</v>
       </c>
-      <c r="B57" s="87"/>
+      <c r="B57" s="86"/>
       <c r="C57" s="16"/>
-      <c r="D57" s="87"/>
-      <c r="E57" s="102"/>
+      <c r="D57" s="86"/>
+      <c r="E57" s="101"/>
       <c r="F57" s="8">
         <v>75.849999999999994</v>
       </c>
@@ -19882,10 +21525,10 @@
       <c r="A58" s="52">
         <v>3</v>
       </c>
-      <c r="B58" s="82"/>
-      <c r="C58" s="83"/>
-      <c r="D58" s="82"/>
-      <c r="E58" s="102"/>
+      <c r="B58" s="81"/>
+      <c r="C58" s="82"/>
+      <c r="D58" s="81"/>
+      <c r="E58" s="101"/>
       <c r="F58" s="8">
         <v>108.84</v>
       </c>
@@ -19897,13 +21540,13 @@
       <c r="K58" s="35"/>
     </row>
     <row r="59" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A59" s="58">
+      <c r="A59" s="57">
         <v>4</v>
       </c>
-      <c r="B59" s="87"/>
+      <c r="B59" s="86"/>
       <c r="C59" s="16"/>
-      <c r="D59" s="87"/>
-      <c r="E59" s="102"/>
+      <c r="D59" s="86"/>
+      <c r="E59" s="101"/>
       <c r="F59" s="8">
         <v>6.54</v>
       </c>
@@ -19918,10 +21561,10 @@
       <c r="A60" s="52">
         <v>5</v>
       </c>
-      <c r="B60" s="82"/>
-      <c r="C60" s="83"/>
-      <c r="D60" s="82"/>
-      <c r="E60" s="102"/>
+      <c r="B60" s="81"/>
+      <c r="C60" s="82"/>
+      <c r="D60" s="81"/>
+      <c r="E60" s="101"/>
       <c r="F60" s="8">
         <v>81.099999999999994</v>
       </c>
@@ -19933,13 +21576,13 @@
       <c r="K60" s="35"/>
     </row>
     <row r="61" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A61" s="58">
+      <c r="A61" s="57">
         <v>6</v>
       </c>
-      <c r="B61" s="87"/>
+      <c r="B61" s="86"/>
       <c r="C61" s="16"/>
-      <c r="D61" s="87"/>
-      <c r="E61" s="102"/>
+      <c r="D61" s="86"/>
+      <c r="E61" s="101"/>
       <c r="F61" s="8">
         <v>60</v>
       </c>
@@ -19954,10 +21597,10 @@
       <c r="A62" s="52">
         <v>7</v>
       </c>
-      <c r="B62" s="82"/>
-      <c r="C62" s="83"/>
-      <c r="D62" s="82"/>
-      <c r="E62" s="102"/>
+      <c r="B62" s="81"/>
+      <c r="C62" s="82"/>
+      <c r="D62" s="81"/>
+      <c r="E62" s="101"/>
       <c r="F62" s="8">
         <v>75.569999999999993</v>
       </c>
@@ -19968,13 +21611,13 @@
       <c r="I62"/>
     </row>
     <row r="63" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A63" s="58">
+      <c r="A63" s="57">
         <v>8</v>
       </c>
-      <c r="B63" s="87"/>
+      <c r="B63" s="86"/>
       <c r="C63" s="16"/>
-      <c r="D63" s="87"/>
-      <c r="E63" s="102"/>
+      <c r="D63" s="86"/>
+      <c r="E63" s="101"/>
       <c r="F63" s="8">
         <v>41.66</v>
       </c>
@@ -19988,10 +21631,10 @@
       <c r="A64" s="52">
         <v>9</v>
       </c>
-      <c r="B64" s="82"/>
-      <c r="C64" s="83"/>
-      <c r="D64" s="82"/>
-      <c r="E64" s="102"/>
+      <c r="B64" s="81"/>
+      <c r="C64" s="82"/>
+      <c r="D64" s="81"/>
+      <c r="E64" s="101"/>
       <c r="F64" s="8">
         <v>93.52</v>
       </c>
@@ -20002,13 +21645,13 @@
       <c r="I64"/>
     </row>
     <row r="65" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A65" s="58">
+      <c r="A65" s="57">
         <v>10</v>
       </c>
-      <c r="B65" s="87"/>
+      <c r="B65" s="86"/>
       <c r="C65" s="16"/>
-      <c r="D65" s="87"/>
-      <c r="E65" s="102"/>
+      <c r="D65" s="86"/>
+      <c r="E65" s="101"/>
       <c r="F65" s="8">
         <v>60.98</v>
       </c>
@@ -20019,11 +21662,11 @@
       <c r="I65"/>
     </row>
     <row r="66" spans="1:11" ht="15.45" x14ac:dyDescent="0.4">
-      <c r="A66" s="68"/>
-      <c r="B66" s="69"/>
-      <c r="C66" s="70"/>
-      <c r="D66" s="71"/>
-      <c r="E66" s="103"/>
+      <c r="A66" s="67"/>
+      <c r="B66" s="68"/>
+      <c r="C66" s="69"/>
+      <c r="D66" s="70"/>
+      <c r="E66" s="102"/>
       <c r="F66" s="36" t="s">
         <v>28</v>
       </c>
@@ -20053,19 +21696,19 @@
       <c r="I67"/>
     </row>
     <row r="68" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A68" s="75" t="s">
+      <c r="A68" s="74" t="s">
         <v>31</v>
       </c>
-      <c r="B68" s="104" t="s">
+      <c r="B68" s="103" t="s">
         <v>1</v>
       </c>
-      <c r="C68" s="77" t="s">
+      <c r="C68" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="D68" s="77" t="s">
+      <c r="D68" s="76" t="s">
         <v>3</v>
       </c>
-      <c r="E68" s="105" t="s">
+      <c r="E68" s="104" t="s">
         <v>0</v>
       </c>
       <c r="F68" s="32" t="s">
@@ -20079,19 +21722,19 @@
       </c>
     </row>
     <row r="69" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A69" s="81">
+      <c r="A69" s="80">
         <v>1</v>
       </c>
-      <c r="B69" s="82" t="s">
+      <c r="B69" s="81" t="s">
         <v>79</v>
       </c>
-      <c r="C69" s="83" t="s">
+      <c r="C69" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="D69" s="82" t="s">
+      <c r="D69" s="81" t="s">
         <v>80</v>
       </c>
-      <c r="E69" s="106">
+      <c r="E69" s="105">
         <v>60</v>
       </c>
       <c r="F69" s="8">
@@ -20103,19 +21746,19 @@
       <c r="H69" s="4"/>
     </row>
     <row r="70" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A70" s="86">
+      <c r="A70" s="85">
         <v>2</v>
       </c>
-      <c r="B70" s="87" t="s">
+      <c r="B70" s="86" t="s">
         <v>83</v>
       </c>
       <c r="C70" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="D70" s="87" t="s">
+      <c r="D70" s="86" t="s">
         <v>84</v>
       </c>
-      <c r="E70" s="106">
+      <c r="E70" s="105">
         <v>41.66</v>
       </c>
       <c r="F70" s="8">
@@ -20129,19 +21772,19 @@
       <c r="J70" s="27"/>
     </row>
     <row r="71" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A71" s="81">
+      <c r="A71" s="80">
         <v>3</v>
       </c>
-      <c r="B71" s="82" t="s">
+      <c r="B71" s="81" t="s">
         <v>90</v>
       </c>
-      <c r="C71" s="83" t="s">
+      <c r="C71" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="D71" s="82" t="s">
+      <c r="D71" s="81" t="s">
         <v>91</v>
       </c>
-      <c r="E71" s="106">
+      <c r="E71" s="105">
         <v>46.42</v>
       </c>
       <c r="F71" s="8">
@@ -20155,19 +21798,19 @@
       <c r="J71" s="27"/>
     </row>
     <row r="72" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A72" s="86">
+      <c r="A72" s="85">
         <v>4</v>
       </c>
-      <c r="B72" s="87" t="s">
+      <c r="B72" s="86" t="s">
         <v>92</v>
       </c>
       <c r="C72" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="D72" s="87" t="s">
+      <c r="D72" s="86" t="s">
         <v>93</v>
       </c>
-      <c r="E72" s="106">
+      <c r="E72" s="105">
         <v>137</v>
       </c>
       <c r="F72" s="8">
@@ -20181,19 +21824,19 @@
       <c r="J72" s="39"/>
     </row>
     <row r="73" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A73" s="81">
+      <c r="A73" s="80">
         <v>5</v>
       </c>
-      <c r="B73" s="82" t="s">
+      <c r="B73" s="81" t="s">
         <v>94</v>
       </c>
-      <c r="C73" s="83" t="s">
+      <c r="C73" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="D73" s="82" t="s">
+      <c r="D73" s="81" t="s">
         <v>95</v>
       </c>
-      <c r="E73" s="106">
+      <c r="E73" s="105">
         <v>13.46</v>
       </c>
       <c r="F73" s="8">
@@ -20207,19 +21850,19 @@
       <c r="J73" s="39"/>
     </row>
     <row r="74" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A74" s="86">
+      <c r="A74" s="85">
         <v>6</v>
       </c>
-      <c r="B74" s="87" t="s">
+      <c r="B74" s="86" t="s">
         <v>96</v>
       </c>
       <c r="C74" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="D74" s="87" t="s">
+      <c r="D74" s="86" t="s">
         <v>97</v>
       </c>
-      <c r="E74" s="106">
+      <c r="E74" s="105">
         <v>75.599999999999994</v>
       </c>
       <c r="F74" s="8">
@@ -20233,19 +21876,19 @@
       <c r="J74" s="39"/>
     </row>
     <row r="75" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A75" s="81">
+      <c r="A75" s="80">
         <v>7</v>
       </c>
-      <c r="B75" s="82" t="s">
+      <c r="B75" s="81" t="s">
         <v>81</v>
       </c>
-      <c r="C75" s="83" t="s">
+      <c r="C75" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="D75" s="82" t="s">
+      <c r="D75" s="81" t="s">
         <v>82</v>
       </c>
-      <c r="E75" s="106">
+      <c r="E75" s="105">
         <v>75.569999999999993</v>
       </c>
       <c r="F75" s="8">
@@ -20259,19 +21902,19 @@
       <c r="J75" s="39"/>
     </row>
     <row r="76" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A76" s="86">
+      <c r="A76" s="85">
         <v>8</v>
       </c>
-      <c r="B76" s="87" t="s">
+      <c r="B76" s="86" t="s">
         <v>85</v>
       </c>
       <c r="C76" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="D76" s="87" t="s">
+      <c r="D76" s="86" t="s">
         <v>86</v>
       </c>
-      <c r="E76" s="106">
+      <c r="E76" s="105">
         <v>93.52</v>
       </c>
       <c r="F76" s="8">
@@ -20285,19 +21928,19 @@
       <c r="J76" s="27"/>
     </row>
     <row r="77" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A77" s="81">
+      <c r="A77" s="80">
         <v>9</v>
       </c>
-      <c r="B77" s="82" t="s">
+      <c r="B77" s="81" t="s">
         <v>87</v>
       </c>
-      <c r="C77" s="83" t="s">
+      <c r="C77" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="D77" s="82" t="s">
+      <c r="D77" s="81" t="s">
         <v>88</v>
       </c>
-      <c r="E77" s="106">
+      <c r="E77" s="105">
         <v>60.98</v>
       </c>
       <c r="F77" s="8">
@@ -20311,19 +21954,19 @@
       <c r="J77" s="27"/>
     </row>
     <row r="78" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A78" s="107">
+      <c r="A78" s="106">
         <v>10</v>
       </c>
-      <c r="B78" s="108" t="s">
+      <c r="B78" s="107" t="s">
         <v>98</v>
       </c>
-      <c r="C78" s="109" t="s">
+      <c r="C78" s="108" t="s">
         <v>9</v>
       </c>
-      <c r="D78" s="108" t="s">
+      <c r="D78" s="107" t="s">
         <v>99</v>
       </c>
-      <c r="E78" s="110">
+      <c r="E78" s="109">
         <v>123.85</v>
       </c>
       <c r="F78" s="8">
@@ -20353,25 +21996,25 @@
       <c r="I80"/>
     </row>
     <row r="81" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A81" s="75" t="s">
+      <c r="A81" s="74" t="s">
         <v>0</v>
       </c>
-      <c r="B81" s="76" t="s">
+      <c r="B81" s="75" t="s">
         <v>100</v>
       </c>
-      <c r="C81" s="77" t="s">
+      <c r="C81" s="76" t="s">
         <v>101</v>
       </c>
-      <c r="D81" s="77" t="s">
+      <c r="D81" s="76" t="s">
         <v>3</v>
       </c>
-      <c r="E81" s="78" t="s">
+      <c r="E81" s="77" t="s">
         <v>51</v>
       </c>
-      <c r="F81" s="79" t="s">
+      <c r="F81" s="78" t="s">
         <v>5</v>
       </c>
-      <c r="G81" s="80" t="s">
+      <c r="G81" s="79" t="s">
         <v>6</v>
       </c>
       <c r="H81" s="20">
@@ -20380,162 +22023,162 @@
       <c r="I81"/>
     </row>
     <row r="82" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A82" s="81">
+      <c r="A82" s="80">
         <v>1</v>
       </c>
-      <c r="B82" s="82"/>
-      <c r="C82" s="83"/>
-      <c r="D82" s="82"/>
-      <c r="E82" s="84"/>
-      <c r="F82" s="56"/>
-      <c r="G82" s="85" t="e">
+      <c r="B82" s="81"/>
+      <c r="C82" s="82"/>
+      <c r="D82" s="81"/>
+      <c r="E82" s="83"/>
+      <c r="F82" s="55"/>
+      <c r="G82" s="84" t="e">
         <v>#VALUE!</v>
       </c>
       <c r="H82"/>
       <c r="I82"/>
     </row>
     <row r="83" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A83" s="86">
+      <c r="A83" s="85">
         <v>2</v>
       </c>
-      <c r="B83" s="87"/>
+      <c r="B83" s="86"/>
       <c r="C83" s="16"/>
-      <c r="D83" s="87"/>
-      <c r="E83" s="84"/>
-      <c r="F83" s="56"/>
-      <c r="G83" s="85" t="e">
+      <c r="D83" s="86"/>
+      <c r="E83" s="83"/>
+      <c r="F83" s="55"/>
+      <c r="G83" s="84" t="e">
         <v>#VALUE!</v>
       </c>
       <c r="H83"/>
       <c r="I83"/>
     </row>
     <row r="84" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A84" s="81">
+      <c r="A84" s="80">
         <v>3</v>
       </c>
-      <c r="B84" s="82"/>
-      <c r="C84" s="83"/>
-      <c r="D84" s="82"/>
-      <c r="E84" s="84"/>
-      <c r="F84" s="56"/>
-      <c r="G84" s="85" t="e">
+      <c r="B84" s="81"/>
+      <c r="C84" s="82"/>
+      <c r="D84" s="81"/>
+      <c r="E84" s="83"/>
+      <c r="F84" s="55"/>
+      <c r="G84" s="84" t="e">
         <v>#VALUE!</v>
       </c>
       <c r="H84"/>
       <c r="I84"/>
     </row>
     <row r="85" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A85" s="86">
+      <c r="A85" s="85">
         <v>4</v>
       </c>
-      <c r="B85" s="87"/>
-      <c r="C85" s="88"/>
-      <c r="D85" s="87"/>
-      <c r="E85" s="84"/>
-      <c r="F85" s="56"/>
-      <c r="G85" s="85" t="e">
+      <c r="B85" s="86"/>
+      <c r="C85" s="87"/>
+      <c r="D85" s="86"/>
+      <c r="E85" s="83"/>
+      <c r="F85" s="55"/>
+      <c r="G85" s="84" t="e">
         <v>#VALUE!</v>
       </c>
       <c r="H85"/>
       <c r="I85"/>
     </row>
     <row r="86" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A86" s="81">
+      <c r="A86" s="80">
         <v>5</v>
       </c>
-      <c r="B86" s="82"/>
-      <c r="C86" s="88"/>
-      <c r="D86" s="82"/>
-      <c r="E86" s="84"/>
-      <c r="F86" s="56"/>
-      <c r="G86" s="85" t="e">
+      <c r="B86" s="81"/>
+      <c r="C86" s="87"/>
+      <c r="D86" s="81"/>
+      <c r="E86" s="83"/>
+      <c r="F86" s="55"/>
+      <c r="G86" s="84" t="e">
         <v>#VALUE!</v>
       </c>
       <c r="H86"/>
       <c r="I86"/>
     </row>
     <row r="87" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A87" s="86">
+      <c r="A87" s="85">
         <v>6</v>
       </c>
-      <c r="B87" s="87"/>
-      <c r="C87" s="88"/>
-      <c r="D87" s="87"/>
-      <c r="E87" s="84"/>
-      <c r="F87" s="56"/>
-      <c r="G87" s="85" t="e">
+      <c r="B87" s="86"/>
+      <c r="C87" s="87"/>
+      <c r="D87" s="86"/>
+      <c r="E87" s="83"/>
+      <c r="F87" s="55"/>
+      <c r="G87" s="84" t="e">
         <v>#VALUE!</v>
       </c>
       <c r="H87"/>
       <c r="I87"/>
     </row>
     <row r="88" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A88" s="81">
+      <c r="A88" s="80">
         <v>7</v>
       </c>
-      <c r="B88" s="82"/>
-      <c r="C88" s="83"/>
-      <c r="D88" s="82"/>
-      <c r="E88" s="84"/>
-      <c r="F88" s="56"/>
-      <c r="G88" s="85" t="e">
+      <c r="B88" s="81"/>
+      <c r="C88" s="82"/>
+      <c r="D88" s="81"/>
+      <c r="E88" s="83"/>
+      <c r="F88" s="55"/>
+      <c r="G88" s="84" t="e">
         <v>#VALUE!</v>
       </c>
       <c r="H88"/>
       <c r="I88"/>
     </row>
     <row r="89" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A89" s="86">
+      <c r="A89" s="85">
         <v>8</v>
       </c>
-      <c r="B89" s="87"/>
-      <c r="C89" s="88"/>
-      <c r="D89" s="87"/>
-      <c r="E89" s="84"/>
-      <c r="F89" s="56"/>
-      <c r="G89" s="85" t="e">
+      <c r="B89" s="86"/>
+      <c r="C89" s="87"/>
+      <c r="D89" s="86"/>
+      <c r="E89" s="83"/>
+      <c r="F89" s="55"/>
+      <c r="G89" s="84" t="e">
         <v>#VALUE!</v>
       </c>
       <c r="H89"/>
       <c r="I89"/>
     </row>
     <row r="90" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A90" s="81">
+      <c r="A90" s="80">
         <v>9</v>
       </c>
-      <c r="B90" s="82"/>
-      <c r="C90" s="83"/>
-      <c r="D90" s="82"/>
-      <c r="E90" s="84"/>
-      <c r="F90" s="56"/>
-      <c r="G90" s="85" t="e">
+      <c r="B90" s="81"/>
+      <c r="C90" s="82"/>
+      <c r="D90" s="81"/>
+      <c r="E90" s="83"/>
+      <c r="F90" s="55"/>
+      <c r="G90" s="84" t="e">
         <v>#VALUE!</v>
       </c>
       <c r="H90"/>
       <c r="I90"/>
     </row>
     <row r="91" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A91" s="86">
+      <c r="A91" s="85">
         <v>10</v>
       </c>
-      <c r="B91" s="87"/>
+      <c r="B91" s="86"/>
       <c r="C91" s="16"/>
-      <c r="D91" s="87"/>
-      <c r="E91" s="84"/>
-      <c r="F91" s="56"/>
-      <c r="G91" s="85" t="e">
+      <c r="D91" s="86"/>
+      <c r="E91" s="83"/>
+      <c r="F91" s="55"/>
+      <c r="G91" s="84" t="e">
         <v>#VALUE!</v>
       </c>
       <c r="H91"/>
       <c r="I91"/>
     </row>
     <row r="92" spans="1:12" ht="15.45" x14ac:dyDescent="0.4">
-      <c r="A92" s="89"/>
-      <c r="B92" s="90"/>
-      <c r="C92" s="91"/>
+      <c r="A92" s="88"/>
+      <c r="B92" s="89"/>
+      <c r="C92" s="90"/>
       <c r="D92" s="35"/>
-      <c r="E92" s="92"/>
-      <c r="F92" s="73" t="s">
+      <c r="E92" s="91"/>
+      <c r="F92" s="72" t="s">
         <v>28</v>
       </c>
       <c r="G92" s="30" t="e">
@@ -20566,25 +22209,25 @@
       <c r="K94" s="20"/>
     </row>
     <row r="95" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A95" s="75" t="s">
+      <c r="A95" s="74" t="s">
         <v>0</v>
       </c>
-      <c r="B95" s="76" t="s">
+      <c r="B95" s="75" t="s">
         <v>102</v>
       </c>
-      <c r="C95" s="77" t="s">
+      <c r="C95" s="76" t="s">
         <v>101</v>
       </c>
-      <c r="D95" s="78" t="s">
+      <c r="D95" s="77" t="s">
         <v>51</v>
       </c>
-      <c r="E95" s="78" t="s">
+      <c r="E95" s="77" t="s">
         <v>103</v>
       </c>
-      <c r="F95" s="79" t="s">
+      <c r="F95" s="78" t="s">
         <v>5</v>
       </c>
-      <c r="G95" s="80" t="s">
+      <c r="G95" s="79" t="s">
         <v>6</v>
       </c>
       <c r="H95" s="3" t="s">
@@ -20595,29 +22238,29 @@
       <c r="L95" s="45"/>
     </row>
     <row r="96" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A96" s="81">
+      <c r="A96" s="80">
         <v>1</v>
       </c>
-      <c r="B96" s="82"/>
-      <c r="C96" s="83"/>
-      <c r="D96" s="82"/>
-      <c r="E96" s="55"/>
-      <c r="F96" s="56"/>
-      <c r="G96" s="85" t="e">
+      <c r="B96" s="81"/>
+      <c r="C96" s="82"/>
+      <c r="D96" s="81"/>
+      <c r="E96" s="54"/>
+      <c r="F96" s="55"/>
+      <c r="G96" s="84" t="e">
         <v>#VALUE!</v>
       </c>
       <c r="H96" s="4"/>
     </row>
     <row r="97" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A97" s="86">
+      <c r="A97" s="85">
         <v>2</v>
       </c>
-      <c r="B97" s="87"/>
+      <c r="B97" s="86"/>
       <c r="C97" s="16"/>
-      <c r="D97" s="87"/>
-      <c r="E97" s="55"/>
-      <c r="F97" s="56"/>
-      <c r="G97" s="85" t="e">
+      <c r="D97" s="86"/>
+      <c r="E97" s="54"/>
+      <c r="F97" s="55"/>
+      <c r="G97" s="84" t="e">
         <v>#VALUE!</v>
       </c>
       <c r="H97" s="4"/>
@@ -20625,45 +22268,45 @@
       <c r="J97" s="24"/>
     </row>
     <row r="98" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A98" s="81">
+      <c r="A98" s="80">
         <v>3</v>
       </c>
-      <c r="B98" s="82"/>
-      <c r="C98" s="83"/>
-      <c r="D98" s="82"/>
-      <c r="E98" s="55"/>
-      <c r="F98" s="56"/>
-      <c r="G98" s="85" t="e">
+      <c r="B98" s="81"/>
+      <c r="C98" s="82"/>
+      <c r="D98" s="81"/>
+      <c r="E98" s="54"/>
+      <c r="F98" s="55"/>
+      <c r="G98" s="84" t="e">
         <v>#VALUE!</v>
       </c>
       <c r="H98" s="4"/>
       <c r="I98"/>
     </row>
     <row r="99" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A99" s="86">
+      <c r="A99" s="85">
         <v>4</v>
       </c>
-      <c r="B99" s="87"/>
+      <c r="B99" s="86"/>
       <c r="C99" s="16"/>
-      <c r="D99" s="87"/>
-      <c r="E99" s="55"/>
-      <c r="F99" s="56"/>
-      <c r="G99" s="85" t="e">
+      <c r="D99" s="86"/>
+      <c r="E99" s="54"/>
+      <c r="F99" s="55"/>
+      <c r="G99" s="84" t="e">
         <v>#VALUE!</v>
       </c>
       <c r="H99" s="4"/>
       <c r="I99"/>
     </row>
     <row r="100" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A100" s="81">
+      <c r="A100" s="80">
         <v>5</v>
       </c>
-      <c r="B100" s="82"/>
-      <c r="C100" s="83"/>
-      <c r="D100" s="82"/>
-      <c r="E100" s="55"/>
-      <c r="F100" s="56"/>
-      <c r="G100" s="85" t="e">
+      <c r="B100" s="81"/>
+      <c r="C100" s="82"/>
+      <c r="D100" s="81"/>
+      <c r="E100" s="54"/>
+      <c r="F100" s="55"/>
+      <c r="G100" s="84" t="e">
         <v>#VALUE!</v>
       </c>
       <c r="H100" s="4"/>
@@ -20671,15 +22314,15 @@
       <c r="L100" s="45"/>
     </row>
     <row r="101" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A101" s="86">
+      <c r="A101" s="85">
         <v>6</v>
       </c>
-      <c r="B101" s="87"/>
+      <c r="B101" s="86"/>
       <c r="C101" s="16"/>
-      <c r="D101" s="87"/>
-      <c r="E101" s="55"/>
-      <c r="F101" s="56"/>
-      <c r="G101" s="85" t="e">
+      <c r="D101" s="86"/>
+      <c r="E101" s="54"/>
+      <c r="F101" s="55"/>
+      <c r="G101" s="84" t="e">
         <v>#VALUE!</v>
       </c>
       <c r="H101" s="4"/>
@@ -20687,30 +22330,30 @@
       <c r="L101" s="45"/>
     </row>
     <row r="102" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A102" s="81">
+      <c r="A102" s="80">
         <v>7</v>
       </c>
-      <c r="B102" s="82"/>
-      <c r="C102" s="83"/>
-      <c r="D102" s="82"/>
-      <c r="E102" s="55"/>
-      <c r="F102" s="56"/>
-      <c r="G102" s="85" t="e">
+      <c r="B102" s="81"/>
+      <c r="C102" s="82"/>
+      <c r="D102" s="81"/>
+      <c r="E102" s="54"/>
+      <c r="F102" s="55"/>
+      <c r="G102" s="84" t="e">
         <v>#VALUE!</v>
       </c>
       <c r="H102" s="4"/>
       <c r="I102"/>
     </row>
     <row r="103" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A103" s="86">
+      <c r="A103" s="85">
         <v>8</v>
       </c>
-      <c r="B103" s="87"/>
+      <c r="B103" s="86"/>
       <c r="C103" s="16"/>
-      <c r="D103" s="87"/>
-      <c r="E103" s="55"/>
-      <c r="F103" s="56"/>
-      <c r="G103" s="85" t="e">
+      <c r="D103" s="86"/>
+      <c r="E103" s="54"/>
+      <c r="F103" s="55"/>
+      <c r="G103" s="84" t="e">
         <v>#VALUE!</v>
       </c>
       <c r="H103" s="4"/>
@@ -20718,15 +22361,15 @@
       <c r="J103" s="24"/>
     </row>
     <row r="104" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A104" s="81">
+      <c r="A104" s="80">
         <v>9</v>
       </c>
-      <c r="B104" s="82"/>
-      <c r="C104" s="83"/>
-      <c r="D104" s="82"/>
-      <c r="E104" s="55"/>
-      <c r="F104" s="56"/>
-      <c r="G104" s="85" t="e">
+      <c r="B104" s="81"/>
+      <c r="C104" s="82"/>
+      <c r="D104" s="81"/>
+      <c r="E104" s="54"/>
+      <c r="F104" s="55"/>
+      <c r="G104" s="84" t="e">
         <v>#VALUE!</v>
       </c>
       <c r="H104" s="4"/>
@@ -20734,27 +22377,27 @@
       <c r="K104" s="24"/>
     </row>
     <row r="105" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A105" s="86">
+      <c r="A105" s="85">
         <v>10</v>
       </c>
-      <c r="B105" s="87"/>
+      <c r="B105" s="86"/>
       <c r="C105" s="16"/>
-      <c r="D105" s="87"/>
-      <c r="E105" s="55"/>
-      <c r="F105" s="56"/>
-      <c r="G105" s="85" t="e">
+      <c r="D105" s="86"/>
+      <c r="E105" s="54"/>
+      <c r="F105" s="55"/>
+      <c r="G105" s="84" t="e">
         <v>#VALUE!</v>
       </c>
       <c r="H105" s="4"/>
       <c r="I105"/>
     </row>
     <row r="106" spans="1:12" ht="15.45" x14ac:dyDescent="0.4">
-      <c r="A106" s="89"/>
-      <c r="B106" s="90"/>
-      <c r="C106" s="91"/>
+      <c r="A106" s="88"/>
+      <c r="B106" s="89"/>
+      <c r="C106" s="90"/>
       <c r="D106" s="35"/>
-      <c r="E106" s="92"/>
-      <c r="F106" s="111" t="s">
+      <c r="E106" s="91"/>
+      <c r="F106" s="110" t="s">
         <v>28</v>
       </c>
       <c r="G106" s="30" t="e">
@@ -20815,4 +22458,2628 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74CEF4FA-00A5-4BE8-BE05-AE5CB981057F}">
+  <dimension ref="A1:V111"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="13.07421875" style="10" customWidth="1"/>
+    <col min="3" max="3" width="10.4609375" customWidth="1"/>
+    <col min="4" max="4" width="27.07421875" customWidth="1"/>
+    <col min="5" max="5" width="12.69140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.07421875" style="10"/>
+    <col min="9" max="9" width="6.3046875" style="4" customWidth="1"/>
+    <col min="11" max="11" width="6.765625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="115" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="116" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="115" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="115" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="117" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="119" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="120" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="P1" s="5"/>
+      <c r="Q1" s="6"/>
+      <c r="R1" s="6"/>
+      <c r="S1" s="7"/>
+      <c r="T1" s="7"/>
+      <c r="U1" s="7"/>
+      <c r="V1" s="7"/>
+    </row>
+    <row r="2" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="112">
+        <v>1</v>
+      </c>
+      <c r="B2" s="53" t="s">
+        <v>96</v>
+      </c>
+      <c r="C2" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="E2" s="54">
+        <v>75.2</v>
+      </c>
+      <c r="F2" s="55">
+        <f t="shared" ref="F2:F11" si="0">IFERROR(((VLOOKUP(B2,cours,7,FALSE))),"")</f>
+        <v>75.599999999999994</v>
+      </c>
+      <c r="G2" s="56">
+        <f t="shared" ref="G2:G11" si="1">(F2/E2-1)</f>
+        <v>5.3191489361701372E-3</v>
+      </c>
+      <c r="I2" s="11"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="13"/>
+      <c r="T2" s="7"/>
+      <c r="U2" s="7"/>
+      <c r="V2" s="7"/>
+    </row>
+    <row r="3" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="113">
+        <v>2</v>
+      </c>
+      <c r="B3" s="53" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="53" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="54">
+        <v>15</v>
+      </c>
+      <c r="F3" s="55">
+        <f t="shared" si="0"/>
+        <v>15.04</v>
+      </c>
+      <c r="G3" s="56">
+        <f t="shared" si="1"/>
+        <v>2.666666666666595E-3</v>
+      </c>
+      <c r="H3" s="4"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="12"/>
+      <c r="L3" s="13"/>
+      <c r="Q3" s="14"/>
+    </row>
+    <row r="4" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="112">
+        <v>3</v>
+      </c>
+      <c r="B4" s="53" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="54">
+        <v>0.20100000000000001</v>
+      </c>
+      <c r="F4" s="55">
+        <f t="shared" si="0"/>
+        <v>0.20200000000000001</v>
+      </c>
+      <c r="G4" s="56">
+        <f t="shared" si="1"/>
+        <v>4.9751243781095411E-3</v>
+      </c>
+      <c r="H4" s="4"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="12"/>
+      <c r="L4" s="13"/>
+      <c r="Q4" s="14"/>
+    </row>
+    <row r="5" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="113">
+        <v>4</v>
+      </c>
+      <c r="B5" s="53" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="54">
+        <v>3.8149999999999999</v>
+      </c>
+      <c r="F5" s="55">
+        <f t="shared" si="0"/>
+        <v>3.9750000000000001</v>
+      </c>
+      <c r="G5" s="56">
+        <f t="shared" si="1"/>
+        <v>4.1939711664482404E-2</v>
+      </c>
+      <c r="H5" s="4"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="13"/>
+      <c r="Q5" s="14"/>
+    </row>
+    <row r="6" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="112">
+        <v>5</v>
+      </c>
+      <c r="B6" s="53" t="s">
+        <v>105</v>
+      </c>
+      <c r="C6" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="E6" s="54">
+        <v>124.2</v>
+      </c>
+      <c r="F6" s="55">
+        <f t="shared" si="0"/>
+        <v>124.7</v>
+      </c>
+      <c r="G6" s="56">
+        <f t="shared" si="1"/>
+        <v>4.0257648953301306E-3</v>
+      </c>
+      <c r="H6" s="4"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="13"/>
+      <c r="Q6" s="14"/>
+    </row>
+    <row r="7" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="113">
+        <v>6</v>
+      </c>
+      <c r="B7" s="53" t="s">
+        <v>107</v>
+      </c>
+      <c r="C7" s="53" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="E7" s="54">
+        <v>13</v>
+      </c>
+      <c r="F7" s="55">
+        <f t="shared" si="0"/>
+        <v>11.9</v>
+      </c>
+      <c r="G7" s="56">
+        <f t="shared" si="1"/>
+        <v>-8.4615384615384537E-2</v>
+      </c>
+      <c r="H7" s="4"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="12"/>
+      <c r="L7" s="13"/>
+      <c r="Q7" s="14"/>
+    </row>
+    <row r="8" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="112">
+        <v>7</v>
+      </c>
+      <c r="B8" s="53" t="s">
+        <v>108</v>
+      </c>
+      <c r="C8" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="E8" s="54">
+        <v>62.1</v>
+      </c>
+      <c r="F8" s="55">
+        <f t="shared" si="0"/>
+        <v>56.45</v>
+      </c>
+      <c r="G8" s="56">
+        <f t="shared" si="1"/>
+        <v>-9.0982286634460507E-2</v>
+      </c>
+      <c r="H8" s="4"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="12"/>
+      <c r="L8" s="13"/>
+      <c r="Q8" s="14"/>
+    </row>
+    <row r="9" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="113">
+        <v>8</v>
+      </c>
+      <c r="B9" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="C9" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="E9" s="54">
+        <v>40.1</v>
+      </c>
+      <c r="F9" s="55">
+        <f t="shared" si="0"/>
+        <v>41.66</v>
+      </c>
+      <c r="G9" s="56">
+        <f t="shared" si="1"/>
+        <v>3.890274314214448E-2</v>
+      </c>
+      <c r="H9" s="4"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="12"/>
+      <c r="L9" s="13"/>
+      <c r="Q9" s="14"/>
+    </row>
+    <row r="10" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="112">
+        <v>9</v>
+      </c>
+      <c r="B10" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" s="54">
+        <v>21.96</v>
+      </c>
+      <c r="F10" s="55">
+        <f t="shared" si="0"/>
+        <v>22.96</v>
+      </c>
+      <c r="G10" s="56">
+        <f t="shared" si="1"/>
+        <v>4.5537340619307809E-2</v>
+      </c>
+      <c r="H10" s="4"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="12"/>
+      <c r="L10" s="13"/>
+      <c r="Q10" s="14"/>
+    </row>
+    <row r="11" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A11" s="113">
+        <v>10</v>
+      </c>
+      <c r="B11" s="53" t="s">
+        <v>90</v>
+      </c>
+      <c r="C11" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="E11" s="54">
+        <v>47.68</v>
+      </c>
+      <c r="F11" s="55">
+        <f t="shared" si="0"/>
+        <v>46.42</v>
+      </c>
+      <c r="G11" s="56">
+        <f t="shared" si="1"/>
+        <v>-2.6426174496644306E-2</v>
+      </c>
+      <c r="H11" s="4"/>
+      <c r="I11" s="15"/>
+      <c r="J11" s="15"/>
+      <c r="K11" s="12"/>
+      <c r="L11" s="13"/>
+      <c r="Q11" s="14"/>
+    </row>
+    <row r="12" spans="1:22" ht="15.9" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="112"/>
+      <c r="B12" s="53"/>
+      <c r="C12" s="82"/>
+      <c r="D12" s="95"/>
+      <c r="E12" s="54"/>
+      <c r="F12" s="121" t="s">
+        <v>28</v>
+      </c>
+      <c r="G12" s="122">
+        <f>AVERAGE(G2:G11)</f>
+        <v>-5.8657345444278249E-3</v>
+      </c>
+      <c r="H12" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="I12" s="18">
+        <f>COUNTIF(G2:G11,"&gt;0")</f>
+        <v>7</v>
+      </c>
+      <c r="J12" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="K12" s="20">
+        <f>COUNTIF(G2:G11,"&lt;0")</f>
+        <v>3</v>
+      </c>
+      <c r="L12" s="13"/>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="F13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13"/>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="F14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14"/>
+    </row>
+    <row r="15" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A15" s="115" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" s="116" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" s="115" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15" s="115" t="s">
+        <v>3</v>
+      </c>
+      <c r="E15" s="111" t="s">
+        <v>0</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="112">
+        <v>1</v>
+      </c>
+      <c r="B16" s="53" t="s">
+        <v>110</v>
+      </c>
+      <c r="C16" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="E16" s="94">
+        <v>0.51100000000000001</v>
+      </c>
+      <c r="F16" s="8">
+        <f t="shared" ref="F16:F25" si="2">IFERROR(((VLOOKUP(B16,cours,7,FALSE))),"")</f>
+        <v>0.53100000000000003</v>
+      </c>
+      <c r="G16" s="9">
+        <f t="shared" ref="G16:G25" si="3">(F16/E16-1)</f>
+        <v>3.9138943248532287E-2</v>
+      </c>
+      <c r="H16" s="21"/>
+      <c r="I16"/>
+    </row>
+    <row r="17" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="113">
+        <v>2</v>
+      </c>
+      <c r="B17" s="53" t="s">
+        <v>112</v>
+      </c>
+      <c r="C17" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E17" s="94">
+        <v>6.6349999999999998</v>
+      </c>
+      <c r="F17" s="8">
+        <f t="shared" si="2"/>
+        <v>7.125</v>
+      </c>
+      <c r="G17" s="9">
+        <f t="shared" si="3"/>
+        <v>7.3850791258477821E-2</v>
+      </c>
+      <c r="H17" s="4"/>
+      <c r="I17"/>
+    </row>
+    <row r="18" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="112">
+        <v>3</v>
+      </c>
+      <c r="B18" s="53" t="s">
+        <v>114</v>
+      </c>
+      <c r="C18" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E18" s="94">
+        <v>8.69</v>
+      </c>
+      <c r="F18" s="8">
+        <f t="shared" si="2"/>
+        <v>8.56</v>
+      </c>
+      <c r="G18" s="9">
+        <f t="shared" si="3"/>
+        <v>-1.4959723820483162E-2</v>
+      </c>
+      <c r="H18" s="4"/>
+      <c r="I18" s="11"/>
+    </row>
+    <row r="19" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="113">
+        <v>4</v>
+      </c>
+      <c r="B19" s="53" t="s">
+        <v>116</v>
+      </c>
+      <c r="C19" s="53" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="E19" s="94">
+        <v>5.56</v>
+      </c>
+      <c r="F19" s="8">
+        <f t="shared" si="2"/>
+        <v>6.86</v>
+      </c>
+      <c r="G19" s="9">
+        <f t="shared" si="3"/>
+        <v>0.23381294964028787</v>
+      </c>
+      <c r="H19" s="4"/>
+      <c r="I19"/>
+    </row>
+    <row r="20" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="112">
+        <v>5</v>
+      </c>
+      <c r="B20" s="53" t="s">
+        <v>118</v>
+      </c>
+      <c r="C20" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="E20" s="94">
+        <v>0.52200000000000002</v>
+      </c>
+      <c r="F20" s="8">
+        <f t="shared" si="2"/>
+        <v>0.57499999999999996</v>
+      </c>
+      <c r="G20" s="9">
+        <f t="shared" si="3"/>
+        <v>0.1015325670498084</v>
+      </c>
+      <c r="H20" s="4"/>
+      <c r="I20" s="11"/>
+    </row>
+    <row r="21" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="113">
+        <v>6</v>
+      </c>
+      <c r="B21" s="53" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="E21" s="94">
+        <v>158.4</v>
+      </c>
+      <c r="F21" s="8">
+        <f t="shared" si="2"/>
+        <v>157.19999999999999</v>
+      </c>
+      <c r="G21" s="9">
+        <f t="shared" si="3"/>
+        <v>-7.5757575757576801E-3</v>
+      </c>
+      <c r="H21" s="4"/>
+      <c r="I21"/>
+    </row>
+    <row r="22" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="112">
+        <v>7</v>
+      </c>
+      <c r="B22" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" s="53" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="E22" s="94">
+        <v>19.100000000000001</v>
+      </c>
+      <c r="F22" s="8">
+        <f t="shared" si="2"/>
+        <v>19.100000000000001</v>
+      </c>
+      <c r="G22" s="9">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H22" s="4"/>
+      <c r="I22"/>
+    </row>
+    <row r="23" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="113">
+        <v>8</v>
+      </c>
+      <c r="B23" s="53" t="s">
+        <v>120</v>
+      </c>
+      <c r="C23" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="E23" s="94">
+        <v>0.17199999999999999</v>
+      </c>
+      <c r="F23" s="8">
+        <f t="shared" si="2"/>
+        <v>0.187</v>
+      </c>
+      <c r="G23" s="9">
+        <f t="shared" si="3"/>
+        <v>8.720930232558155E-2</v>
+      </c>
+      <c r="H23" s="4"/>
+      <c r="I23"/>
+    </row>
+    <row r="24" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A24" s="112">
+        <v>9</v>
+      </c>
+      <c r="B24" s="53" t="s">
+        <v>122</v>
+      </c>
+      <c r="C24" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="E24" s="94">
+        <v>76.03</v>
+      </c>
+      <c r="F24" s="8">
+        <f t="shared" si="2"/>
+        <v>72.77</v>
+      </c>
+      <c r="G24" s="9">
+        <f t="shared" si="3"/>
+        <v>-4.2877811390240717E-2</v>
+      </c>
+      <c r="H24" s="4"/>
+      <c r="I24"/>
+    </row>
+    <row r="25" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="113">
+        <v>10</v>
+      </c>
+      <c r="B25" s="53" t="s">
+        <v>124</v>
+      </c>
+      <c r="C25" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="E25" s="94">
+        <v>8.5500000000000007</v>
+      </c>
+      <c r="F25" s="8">
+        <f t="shared" si="2"/>
+        <v>8.56</v>
+      </c>
+      <c r="G25" s="9">
+        <f t="shared" si="3"/>
+        <v>1.1695906432749315E-3</v>
+      </c>
+      <c r="H25" s="4"/>
+      <c r="I25"/>
+    </row>
+    <row r="26" spans="1:11" ht="15.9" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="112"/>
+      <c r="B26" s="53"/>
+      <c r="C26" s="82"/>
+      <c r="D26" s="95"/>
+      <c r="E26" s="94"/>
+      <c r="F26" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="G26" s="23">
+        <f>AVERAGE(G16:G25)</f>
+        <v>4.7130085137948127E-2</v>
+      </c>
+      <c r="H26" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="I26" s="18">
+        <f>COUNTIF(G16:G25,"&gt;0")</f>
+        <v>6</v>
+      </c>
+      <c r="J26" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="K26" s="20">
+        <f>COUNTIF(G16:G25,"&lt;0")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A27" s="113"/>
+      <c r="B27" s="114"/>
+      <c r="C27" s="53"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="118"/>
+      <c r="F27" s="4"/>
+      <c r="H27" s="4"/>
+      <c r="I27"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="F28" s="4"/>
+      <c r="H28" s="4"/>
+    </row>
+    <row r="29" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="115" t="s">
+        <v>31</v>
+      </c>
+      <c r="B29" s="116" t="s">
+        <v>1</v>
+      </c>
+      <c r="C29" s="115" t="s">
+        <v>2</v>
+      </c>
+      <c r="D29" s="115" t="s">
+        <v>3</v>
+      </c>
+      <c r="E29" s="117" t="s">
+        <v>51</v>
+      </c>
+      <c r="F29" s="119" t="s">
+        <v>5</v>
+      </c>
+      <c r="G29" s="120" t="s">
+        <v>6</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="I29"/>
+    </row>
+    <row r="30" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="112">
+        <v>1</v>
+      </c>
+      <c r="B30" s="53" t="s">
+        <v>126</v>
+      </c>
+      <c r="C30" s="53" t="s">
+        <v>63</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="E30" s="54">
+        <v>1.49</v>
+      </c>
+      <c r="F30" s="55">
+        <f t="shared" ref="F30:F39" si="4">IFERROR(((VLOOKUP(B30,cours,7,FALSE))),"")</f>
+        <v>1.49</v>
+      </c>
+      <c r="G30" s="56">
+        <f t="shared" ref="G30:G39" si="5">(F30/E30-1)</f>
+        <v>0</v>
+      </c>
+      <c r="H30"/>
+      <c r="I30"/>
+    </row>
+    <row r="31" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="113">
+        <v>2</v>
+      </c>
+      <c r="B31" s="53" t="s">
+        <v>128</v>
+      </c>
+      <c r="C31" s="53" t="s">
+        <v>54</v>
+      </c>
+      <c r="D31" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="E31" s="54">
+        <v>20.5</v>
+      </c>
+      <c r="F31" s="55">
+        <f t="shared" si="4"/>
+        <v>20.195</v>
+      </c>
+      <c r="G31" s="56">
+        <f t="shared" si="5"/>
+        <v>-1.4878048780487818E-2</v>
+      </c>
+      <c r="H31"/>
+      <c r="I31"/>
+    </row>
+    <row r="32" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A32" s="112">
+        <v>3</v>
+      </c>
+      <c r="B32" s="53" t="s">
+        <v>130</v>
+      </c>
+      <c r="C32" s="53" t="s">
+        <v>54</v>
+      </c>
+      <c r="D32" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="E32" s="54">
+        <v>0.22</v>
+      </c>
+      <c r="F32" s="55">
+        <f t="shared" si="4"/>
+        <v>0.32</v>
+      </c>
+      <c r="G32" s="56">
+        <f t="shared" si="5"/>
+        <v>0.45454545454545459</v>
+      </c>
+      <c r="H32"/>
+      <c r="I32"/>
+    </row>
+    <row r="33" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="113">
+        <v>4</v>
+      </c>
+      <c r="B33" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="C33" s="53" t="s">
+        <v>54</v>
+      </c>
+      <c r="D33" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="E33" s="54">
+        <v>27.58</v>
+      </c>
+      <c r="F33" s="55">
+        <f t="shared" si="4"/>
+        <v>26.58</v>
+      </c>
+      <c r="G33" s="56">
+        <f t="shared" si="5"/>
+        <v>-3.6258158085569203E-2</v>
+      </c>
+      <c r="H33"/>
+      <c r="I33"/>
+    </row>
+    <row r="34" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="112">
+        <v>5</v>
+      </c>
+      <c r="B34" s="53" t="s">
+        <v>132</v>
+      </c>
+      <c r="C34" s="53" t="s">
+        <v>54</v>
+      </c>
+      <c r="D34" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="E34" s="54">
+        <v>1.6479999999999999</v>
+      </c>
+      <c r="F34" s="55">
+        <f t="shared" si="4"/>
+        <v>1.744</v>
+      </c>
+      <c r="G34" s="56">
+        <f t="shared" si="5"/>
+        <v>5.8252427184465994E-2</v>
+      </c>
+      <c r="H34"/>
+      <c r="I34"/>
+    </row>
+    <row r="35" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A35" s="113">
+        <v>6</v>
+      </c>
+      <c r="B35" s="53" t="s">
+        <v>73</v>
+      </c>
+      <c r="C35" s="53" t="s">
+        <v>54</v>
+      </c>
+      <c r="D35" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="E35" s="54">
+        <v>0.72799999999999998</v>
+      </c>
+      <c r="F35" s="55">
+        <f t="shared" si="4"/>
+        <v>0.72799999999999998</v>
+      </c>
+      <c r="G35" s="56">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="H35"/>
+      <c r="I35"/>
+    </row>
+    <row r="36" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A36" s="112">
+        <v>7</v>
+      </c>
+      <c r="B36" s="53" t="s">
+        <v>134</v>
+      </c>
+      <c r="C36" s="53" t="s">
+        <v>54</v>
+      </c>
+      <c r="D36" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="E36" s="54">
+        <v>0.58199999999999996</v>
+      </c>
+      <c r="F36" s="55">
+        <f t="shared" si="4"/>
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="G36" s="56">
+        <f t="shared" si="5"/>
+        <v>-2.0618556701030966E-2</v>
+      </c>
+      <c r="H36"/>
+      <c r="I36"/>
+    </row>
+    <row r="37" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A37" s="113">
+        <v>8</v>
+      </c>
+      <c r="B37" s="53" t="s">
+        <v>136</v>
+      </c>
+      <c r="C37" s="53" t="s">
+        <v>54</v>
+      </c>
+      <c r="D37" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="E37" s="54">
+        <v>1.125</v>
+      </c>
+      <c r="F37" s="55">
+        <f t="shared" si="4"/>
+        <v>1.115</v>
+      </c>
+      <c r="G37" s="56">
+        <f t="shared" si="5"/>
+        <v>-8.8888888888889461E-3</v>
+      </c>
+      <c r="H37"/>
+      <c r="I37"/>
+      <c r="P37" s="24"/>
+    </row>
+    <row r="38" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A38" s="112">
+        <v>9</v>
+      </c>
+      <c r="B38" s="53" t="s">
+        <v>138</v>
+      </c>
+      <c r="C38" s="53" t="s">
+        <v>54</v>
+      </c>
+      <c r="D38" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="E38" s="54">
+        <v>1.21</v>
+      </c>
+      <c r="F38" s="55">
+        <f t="shared" si="4"/>
+        <v>1.145</v>
+      </c>
+      <c r="G38" s="56">
+        <f t="shared" si="5"/>
+        <v>-5.3719008264462742E-2</v>
+      </c>
+      <c r="H38"/>
+      <c r="I38"/>
+      <c r="P38" s="24"/>
+    </row>
+    <row r="39" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A39" s="113">
+        <v>10</v>
+      </c>
+      <c r="B39" s="53" t="s">
+        <v>140</v>
+      </c>
+      <c r="C39" s="53" t="s">
+        <v>54</v>
+      </c>
+      <c r="D39" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="E39" s="54">
+        <v>204</v>
+      </c>
+      <c r="F39" s="55">
+        <f t="shared" si="4"/>
+        <v>206</v>
+      </c>
+      <c r="G39" s="56">
+        <f t="shared" si="5"/>
+        <v>9.8039215686274161E-3</v>
+      </c>
+      <c r="H39"/>
+      <c r="I39"/>
+    </row>
+    <row r="40" spans="1:16" ht="15.9" thickTop="1" x14ac:dyDescent="0.4">
+      <c r="A40" s="127"/>
+      <c r="B40" s="128"/>
+      <c r="C40" s="129"/>
+      <c r="D40" s="130"/>
+      <c r="E40" s="131"/>
+      <c r="F40" s="121" t="s">
+        <v>28</v>
+      </c>
+      <c r="G40" s="132">
+        <f>AVERAGE(G30:G39)</f>
+        <v>3.8823914257810829E-2</v>
+      </c>
+      <c r="H40">
+        <f>COUNTIF(G30:G39,"&lt;0")</f>
+        <v>5</v>
+      </c>
+      <c r="I40"/>
+    </row>
+    <row r="41" spans="1:16" ht="15.45" x14ac:dyDescent="0.4">
+      <c r="B41" s="25"/>
+      <c r="C41" s="26"/>
+      <c r="D41" s="27"/>
+      <c r="F41" s="28"/>
+      <c r="G41" s="29"/>
+      <c r="H41"/>
+      <c r="I41"/>
+      <c r="K41" s="20"/>
+    </row>
+    <row r="42" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A42" s="115" t="s">
+        <v>31</v>
+      </c>
+      <c r="B42" s="116" t="s">
+        <v>1</v>
+      </c>
+      <c r="C42" s="115" t="s">
+        <v>2</v>
+      </c>
+      <c r="D42" s="115" t="s">
+        <v>3</v>
+      </c>
+      <c r="E42" s="117" t="s">
+        <v>75</v>
+      </c>
+      <c r="F42" s="119" t="s">
+        <v>5</v>
+      </c>
+      <c r="G42" s="124" t="s">
+        <v>6</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I42"/>
+    </row>
+    <row r="43" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A43" s="112">
+        <v>1</v>
+      </c>
+      <c r="B43" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="C43" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="E43" s="54">
+        <v>360.5</v>
+      </c>
+      <c r="F43" s="55">
+        <f t="shared" ref="F43:F52" si="6">IFERROR(((VLOOKUP(B43,cours,7,FALSE))),"")</f>
+        <v>364</v>
+      </c>
+      <c r="G43" s="123">
+        <f t="shared" ref="G43:G52" si="7">(F43/E43-1)</f>
+        <v>9.7087378640776656E-3</v>
+      </c>
+      <c r="H43"/>
+      <c r="I43"/>
+    </row>
+    <row r="44" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A44" s="113">
+        <v>2</v>
+      </c>
+      <c r="B44" s="53" t="s">
+        <v>144</v>
+      </c>
+      <c r="C44" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="E44" s="54">
+        <v>25.95</v>
+      </c>
+      <c r="F44" s="55">
+        <f t="shared" si="6"/>
+        <v>25.45</v>
+      </c>
+      <c r="G44" s="123">
+        <f t="shared" si="7"/>
+        <v>-1.9267822736030782E-2</v>
+      </c>
+      <c r="H44"/>
+      <c r="I44"/>
+    </row>
+    <row r="45" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A45" s="112">
+        <v>3</v>
+      </c>
+      <c r="B45" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="C45" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="D45" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="E45" s="54">
+        <v>40.1</v>
+      </c>
+      <c r="F45" s="55">
+        <f t="shared" si="6"/>
+        <v>41.66</v>
+      </c>
+      <c r="G45" s="123">
+        <f t="shared" si="7"/>
+        <v>3.890274314214448E-2</v>
+      </c>
+      <c r="H45"/>
+      <c r="I45"/>
+    </row>
+    <row r="46" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A46" s="113">
+        <v>4</v>
+      </c>
+      <c r="B46" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="C46" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="D46" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="E46" s="54">
+        <v>21.96</v>
+      </c>
+      <c r="F46" s="55">
+        <f t="shared" si="6"/>
+        <v>22.96</v>
+      </c>
+      <c r="G46" s="123">
+        <f t="shared" si="7"/>
+        <v>4.5537340619307809E-2</v>
+      </c>
+      <c r="H46"/>
+      <c r="I46"/>
+    </row>
+    <row r="47" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A47" s="112">
+        <v>5</v>
+      </c>
+      <c r="B47" s="53" t="s">
+        <v>87</v>
+      </c>
+      <c r="C47" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="D47" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="E47" s="54">
+        <v>56.32</v>
+      </c>
+      <c r="F47" s="55">
+        <f t="shared" si="6"/>
+        <v>60.98</v>
+      </c>
+      <c r="G47" s="123">
+        <f t="shared" si="7"/>
+        <v>8.2741477272727293E-2</v>
+      </c>
+      <c r="H47"/>
+      <c r="I47"/>
+    </row>
+    <row r="48" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A48" s="113">
+        <v>6</v>
+      </c>
+      <c r="B48" s="53" t="s">
+        <v>146</v>
+      </c>
+      <c r="C48" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="D48" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="E48" s="54">
+        <v>27.79</v>
+      </c>
+      <c r="F48" s="55">
+        <f t="shared" si="6"/>
+        <v>26.07</v>
+      </c>
+      <c r="G48" s="123">
+        <f t="shared" si="7"/>
+        <v>-6.1892767182439634E-2</v>
+      </c>
+      <c r="H48"/>
+      <c r="I48"/>
+    </row>
+    <row r="49" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A49" s="112">
+        <v>7</v>
+      </c>
+      <c r="B49" s="53" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="D49" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="E49" s="54">
+        <v>55.8</v>
+      </c>
+      <c r="F49" s="55">
+        <f t="shared" si="6"/>
+        <v>61.1</v>
+      </c>
+      <c r="G49" s="123">
+        <f t="shared" si="7"/>
+        <v>9.4982078853046659E-2</v>
+      </c>
+      <c r="H49"/>
+      <c r="I49"/>
+    </row>
+    <row r="50" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A50" s="113">
+        <v>8</v>
+      </c>
+      <c r="B50" s="53" t="s">
+        <v>148</v>
+      </c>
+      <c r="C50" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="D50" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="E50" s="54">
+        <v>55.5</v>
+      </c>
+      <c r="F50" s="55">
+        <f t="shared" si="6"/>
+        <v>57.5</v>
+      </c>
+      <c r="G50" s="123">
+        <f t="shared" si="7"/>
+        <v>3.6036036036036112E-2</v>
+      </c>
+      <c r="H50"/>
+      <c r="I50"/>
+    </row>
+    <row r="51" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A51" s="112">
+        <v>9</v>
+      </c>
+      <c r="B51" s="53" t="s">
+        <v>19</v>
+      </c>
+      <c r="C51" s="53" t="s">
+        <v>20</v>
+      </c>
+      <c r="D51" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="E51" s="54">
+        <v>0.214</v>
+      </c>
+      <c r="F51" s="55">
+        <f t="shared" si="6"/>
+        <v>0.23499999999999999</v>
+      </c>
+      <c r="G51" s="123">
+        <f t="shared" si="7"/>
+        <v>9.8130841121495394E-2</v>
+      </c>
+      <c r="H51"/>
+      <c r="I51"/>
+    </row>
+    <row r="52" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A52" s="113">
+        <v>10</v>
+      </c>
+      <c r="B52" s="53" t="s">
+        <v>150</v>
+      </c>
+      <c r="C52" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="D52" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="E52" s="54">
+        <v>32.72</v>
+      </c>
+      <c r="F52" s="55">
+        <f t="shared" si="6"/>
+        <v>33.520000000000003</v>
+      </c>
+      <c r="G52" s="123">
+        <f t="shared" si="7"/>
+        <v>2.4449877750611471E-2</v>
+      </c>
+      <c r="H52"/>
+      <c r="I52"/>
+    </row>
+    <row r="53" spans="1:11" ht="15.9" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A53" s="112"/>
+      <c r="B53" s="53"/>
+      <c r="C53" s="82"/>
+      <c r="D53" s="95"/>
+      <c r="E53" s="112"/>
+      <c r="F53" s="125" t="s">
+        <v>28</v>
+      </c>
+      <c r="G53" s="126">
+        <f>AVERAGE(G43:G52)</f>
+        <v>3.4932854274097647E-2</v>
+      </c>
+      <c r="H53" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="I53" s="18">
+        <f>COUNTIF(G43:G52,"&gt;0")</f>
+        <v>8</v>
+      </c>
+      <c r="J53" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="K53" s="20">
+        <f>COUNTIF(G43:G52,"&lt;0")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" ht="15.45" x14ac:dyDescent="0.4">
+      <c r="B54" s="6"/>
+      <c r="C54" s="26"/>
+      <c r="D54" s="27"/>
+      <c r="F54" s="28"/>
+      <c r="G54" s="31"/>
+      <c r="H54" s="4"/>
+      <c r="I54"/>
+    </row>
+    <row r="55" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A55" s="115" t="s">
+        <v>31</v>
+      </c>
+      <c r="B55" s="116" t="s">
+        <v>1</v>
+      </c>
+      <c r="C55" s="115" t="s">
+        <v>2</v>
+      </c>
+      <c r="D55" s="115" t="s">
+        <v>3</v>
+      </c>
+      <c r="E55" s="117" t="s">
+        <v>77</v>
+      </c>
+      <c r="F55" s="32" t="s">
+        <v>5</v>
+      </c>
+      <c r="G55" s="33" t="s">
+        <v>6</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A56" s="112">
+        <v>1</v>
+      </c>
+      <c r="B56" s="81" t="s">
+        <v>152</v>
+      </c>
+      <c r="C56" s="82" t="s">
+        <v>9</v>
+      </c>
+      <c r="D56" s="81" t="s">
+        <v>153</v>
+      </c>
+      <c r="E56" s="83">
+        <v>8.6050000000000004</v>
+      </c>
+      <c r="F56" s="8">
+        <f t="shared" ref="F56:F65" si="8">IFERROR(((VLOOKUP(B56,cours,7,0))),"")</f>
+        <v>8.1199999999999992</v>
+      </c>
+      <c r="G56" s="34">
+        <f t="shared" ref="G56:G65" si="9">(F56/E56-1)</f>
+        <v>-5.6362579895409826E-2</v>
+      </c>
+      <c r="H56" s="4"/>
+    </row>
+    <row r="57" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A57" s="113">
+        <v>2</v>
+      </c>
+      <c r="B57" s="86" t="s">
+        <v>154</v>
+      </c>
+      <c r="C57" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D57" s="86" t="s">
+        <v>155</v>
+      </c>
+      <c r="E57" s="83">
+        <v>105.92</v>
+      </c>
+      <c r="F57" s="8">
+        <f t="shared" si="8"/>
+        <v>108.84</v>
+      </c>
+      <c r="G57" s="34">
+        <f t="shared" si="9"/>
+        <v>2.7567975830815827E-2</v>
+      </c>
+      <c r="H57" s="4"/>
+      <c r="I57"/>
+    </row>
+    <row r="58" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A58" s="112">
+        <v>3</v>
+      </c>
+      <c r="B58" s="81" t="s">
+        <v>81</v>
+      </c>
+      <c r="C58" s="82" t="s">
+        <v>9</v>
+      </c>
+      <c r="D58" s="81" t="s">
+        <v>82</v>
+      </c>
+      <c r="E58" s="83">
+        <v>75.900000000000006</v>
+      </c>
+      <c r="F58" s="8">
+        <f t="shared" si="8"/>
+        <v>75.569999999999993</v>
+      </c>
+      <c r="G58" s="34">
+        <f t="shared" si="9"/>
+        <v>-4.3478260869567187E-3</v>
+      </c>
+      <c r="H58" s="4"/>
+      <c r="I58"/>
+      <c r="K58" s="35"/>
+    </row>
+    <row r="59" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A59" s="113">
+        <v>4</v>
+      </c>
+      <c r="B59" s="86" t="s">
+        <v>146</v>
+      </c>
+      <c r="C59" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D59" s="86" t="s">
+        <v>147</v>
+      </c>
+      <c r="E59" s="83">
+        <v>27.79</v>
+      </c>
+      <c r="F59" s="8">
+        <f t="shared" si="8"/>
+        <v>26.07</v>
+      </c>
+      <c r="G59" s="34">
+        <f t="shared" si="9"/>
+        <v>-6.1892767182439634E-2</v>
+      </c>
+      <c r="H59" s="4"/>
+      <c r="I59"/>
+      <c r="K59" s="35"/>
+    </row>
+    <row r="60" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A60" s="112">
+        <v>5</v>
+      </c>
+      <c r="B60" s="81" t="s">
+        <v>83</v>
+      </c>
+      <c r="C60" s="82" t="s">
+        <v>9</v>
+      </c>
+      <c r="D60" s="81" t="s">
+        <v>84</v>
+      </c>
+      <c r="E60" s="83">
+        <v>40.1</v>
+      </c>
+      <c r="F60" s="8">
+        <f t="shared" si="8"/>
+        <v>41.66</v>
+      </c>
+      <c r="G60" s="34">
+        <f t="shared" si="9"/>
+        <v>3.890274314214448E-2</v>
+      </c>
+      <c r="H60" s="4"/>
+      <c r="I60"/>
+      <c r="K60" s="35"/>
+    </row>
+    <row r="61" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A61" s="113">
+        <v>6</v>
+      </c>
+      <c r="B61" s="86" t="s">
+        <v>90</v>
+      </c>
+      <c r="C61" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D61" s="86" t="s">
+        <v>91</v>
+      </c>
+      <c r="E61" s="83">
+        <v>47.68</v>
+      </c>
+      <c r="F61" s="8">
+        <f t="shared" si="8"/>
+        <v>46.42</v>
+      </c>
+      <c r="G61" s="34">
+        <f t="shared" si="9"/>
+        <v>-2.6426174496644306E-2</v>
+      </c>
+      <c r="H61" s="4"/>
+      <c r="I61"/>
+      <c r="K61" s="35"/>
+    </row>
+    <row r="62" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A62" s="112">
+        <v>7</v>
+      </c>
+      <c r="B62" s="81" t="s">
+        <v>156</v>
+      </c>
+      <c r="C62" s="82" t="s">
+        <v>9</v>
+      </c>
+      <c r="D62" s="81" t="s">
+        <v>157</v>
+      </c>
+      <c r="E62" s="83">
+        <v>33.840000000000003</v>
+      </c>
+      <c r="F62" s="8">
+        <f t="shared" si="8"/>
+        <v>34.42</v>
+      </c>
+      <c r="G62" s="34">
+        <f t="shared" si="9"/>
+        <v>1.7139479905437405E-2</v>
+      </c>
+      <c r="H62" s="4"/>
+      <c r="I62"/>
+    </row>
+    <row r="63" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A63" s="113">
+        <v>8</v>
+      </c>
+      <c r="B63" s="86" t="s">
+        <v>158</v>
+      </c>
+      <c r="C63" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D63" s="86" t="s">
+        <v>159</v>
+      </c>
+      <c r="E63" s="83">
+        <v>154.9</v>
+      </c>
+      <c r="F63" s="8">
+        <f t="shared" si="8"/>
+        <v>190.7</v>
+      </c>
+      <c r="G63" s="34">
+        <f t="shared" si="9"/>
+        <v>0.23111684958037437</v>
+      </c>
+      <c r="H63" s="4"/>
+      <c r="I63"/>
+    </row>
+    <row r="64" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A64" s="112">
+        <v>9</v>
+      </c>
+      <c r="B64" s="81" t="s">
+        <v>160</v>
+      </c>
+      <c r="C64" s="82" t="s">
+        <v>9</v>
+      </c>
+      <c r="D64" s="81" t="s">
+        <v>161</v>
+      </c>
+      <c r="E64" s="83">
+        <v>18.504999999999999</v>
+      </c>
+      <c r="F64" s="8">
+        <f t="shared" si="8"/>
+        <v>18.785</v>
+      </c>
+      <c r="G64" s="34">
+        <f t="shared" si="9"/>
+        <v>1.5131045663334231E-2</v>
+      </c>
+      <c r="H64" s="4"/>
+      <c r="I64"/>
+    </row>
+    <row r="65" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A65" s="113">
+        <v>10</v>
+      </c>
+      <c r="B65" s="86" t="s">
+        <v>85</v>
+      </c>
+      <c r="C65" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D65" s="86" t="s">
+        <v>86</v>
+      </c>
+      <c r="E65" s="83">
+        <v>88.42</v>
+      </c>
+      <c r="F65" s="8">
+        <f t="shared" si="8"/>
+        <v>93.52</v>
+      </c>
+      <c r="G65" s="34">
+        <f t="shared" si="9"/>
+        <v>5.7679258086405616E-2</v>
+      </c>
+      <c r="H65" s="4"/>
+      <c r="I65"/>
+    </row>
+    <row r="66" spans="1:11" ht="15.45" x14ac:dyDescent="0.4">
+      <c r="A66" s="112"/>
+      <c r="B66" s="53"/>
+      <c r="C66" s="82"/>
+      <c r="D66" s="95"/>
+      <c r="E66" s="112"/>
+      <c r="F66" s="36" t="s">
+        <v>28</v>
+      </c>
+      <c r="G66" s="30">
+        <f>AVERAGE(G56:G65)</f>
+        <v>2.3850800454706146E-2</v>
+      </c>
+      <c r="H66" s="37" t="s">
+        <v>29</v>
+      </c>
+      <c r="I66" s="4">
+        <f>COUNTIF(G56:G65,"&gt;0")</f>
+        <v>6</v>
+      </c>
+      <c r="J66" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="K66" s="20">
+        <f>COUNTIF(G56:G65,"&lt;0")</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" ht="15.45" x14ac:dyDescent="0.4">
+      <c r="B67" s="6"/>
+      <c r="C67" s="26"/>
+      <c r="D67" s="27"/>
+      <c r="F67" s="38"/>
+      <c r="G67" s="31"/>
+      <c r="H67" s="4"/>
+      <c r="I67"/>
+    </row>
+    <row r="68" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A68" s="115" t="s">
+        <v>31</v>
+      </c>
+      <c r="B68" s="116" t="s">
+        <v>1</v>
+      </c>
+      <c r="C68" s="115" t="s">
+        <v>2</v>
+      </c>
+      <c r="D68" s="115" t="s">
+        <v>3</v>
+      </c>
+      <c r="E68" s="117" t="s">
+        <v>0</v>
+      </c>
+      <c r="F68" s="32" t="s">
+        <v>5</v>
+      </c>
+      <c r="G68" s="33" t="s">
+        <v>6</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A69" s="112">
+        <v>1</v>
+      </c>
+      <c r="B69" s="81" t="s">
+        <v>152</v>
+      </c>
+      <c r="C69" s="82" t="s">
+        <v>9</v>
+      </c>
+      <c r="D69" s="81" t="s">
+        <v>153</v>
+      </c>
+      <c r="E69" s="83">
+        <v>8.6050000000000004</v>
+      </c>
+      <c r="F69" s="8">
+        <f t="shared" ref="F69" si="10">IFERROR(((VLOOKUP(B69,cours,7,FALSE))),"")</f>
+        <v>8.1199999999999992</v>
+      </c>
+      <c r="G69" s="34">
+        <f t="shared" ref="G69:G78" si="11">(F69/E69-1)</f>
+        <v>-5.6362579895409826E-2</v>
+      </c>
+      <c r="H69" s="4"/>
+    </row>
+    <row r="70" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A70" s="113">
+        <v>2</v>
+      </c>
+      <c r="B70" s="86" t="s">
+        <v>162</v>
+      </c>
+      <c r="C70" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D70" s="86" t="s">
+        <v>163</v>
+      </c>
+      <c r="E70" s="83">
+        <v>22.11</v>
+      </c>
+      <c r="F70" s="8">
+        <f t="shared" ref="F70:F78" si="12">IFERROR(((VLOOKUP(B70,cours,7,0))),"")</f>
+        <v>20.86</v>
+      </c>
+      <c r="G70" s="34">
+        <f t="shared" si="11"/>
+        <v>-5.6535504296698291E-2</v>
+      </c>
+      <c r="H70" s="4"/>
+      <c r="I70"/>
+      <c r="J70" s="27"/>
+    </row>
+    <row r="71" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A71" s="112">
+        <v>3</v>
+      </c>
+      <c r="B71" s="81" t="s">
+        <v>94</v>
+      </c>
+      <c r="C71" s="82" t="s">
+        <v>9</v>
+      </c>
+      <c r="D71" s="81" t="s">
+        <v>95</v>
+      </c>
+      <c r="E71" s="83">
+        <v>12.78</v>
+      </c>
+      <c r="F71" s="8">
+        <f t="shared" si="12"/>
+        <v>13.46</v>
+      </c>
+      <c r="G71" s="34">
+        <f t="shared" si="11"/>
+        <v>5.3208137715180071E-2</v>
+      </c>
+      <c r="H71" s="4"/>
+      <c r="I71"/>
+      <c r="J71" s="27"/>
+    </row>
+    <row r="72" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A72" s="113">
+        <v>4</v>
+      </c>
+      <c r="B72" s="86" t="s">
+        <v>16</v>
+      </c>
+      <c r="C72" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D72" s="86" t="s">
+        <v>17</v>
+      </c>
+      <c r="E72" s="83">
+        <v>21.96</v>
+      </c>
+      <c r="F72" s="8">
+        <f t="shared" si="12"/>
+        <v>22.96</v>
+      </c>
+      <c r="G72" s="34">
+        <f t="shared" si="11"/>
+        <v>4.5537340619307809E-2</v>
+      </c>
+      <c r="H72" s="4"/>
+      <c r="I72"/>
+      <c r="J72" s="39"/>
+    </row>
+    <row r="73" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A73" s="112">
+        <v>5</v>
+      </c>
+      <c r="B73" s="81" t="s">
+        <v>154</v>
+      </c>
+      <c r="C73" s="82" t="s">
+        <v>9</v>
+      </c>
+      <c r="D73" s="81" t="s">
+        <v>155</v>
+      </c>
+      <c r="E73" s="83">
+        <v>105.92</v>
+      </c>
+      <c r="F73" s="8">
+        <f t="shared" si="12"/>
+        <v>108.84</v>
+      </c>
+      <c r="G73" s="34">
+        <f t="shared" si="11"/>
+        <v>2.7567975830815827E-2</v>
+      </c>
+      <c r="H73" s="4"/>
+      <c r="I73"/>
+      <c r="J73" s="39"/>
+    </row>
+    <row r="74" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A74" s="113">
+        <v>6</v>
+      </c>
+      <c r="B74" s="86" t="s">
+        <v>81</v>
+      </c>
+      <c r="C74" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D74" s="86" t="s">
+        <v>82</v>
+      </c>
+      <c r="E74" s="83">
+        <v>75.900000000000006</v>
+      </c>
+      <c r="F74" s="8">
+        <f t="shared" si="12"/>
+        <v>75.569999999999993</v>
+      </c>
+      <c r="G74" s="34">
+        <f t="shared" si="11"/>
+        <v>-4.3478260869567187E-3</v>
+      </c>
+      <c r="H74" s="4"/>
+      <c r="I74"/>
+      <c r="J74" s="39"/>
+    </row>
+    <row r="75" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A75" s="112">
+        <v>7</v>
+      </c>
+      <c r="B75" s="81" t="s">
+        <v>83</v>
+      </c>
+      <c r="C75" s="82" t="s">
+        <v>9</v>
+      </c>
+      <c r="D75" s="81" t="s">
+        <v>84</v>
+      </c>
+      <c r="E75" s="83">
+        <v>40.1</v>
+      </c>
+      <c r="F75" s="8">
+        <f t="shared" si="12"/>
+        <v>41.66</v>
+      </c>
+      <c r="G75" s="34">
+        <f t="shared" si="11"/>
+        <v>3.890274314214448E-2</v>
+      </c>
+      <c r="H75" s="4"/>
+      <c r="I75" s="24"/>
+      <c r="J75" s="39"/>
+    </row>
+    <row r="76" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A76" s="113">
+        <v>8</v>
+      </c>
+      <c r="B76" s="86" t="s">
+        <v>164</v>
+      </c>
+      <c r="C76" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D76" s="86" t="s">
+        <v>165</v>
+      </c>
+      <c r="E76" s="83">
+        <v>13.54</v>
+      </c>
+      <c r="F76" s="8">
+        <f t="shared" si="12"/>
+        <v>13.99</v>
+      </c>
+      <c r="G76" s="34">
+        <f t="shared" si="11"/>
+        <v>3.3234859675036921E-2</v>
+      </c>
+      <c r="H76" s="4"/>
+      <c r="I76"/>
+      <c r="J76" s="27"/>
+    </row>
+    <row r="77" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A77" s="112">
+        <v>9</v>
+      </c>
+      <c r="B77" s="81" t="s">
+        <v>148</v>
+      </c>
+      <c r="C77" s="82" t="s">
+        <v>9</v>
+      </c>
+      <c r="D77" s="81" t="s">
+        <v>149</v>
+      </c>
+      <c r="E77" s="83">
+        <v>55.5</v>
+      </c>
+      <c r="F77" s="8">
+        <f t="shared" si="12"/>
+        <v>57.5</v>
+      </c>
+      <c r="G77" s="34">
+        <f t="shared" si="11"/>
+        <v>3.6036036036036112E-2</v>
+      </c>
+      <c r="H77" s="4"/>
+      <c r="I77"/>
+      <c r="J77" s="27"/>
+    </row>
+    <row r="78" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A78" s="113">
+        <v>10</v>
+      </c>
+      <c r="B78" s="86" t="s">
+        <v>166</v>
+      </c>
+      <c r="C78" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D78" s="86" t="s">
+        <v>167</v>
+      </c>
+      <c r="E78" s="83">
+        <v>47.5</v>
+      </c>
+      <c r="F78" s="8">
+        <f t="shared" si="12"/>
+        <v>43.9</v>
+      </c>
+      <c r="G78" s="34">
+        <f t="shared" si="11"/>
+        <v>-7.5789473684210518E-2</v>
+      </c>
+      <c r="H78" s="4"/>
+      <c r="I78"/>
+      <c r="J78" s="27"/>
+    </row>
+    <row r="79" spans="1:11" ht="15.45" x14ac:dyDescent="0.4">
+      <c r="F79" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="G79" s="30">
+        <f>AVERAGE(G69:G78)</f>
+        <v>4.1451709055245868E-3</v>
+      </c>
+      <c r="H79" s="4"/>
+      <c r="I79"/>
+    </row>
+    <row r="80" spans="1:11" ht="15.45" x14ac:dyDescent="0.4">
+      <c r="F80" s="28"/>
+      <c r="G80" s="41"/>
+      <c r="H80" s="4"/>
+      <c r="I80"/>
+    </row>
+    <row r="81" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A81" s="74"/>
+      <c r="B81" s="75"/>
+      <c r="C81" s="76"/>
+      <c r="D81" s="76"/>
+      <c r="E81" s="77"/>
+      <c r="F81" s="78"/>
+      <c r="G81" s="79"/>
+      <c r="H81" s="20"/>
+      <c r="I81"/>
+    </row>
+    <row r="82" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A82" s="80"/>
+      <c r="B82" s="81"/>
+      <c r="C82" s="82"/>
+      <c r="D82" s="81"/>
+      <c r="E82" s="83"/>
+      <c r="F82" s="55"/>
+      <c r="G82" s="84"/>
+      <c r="H82"/>
+      <c r="I82"/>
+    </row>
+    <row r="83" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A83" s="85"/>
+      <c r="B83" s="86"/>
+      <c r="C83" s="16"/>
+      <c r="D83" s="86"/>
+      <c r="E83" s="83"/>
+      <c r="F83" s="55"/>
+      <c r="G83" s="84"/>
+      <c r="H83"/>
+      <c r="I83"/>
+    </row>
+    <row r="84" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A84" s="80"/>
+      <c r="B84" s="81"/>
+      <c r="C84" s="82"/>
+      <c r="D84" s="81"/>
+      <c r="E84" s="83"/>
+      <c r="F84" s="55"/>
+      <c r="G84" s="84"/>
+      <c r="H84"/>
+      <c r="I84"/>
+    </row>
+    <row r="85" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A85" s="85"/>
+      <c r="B85" s="86"/>
+      <c r="C85" s="87"/>
+      <c r="D85" s="86"/>
+      <c r="E85" s="83"/>
+      <c r="F85" s="55"/>
+      <c r="G85" s="84"/>
+      <c r="H85"/>
+      <c r="I85"/>
+    </row>
+    <row r="86" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A86" s="80"/>
+      <c r="B86" s="81"/>
+      <c r="C86" s="87"/>
+      <c r="D86" s="81"/>
+      <c r="E86" s="83"/>
+      <c r="F86" s="55"/>
+      <c r="G86" s="84"/>
+      <c r="H86"/>
+      <c r="I86"/>
+    </row>
+    <row r="87" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A87" s="85"/>
+      <c r="B87" s="86"/>
+      <c r="C87" s="87"/>
+      <c r="D87" s="86"/>
+      <c r="E87" s="83"/>
+      <c r="F87" s="55"/>
+      <c r="G87" s="84"/>
+      <c r="H87"/>
+      <c r="I87"/>
+    </row>
+    <row r="88" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A88" s="80"/>
+      <c r="B88" s="81"/>
+      <c r="C88" s="82"/>
+      <c r="D88" s="81"/>
+      <c r="E88" s="83"/>
+      <c r="F88" s="55"/>
+      <c r="G88" s="84"/>
+      <c r="H88"/>
+      <c r="I88"/>
+    </row>
+    <row r="89" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A89" s="85"/>
+      <c r="B89" s="86"/>
+      <c r="C89" s="87"/>
+      <c r="D89" s="86"/>
+      <c r="E89" s="83"/>
+      <c r="F89" s="55"/>
+      <c r="G89" s="84"/>
+      <c r="H89"/>
+      <c r="I89"/>
+    </row>
+    <row r="90" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A90" s="80"/>
+      <c r="B90" s="81"/>
+      <c r="C90" s="82"/>
+      <c r="D90" s="81"/>
+      <c r="E90" s="83"/>
+      <c r="F90" s="55"/>
+      <c r="G90" s="84"/>
+      <c r="H90"/>
+      <c r="I90"/>
+    </row>
+    <row r="91" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A91" s="85"/>
+      <c r="B91" s="86"/>
+      <c r="C91" s="16"/>
+      <c r="D91" s="86"/>
+      <c r="E91" s="83"/>
+      <c r="F91" s="55"/>
+      <c r="G91" s="84"/>
+      <c r="H91"/>
+      <c r="I91"/>
+    </row>
+    <row r="92" spans="1:12" ht="15.45" x14ac:dyDescent="0.4">
+      <c r="A92" s="88"/>
+      <c r="B92" s="89"/>
+      <c r="C92" s="90"/>
+      <c r="D92" s="35"/>
+      <c r="E92" s="91"/>
+      <c r="F92" s="72"/>
+      <c r="G92" s="30"/>
+      <c r="H92"/>
+      <c r="I92"/>
+    </row>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="F93" s="4"/>
+      <c r="H93" s="37"/>
+      <c r="J93" s="37"/>
+      <c r="K93" s="20"/>
+    </row>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="F94" s="4"/>
+      <c r="H94" s="37"/>
+      <c r="J94" s="37"/>
+      <c r="K94" s="20"/>
+    </row>
+    <row r="95" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A95" s="74"/>
+      <c r="B95" s="75"/>
+      <c r="C95" s="76"/>
+      <c r="D95" s="77"/>
+      <c r="E95" s="77"/>
+      <c r="F95" s="78"/>
+      <c r="G95" s="79"/>
+      <c r="H95" s="3"/>
+      <c r="I95" s="43"/>
+      <c r="J95" s="44"/>
+      <c r="L95" s="45"/>
+    </row>
+    <row r="96" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A96" s="80"/>
+      <c r="B96" s="81"/>
+      <c r="C96" s="82"/>
+      <c r="D96" s="81"/>
+      <c r="E96" s="54"/>
+      <c r="F96" s="55"/>
+      <c r="G96" s="84"/>
+      <c r="H96" s="4"/>
+    </row>
+    <row r="97" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A97" s="85"/>
+      <c r="B97" s="86"/>
+      <c r="C97" s="16"/>
+      <c r="D97" s="86"/>
+      <c r="E97" s="54"/>
+      <c r="F97" s="55"/>
+      <c r="G97" s="84"/>
+      <c r="H97" s="4"/>
+      <c r="I97"/>
+      <c r="J97" s="24"/>
+    </row>
+    <row r="98" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A98" s="80"/>
+      <c r="B98" s="81"/>
+      <c r="C98" s="82"/>
+      <c r="D98" s="81"/>
+      <c r="E98" s="54"/>
+      <c r="F98" s="55"/>
+      <c r="G98" s="84"/>
+      <c r="H98" s="4"/>
+      <c r="I98"/>
+    </row>
+    <row r="99" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A99" s="85"/>
+      <c r="B99" s="86"/>
+      <c r="C99" s="16"/>
+      <c r="D99" s="86"/>
+      <c r="E99" s="54"/>
+      <c r="F99" s="55"/>
+      <c r="G99" s="84"/>
+      <c r="H99" s="4"/>
+      <c r="I99"/>
+    </row>
+    <row r="100" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A100" s="80"/>
+      <c r="B100" s="81"/>
+      <c r="C100" s="82"/>
+      <c r="D100" s="81"/>
+      <c r="E100" s="54"/>
+      <c r="F100" s="55"/>
+      <c r="G100" s="84"/>
+      <c r="H100" s="4"/>
+      <c r="I100"/>
+      <c r="L100" s="45"/>
+    </row>
+    <row r="101" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A101" s="85"/>
+      <c r="B101" s="86"/>
+      <c r="C101" s="16"/>
+      <c r="D101" s="86"/>
+      <c r="E101" s="54"/>
+      <c r="F101" s="55"/>
+      <c r="G101" s="84"/>
+      <c r="H101" s="4"/>
+      <c r="I101"/>
+      <c r="L101" s="45"/>
+    </row>
+    <row r="102" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A102" s="80"/>
+      <c r="B102" s="81"/>
+      <c r="C102" s="82"/>
+      <c r="D102" s="81"/>
+      <c r="E102" s="54"/>
+      <c r="F102" s="55"/>
+      <c r="G102" s="84"/>
+      <c r="H102" s="4"/>
+      <c r="I102"/>
+    </row>
+    <row r="103" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A103" s="85"/>
+      <c r="B103" s="86"/>
+      <c r="C103" s="16"/>
+      <c r="D103" s="86"/>
+      <c r="E103" s="54"/>
+      <c r="F103" s="55"/>
+      <c r="G103" s="84"/>
+      <c r="H103" s="4"/>
+      <c r="I103"/>
+      <c r="J103" s="24"/>
+    </row>
+    <row r="104" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A104" s="80"/>
+      <c r="B104" s="81"/>
+      <c r="C104" s="82"/>
+      <c r="D104" s="81"/>
+      <c r="E104" s="54"/>
+      <c r="F104" s="55"/>
+      <c r="G104" s="84"/>
+      <c r="H104" s="4"/>
+      <c r="I104"/>
+      <c r="K104" s="24"/>
+    </row>
+    <row r="105" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A105" s="85"/>
+      <c r="B105" s="86"/>
+      <c r="C105" s="16"/>
+      <c r="D105" s="86"/>
+      <c r="E105" s="54"/>
+      <c r="F105" s="55"/>
+      <c r="G105" s="84"/>
+      <c r="H105" s="4"/>
+      <c r="I105"/>
+    </row>
+    <row r="106" spans="1:12" ht="15.45" x14ac:dyDescent="0.4">
+      <c r="A106" s="88"/>
+      <c r="B106" s="89"/>
+      <c r="C106" s="90"/>
+      <c r="D106" s="35"/>
+      <c r="E106" s="91"/>
+      <c r="F106" s="110"/>
+      <c r="G106" s="30"/>
+      <c r="H106" s="4"/>
+      <c r="I106"/>
+    </row>
+    <row r="107" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="B107" s="42"/>
+      <c r="C107" s="26"/>
+      <c r="D107" s="27"/>
+      <c r="E107" s="27"/>
+      <c r="H107" s="37"/>
+      <c r="J107" s="37"/>
+      <c r="K107" s="4"/>
+    </row>
+    <row r="108" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="D108" s="27"/>
+      <c r="H108"/>
+      <c r="I108"/>
+    </row>
+    <row r="109" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="D109" s="39"/>
+      <c r="H109" s="37"/>
+      <c r="J109" s="37"/>
+      <c r="K109" s="4"/>
+    </row>
+    <row r="110" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="D110" s="39"/>
+      <c r="H110"/>
+      <c r="I110"/>
+    </row>
+    <row r="111" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="D111" s="39"/>
+      <c r="H111"/>
+      <c r="I111"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B56:B65">
+    <cfRule type="expression" dxfId="119" priority="5" stopIfTrue="1">
+      <formula>IF(AO56&gt;0,TRUE,FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B69:B78">
+    <cfRule type="expression" dxfId="118" priority="3" stopIfTrue="1">
+      <formula>IF(AO69&gt;0,TRUE,FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D56:D65">
+    <cfRule type="expression" dxfId="117" priority="4" stopIfTrue="1">
+      <formula>IF(AQ56&gt;0,TRUE,FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D69:D78">
+    <cfRule type="expression" dxfId="116" priority="2" stopIfTrue="1">
+      <formula>IF(AQ69&gt;0,TRUE,FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F11 F16:F25">
+    <cfRule type="expression" dxfId="115" priority="13" stopIfTrue="1">
+      <formula>IF(#REF!="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="114" priority="14" stopIfTrue="1">
+      <formula>IF($T200="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="113" priority="15" stopIfTrue="1">
+      <formula>IF($U200="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="112" priority="16" stopIfTrue="1">
+      <formula>IF($AN1048554="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="111" priority="17" stopIfTrue="1">
+      <formula>IF($T200="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="110" priority="18" stopIfTrue="1">
+      <formula>IF($U200="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F30:F39">
+    <cfRule type="expression" dxfId="109" priority="41" stopIfTrue="1">
+      <formula>IF(#REF!="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="108" priority="42" stopIfTrue="1">
+      <formula>IF($T230="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="107" priority="43" stopIfTrue="1">
+      <formula>IF($U230="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="106" priority="44" stopIfTrue="1">
+      <formula>IF($AN5="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="105" priority="45" stopIfTrue="1">
+      <formula>IF($T230="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="104" priority="46" stopIfTrue="1">
+      <formula>IF($U230="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F43:F52">
+    <cfRule type="expression" dxfId="103" priority="47" stopIfTrue="1">
+      <formula>IF(#REF!="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="102" priority="48" stopIfTrue="1">
+      <formula>IF($T242="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="101" priority="49" stopIfTrue="1">
+      <formula>IF($U242="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="100" priority="50" stopIfTrue="1">
+      <formula>IF($AN17="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="99" priority="51" stopIfTrue="1">
+      <formula>IF($T242="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="98" priority="52" stopIfTrue="1">
+      <formula>IF($U242="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F56">
+    <cfRule type="expression" dxfId="97" priority="37" stopIfTrue="1">
+      <formula>IF(#REF!="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="96" priority="38" stopIfTrue="1">
+      <formula>IF($AN28="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="95" priority="39" stopIfTrue="1">
+      <formula>IF($T254="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="94" priority="40" stopIfTrue="1">
+      <formula>IF($U254="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F69:F78">
+    <cfRule type="expression" dxfId="93" priority="1" stopIfTrue="1">
+      <formula>IF(#REF!="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G16:G26 G30:G41 G2:G12">
+    <cfRule type="cellIs" dxfId="92" priority="33" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="91" priority="34" stopIfTrue="1" operator="greaterThanOrEqual">
+      <formula>#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G16:G28 G2:G12">
+    <cfRule type="cellIs" dxfId="90" priority="19" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G30:G41 G16:G26 G2:G12">
+    <cfRule type="cellIs" dxfId="89" priority="32" operator="greaterThan">
+      <formula>#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G43:G54 G30:G41 G56:G67">
+    <cfRule type="cellIs" dxfId="88" priority="28" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G43:G54">
+    <cfRule type="cellIs" dxfId="87" priority="24" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="86" priority="25" operator="greaterThan">
+      <formula>#REF!</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="85" priority="26" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="84" priority="27" stopIfTrue="1" operator="greaterThanOrEqual">
+      <formula>#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G53:G54">
+    <cfRule type="cellIs" dxfId="83" priority="10" operator="greaterThan">
+      <formula>#REF!</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="82" priority="11" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="81" priority="12" stopIfTrue="1" operator="greaterThanOrEqual">
+      <formula>#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G56:G67">
+    <cfRule type="cellIs" dxfId="80" priority="29" operator="greaterThan">
+      <formula>#REF!</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="79" priority="30" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="78" priority="31" stopIfTrue="1" operator="greaterThanOrEqual">
+      <formula>#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G69:G80">
+    <cfRule type="cellIs" dxfId="77" priority="20" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="76" priority="21" operator="greaterThan">
+      <formula>#REF!</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="75" priority="22" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="74" priority="23" stopIfTrue="1" operator="greaterThanOrEqual">
+      <formula>#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I12 I53 K53 I66 K66">
+    <cfRule type="cellIs" dxfId="73" priority="35" operator="greaterThan">
+      <formula>$K12</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I26">
+    <cfRule type="cellIs" dxfId="72" priority="6" operator="greaterThan">
+      <formula>$K26</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I75">
+    <cfRule type="cellIs" dxfId="71" priority="36" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K12">
+    <cfRule type="cellIs" dxfId="70" priority="9" operator="greaterThan">
+      <formula>$K12</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K26">
+    <cfRule type="cellIs" dxfId="69" priority="8" operator="greaterThan">
+      <formula>$K26</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K41">
+    <cfRule type="cellIs" dxfId="68" priority="7" operator="greaterThan">
+      <formula>$K41</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F57:F67">
+    <cfRule type="expression" dxfId="67" priority="53" stopIfTrue="1">
+      <formula>IF(#REF!="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="66" priority="54" stopIfTrue="1">
+      <formula>IF($AK29="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="65" priority="55" stopIfTrue="1">
+      <formula>IF($T255="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="64" priority="56" stopIfTrue="1">
+      <formula>IF($U255="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F69">
+    <cfRule type="expression" dxfId="63" priority="57" stopIfTrue="1">
+      <formula>IF($T268="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="62" priority="58" stopIfTrue="1">
+      <formula>IF($U268="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="61" priority="59" stopIfTrue="1">
+      <formula>IF($AJ43="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="60" priority="60" stopIfTrue="1">
+      <formula>IF($T268="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="59" priority="61" stopIfTrue="1">
+      <formula>IF($U268="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F70:F78">
+    <cfRule type="expression" dxfId="58" priority="62" stopIfTrue="1">
+      <formula>IF($AJ42="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="57" priority="63" stopIfTrue="1">
+      <formula>IF($T267="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="56" priority="64" stopIfTrue="1">
+      <formula>IF($U267="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="6">
+    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
+    <tablePart r:id="rId5"/>
+    <tablePart r:id="rId6"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/Twitter_Donnees.xlsx
+++ b/Twitter_Donnees.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\charl\Documents\Bourse\mon-projet-react\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4FC28FDA-4C88-4170-977A-F492FAEAC384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F2C010BF-8BEA-491C-9EAA-C33992D3F922}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{197DE6B7-0A4B-4688-9519-B46A8B51F575}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="183">
   <si>
     <t>Colonne1</t>
   </si>
@@ -290,24 +290,6 @@
     <t>Les valeurs de confiance pour le LT👍:</t>
   </si>
   <si>
-    <t>BSD</t>
-  </si>
-  <si>
-    <t>BOURSE DIRECT</t>
-  </si>
-  <si>
-    <t>TFI</t>
-  </si>
-  <si>
-    <t>TF1</t>
-  </si>
-  <si>
-    <t>ASY</t>
-  </si>
-  <si>
-    <t>ASSYSTEM</t>
-  </si>
-  <si>
     <t>CAP</t>
   </si>
   <si>
@@ -320,34 +302,10 @@
     <t>PLUXEE</t>
   </si>
   <si>
-    <t>VAC</t>
-  </si>
-  <si>
-    <t>PIERRE &amp; VACANCES</t>
-  </si>
-  <si>
-    <t>PLNW</t>
-  </si>
-  <si>
-    <t>PLANISWARE</t>
-  </si>
-  <si>
-    <t>BOI</t>
-  </si>
-  <si>
-    <t>BOIRON</t>
-  </si>
-  <si>
     <t>TTE</t>
   </si>
   <si>
     <t>TOTALENERGIES</t>
-  </si>
-  <si>
-    <t>MMT</t>
-  </si>
-  <si>
-    <t>MÉTROPOLE TV (M6)</t>
   </si>
   <si>
     <t>15-janv</t>
@@ -374,9 +332,6 @@
     <t>SOPRA STERIA GROUP</t>
   </si>
   <si>
-    <t>SMCP</t>
-  </si>
-  <si>
     <t>SK</t>
   </si>
   <si>
@@ -387,12 +342,6 @@
   </si>
   <si>
     <t>PUBLICIS GRP</t>
-  </si>
-  <si>
-    <t>SGO</t>
-  </si>
-  <si>
-    <t>SAINT GOBAIN</t>
   </si>
   <si>
     <t xml:space="preserve">Etoiles </t>
@@ -1300,7 +1249,7 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="132">
+  <cellXfs count="130">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1460,7 +1409,7 @@
     <xf numFmtId="16" fontId="2" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1476,11 +1425,11 @@
     <xf numFmtId="10" fontId="6" fillId="8" borderId="21" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1500,7 +1449,7 @@
     <xf numFmtId="2" fontId="5" fillId="10" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1516,31 +1465,29 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="2" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="28" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="5" fillId="10" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="31" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="30" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="5" borderId="31" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="4" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="32" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="2" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="5" fillId="6" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="2" fontId="5" fillId="7" borderId="34" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="5" borderId="31" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="6" borderId="31" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="31" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
     <xf numFmtId="16" fontId="2" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1572,7 +1519,7 @@
     <xf numFmtId="10" fontId="6" fillId="8" borderId="39" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="31" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="8" fillId="8" borderId="40" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1594,142 +1541,7 @@
     <cellStyle name="Normal 4" xfId="3" xr:uid="{A416AD94-1484-48BB-B96D-2B11E7D97C8C}"/>
     <cellStyle name="Pourcentage" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="212">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
+  <dxfs count="105">
     <dxf>
       <font>
         <condense val="0"/>
@@ -1763,16 +1575,6 @@
         <extend val="0"/>
         <color indexed="10"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -1887,17 +1689,16 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color auto="1"/>
+        <color rgb="FF006100"/>
       </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
         <condense val="0"/>
         <extend val="0"/>
         <color indexed="10"/>
@@ -1917,6 +1718,8 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
         <condense val="0"/>
         <extend val="0"/>
         <color indexed="10"/>
@@ -1933,82 +1736,6 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
         <condense val="0"/>
         <extend val="0"/>
         <color indexed="10"/>
@@ -2058,6 +1785,15 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <b/>
         <i val="0"/>
         <condense val="0"/>
@@ -2067,8 +1803,73 @@
     </dxf>
     <dxf>
       <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <b val="0"/>
         <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <condense val="0"/>
         <extend val="0"/>
         <color indexed="10"/>
@@ -2088,9 +1889,20 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
         <condense val="0"/>
         <extend val="0"/>
         <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color auto="1"/>
       </font>
     </dxf>
     <dxf>
@@ -2261,845 +2073,6 @@
         <condense val="0"/>
         <extend val="0"/>
         <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
       </font>
     </dxf>
     <dxf>
@@ -19575,13 +18548,13 @@
       <c r="D1" s="93" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="112" t="s">
+      <c r="E1" s="110" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="113" t="s">
+      <c r="F1" s="111" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="114" t="s">
+      <c r="G1" s="112" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="6" t="s">
@@ -19599,13 +18572,13 @@
       <c r="A2" s="95">
         <v>1</v>
       </c>
-      <c r="B2" s="104" t="s">
+      <c r="B2" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="104" t="s">
+      <c r="C2" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="105" t="s">
+      <c r="D2" s="21" t="s">
         <v>10</v>
       </c>
       <c r="E2" s="74">
@@ -19614,7 +18587,7 @@
       <c r="F2" s="75">
         <v>43.12</v>
       </c>
-      <c r="G2" s="115">
+      <c r="G2" s="113">
         <v>0</v>
       </c>
       <c r="I2" s="16"/>
@@ -19629,13 +18602,13 @@
       <c r="A3" s="97">
         <v>2</v>
       </c>
-      <c r="B3" s="104" t="s">
+      <c r="B3" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="104" t="s">
+      <c r="C3" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="105" t="s">
+      <c r="D3" s="21" t="s">
         <v>11</v>
       </c>
       <c r="E3" s="74">
@@ -19644,7 +18617,7 @@
       <c r="F3" s="75">
         <v>0.21</v>
       </c>
-      <c r="G3" s="115">
+      <c r="G3" s="113">
         <v>0</v>
       </c>
       <c r="H3" s="7"/>
@@ -19658,13 +18631,13 @@
       <c r="A4" s="95">
         <v>3</v>
       </c>
-      <c r="B4" s="104" t="s">
+      <c r="B4" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="104" t="s">
+      <c r="C4" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="105" t="s">
+      <c r="D4" s="21" t="s">
         <v>13</v>
       </c>
       <c r="E4" s="74">
@@ -19673,7 +18646,7 @@
       <c r="F4" s="75">
         <v>69</v>
       </c>
-      <c r="G4" s="115">
+      <c r="G4" s="113">
         <v>0</v>
       </c>
       <c r="H4" s="7"/>
@@ -19687,13 +18660,13 @@
       <c r="A5" s="97">
         <v>4</v>
       </c>
-      <c r="B5" s="104" t="s">
+      <c r="B5" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="104" t="s">
+      <c r="C5" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="105" t="s">
+      <c r="D5" s="21" t="s">
         <v>16</v>
       </c>
       <c r="E5" s="74">
@@ -19702,7 +18675,7 @@
       <c r="F5" s="75">
         <v>12.188000000000001</v>
       </c>
-      <c r="G5" s="115">
+      <c r="G5" s="113">
         <v>0</v>
       </c>
       <c r="H5" s="7"/>
@@ -19716,13 +18689,13 @@
       <c r="A6" s="95">
         <v>5</v>
       </c>
-      <c r="B6" s="104" t="s">
+      <c r="B6" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="104" t="s">
+      <c r="C6" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="105" t="s">
+      <c r="D6" s="21" t="s">
         <v>19</v>
       </c>
       <c r="E6" s="74">
@@ -19731,7 +18704,7 @@
       <c r="F6" s="75">
         <v>92.9</v>
       </c>
-      <c r="G6" s="115">
+      <c r="G6" s="113">
         <v>0</v>
       </c>
       <c r="H6" s="7"/>
@@ -19745,13 +18718,13 @@
       <c r="A7" s="97">
         <v>6</v>
       </c>
-      <c r="B7" s="104" t="s">
+      <c r="B7" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="104" t="s">
+      <c r="C7" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="105" t="s">
+      <c r="D7" s="21" t="s">
         <v>21</v>
       </c>
       <c r="E7" s="74">
@@ -19760,7 +18733,7 @@
       <c r="F7" s="75">
         <v>28.52</v>
       </c>
-      <c r="G7" s="115">
+      <c r="G7" s="113">
         <v>0</v>
       </c>
       <c r="H7" s="7"/>
@@ -19774,13 +18747,13 @@
       <c r="A8" s="95">
         <v>7</v>
       </c>
-      <c r="B8" s="104" t="s">
+      <c r="B8" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="104" t="s">
+      <c r="C8" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="105" t="s">
+      <c r="D8" s="21" t="s">
         <v>23</v>
       </c>
       <c r="E8" s="74">
@@ -19789,7 +18762,7 @@
       <c r="F8" s="75">
         <v>22</v>
       </c>
-      <c r="G8" s="115">
+      <c r="G8" s="113">
         <v>0</v>
       </c>
       <c r="H8" s="7"/>
@@ -19803,13 +18776,13 @@
       <c r="A9" s="97">
         <v>8</v>
       </c>
-      <c r="B9" s="104" t="s">
+      <c r="B9" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="104" t="s">
+      <c r="C9" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="105" t="s">
+      <c r="D9" s="21" t="s">
         <v>25</v>
       </c>
       <c r="E9" s="74">
@@ -19818,7 +18791,7 @@
       <c r="F9" s="75">
         <v>0.24199999999999999</v>
       </c>
-      <c r="G9" s="115">
+      <c r="G9" s="113">
         <v>0</v>
       </c>
       <c r="H9" s="7"/>
@@ -19832,13 +18805,13 @@
       <c r="A10" s="95">
         <v>9</v>
       </c>
-      <c r="B10" s="104" t="s">
+      <c r="B10" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="104" t="s">
+      <c r="C10" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="105" t="s">
+      <c r="D10" s="21" t="s">
         <v>27</v>
       </c>
       <c r="E10" s="74">
@@ -19847,7 +18820,7 @@
       <c r="F10" s="75">
         <v>1.88</v>
       </c>
-      <c r="G10" s="115">
+      <c r="G10" s="113">
         <v>0</v>
       </c>
       <c r="H10" s="7"/>
@@ -19861,13 +18834,13 @@
       <c r="A11" s="97">
         <v>10</v>
       </c>
-      <c r="B11" s="104" t="s">
+      <c r="B11" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="104" t="s">
+      <c r="C11" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="105" t="s">
+      <c r="D11" s="21" t="s">
         <v>29</v>
       </c>
       <c r="E11" s="74">
@@ -19876,7 +18849,7 @@
       <c r="F11" s="75">
         <v>158.6</v>
       </c>
-      <c r="G11" s="115">
+      <c r="G11" s="113">
         <v>0</v>
       </c>
       <c r="H11" s="7"/>
@@ -19891,8 +18864,8 @@
       <c r="B12" s="99"/>
       <c r="C12" s="100"/>
       <c r="D12" s="101"/>
-      <c r="E12" s="116"/>
-      <c r="F12" s="117" t="s">
+      <c r="E12" s="114"/>
+      <c r="F12" s="115" t="s">
         <v>30</v>
       </c>
       <c r="G12" s="32">
@@ -19952,16 +18925,16 @@
       <c r="A16" s="95">
         <v>1</v>
       </c>
-      <c r="B16" s="104" t="s">
+      <c r="B16" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="C16" s="104" t="s">
+      <c r="C16" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="D16" s="105" t="s">
+      <c r="D16" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="E16" s="106">
+      <c r="E16" s="104">
         <v>1.5960000000000001</v>
       </c>
       <c r="F16" s="13">
@@ -19977,16 +18950,16 @@
       <c r="A17" s="97">
         <v>2</v>
       </c>
-      <c r="B17" s="104" t="s">
+      <c r="B17" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="C17" s="104" t="s">
+      <c r="C17" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="D17" s="105" t="s">
+      <c r="D17" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="E17" s="106">
+      <c r="E17" s="104">
         <v>163</v>
       </c>
       <c r="F17" s="13">
@@ -20002,16 +18975,16 @@
       <c r="A18" s="95">
         <v>3</v>
       </c>
-      <c r="B18" s="104" t="s">
+      <c r="B18" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="C18" s="104" t="s">
+      <c r="C18" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="D18" s="105" t="s">
+      <c r="D18" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="E18" s="106">
+      <c r="E18" s="104">
         <v>166.7</v>
       </c>
       <c r="F18" s="13">
@@ -20027,16 +19000,16 @@
       <c r="A19" s="97">
         <v>4</v>
       </c>
-      <c r="B19" s="104" t="s">
+      <c r="B19" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="104" t="s">
+      <c r="C19" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="D19" s="105" t="s">
+      <c r="D19" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="E19" s="106">
+      <c r="E19" s="104">
         <v>1.8560000000000001</v>
       </c>
       <c r="F19" s="13">
@@ -20052,16 +19025,16 @@
       <c r="A20" s="95">
         <v>5</v>
       </c>
-      <c r="B20" s="104" t="s">
+      <c r="B20" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="C20" s="104" t="s">
+      <c r="C20" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="D20" s="105" t="s">
+      <c r="D20" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="E20" s="106">
+      <c r="E20" s="104">
         <v>35.74</v>
       </c>
       <c r="F20" s="13">
@@ -20077,16 +19050,16 @@
       <c r="A21" s="97">
         <v>6</v>
       </c>
-      <c r="B21" s="104" t="s">
+      <c r="B21" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="C21" s="104" t="s">
+      <c r="C21" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="D21" s="105" t="s">
+      <c r="D21" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="E21" s="106">
+      <c r="E21" s="104">
         <v>2.35</v>
       </c>
       <c r="F21" s="13">
@@ -20102,16 +19075,16 @@
       <c r="A22" s="95">
         <v>7</v>
       </c>
-      <c r="B22" s="104" t="s">
+      <c r="B22" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="C22" s="104" t="s">
+      <c r="C22" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="D22" s="105" t="s">
+      <c r="D22" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="E22" s="106">
+      <c r="E22" s="104">
         <v>32.75</v>
       </c>
       <c r="F22" s="13">
@@ -20127,16 +19100,16 @@
       <c r="A23" s="97">
         <v>8</v>
       </c>
-      <c r="B23" s="104" t="s">
+      <c r="B23" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="C23" s="104" t="s">
+      <c r="C23" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="D23" s="105" t="s">
+      <c r="D23" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E23" s="106">
+      <c r="E23" s="104">
         <v>6.4850000000000003</v>
       </c>
       <c r="F23" s="13">
@@ -20152,16 +19125,16 @@
       <c r="A24" s="95">
         <v>9</v>
       </c>
-      <c r="B24" s="104" t="s">
+      <c r="B24" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="C24" s="104" t="s">
+      <c r="C24" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="D24" s="105" t="s">
+      <c r="D24" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="E24" s="106">
+      <c r="E24" s="104">
         <v>4.9710000000000001</v>
       </c>
       <c r="F24" s="13">
@@ -20177,16 +19150,16 @@
       <c r="A25" s="97">
         <v>10</v>
       </c>
-      <c r="B25" s="104" t="s">
+      <c r="B25" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="C25" s="104" t="s">
+      <c r="C25" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="D25" s="105" t="s">
+      <c r="D25" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="E25" s="106">
+      <c r="E25" s="104">
         <v>46.52</v>
       </c>
       <c r="F25" s="13">
@@ -20200,10 +19173,10 @@
     </row>
     <row r="26" spans="1:11" ht="15.9" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A26" s="95"/>
-      <c r="B26" s="104"/>
+      <c r="B26" s="34"/>
       <c r="C26" s="73"/>
-      <c r="D26" s="107"/>
-      <c r="E26" s="106"/>
+      <c r="D26" s="105"/>
+      <c r="E26" s="104"/>
       <c r="F26" s="31" t="s">
         <v>30</v>
       </c>
@@ -20224,11 +19197,11 @@
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A27" s="108"/>
-      <c r="B27" s="109"/>
+      <c r="A27" s="106"/>
+      <c r="B27" s="107"/>
       <c r="C27" s="99"/>
-      <c r="D27" s="110"/>
-      <c r="E27" s="111"/>
+      <c r="D27" s="108"/>
+      <c r="E27" s="109"/>
       <c r="F27" s="7"/>
       <c r="H27" s="7"/>
       <c r="I27"/>
@@ -20250,13 +19223,13 @@
       <c r="D29" s="93" t="s">
         <v>3</v>
       </c>
-      <c r="E29" s="112" t="s">
+      <c r="E29" s="110" t="s">
         <v>54</v>
       </c>
-      <c r="F29" s="113" t="s">
+      <c r="F29" s="111" t="s">
         <v>5</v>
       </c>
-      <c r="G29" s="114" t="s">
+      <c r="G29" s="112" t="s">
         <v>6</v>
       </c>
       <c r="H29" s="6" t="s">
@@ -20268,13 +19241,13 @@
       <c r="A30" s="95">
         <v>1</v>
       </c>
-      <c r="B30" s="104" t="s">
+      <c r="B30" s="34" t="s">
         <v>56</v>
       </c>
-      <c r="C30" s="104" t="s">
+      <c r="C30" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="D30" s="105" t="s">
+      <c r="D30" s="21" t="s">
         <v>58</v>
       </c>
       <c r="E30" s="74">
@@ -20283,7 +19256,7 @@
       <c r="F30" s="75">
         <v>21</v>
       </c>
-      <c r="G30" s="115">
+      <c r="G30" s="113">
         <v>0</v>
       </c>
       <c r="H30"/>
@@ -20293,13 +19266,13 @@
       <c r="A31" s="97">
         <v>2</v>
       </c>
-      <c r="B31" s="104" t="s">
+      <c r="B31" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="C31" s="104" t="s">
+      <c r="C31" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="D31" s="105" t="s">
+      <c r="D31" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E31" s="74">
@@ -20308,7 +19281,7 @@
       <c r="F31" s="75">
         <v>0.32500000000000001</v>
       </c>
-      <c r="G31" s="115">
+      <c r="G31" s="113">
         <v>0</v>
       </c>
       <c r="H31"/>
@@ -20318,13 +19291,13 @@
       <c r="A32" s="95">
         <v>3</v>
       </c>
-      <c r="B32" s="104" t="s">
+      <c r="B32" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="C32" s="104" t="s">
+      <c r="C32" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="D32" s="105" t="s">
+      <c r="D32" s="21" t="s">
         <v>62</v>
       </c>
       <c r="E32" s="74">
@@ -20333,7 +19306,7 @@
       <c r="F32" s="75">
         <v>1.53</v>
       </c>
-      <c r="G32" s="115">
+      <c r="G32" s="113">
         <v>0</v>
       </c>
       <c r="H32"/>
@@ -20343,13 +19316,13 @@
       <c r="A33" s="97">
         <v>4</v>
       </c>
-      <c r="B33" s="104" t="s">
+      <c r="B33" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="C33" s="104" t="s">
+      <c r="C33" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="D33" s="105" t="s">
+      <c r="D33" s="21" t="s">
         <v>64</v>
       </c>
       <c r="E33" s="74">
@@ -20358,7 +19331,7 @@
       <c r="F33" s="75">
         <v>2E-3</v>
       </c>
-      <c r="G33" s="115">
+      <c r="G33" s="113">
         <v>0</v>
       </c>
       <c r="H33"/>
@@ -20368,13 +19341,13 @@
       <c r="A34" s="95">
         <v>5</v>
       </c>
-      <c r="B34" s="104" t="s">
+      <c r="B34" s="34" t="s">
         <v>65</v>
       </c>
-      <c r="C34" s="104" t="s">
+      <c r="C34" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="D34" s="105" t="s">
+      <c r="D34" s="21" t="s">
         <v>66</v>
       </c>
       <c r="E34" s="74">
@@ -20383,7 +19356,7 @@
       <c r="F34" s="75">
         <v>6.72</v>
       </c>
-      <c r="G34" s="115">
+      <c r="G34" s="113">
         <v>0</v>
       </c>
       <c r="H34"/>
@@ -20393,13 +19366,13 @@
       <c r="A35" s="97">
         <v>6</v>
       </c>
-      <c r="B35" s="104" t="s">
+      <c r="B35" s="34" t="s">
         <v>67</v>
       </c>
-      <c r="C35" s="104" t="s">
+      <c r="C35" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="D35" s="105" t="s">
+      <c r="D35" s="21" t="s">
         <v>68</v>
       </c>
       <c r="E35" s="74">
@@ -20408,7 +19381,7 @@
       <c r="F35" s="75">
         <v>3.88</v>
       </c>
-      <c r="G35" s="115">
+      <c r="G35" s="113">
         <v>0</v>
       </c>
       <c r="H35"/>
@@ -20418,13 +19391,13 @@
       <c r="A36" s="95">
         <v>7</v>
       </c>
-      <c r="B36" s="104" t="s">
+      <c r="B36" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="C36" s="104" t="s">
+      <c r="C36" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="D36" s="105" t="s">
+      <c r="D36" s="21" t="s">
         <v>70</v>
       </c>
       <c r="E36" s="74">
@@ -20433,7 +19406,7 @@
       <c r="F36" s="75">
         <v>6.04</v>
       </c>
-      <c r="G36" s="115">
+      <c r="G36" s="113">
         <v>0</v>
       </c>
       <c r="H36"/>
@@ -20443,13 +19416,13 @@
       <c r="A37" s="97">
         <v>8</v>
       </c>
-      <c r="B37" s="104" t="s">
+      <c r="B37" s="34" t="s">
         <v>71</v>
       </c>
-      <c r="C37" s="104" t="s">
+      <c r="C37" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="D37" s="105" t="s">
+      <c r="D37" s="21" t="s">
         <v>72</v>
       </c>
       <c r="E37" s="74">
@@ -20458,7 +19431,7 @@
       <c r="F37" s="75">
         <v>8.26</v>
       </c>
-      <c r="G37" s="115">
+      <c r="G37" s="113">
         <v>0</v>
       </c>
       <c r="H37"/>
@@ -20469,13 +19442,13 @@
       <c r="A38" s="95">
         <v>9</v>
       </c>
-      <c r="B38" s="104" t="s">
+      <c r="B38" s="34" t="s">
         <v>73</v>
       </c>
-      <c r="C38" s="104" t="s">
+      <c r="C38" s="34" t="s">
         <v>74</v>
       </c>
-      <c r="D38" s="105" t="s">
+      <c r="D38" s="21" t="s">
         <v>75</v>
       </c>
       <c r="E38" s="74">
@@ -20484,7 +19457,7 @@
       <c r="F38" s="75">
         <v>2.8</v>
       </c>
-      <c r="G38" s="115">
+      <c r="G38" s="113">
         <v>0</v>
       </c>
       <c r="H38"/>
@@ -20495,13 +19468,13 @@
       <c r="A39" s="97">
         <v>10</v>
       </c>
-      <c r="B39" s="104" t="s">
+      <c r="B39" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="C39" s="104" t="s">
+      <c r="C39" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="D39" s="105" t="s">
+      <c r="D39" s="21" t="s">
         <v>77</v>
       </c>
       <c r="E39" s="74">
@@ -20510,22 +19483,22 @@
       <c r="F39" s="75">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G39" s="115">
+      <c r="G39" s="113">
         <v>0</v>
       </c>
       <c r="H39"/>
       <c r="I39"/>
     </row>
     <row r="40" spans="1:16" ht="15.9" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="125"/>
-      <c r="B40" s="126"/>
-      <c r="C40" s="127"/>
-      <c r="D40" s="128"/>
-      <c r="E40" s="129"/>
-      <c r="F40" s="117" t="s">
+      <c r="A40" s="123"/>
+      <c r="B40" s="124"/>
+      <c r="C40" s="125"/>
+      <c r="D40" s="126"/>
+      <c r="E40" s="127"/>
+      <c r="F40" s="115" t="s">
         <v>30</v>
       </c>
-      <c r="G40" s="130">
+      <c r="G40" s="128">
         <v>0</v>
       </c>
       <c r="H40">
@@ -20556,13 +19529,13 @@
       <c r="D42" s="93" t="s">
         <v>3</v>
       </c>
-      <c r="E42" s="112" t="s">
+      <c r="E42" s="110" t="s">
         <v>78</v>
       </c>
-      <c r="F42" s="113" t="s">
+      <c r="F42" s="111" t="s">
         <v>5</v>
       </c>
-      <c r="G42" s="121" t="s">
+      <c r="G42" s="119" t="s">
         <v>6</v>
       </c>
       <c r="H42" s="6" t="s">
@@ -20571,250 +19544,150 @@
       <c r="I42"/>
     </row>
     <row r="43" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A43" s="95">
-        <v>1</v>
-      </c>
-      <c r="B43" s="104" t="s">
-        <v>80</v>
-      </c>
-      <c r="C43" s="104" t="s">
-        <v>18</v>
-      </c>
-      <c r="D43" s="105" t="s">
-        <v>81</v>
-      </c>
-      <c r="E43" s="74">
-        <v>5.48</v>
-      </c>
+      <c r="A43" s="95"/>
+      <c r="B43" s="34"/>
+      <c r="C43" s="34"/>
+      <c r="D43" s="21"/>
+      <c r="E43" s="74"/>
       <c r="F43" s="75">
         <v>5.48</v>
       </c>
-      <c r="G43" s="122">
+      <c r="G43" s="120">
         <v>0</v>
       </c>
       <c r="H43"/>
       <c r="I43"/>
     </row>
     <row r="44" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A44" s="97">
-        <v>2</v>
-      </c>
-      <c r="B44" s="104" t="s">
-        <v>82</v>
-      </c>
-      <c r="C44" s="104" t="s">
-        <v>9</v>
-      </c>
-      <c r="D44" s="105" t="s">
-        <v>83</v>
-      </c>
-      <c r="E44" s="74">
-        <v>7.0949999999999998</v>
-      </c>
+      <c r="A44" s="97"/>
+      <c r="B44" s="34"/>
+      <c r="C44" s="34"/>
+      <c r="D44" s="21"/>
+      <c r="E44" s="74"/>
       <c r="F44" s="75">
         <v>7.0949999999999998</v>
       </c>
-      <c r="G44" s="122">
+      <c r="G44" s="120">
         <v>0</v>
       </c>
       <c r="H44"/>
       <c r="I44"/>
     </row>
     <row r="45" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A45" s="95">
-        <v>3</v>
-      </c>
-      <c r="B45" s="104" t="s">
-        <v>84</v>
-      </c>
-      <c r="C45" s="104" t="s">
-        <v>9</v>
-      </c>
-      <c r="D45" s="105" t="s">
-        <v>85</v>
-      </c>
-      <c r="E45" s="74">
-        <v>42</v>
-      </c>
+      <c r="A45" s="95"/>
+      <c r="B45" s="34"/>
+      <c r="C45" s="34"/>
+      <c r="D45" s="21"/>
+      <c r="E45" s="74"/>
       <c r="F45" s="75">
         <v>42</v>
       </c>
-      <c r="G45" s="122">
+      <c r="G45" s="120">
         <v>0</v>
       </c>
       <c r="H45"/>
       <c r="I45"/>
     </row>
     <row r="46" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A46" s="97">
-        <v>4</v>
-      </c>
-      <c r="B46" s="104" t="s">
-        <v>86</v>
-      </c>
-      <c r="C46" s="104" t="s">
-        <v>9</v>
-      </c>
-      <c r="D46" s="105" t="s">
-        <v>87</v>
-      </c>
-      <c r="E46" s="74">
-        <v>102.5</v>
-      </c>
+      <c r="A46" s="97"/>
+      <c r="B46" s="34"/>
+      <c r="C46" s="34"/>
+      <c r="D46" s="21"/>
+      <c r="E46" s="74"/>
       <c r="F46" s="75">
         <v>102.5</v>
       </c>
-      <c r="G46" s="122">
+      <c r="G46" s="120">
         <v>0</v>
       </c>
       <c r="H46"/>
       <c r="I46"/>
     </row>
     <row r="47" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A47" s="95">
-        <v>5</v>
-      </c>
-      <c r="B47" s="104" t="s">
-        <v>88</v>
-      </c>
-      <c r="C47" s="104" t="s">
-        <v>9</v>
-      </c>
-      <c r="D47" s="105" t="s">
-        <v>89</v>
-      </c>
-      <c r="E47" s="74">
-        <v>14.18</v>
-      </c>
+      <c r="A47" s="95"/>
+      <c r="B47" s="34"/>
+      <c r="C47" s="34"/>
+      <c r="D47" s="21"/>
+      <c r="E47" s="74"/>
       <c r="F47" s="75">
         <v>14.18</v>
       </c>
-      <c r="G47" s="122">
+      <c r="G47" s="120">
         <v>0</v>
       </c>
       <c r="H47"/>
       <c r="I47"/>
     </row>
     <row r="48" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A48" s="97">
-        <v>6</v>
-      </c>
-      <c r="B48" s="104" t="s">
-        <v>90</v>
-      </c>
-      <c r="C48" s="104" t="s">
-        <v>9</v>
-      </c>
-      <c r="D48" s="105" t="s">
-        <v>91</v>
-      </c>
-      <c r="E48" s="74">
-        <v>1.8759999999999999</v>
-      </c>
+      <c r="A48" s="97"/>
+      <c r="B48" s="34"/>
+      <c r="C48" s="34"/>
+      <c r="D48" s="21"/>
+      <c r="E48" s="74"/>
       <c r="F48" s="75">
         <v>1.8759999999999999</v>
       </c>
-      <c r="G48" s="122">
+      <c r="G48" s="120">
         <v>0</v>
       </c>
       <c r="H48"/>
       <c r="I48"/>
     </row>
     <row r="49" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A49" s="95">
-        <v>7</v>
-      </c>
-      <c r="B49" s="104" t="s">
-        <v>92</v>
-      </c>
-      <c r="C49" s="104" t="s">
-        <v>9</v>
-      </c>
-      <c r="D49" s="105" t="s">
-        <v>93</v>
-      </c>
-      <c r="E49" s="74">
-        <v>23.1</v>
-      </c>
+      <c r="A49" s="95"/>
+      <c r="B49" s="34"/>
+      <c r="C49" s="34"/>
+      <c r="D49" s="21"/>
+      <c r="E49" s="74"/>
       <c r="F49" s="75">
         <v>23.1</v>
       </c>
-      <c r="G49" s="122">
+      <c r="G49" s="120">
         <v>0</v>
       </c>
       <c r="H49"/>
       <c r="I49"/>
     </row>
     <row r="50" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A50" s="97">
-        <v>8</v>
-      </c>
-      <c r="B50" s="104" t="s">
-        <v>94</v>
-      </c>
-      <c r="C50" s="104" t="s">
-        <v>18</v>
-      </c>
-      <c r="D50" s="105" t="s">
-        <v>95</v>
-      </c>
-      <c r="E50" s="74">
-        <v>27.4</v>
-      </c>
+      <c r="A50" s="97"/>
+      <c r="B50" s="34"/>
+      <c r="C50" s="34"/>
+      <c r="D50" s="21"/>
+      <c r="E50" s="74"/>
       <c r="F50" s="75">
         <v>27.4</v>
       </c>
-      <c r="G50" s="122">
+      <c r="G50" s="120">
         <v>0</v>
       </c>
       <c r="H50"/>
       <c r="I50"/>
     </row>
     <row r="51" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A51" s="95">
-        <v>9</v>
-      </c>
-      <c r="B51" s="104" t="s">
-        <v>96</v>
-      </c>
-      <c r="C51" s="104" t="s">
-        <v>9</v>
-      </c>
-      <c r="D51" s="105" t="s">
-        <v>97</v>
-      </c>
-      <c r="E51" s="74">
-        <v>76.42</v>
-      </c>
+      <c r="A51" s="95"/>
+      <c r="B51" s="34"/>
+      <c r="C51" s="34"/>
+      <c r="D51" s="21"/>
+      <c r="E51" s="74"/>
       <c r="F51" s="75">
         <v>76.42</v>
       </c>
-      <c r="G51" s="122">
+      <c r="G51" s="120">
         <v>0</v>
       </c>
       <c r="H51"/>
       <c r="I51"/>
     </row>
     <row r="52" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A52" s="97">
-        <v>10</v>
-      </c>
-      <c r="B52" s="104" t="s">
-        <v>98</v>
-      </c>
-      <c r="C52" s="104" t="s">
-        <v>9</v>
-      </c>
-      <c r="D52" s="105" t="s">
-        <v>99</v>
-      </c>
-      <c r="E52" s="74">
-        <v>12.1</v>
-      </c>
+      <c r="A52" s="97"/>
+      <c r="B52" s="34"/>
+      <c r="C52" s="34"/>
+      <c r="D52" s="21"/>
+      <c r="E52" s="74"/>
       <c r="F52" s="75">
         <v>12.1</v>
       </c>
-      <c r="G52" s="122">
+      <c r="G52" s="120">
         <v>0</v>
       </c>
       <c r="H52"/>
@@ -20825,11 +19698,11 @@
       <c r="B53" s="99"/>
       <c r="C53" s="100"/>
       <c r="D53" s="101"/>
-      <c r="E53" s="123"/>
-      <c r="F53" s="120" t="s">
+      <c r="E53" s="121"/>
+      <c r="F53" s="118" t="s">
         <v>30</v>
       </c>
-      <c r="G53" s="124">
+      <c r="G53" s="122">
         <v>0</v>
       </c>
       <c r="H53" s="26" t="s">
@@ -20868,7 +19741,7 @@
         <v>3</v>
       </c>
       <c r="E55" s="94" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="F55" s="46" t="s">
         <v>5</v>
@@ -20877,25 +19750,15 @@
         <v>6</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
     </row>
     <row r="56" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A56" s="95">
-        <v>1</v>
-      </c>
-      <c r="B56" s="72" t="s">
-        <v>12</v>
-      </c>
-      <c r="C56" s="73" t="s">
-        <v>9</v>
-      </c>
-      <c r="D56" s="72" t="s">
-        <v>13</v>
-      </c>
-      <c r="E56" s="96">
-        <v>69</v>
-      </c>
+      <c r="A56" s="95"/>
+      <c r="B56" s="72"/>
+      <c r="C56" s="73"/>
+      <c r="D56" s="72"/>
+      <c r="E56" s="96"/>
       <c r="F56" s="13">
         <v>69</v>
       </c>
@@ -20905,21 +19768,11 @@
       <c r="H56" s="7"/>
     </row>
     <row r="57" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A57" s="97">
-        <v>2</v>
-      </c>
-      <c r="B57" s="78" t="s">
-        <v>102</v>
-      </c>
-      <c r="C57" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D57" s="78" t="s">
-        <v>103</v>
-      </c>
-      <c r="E57" s="96">
-        <v>75.099999999999994</v>
-      </c>
+      <c r="A57" s="97"/>
+      <c r="B57" s="78"/>
+      <c r="C57" s="22"/>
+      <c r="D57" s="78"/>
+      <c r="E57" s="96"/>
       <c r="F57" s="13">
         <v>75.099999999999994</v>
       </c>
@@ -20930,21 +19783,11 @@
       <c r="I57"/>
     </row>
     <row r="58" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A58" s="95">
-        <v>3</v>
-      </c>
-      <c r="B58" s="72" t="s">
-        <v>104</v>
-      </c>
-      <c r="C58" s="73" t="s">
-        <v>9</v>
-      </c>
-      <c r="D58" s="72" t="s">
-        <v>105</v>
-      </c>
-      <c r="E58" s="96">
-        <v>109.66</v>
-      </c>
+      <c r="A58" s="95"/>
+      <c r="B58" s="72"/>
+      <c r="C58" s="73"/>
+      <c r="D58" s="72"/>
+      <c r="E58" s="96"/>
       <c r="F58" s="13">
         <v>109.66</v>
       </c>
@@ -20956,21 +19799,11 @@
       <c r="K58" s="51"/>
     </row>
     <row r="59" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A59" s="97">
-        <v>4</v>
-      </c>
-      <c r="B59" s="78" t="s">
-        <v>106</v>
-      </c>
-      <c r="C59" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D59" s="78" t="s">
-        <v>107</v>
-      </c>
-      <c r="E59" s="96">
-        <v>183</v>
-      </c>
+      <c r="A59" s="97"/>
+      <c r="B59" s="78"/>
+      <c r="C59" s="22"/>
+      <c r="D59" s="78"/>
+      <c r="E59" s="96"/>
       <c r="F59" s="13">
         <v>183</v>
       </c>
@@ -20982,21 +19815,11 @@
       <c r="K59" s="51"/>
     </row>
     <row r="60" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A60" s="95">
-        <v>5</v>
-      </c>
-      <c r="B60" s="72" t="s">
-        <v>108</v>
-      </c>
-      <c r="C60" s="73" t="s">
-        <v>9</v>
-      </c>
-      <c r="D60" s="72" t="s">
-        <v>108</v>
-      </c>
-      <c r="E60" s="96">
-        <v>6.66</v>
-      </c>
+      <c r="A60" s="95"/>
+      <c r="B60" s="72"/>
+      <c r="C60" s="73"/>
+      <c r="D60" s="72"/>
+      <c r="E60" s="96"/>
       <c r="F60" s="13">
         <v>6.66</v>
       </c>
@@ -21008,21 +19831,11 @@
       <c r="K60" s="51"/>
     </row>
     <row r="61" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A61" s="97">
-        <v>6</v>
-      </c>
-      <c r="B61" s="78" t="s">
-        <v>96</v>
-      </c>
-      <c r="C61" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D61" s="78" t="s">
-        <v>97</v>
-      </c>
-      <c r="E61" s="96">
-        <v>76.42</v>
-      </c>
+      <c r="A61" s="97"/>
+      <c r="B61" s="78"/>
+      <c r="C61" s="22"/>
+      <c r="D61" s="78"/>
+      <c r="E61" s="96"/>
       <c r="F61" s="13">
         <v>76.42</v>
       </c>
@@ -21034,21 +19847,11 @@
       <c r="K61" s="51"/>
     </row>
     <row r="62" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A62" s="95">
-        <v>7</v>
-      </c>
-      <c r="B62" s="72" t="s">
-        <v>22</v>
-      </c>
-      <c r="C62" s="73" t="s">
-        <v>9</v>
-      </c>
-      <c r="D62" s="72" t="s">
-        <v>23</v>
-      </c>
-      <c r="E62" s="96">
-        <v>22</v>
-      </c>
+      <c r="A62" s="95"/>
+      <c r="B62" s="72"/>
+      <c r="C62" s="73"/>
+      <c r="D62" s="72"/>
+      <c r="E62" s="96"/>
       <c r="F62" s="13">
         <v>22</v>
       </c>
@@ -21059,21 +19862,11 @@
       <c r="I62"/>
     </row>
     <row r="63" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A63" s="97">
-        <v>8</v>
-      </c>
-      <c r="B63" s="78" t="s">
-        <v>109</v>
-      </c>
-      <c r="C63" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D63" s="78" t="s">
-        <v>110</v>
-      </c>
-      <c r="E63" s="96">
-        <v>58.25</v>
-      </c>
+      <c r="A63" s="97"/>
+      <c r="B63" s="78"/>
+      <c r="C63" s="22"/>
+      <c r="D63" s="78"/>
+      <c r="E63" s="96"/>
       <c r="F63" s="13">
         <v>58.25</v>
       </c>
@@ -21084,21 +19877,11 @@
       <c r="I63"/>
     </row>
     <row r="64" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A64" s="95">
-        <v>9</v>
-      </c>
-      <c r="B64" s="72" t="s">
-        <v>111</v>
-      </c>
-      <c r="C64" s="73" t="s">
-        <v>9</v>
-      </c>
-      <c r="D64" s="72" t="s">
-        <v>112</v>
-      </c>
-      <c r="E64" s="96">
-        <v>92.62</v>
-      </c>
+      <c r="A64" s="95"/>
+      <c r="B64" s="72"/>
+      <c r="C64" s="73"/>
+      <c r="D64" s="72"/>
+      <c r="E64" s="96"/>
       <c r="F64" s="13">
         <v>92.62</v>
       </c>
@@ -21109,21 +19892,11 @@
       <c r="I64"/>
     </row>
     <row r="65" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A65" s="97">
-        <v>10</v>
-      </c>
-      <c r="B65" s="78" t="s">
-        <v>113</v>
-      </c>
-      <c r="C65" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D65" s="78" t="s">
-        <v>114</v>
-      </c>
-      <c r="E65" s="96">
-        <v>81.28</v>
-      </c>
+      <c r="A65" s="97"/>
+      <c r="B65" s="78"/>
+      <c r="C65" s="22"/>
+      <c r="D65" s="78"/>
+      <c r="E65" s="96"/>
       <c r="F65" s="13">
         <v>81.28</v>
       </c>
@@ -21190,7 +19963,7 @@
         <v>6</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
     </row>
     <row r="69" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
@@ -21198,13 +19971,13 @@
         <v>1</v>
       </c>
       <c r="B69" s="72" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="C69" s="73" t="s">
         <v>9</v>
       </c>
       <c r="D69" s="72" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="E69" s="86">
         <v>75.099999999999994</v>
@@ -21222,13 +19995,13 @@
         <v>2</v>
       </c>
       <c r="B70" s="78" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="C70" s="22" t="s">
         <v>9</v>
       </c>
       <c r="D70" s="78" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="E70" s="86">
         <v>109.66</v>
@@ -21248,13 +20021,13 @@
         <v>3</v>
       </c>
       <c r="B71" s="72" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="C71" s="73" t="s">
         <v>9</v>
       </c>
       <c r="D71" s="72" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="E71" s="86">
         <v>92.62</v>
@@ -21274,13 +20047,13 @@
         <v>4</v>
       </c>
       <c r="B72" s="78" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="C72" s="22" t="s">
         <v>9</v>
       </c>
       <c r="D72" s="78" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="E72" s="86">
         <v>47.4</v>
@@ -21300,13 +20073,13 @@
         <v>5</v>
       </c>
       <c r="B73" s="72" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="C73" s="73" t="s">
         <v>9</v>
       </c>
       <c r="D73" s="72" t="s">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="E73" s="86">
         <v>31.3</v>
@@ -21326,13 +20099,13 @@
         <v>6</v>
       </c>
       <c r="B74" s="78" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="C74" s="22" t="s">
         <v>9</v>
       </c>
       <c r="D74" s="78" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="E74" s="86">
         <v>13.58</v>
@@ -21352,13 +20125,13 @@
         <v>7</v>
       </c>
       <c r="B75" s="72" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="C75" s="73" t="s">
         <v>9</v>
       </c>
       <c r="D75" s="72" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="E75" s="86">
         <v>76.42</v>
@@ -21378,13 +20151,13 @@
         <v>8</v>
       </c>
       <c r="B76" s="78" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="C76" s="22" t="s">
         <v>9</v>
       </c>
       <c r="D76" s="78" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="E76" s="86">
         <v>58.25</v>
@@ -21404,13 +20177,13 @@
         <v>9</v>
       </c>
       <c r="B77" s="72" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="C77" s="73" t="s">
         <v>9</v>
       </c>
       <c r="D77" s="72" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="E77" s="86">
         <v>19.274999999999999</v>
@@ -21430,13 +20203,13 @@
         <v>10</v>
       </c>
       <c r="B78" s="88" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C78" s="89" t="s">
         <v>9</v>
       </c>
       <c r="D78" s="88" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="E78" s="90">
         <v>102.5</v>
@@ -21472,10 +20245,10 @@
         <v>0</v>
       </c>
       <c r="B81" s="66" t="s">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="C81" s="67" t="s">
-        <v>125</v>
+        <v>108</v>
       </c>
       <c r="D81" s="67" t="s">
         <v>3</v>
@@ -21501,7 +20274,7 @@
       <c r="B82" s="72"/>
       <c r="C82" s="73"/>
       <c r="D82" s="72"/>
-      <c r="E82" s="118"/>
+      <c r="E82" s="116"/>
       <c r="F82" s="75"/>
       <c r="G82" s="76" t="e">
         <v>#VALUE!</v>
@@ -21516,7 +20289,7 @@
       <c r="B83" s="78"/>
       <c r="C83" s="22"/>
       <c r="D83" s="78"/>
-      <c r="E83" s="118"/>
+      <c r="E83" s="116"/>
       <c r="F83" s="75"/>
       <c r="G83" s="76" t="e">
         <v>#VALUE!</v>
@@ -21531,7 +20304,7 @@
       <c r="B84" s="72"/>
       <c r="C84" s="73"/>
       <c r="D84" s="72"/>
-      <c r="E84" s="118"/>
+      <c r="E84" s="116"/>
       <c r="F84" s="75"/>
       <c r="G84" s="76" t="e">
         <v>#VALUE!</v>
@@ -21544,9 +20317,9 @@
         <v>4</v>
       </c>
       <c r="B85" s="78"/>
-      <c r="C85" s="119"/>
+      <c r="C85" s="117"/>
       <c r="D85" s="78"/>
-      <c r="E85" s="118"/>
+      <c r="E85" s="116"/>
       <c r="F85" s="75"/>
       <c r="G85" s="76" t="e">
         <v>#VALUE!</v>
@@ -21559,9 +20332,9 @@
         <v>5</v>
       </c>
       <c r="B86" s="72"/>
-      <c r="C86" s="119"/>
+      <c r="C86" s="117"/>
       <c r="D86" s="72"/>
-      <c r="E86" s="118"/>
+      <c r="E86" s="116"/>
       <c r="F86" s="75"/>
       <c r="G86" s="76" t="e">
         <v>#VALUE!</v>
@@ -21574,9 +20347,9 @@
         <v>6</v>
       </c>
       <c r="B87" s="78"/>
-      <c r="C87" s="119"/>
+      <c r="C87" s="117"/>
       <c r="D87" s="78"/>
-      <c r="E87" s="118"/>
+      <c r="E87" s="116"/>
       <c r="F87" s="75"/>
       <c r="G87" s="76" t="e">
         <v>#VALUE!</v>
@@ -21591,7 +20364,7 @@
       <c r="B88" s="72"/>
       <c r="C88" s="73"/>
       <c r="D88" s="72"/>
-      <c r="E88" s="118"/>
+      <c r="E88" s="116"/>
       <c r="F88" s="75"/>
       <c r="G88" s="76" t="e">
         <v>#VALUE!</v>
@@ -21604,9 +20377,9 @@
         <v>8</v>
       </c>
       <c r="B89" s="78"/>
-      <c r="C89" s="119"/>
+      <c r="C89" s="117"/>
       <c r="D89" s="78"/>
-      <c r="E89" s="118"/>
+      <c r="E89" s="116"/>
       <c r="F89" s="75"/>
       <c r="G89" s="76" t="e">
         <v>#VALUE!</v>
@@ -21621,7 +20394,7 @@
       <c r="B90" s="72"/>
       <c r="C90" s="73"/>
       <c r="D90" s="72"/>
-      <c r="E90" s="118"/>
+      <c r="E90" s="116"/>
       <c r="F90" s="75"/>
       <c r="G90" s="76" t="e">
         <v>#VALUE!</v>
@@ -21636,7 +20409,7 @@
       <c r="B91" s="78"/>
       <c r="C91" s="22"/>
       <c r="D91" s="78"/>
-      <c r="E91" s="118"/>
+      <c r="E91" s="116"/>
       <c r="F91" s="75"/>
       <c r="G91" s="76" t="e">
         <v>#VALUE!</v>
@@ -21650,7 +20423,7 @@
       <c r="C92" s="81"/>
       <c r="D92" s="51"/>
       <c r="E92" s="82"/>
-      <c r="F92" s="120" t="s">
+      <c r="F92" s="118" t="s">
         <v>30</v>
       </c>
       <c r="G92" s="44" t="e">
@@ -21685,16 +20458,16 @@
         <v>0</v>
       </c>
       <c r="B95" s="66" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="C95" s="67" t="s">
-        <v>125</v>
+        <v>108</v>
       </c>
       <c r="D95" s="68" t="s">
         <v>54</v>
       </c>
       <c r="E95" s="68" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="F95" s="69" t="s">
         <v>5</v>
@@ -21703,7 +20476,7 @@
         <v>6</v>
       </c>
       <c r="H95" s="6" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="I95" s="61"/>
       <c r="J95" s="62"/>
@@ -21947,8 +20720,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="131" t="s">
-        <v>129</v>
+      <c r="A1" s="129" t="s">
+        <v>112</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -21985,13 +20758,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>9</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="E2" s="12">
         <v>75.2</v>
@@ -22016,13 +20789,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>15</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="E3" s="12">
         <v>15</v>
@@ -22074,13 +20847,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>9</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="E5" s="12">
         <v>3.8149999999999999</v>
@@ -22103,13 +20876,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>9</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="E6" s="12">
         <v>124.2</v>
@@ -22132,13 +20905,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>18</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="E7" s="12">
         <v>13</v>
@@ -22161,13 +20934,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>9</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="E8" s="12">
         <v>62.1</v>
@@ -22219,13 +20992,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>9</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="E10" s="12">
         <v>21.96</v>
@@ -22248,13 +21021,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>9</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="E11" s="12">
         <v>47.68</v>
@@ -22340,13 +21113,13 @@
         <v>1</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>9</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="E16" s="12">
         <v>0.51100000000000001</v>
@@ -22364,13 +21137,13 @@
         <v>2</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="C17" s="9" t="s">
         <v>9</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="E17" s="12">
         <v>6.6349999999999998</v>
@@ -22388,13 +21161,13 @@
         <v>3</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="C18" s="9" t="s">
         <v>9</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="E18" s="12">
         <v>8.69</v>
@@ -22413,13 +21186,13 @@
         <v>4</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>149</v>
+        <v>132</v>
       </c>
       <c r="C19" s="9" t="s">
         <v>18</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="E19" s="12">
         <v>5.56</v>
@@ -22437,13 +21210,13 @@
         <v>5</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>151</v>
+        <v>134</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>9</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>152</v>
+        <v>135</v>
       </c>
       <c r="E20" s="12">
         <v>0.52200000000000002</v>
@@ -22462,13 +21235,13 @@
         <v>6</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>153</v>
+        <v>136</v>
       </c>
       <c r="C21" s="9" t="s">
         <v>9</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>154</v>
+        <v>137</v>
       </c>
       <c r="E21" s="12">
         <v>158.4</v>
@@ -22486,13 +21259,13 @@
         <v>7</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>155</v>
+        <v>138</v>
       </c>
       <c r="C22" s="9" t="s">
         <v>18</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>156</v>
+        <v>139</v>
       </c>
       <c r="E22" s="12">
         <v>19.100000000000001</v>
@@ -22510,13 +21283,13 @@
         <v>8</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>157</v>
+        <v>140</v>
       </c>
       <c r="C23" s="9" t="s">
         <v>9</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="E23" s="12">
         <v>0.17199999999999999</v>
@@ -22534,13 +21307,13 @@
         <v>9</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="C24" s="9" t="s">
         <v>9</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>160</v>
+        <v>143</v>
       </c>
       <c r="E24" s="12">
         <v>76.03</v>
@@ -22558,13 +21331,13 @@
         <v>10</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>161</v>
+        <v>144</v>
       </c>
       <c r="C25" s="9" t="s">
         <v>9</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="E25" s="12">
         <v>8.5500000000000007</v>
@@ -22647,13 +21420,13 @@
         <v>1</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>163</v>
+        <v>146</v>
       </c>
       <c r="C30" s="9" t="s">
         <v>74</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="E30" s="12">
         <v>1.49</v>
@@ -22716,13 +21489,13 @@
         <v>4</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>165</v>
+        <v>148</v>
       </c>
       <c r="C33" s="9" t="s">
         <v>57</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="E33" s="12">
         <v>27.58</v>
@@ -22739,13 +21512,13 @@
         <v>5</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="C34" s="9" t="s">
         <v>57</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>168</v>
+        <v>151</v>
       </c>
       <c r="E34" s="12">
         <v>1.6479999999999999</v>
@@ -22762,13 +21535,13 @@
         <v>6</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="C35" s="9" t="s">
         <v>57</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>170</v>
+        <v>153</v>
       </c>
       <c r="E35" s="12">
         <v>0.72799999999999998</v>
@@ -22785,19 +21558,19 @@
         <v>7</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>171</v>
+        <v>154</v>
       </c>
       <c r="C36" s="9" t="s">
         <v>57</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>172</v>
+        <v>155</v>
       </c>
       <c r="E36" s="12">
         <v>0.58199999999999996</v>
       </c>
       <c r="F36" s="13" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="G36" s="14" t="e">
         <v>#VALUE!</v>
@@ -22808,13 +21581,13 @@
         <v>8</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="C37" s="9" t="s">
         <v>57</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>175</v>
+        <v>158</v>
       </c>
       <c r="E37" s="12">
         <v>1.125</v>
@@ -22832,13 +21605,13 @@
         <v>9</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>176</v>
+        <v>159</v>
       </c>
       <c r="C38" s="9" t="s">
         <v>57</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="E38" s="12">
         <v>1.21</v>
@@ -22856,13 +21629,13 @@
         <v>10</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>178</v>
+        <v>161</v>
       </c>
       <c r="C39" s="9" t="s">
         <v>57</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="E39" s="12">
         <v>204</v>
@@ -22928,13 +21701,13 @@
         <v>1</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="C43" s="9" t="s">
         <v>9</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>181</v>
+        <v>164</v>
       </c>
       <c r="E43" s="12">
         <v>360.5</v>
@@ -22951,13 +21724,13 @@
         <v>2</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>182</v>
+        <v>165</v>
       </c>
       <c r="C44" s="9" t="s">
         <v>9</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="E44" s="12">
         <v>25.95</v>
@@ -22997,13 +21770,13 @@
         <v>4</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="C46" s="9" t="s">
         <v>9</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="E46" s="12">
         <v>21.96</v>
@@ -23043,13 +21816,13 @@
         <v>6</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>184</v>
+        <v>167</v>
       </c>
       <c r="C48" s="9" t="s">
         <v>9</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>185</v>
+        <v>168</v>
       </c>
       <c r="E48" s="12">
         <v>27.79</v>
@@ -23066,13 +21839,13 @@
         <v>7</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>186</v>
+        <v>169</v>
       </c>
       <c r="C49" s="9" t="s">
         <v>9</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>187</v>
+        <v>170</v>
       </c>
       <c r="E49" s="12">
         <v>55.8</v>
@@ -23089,13 +21862,13 @@
         <v>8</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>188</v>
+        <v>171</v>
       </c>
       <c r="C50" s="9" t="s">
         <v>9</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>189</v>
+        <v>172</v>
       </c>
       <c r="E50" s="12">
         <v>55.5</v>
@@ -23135,13 +21908,13 @@
         <v>10</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>190</v>
+        <v>173</v>
       </c>
       <c r="C52" s="9" t="s">
         <v>9</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>191</v>
+        <v>174</v>
       </c>
       <c r="E52" s="12">
         <v>32.72</v>
@@ -23199,7 +21972,7 @@
         <v>3</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="F55" s="46" t="s">
         <v>5</v>
@@ -23208,7 +21981,7 @@
         <v>6</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="I55" s="7"/>
     </row>
@@ -23217,13 +21990,13 @@
         <v>1</v>
       </c>
       <c r="B56" s="48" t="s">
-        <v>192</v>
+        <v>175</v>
       </c>
       <c r="C56" s="40" t="s">
         <v>9</v>
       </c>
       <c r="D56" s="48" t="s">
-        <v>193</v>
+        <v>176</v>
       </c>
       <c r="E56" s="49">
         <v>8.6050000000000004</v>
@@ -23242,13 +22015,13 @@
         <v>2</v>
       </c>
       <c r="B57" s="48" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="C57" s="40" t="s">
         <v>9</v>
       </c>
       <c r="D57" s="48" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="E57" s="49">
         <v>105.92</v>
@@ -23266,13 +22039,13 @@
         <v>3</v>
       </c>
       <c r="B58" s="48" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="C58" s="40" t="s">
         <v>9</v>
       </c>
       <c r="D58" s="48" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="E58" s="49">
         <v>75.900000000000006</v>
@@ -23291,13 +22064,13 @@
         <v>4</v>
       </c>
       <c r="B59" s="48" t="s">
-        <v>184</v>
+        <v>167</v>
       </c>
       <c r="C59" s="40" t="s">
         <v>9</v>
       </c>
       <c r="D59" s="48" t="s">
-        <v>185</v>
+        <v>168</v>
       </c>
       <c r="E59" s="49">
         <v>27.79</v>
@@ -23341,13 +22114,13 @@
         <v>6</v>
       </c>
       <c r="B61" s="48" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="C61" s="40" t="s">
         <v>9</v>
       </c>
       <c r="D61" s="48" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="E61" s="49">
         <v>47.68</v>
@@ -23366,13 +22139,13 @@
         <v>7</v>
       </c>
       <c r="B62" s="48" t="s">
-        <v>194</v>
+        <v>177</v>
       </c>
       <c r="C62" s="40" t="s">
         <v>9</v>
       </c>
       <c r="D62" s="48" t="s">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="E62" s="49">
         <v>33.840000000000003</v>
@@ -23390,13 +22163,13 @@
         <v>8</v>
       </c>
       <c r="B63" s="48" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="C63" s="40" t="s">
         <v>9</v>
       </c>
       <c r="D63" s="48" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="E63" s="49">
         <v>154.9</v>
@@ -23414,13 +22187,13 @@
         <v>9</v>
       </c>
       <c r="B64" s="48" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="C64" s="40" t="s">
         <v>9</v>
       </c>
       <c r="D64" s="48" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="E64" s="49">
         <v>18.504999999999999</v>
@@ -23438,13 +22211,13 @@
         <v>10</v>
       </c>
       <c r="B65" s="48" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="C65" s="40" t="s">
         <v>9</v>
       </c>
       <c r="D65" s="48" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="E65" s="49">
         <v>88.42</v>
@@ -23512,7 +22285,7 @@
         <v>6</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="I68" s="7"/>
     </row>
@@ -23521,13 +22294,13 @@
         <v>1</v>
       </c>
       <c r="B69" s="48" t="s">
-        <v>192</v>
+        <v>175</v>
       </c>
       <c r="C69" s="40" t="s">
         <v>9</v>
       </c>
       <c r="D69" s="48" t="s">
-        <v>193</v>
+        <v>176</v>
       </c>
       <c r="E69" s="49">
         <v>8.6050000000000004</v>
@@ -23546,13 +22319,13 @@
         <v>2</v>
       </c>
       <c r="B70" s="48" t="s">
-        <v>196</v>
+        <v>179</v>
       </c>
       <c r="C70" s="40" t="s">
         <v>9</v>
       </c>
       <c r="D70" s="48" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="E70" s="49">
         <v>22.11</v>
@@ -23571,13 +22344,13 @@
         <v>3</v>
       </c>
       <c r="B71" s="48" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="C71" s="40" t="s">
         <v>9</v>
       </c>
       <c r="D71" s="48" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="E71" s="49">
         <v>12.78</v>
@@ -23596,13 +22369,13 @@
         <v>4</v>
       </c>
       <c r="B72" s="48" t="s">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="C72" s="40" t="s">
         <v>9</v>
       </c>
       <c r="D72" s="48" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="E72" s="49">
         <v>21.96</v>
@@ -23621,13 +22394,13 @@
         <v>5</v>
       </c>
       <c r="B73" s="48" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="C73" s="40" t="s">
         <v>9</v>
       </c>
       <c r="D73" s="48" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="E73" s="49">
         <v>105.92</v>
@@ -23646,13 +22419,13 @@
         <v>6</v>
       </c>
       <c r="B74" s="48" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="C74" s="40" t="s">
         <v>9</v>
       </c>
       <c r="D74" s="48" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="E74" s="49">
         <v>75.900000000000006</v>
@@ -23697,13 +22470,13 @@
         <v>8</v>
       </c>
       <c r="B76" s="48" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C76" s="40" t="s">
         <v>9</v>
       </c>
       <c r="D76" s="48" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E76" s="49">
         <v>13.54</v>
@@ -23722,13 +22495,13 @@
         <v>9</v>
       </c>
       <c r="B77" s="48" t="s">
-        <v>188</v>
+        <v>171</v>
       </c>
       <c r="C77" s="40" t="s">
         <v>9</v>
       </c>
       <c r="D77" s="48" t="s">
-        <v>189</v>
+        <v>172</v>
       </c>
       <c r="E77" s="49">
         <v>55.5</v>
@@ -23747,13 +22520,13 @@
         <v>10</v>
       </c>
       <c r="B78" s="48" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="C78" s="40" t="s">
         <v>18</v>
       </c>
       <c r="D78" s="48" t="s">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="E78" s="49">
         <v>47.5</v>
@@ -23788,10 +22561,10 @@
         <v>0</v>
       </c>
       <c r="B81" s="58" t="s">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="C81" t="s">
-        <v>125</v>
+        <v>108</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>3</v>
@@ -23818,7 +22591,7 @@
       <c r="D82" s="48"/>
       <c r="E82" s="49"/>
       <c r="F82" s="13" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="G82" s="50" t="e">
         <v>#VALUE!</v>
@@ -23833,7 +22606,7 @@
       <c r="D83" s="48"/>
       <c r="E83" s="49"/>
       <c r="F83" s="13" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="G83" s="50" t="e">
         <v>#VALUE!</v>
@@ -23848,7 +22621,7 @@
       <c r="D84" s="48"/>
       <c r="E84" s="49"/>
       <c r="F84" s="13" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="G84" s="50" t="e">
         <v>#VALUE!</v>
@@ -23863,7 +22636,7 @@
       <c r="D85" s="48"/>
       <c r="E85" s="49"/>
       <c r="F85" s="13" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="G85" s="50" t="e">
         <v>#VALUE!</v>
@@ -23878,7 +22651,7 @@
       <c r="D86" s="48"/>
       <c r="E86" s="49"/>
       <c r="F86" s="13" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="G86" s="50" t="e">
         <v>#VALUE!</v>
@@ -23893,7 +22666,7 @@
       <c r="D87" s="48"/>
       <c r="E87" s="49"/>
       <c r="F87" s="13" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="G87" s="50" t="e">
         <v>#VALUE!</v>
@@ -23908,7 +22681,7 @@
       <c r="D88" s="48"/>
       <c r="E88" s="49"/>
       <c r="F88" s="13" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="G88" s="50" t="e">
         <v>#VALUE!</v>
@@ -23923,7 +22696,7 @@
       <c r="D89" s="48"/>
       <c r="E89" s="49"/>
       <c r="F89" s="13" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="G89" s="50" t="e">
         <v>#VALUE!</v>
@@ -23938,7 +22711,7 @@
       <c r="D90" s="48"/>
       <c r="E90" s="49"/>
       <c r="F90" s="13" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="G90" s="50" t="e">
         <v>#VALUE!</v>
@@ -23953,7 +22726,7 @@
       <c r="D91" s="48"/>
       <c r="E91" s="49"/>
       <c r="F91" s="13" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="G91" s="50" t="e">
         <v>#VALUE!</v>
@@ -24001,16 +22774,16 @@
         <v>0</v>
       </c>
       <c r="B95" s="58" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="C95" t="s">
-        <v>125</v>
+        <v>108</v>
       </c>
       <c r="D95" s="60" t="s">
         <v>54</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="F95" s="4" t="s">
         <v>5</v>
@@ -24019,7 +22792,7 @@
         <v>6</v>
       </c>
       <c r="H95" s="6" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="I95" s="61"/>
       <c r="J95" s="62"/>
@@ -24034,7 +22807,7 @@
       <c r="D96" s="48"/>
       <c r="E96" s="12"/>
       <c r="F96" s="13" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="G96" s="50" t="e">
         <v>#VALUE!</v>
@@ -24051,7 +22824,7 @@
       <c r="D97" s="48"/>
       <c r="E97" s="12"/>
       <c r="F97" s="13" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="G97" s="50" t="e">
         <v>#VALUE!</v>
@@ -24068,7 +22841,7 @@
       <c r="D98" s="48"/>
       <c r="E98" s="12"/>
       <c r="F98" s="13" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="G98" s="50" t="e">
         <v>#VALUE!</v>
@@ -24084,7 +22857,7 @@
       <c r="D99" s="48"/>
       <c r="E99" s="12"/>
       <c r="F99" s="13" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="G99" s="50" t="e">
         <v>#VALUE!</v>
@@ -24100,7 +22873,7 @@
       <c r="D100" s="48"/>
       <c r="E100" s="12"/>
       <c r="F100" s="13" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="G100" s="50" t="e">
         <v>#VALUE!</v>
@@ -24117,7 +22890,7 @@
       <c r="D101" s="48"/>
       <c r="E101" s="12"/>
       <c r="F101" s="13" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="G101" s="50" t="e">
         <v>#VALUE!</v>
@@ -24134,7 +22907,7 @@
       <c r="D102" s="48"/>
       <c r="E102" s="12"/>
       <c r="F102" s="13" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="G102" s="50" t="e">
         <v>#VALUE!</v>
@@ -24150,7 +22923,7 @@
       <c r="D103" s="48"/>
       <c r="E103" s="12"/>
       <c r="F103" s="13" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="G103" s="50" t="e">
         <v>#VALUE!</v>
@@ -24167,7 +22940,7 @@
       <c r="D104" s="48"/>
       <c r="E104" s="12"/>
       <c r="F104" s="13" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="G104" s="50" t="e">
         <v>#VALUE!</v>
@@ -24184,7 +22957,7 @@
       <c r="D105" s="48"/>
       <c r="E105" s="12"/>
       <c r="F105" s="13" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="G105" s="50" t="e">
         <v>#VALUE!</v>
@@ -24252,429 +23025,428 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B56:B65">
-    <cfRule type="expression" dxfId="105" priority="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="104" priority="5" stopIfTrue="1">
       <formula>IF(AO56&gt;0,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B69:B78">
-    <cfRule type="expression" dxfId="104" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="103" priority="3" stopIfTrue="1">
       <formula>IF(AO69&gt;0,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B81">
-    <cfRule type="expression" dxfId="103" priority="50" stopIfTrue="1">
+    <cfRule type="expression" dxfId="102" priority="50" stopIfTrue="1">
       <formula>IF(AN62&gt;0,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B82:B91">
-    <cfRule type="expression" dxfId="102" priority="9" stopIfTrue="1">
+    <cfRule type="expression" dxfId="101" priority="9" stopIfTrue="1">
       <formula>IF(AL82&gt;0,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B92">
-    <cfRule type="expression" dxfId="101" priority="46" stopIfTrue="1">
+    <cfRule type="expression" dxfId="100" priority="46" stopIfTrue="1">
       <formula>IF(AL91&gt;0,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B95">
-    <cfRule type="expression" dxfId="100" priority="49" stopIfTrue="1">
+    <cfRule type="expression" dxfId="99" priority="49" stopIfTrue="1">
       <formula>IF(AN75&gt;0,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B96:B105">
-    <cfRule type="expression" dxfId="99" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="98" priority="7" stopIfTrue="1">
       <formula>IF(AO96&gt;0,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B106">
-    <cfRule type="expression" dxfId="98" priority="47" stopIfTrue="1">
+    <cfRule type="expression" dxfId="97" priority="47" stopIfTrue="1">
       <formula>IF(AN104&gt;0,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B107">
-    <cfRule type="expression" dxfId="97" priority="48" stopIfTrue="1">
+    <cfRule type="expression" dxfId="96" priority="48" stopIfTrue="1">
       <formula>IF(AN104&gt;0,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D56:D65">
-    <cfRule type="expression" dxfId="96" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="95" priority="4" stopIfTrue="1">
       <formula>IF(AQ56&gt;0,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D69:D78">
-    <cfRule type="expression" dxfId="95" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="94" priority="2" stopIfTrue="1">
       <formula>IF(AQ69&gt;0,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D82:D91">
-    <cfRule type="expression" dxfId="94" priority="8" stopIfTrue="1">
+    <cfRule type="expression" dxfId="93" priority="8" stopIfTrue="1">
       <formula>IF(AN82&gt;0,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D96:D105">
-    <cfRule type="expression" dxfId="93" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="92" priority="6" stopIfTrue="1">
       <formula>IF(AQ96&gt;0,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F11 F16:F25">
-    <cfRule type="expression" dxfId="92" priority="19" stopIfTrue="1">
+    <cfRule type="expression" dxfId="91" priority="19" stopIfTrue="1">
       <formula>IF(#REF!="AAA",TRUE,FALSE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="91" priority="20" stopIfTrue="1">
+    <cfRule type="expression" dxfId="90" priority="20" stopIfTrue="1">
       <formula>IF($T200="AAA",TRUE,FALSE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="90" priority="21" stopIfTrue="1">
+    <cfRule type="expression" dxfId="89" priority="21" stopIfTrue="1">
       <formula>IF($U200="AAA",TRUE,FALSE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="89" priority="22" stopIfTrue="1">
+    <cfRule type="expression" dxfId="88" priority="22" stopIfTrue="1">
       <formula>IF($AN1048554="AAA",TRUE,FALSE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="88" priority="23" stopIfTrue="1">
+    <cfRule type="expression" dxfId="87" priority="23" stopIfTrue="1">
       <formula>IF($T200="AAA",TRUE,FALSE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="87" priority="24" stopIfTrue="1">
+    <cfRule type="expression" dxfId="86" priority="24" stopIfTrue="1">
       <formula>IF($U200="AAA",TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F30:F39">
-    <cfRule type="expression" dxfId="86" priority="80" stopIfTrue="1">
+    <cfRule type="expression" dxfId="85" priority="80" stopIfTrue="1">
       <formula>IF(#REF!="AAA",TRUE,FALSE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="85" priority="81" stopIfTrue="1">
+    <cfRule type="expression" dxfId="84" priority="85" stopIfTrue="1">
+      <formula>IF($U230="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="83" priority="84" stopIfTrue="1">
       <formula>IF($T230="AAA",TRUE,FALSE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="84" priority="82" stopIfTrue="1">
+    <cfRule type="expression" dxfId="82" priority="83" stopIfTrue="1">
+      <formula>IF($AN5="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="81" priority="82" stopIfTrue="1">
       <formula>IF($U230="AAA",TRUE,FALSE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="83" priority="83" stopIfTrue="1">
-      <formula>IF($AN5="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="82" priority="84" stopIfTrue="1">
+    <cfRule type="expression" dxfId="80" priority="81" stopIfTrue="1">
       <formula>IF($T230="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="81" priority="85" stopIfTrue="1">
-      <formula>IF($U230="AAA",TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F43:F52">
-    <cfRule type="expression" dxfId="80" priority="86" stopIfTrue="1">
+    <cfRule type="expression" dxfId="79" priority="91" stopIfTrue="1">
+      <formula>IF($U242="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="78" priority="89" stopIfTrue="1">
+      <formula>IF($AN17="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="77" priority="88" stopIfTrue="1">
+      <formula>IF($U242="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="76" priority="87" stopIfTrue="1">
+      <formula>IF($T242="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="75" priority="86" stopIfTrue="1">
       <formula>IF(#REF!="AAA",TRUE,FALSE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="79" priority="87" stopIfTrue="1">
+    <cfRule type="expression" dxfId="74" priority="90" stopIfTrue="1">
       <formula>IF($T242="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="78" priority="88" stopIfTrue="1">
-      <formula>IF($U242="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="77" priority="89" stopIfTrue="1">
-      <formula>IF($AN17="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="76" priority="90" stopIfTrue="1">
-      <formula>IF($T242="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="75" priority="91" stopIfTrue="1">
-      <formula>IF($U242="AAA",TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F56">
-    <cfRule type="expression" dxfId="74" priority="76" stopIfTrue="1">
-      <formula>IF(#REF!="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="73" priority="77" stopIfTrue="1">
-      <formula>IF($AN28="AAA",TRUE,FALSE)</formula>
+    <cfRule type="expression" dxfId="73" priority="79" stopIfTrue="1">
+      <formula>IF($U254="AAA",TRUE,FALSE)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="72" priority="78" stopIfTrue="1">
       <formula>IF($T254="AAA",TRUE,FALSE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="71" priority="79" stopIfTrue="1">
-      <formula>IF($U254="AAA",TRUE,FALSE)</formula>
+    <cfRule type="expression" dxfId="71" priority="77" stopIfTrue="1">
+      <formula>IF($AN28="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F56:F67">
+    <cfRule type="expression" dxfId="70" priority="76" stopIfTrue="1">
+      <formula>IF(#REF!="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F57:F67">
+    <cfRule type="expression" dxfId="69" priority="93" stopIfTrue="1">
+      <formula>IF($AK29="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="68" priority="94" stopIfTrue="1">
+      <formula>IF($T255="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="67" priority="95" stopIfTrue="1">
+      <formula>IF($U255="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F69">
+    <cfRule type="expression" dxfId="66" priority="96" stopIfTrue="1">
+      <formula>IF($T268="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="65" priority="97" stopIfTrue="1">
+      <formula>IF($U268="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="64" priority="98" stopIfTrue="1">
+      <formula>IF($AJ43="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="63" priority="99" stopIfTrue="1">
+      <formula>IF($T268="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="62" priority="100" stopIfTrue="1">
+      <formula>IF($U268="AAA",TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F69:F78">
-    <cfRule type="expression" dxfId="70" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="61" priority="1" stopIfTrue="1">
       <formula>IF(#REF!="AAA",TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="F70:F78">
+    <cfRule type="expression" dxfId="60" priority="101" stopIfTrue="1">
+      <formula>IF($AJ42="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="59" priority="102" stopIfTrue="1">
+      <formula>IF($T267="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="58" priority="103" stopIfTrue="1">
+      <formula>IF($U267="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F82">
+    <cfRule type="expression" dxfId="57" priority="104" stopIfTrue="1">
+      <formula>IF($AJ53="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="56" priority="105" stopIfTrue="1">
+      <formula>IF($T278="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="55" priority="106" stopIfTrue="1">
+      <formula>IF($U278="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F82:F91">
-    <cfRule type="expression" dxfId="69" priority="65" stopIfTrue="1">
+    <cfRule type="expression" dxfId="54" priority="65" stopIfTrue="1">
       <formula>IF(#REF!="AAA",TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F83:F91">
-    <cfRule type="expression" dxfId="68" priority="66" stopIfTrue="1">
+    <cfRule type="expression" dxfId="53" priority="66" stopIfTrue="1">
       <formula>IF($AN55="AAA",TRUE,FALSE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="67" priority="67" stopIfTrue="1">
+    <cfRule type="expression" dxfId="52" priority="68" stopIfTrue="1">
+      <formula>IF($U279="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="51" priority="67" stopIfTrue="1">
       <formula>IF($T279="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="66" priority="68" stopIfTrue="1">
-      <formula>IF($U279="AAA",TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F96:F97">
-    <cfRule type="expression" dxfId="65" priority="73" stopIfTrue="1">
-      <formula>IF($AN65="AAA",TRUE,FALSE)</formula>
+    <cfRule type="expression" dxfId="50" priority="75" stopIfTrue="1">
+      <formula>IF($U291="AAA",TRUE,FALSE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="64" priority="74" stopIfTrue="1">
+    <cfRule type="expression" dxfId="49" priority="74" stopIfTrue="1">
       <formula>IF($T291="AAA",TRUE,FALSE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="63" priority="75" stopIfTrue="1">
-      <formula>IF($U291="AAA",TRUE,FALSE)</formula>
+    <cfRule type="expression" dxfId="48" priority="73" stopIfTrue="1">
+      <formula>IF($AN65="AAA",TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F96:F106">
-    <cfRule type="expression" dxfId="62" priority="69" stopIfTrue="1">
+    <cfRule type="expression" dxfId="47" priority="69" stopIfTrue="1">
       <formula>IF(#REF!="AAA",TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F98:F106">
-    <cfRule type="expression" dxfId="61" priority="70" stopIfTrue="1">
+    <cfRule type="expression" dxfId="46" priority="72" stopIfTrue="1">
+      <formula>IF($U293="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="45" priority="71" stopIfTrue="1">
+      <formula>IF($T293="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="44" priority="70" stopIfTrue="1">
       <formula>IF($AN68="AAA",TRUE,FALSE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="60" priority="71" stopIfTrue="1">
-      <formula>IF($T293="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="59" priority="72" stopIfTrue="1">
-      <formula>IF($U293="AAA",TRUE,FALSE)</formula>
-    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G16:G26 G30:G41 G2:G12">
-    <cfRule type="cellIs" dxfId="58" priority="52" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="G2:G12 G16:G26 G30:G41">
+    <cfRule type="cellIs" dxfId="43" priority="52" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="57" priority="53" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="42" priority="53" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>#REF!</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G16:G28 G2:G12">
-    <cfRule type="cellIs" dxfId="56" priority="25" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="G2:G12 G16:G28">
+    <cfRule type="cellIs" dxfId="41" priority="25" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G30:G41 G16:G26 G2:G12">
-    <cfRule type="cellIs" dxfId="55" priority="51" operator="greaterThan">
+  <conditionalFormatting sqref="G30:G41 G2:G12 G16:G26">
+    <cfRule type="cellIs" dxfId="40" priority="51" operator="greaterThan">
       <formula>#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G43:G54 G30:G41 G56:G67">
-    <cfRule type="cellIs" dxfId="54" priority="42" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="39" priority="42" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G43:G54">
-    <cfRule type="cellIs" dxfId="53" priority="30" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="38" priority="33" stopIfTrue="1" operator="greaterThanOrEqual">
+      <formula>#REF!</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="37" priority="32" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="52" priority="31" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="36" priority="31" operator="greaterThan">
       <formula>#REF!</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="51" priority="32" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="35" priority="30" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="50" priority="33" stopIfTrue="1" operator="greaterThanOrEqual">
-      <formula>#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G53:G54">
-    <cfRule type="cellIs" dxfId="49" priority="16" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="34" priority="18" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>#REF!</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="48" priority="17" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="33" priority="17" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="47" priority="18" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="32" priority="16" operator="greaterThan">
       <formula>#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G56:G67">
-    <cfRule type="cellIs" dxfId="46" priority="43" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="31" priority="43" operator="greaterThan">
       <formula>#REF!</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="45" priority="44" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="30" priority="45" stopIfTrue="1" operator="greaterThanOrEqual">
+      <formula>#REF!</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="29" priority="44" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="44" priority="45" stopIfTrue="1" operator="greaterThanOrEqual">
-      <formula>#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G69:G80">
-    <cfRule type="cellIs" dxfId="43" priority="26" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="28" priority="26" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="27" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="27" priority="29" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>#REF!</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="41" priority="28" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="26" priority="28" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="29" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="25" priority="27" operator="greaterThan">
       <formula>#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G82:G92">
-    <cfRule type="cellIs" dxfId="39" priority="38" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="24" priority="40" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="38" priority="39" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="23" priority="41" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>#REF!</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="40" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="22" priority="39" operator="greaterThan">
+      <formula>#REF!</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="21" priority="38" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="36" priority="41" stopIfTrue="1" operator="greaterThanOrEqual">
-      <formula>#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G96:G106">
-    <cfRule type="cellIs" dxfId="35" priority="34" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="20" priority="37" stopIfTrue="1" operator="greaterThanOrEqual">
+      <formula>#REF!</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="19" priority="36" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="35" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="18" priority="35" operator="greaterThan">
       <formula>#REF!</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="36" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="17" priority="34" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="32" priority="37" stopIfTrue="1" operator="greaterThanOrEqual">
-      <formula>#REF!</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H81">
+    <cfRule type="cellIs" dxfId="16" priority="15" operator="greaterThan">
+      <formula>$H81</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I12 I53 K53 I66 K66">
-    <cfRule type="cellIs" dxfId="31" priority="59" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="15" priority="59" operator="greaterThan">
       <formula>$K12</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I26">
-    <cfRule type="cellIs" dxfId="30" priority="10" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="14" priority="10" operator="greaterThan">
       <formula>$K26</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I75">
-    <cfRule type="cellIs" dxfId="29" priority="60" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="13" priority="60" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I93:I94">
-    <cfRule type="cellIs" dxfId="28" priority="58" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="12" priority="58" operator="greaterThan">
       <formula>$K93</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I107">
-    <cfRule type="cellIs" dxfId="27" priority="57" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="11" priority="57" operator="greaterThan">
       <formula>$K107</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I109">
-    <cfRule type="cellIs" dxfId="26" priority="55" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="10" priority="55" operator="greaterThan">
       <formula>$K109</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J97">
-    <cfRule type="cellIs" dxfId="25" priority="62" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="9" priority="62" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J103">
-    <cfRule type="cellIs" dxfId="24" priority="61" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="8" priority="61" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="cellIs" dxfId="23" priority="13" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="7" priority="13" operator="greaterThan">
       <formula>$K12</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K26">
-    <cfRule type="cellIs" dxfId="22" priority="12" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="12" operator="greaterThan">
       <formula>$K26</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K41">
-    <cfRule type="cellIs" dxfId="21" priority="11" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="11" operator="greaterThan">
       <formula>$K41</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H81">
-    <cfRule type="cellIs" dxfId="20" priority="15" operator="greaterThan">
-      <formula>$H81</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="K93:K94">
-    <cfRule type="cellIs" dxfId="19" priority="14" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="4" priority="14" operator="greaterThan">
       <formula>$K93</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K104">
-    <cfRule type="cellIs" dxfId="18" priority="63" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="3" priority="63" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K107">
-    <cfRule type="cellIs" dxfId="17" priority="56" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="56" operator="greaterThan">
       <formula>$I107</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K109">
-    <cfRule type="cellIs" dxfId="16" priority="54" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="54" operator="greaterThan">
       <formula>$I109</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P37:P38">
-    <cfRule type="cellIs" dxfId="15" priority="64" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="64" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F57:F67">
-    <cfRule type="expression" dxfId="14" priority="92" stopIfTrue="1">
-      <formula>IF(#REF!="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="13" priority="93" stopIfTrue="1">
-      <formula>IF($AK29="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="12" priority="94" stopIfTrue="1">
-      <formula>IF($T255="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="11" priority="95" stopIfTrue="1">
-      <formula>IF($U255="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F69">
-    <cfRule type="expression" dxfId="10" priority="96" stopIfTrue="1">
-      <formula>IF($T268="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="9" priority="97" stopIfTrue="1">
-      <formula>IF($U268="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="8" priority="98" stopIfTrue="1">
-      <formula>IF($AJ43="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="7" priority="99" stopIfTrue="1">
-      <formula>IF($T268="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="6" priority="100" stopIfTrue="1">
-      <formula>IF($U268="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F70:F78">
-    <cfRule type="expression" dxfId="5" priority="101" stopIfTrue="1">
-      <formula>IF($AJ42="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="102" stopIfTrue="1">
-      <formula>IF($T267="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="3" priority="103" stopIfTrue="1">
-      <formula>IF($U267="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F82">
-    <cfRule type="expression" dxfId="2" priority="104" stopIfTrue="1">
-      <formula>IF($AJ53="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="105" stopIfTrue="1">
-      <formula>IF($T278="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="0" priority="106" stopIfTrue="1">
-      <formula>IF($U278="AAA",TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Twitter_Donnees.xlsx
+++ b/Twitter_Donnees.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\charl\Documents\Bourse\mon-projet-react\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F2C010BF-8BEA-491C-9EAA-C33992D3F922}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A385F3EE-A6B4-4069-81F9-93EE6B8FEA25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{197DE6B7-0A4B-4688-9519-B46A8B51F575}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="183">
   <si>
     <t>Colonne1</t>
   </si>
@@ -1249,7 +1249,7 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="130">
+  <cellXfs count="131">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1534,6 +1534,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="16" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="16" fontId="2" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -18536,8 +18537,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="91" t="s">
-        <v>0</v>
+      <c r="A1" s="130">
+        <v>46234</v>
       </c>
       <c r="B1" s="92" t="s">
         <v>1</v>

--- a/Twitter_Donnees.xlsx
+++ b/Twitter_Donnees.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Bourse\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2316D572-AC98-4AE9-A94C-A1A78820D100}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C379A925-1C94-4466-8D84-700308A296AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{CB1B49A7-9C46-47E8-A7CD-9AB6F7C19107}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="177">
   <si>
     <t>14/08/2026</t>
   </si>
@@ -344,34 +344,10 @@
     <t>PUBLICIS GRP</t>
   </si>
   <si>
-    <t>HO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">THALES </t>
-  </si>
-  <si>
-    <t>SOP</t>
-  </si>
-  <si>
-    <t>SOPRA STERIA GROUP</t>
-  </si>
-  <si>
     <t>ACA</t>
   </si>
   <si>
     <t>CREDIT AGRICOLE SA</t>
-  </si>
-  <si>
-    <t>SAF</t>
-  </si>
-  <si>
-    <t>SAFRAN</t>
-  </si>
-  <si>
-    <t>AIR</t>
-  </si>
-  <si>
-    <t>AIRBUS GROUP</t>
   </si>
   <si>
     <t xml:space="preserve">Etoiles </t>
@@ -393,18 +369,6 @@
   </si>
   <si>
     <t>IPSOS</t>
-  </si>
-  <si>
-    <t>MRN</t>
-  </si>
-  <si>
-    <t>MERSEN</t>
-  </si>
-  <si>
-    <t>SU</t>
-  </si>
-  <si>
-    <t>SCHNEIDER ELECTRIC</t>
   </si>
   <si>
     <t>Décote</t>
@@ -1556,7 +1520,963 @@
     <cellStyle name="Normal 4" xfId="3" xr:uid="{1BE76CE9-5C3F-452B-84A0-4586D845B2A6}"/>
     <cellStyle name="Pourcentage" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="215">
+  <dxfs count="158">
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="18"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="18"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2647,47 +3567,6 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
         <sz val="12"/>
         <color auto="1"/>
         <name val="Arial"/>
@@ -2719,7 +3598,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
+        <b/>
         <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
@@ -2728,16 +3607,16 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="8"/>
         <color auto="1"/>
         <name val="Arial"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
-          <bgColor indexed="43"/>
+          <bgColor indexed="41"/>
         </patternFill>
       </fill>
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -2745,11 +3624,11 @@
         <left style="thin">
           <color auto="1"/>
         </left>
-        <right style="thin">
-          <color auto="1"/>
+        <right style="medium">
+          <color indexed="64"/>
         </right>
-        <top style="thin">
-          <color auto="1"/>
+        <top style="medium">
+          <color indexed="64"/>
         </top>
         <bottom style="thin">
           <color auto="1"/>
@@ -2821,6 +3700,47 @@
       </fill>
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right style="thin">
           <color indexed="64"/>
@@ -2830,6 +3750,39 @@
         <vertical/>
         <horizontal/>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2883,46 +3836,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
       <numFmt numFmtId="167" formatCode="000000"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor indexed="9"/>
-        </patternFill>
-      </fill>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
@@ -2945,34 +3859,6 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="167" formatCode="000000"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
         <color auto="1"/>
         <name val="Arial"/>
         <family val="2"/>
@@ -3031,6 +3917,50 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="167" formatCode="000000"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor indexed="9"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
         <sz val="11"/>
         <color theme="1"/>
         <name val="Calibri"/>
@@ -3045,16 +3975,6 @@
         <bottom/>
         <vertical/>
         <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -3092,1482 +4012,6 @@
           <bgColor theme="9"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="18"/>
-      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -20564,18 +20008,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{744BE250-F264-4768-BE22-5662D7F7372D}" name="Hausses28826" displayName="Hausses28826" ref="A29:G40" totalsRowCount="1" headerRowDxfId="52" tableBorderDxfId="51">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{744BE250-F264-4768-BE22-5662D7F7372D}" name="Hausses28826" displayName="Hausses28826" ref="A29:G40" totalsRowCount="1" headerRowDxfId="157" tableBorderDxfId="156">
   <autoFilter ref="A29:G39" xr:uid="{744BE250-F264-4768-BE22-5662D7F7372D}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{C0860192-37DE-4F17-909A-295A14E1C4E9}" name="Position" dataDxfId="49" totalsRowDxfId="50"/>
-    <tableColumn id="2" xr3:uid="{E3572A17-96F7-4B0A-8E34-9B529DD87680}" name="Code" dataDxfId="47" totalsRowDxfId="48" dataCellStyle="Normal 2"/>
-    <tableColumn id="3" xr3:uid="{DC7FB505-4679-4E5F-9F6A-3F01DE92A850}" name="Marché" dataDxfId="45" totalsRowDxfId="46" dataCellStyle="Normal 2"/>
-    <tableColumn id="4" xr3:uid="{3A07F0B0-C50A-4C2D-93EF-1EA166F1D5B2}" name="Valeur" dataDxfId="43" totalsRowDxfId="44" dataCellStyle="Normal 2"/>
-    <tableColumn id="5" xr3:uid="{95915E51-EA38-4FCC-BAE3-D31D066F90F0}" name="Colonne3" dataDxfId="42" dataCellStyle="Normal 2"/>
-    <tableColumn id="6" xr3:uid="{2A6D4D7A-C8DB-429F-BE8E-5AD4EE05E407}" name="RECO" totalsRowLabel="Moyenne" dataDxfId="40" totalsRowDxfId="41" dataCellStyle="Normal 2">
+    <tableColumn id="1" xr3:uid="{C0860192-37DE-4F17-909A-295A14E1C4E9}" name="Position" dataDxfId="155" totalsRowDxfId="154"/>
+    <tableColumn id="2" xr3:uid="{E3572A17-96F7-4B0A-8E34-9B529DD87680}" name="Code" dataDxfId="153" totalsRowDxfId="152" dataCellStyle="Normal 2"/>
+    <tableColumn id="3" xr3:uid="{DC7FB505-4679-4E5F-9F6A-3F01DE92A850}" name="Marché" dataDxfId="151" totalsRowDxfId="150" dataCellStyle="Normal 2"/>
+    <tableColumn id="4" xr3:uid="{3A07F0B0-C50A-4C2D-93EF-1EA166F1D5B2}" name="Valeur" dataDxfId="149" totalsRowDxfId="148" dataCellStyle="Normal 2"/>
+    <tableColumn id="5" xr3:uid="{95915E51-EA38-4FCC-BAE3-D31D066F90F0}" name="Colonne3" dataDxfId="147" dataCellStyle="Normal 2"/>
+    <tableColumn id="6" xr3:uid="{2A6D4D7A-C8DB-429F-BE8E-5AD4EE05E407}" name="RECO" totalsRowLabel="Moyenne" dataDxfId="146" totalsRowDxfId="145" dataCellStyle="Normal 2">
       <calculatedColumnFormula>IFERROR(((VLOOKUP(B30,cours,7,FALSE))),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{A943ECBF-D5A8-4523-8079-6C4FD8A63D85}" name="Différence" totalsRowFunction="custom" dataDxfId="38" totalsRowDxfId="39" dataCellStyle="Normal 4">
+    <tableColumn id="7" xr3:uid="{A943ECBF-D5A8-4523-8079-6C4FD8A63D85}" name="Différence" totalsRowFunction="custom" dataDxfId="144" totalsRowDxfId="143" dataCellStyle="Normal 4">
       <calculatedColumnFormula>(F30/E30-1)</calculatedColumnFormula>
       <totalsRowFormula>AVERAGE(G30:G39)</totalsRowFormula>
     </tableColumn>
@@ -20585,73 +20029,73 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C5996414-920D-414D-8C5B-645CC9C7AB69}" name="Hausses38927" displayName="Hausses38927" ref="A42:G53" totalsRowShown="0" headerRowDxfId="37" tableBorderDxfId="36">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C5996414-920D-414D-8C5B-645CC9C7AB69}" name="Hausses38927" displayName="Hausses38927" ref="A42:G53" totalsRowShown="0" headerRowDxfId="142" tableBorderDxfId="141">
   <autoFilter ref="A42:G53" xr:uid="{C5996414-920D-414D-8C5B-645CC9C7AB69}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{FC5F0FE5-E484-4444-91D0-E82193591E6B}" name="Position" dataDxfId="35"/>
-    <tableColumn id="2" xr3:uid="{D8A35B94-7C62-4BF2-9D5B-EA9C8A074032}" name="Code" dataDxfId="34" dataCellStyle="Normal 2"/>
-    <tableColumn id="3" xr3:uid="{4A5C029B-DE4E-4957-8EF9-11F667A77972}" name="Marché" dataDxfId="33" dataCellStyle="Normal 2"/>
-    <tableColumn id="4" xr3:uid="{7D250ADA-6B3D-4735-BE65-99738108D11A}" name="Valeur" dataDxfId="32" dataCellStyle="Normal 2"/>
-    <tableColumn id="5" xr3:uid="{F7B3880F-AFCD-4A9E-BF75-A5AA9352095C}" name="Colonne8" dataDxfId="31" dataCellStyle="Normal 2"/>
-    <tableColumn id="6" xr3:uid="{B28A9DE3-ACE1-443B-9BF5-296AA2C7EB82}" name="RECO" dataDxfId="30" dataCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{6C89434B-4D1A-4039-A293-4BB040E7F83F}" name="Différence" dataDxfId="29" dataCellStyle="Normal 4"/>
+    <tableColumn id="1" xr3:uid="{FC5F0FE5-E484-4444-91D0-E82193591E6B}" name="Position" dataDxfId="140"/>
+    <tableColumn id="2" xr3:uid="{D8A35B94-7C62-4BF2-9D5B-EA9C8A074032}" name="Code" dataDxfId="139" dataCellStyle="Normal 2"/>
+    <tableColumn id="3" xr3:uid="{4A5C029B-DE4E-4957-8EF9-11F667A77972}" name="Marché" dataDxfId="138" dataCellStyle="Normal 2"/>
+    <tableColumn id="4" xr3:uid="{7D250ADA-6B3D-4735-BE65-99738108D11A}" name="Valeur" dataDxfId="137" dataCellStyle="Normal 2"/>
+    <tableColumn id="5" xr3:uid="{F7B3880F-AFCD-4A9E-BF75-A5AA9352095C}" name="Colonne8" dataDxfId="136" dataCellStyle="Normal 2"/>
+    <tableColumn id="6" xr3:uid="{B28A9DE3-ACE1-443B-9BF5-296AA2C7EB82}" name="RECO" dataDxfId="135" dataCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{6C89434B-4D1A-4039-A293-4BB040E7F83F}" name="Différence" dataDxfId="134" dataCellStyle="Normal 4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{1C43F6EA-7C90-410E-828F-47C3DDAEC980}" name="Hausses18622516529" displayName="Hausses18622516529" ref="A1:G12" totalsRowShown="0" headerRowDxfId="28" tableBorderDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{1C43F6EA-7C90-410E-828F-47C3DDAEC980}" name="Hausses18622516529" displayName="Hausses18622516529" ref="A1:G12" totalsRowShown="0" headerRowDxfId="133" tableBorderDxfId="132">
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{BE54938E-7A14-4A92-8F7F-601A700D7F5D}" name="31-juil" dataDxfId="26"/>
-    <tableColumn id="2" xr3:uid="{FEF859FC-046F-46D3-BFE5-FF67F6EF5908}" name="Code" dataDxfId="25" dataCellStyle="Normal 2"/>
-    <tableColumn id="3" xr3:uid="{0064B851-969D-4FBC-A8A1-799D30FF9E39}" name="Marché" dataDxfId="24" dataCellStyle="Normal 2"/>
-    <tableColumn id="4" xr3:uid="{9C54DC20-A97B-4321-B66D-2895703B8848}" name="Valeur" dataDxfId="23" dataCellStyle="Normal 2"/>
-    <tableColumn id="5" xr3:uid="{56AEDFFC-7DF2-4837-A9E4-C11E35DFB681}" name="Cours" dataDxfId="22" dataCellStyle="Normal 2"/>
-    <tableColumn id="6" xr3:uid="{CD7B1F5D-6EE7-4D23-9F2E-F3A153B4FEF7}" name="RECO" dataDxfId="21" dataCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{F7B37E98-9ABD-4503-A709-1C2138EA3B3A}" name="Différence" dataDxfId="20" dataCellStyle="Normal 4"/>
+    <tableColumn id="1" xr3:uid="{BE54938E-7A14-4A92-8F7F-601A700D7F5D}" name="31-juil" dataDxfId="131"/>
+    <tableColumn id="2" xr3:uid="{FEF859FC-046F-46D3-BFE5-FF67F6EF5908}" name="Code" dataDxfId="130" dataCellStyle="Normal 2"/>
+    <tableColumn id="3" xr3:uid="{0064B851-969D-4FBC-A8A1-799D30FF9E39}" name="Marché" dataDxfId="129" dataCellStyle="Normal 2"/>
+    <tableColumn id="4" xr3:uid="{9C54DC20-A97B-4321-B66D-2895703B8848}" name="Valeur" dataDxfId="128" dataCellStyle="Normal 2"/>
+    <tableColumn id="5" xr3:uid="{56AEDFFC-7DF2-4837-A9E4-C11E35DFB681}" name="Cours" dataDxfId="127" dataCellStyle="Normal 2"/>
+    <tableColumn id="6" xr3:uid="{CD7B1F5D-6EE7-4D23-9F2E-F3A153B4FEF7}" name="RECO" dataDxfId="126" dataCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{F7B37E98-9ABD-4503-A709-1C2138EA3B3A}" name="Différence" dataDxfId="125" dataCellStyle="Normal 4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{D92BAC71-B1DC-4BF3-AA7C-9B1962D46808}" name="Baisses18722616630" displayName="Baisses18722616630" ref="A15:E27" totalsRowShown="0" headerRowDxfId="19" tableBorderDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{D92BAC71-B1DC-4BF3-AA7C-9B1962D46808}" name="Baisses18722616630" displayName="Baisses18722616630" ref="A15:E27" totalsRowShown="0" headerRowDxfId="124" tableBorderDxfId="123">
   <autoFilter ref="A15:E27" xr:uid="{D92BAC71-B1DC-4BF3-AA7C-9B1962D46808}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{8DD859F8-734F-4CE9-BA57-056BC1E6D343}" name="Position" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{B50A516F-D64E-47C4-99F7-207649AEA279}" name="Code" dataDxfId="16" dataCellStyle="Normal 2"/>
-    <tableColumn id="3" xr3:uid="{6C9523B1-0F3E-49D8-AA4D-569C79CCA593}" name="Marché" dataDxfId="15" dataCellStyle="Normal 2"/>
-    <tableColumn id="4" xr3:uid="{CDAF6207-056D-49A6-B33D-DD8D78E817A2}" name="Valeur" dataDxfId="14" dataCellStyle="Normal 2"/>
-    <tableColumn id="5" xr3:uid="{A9322936-82F2-4F6B-A0A3-7E4D00A37DA9}" name="Colonne1" dataDxfId="13" dataCellStyle="Normal 2"/>
+    <tableColumn id="1" xr3:uid="{8DD859F8-734F-4CE9-BA57-056BC1E6D343}" name="Position" dataDxfId="122"/>
+    <tableColumn id="2" xr3:uid="{B50A516F-D64E-47C4-99F7-207649AEA279}" name="Code" dataDxfId="121" dataCellStyle="Normal 2"/>
+    <tableColumn id="3" xr3:uid="{6C9523B1-0F3E-49D8-AA4D-569C79CCA593}" name="Marché" dataDxfId="120" dataCellStyle="Normal 2"/>
+    <tableColumn id="4" xr3:uid="{CDAF6207-056D-49A6-B33D-DD8D78E817A2}" name="Valeur" dataDxfId="119" dataCellStyle="Normal 2"/>
+    <tableColumn id="5" xr3:uid="{A9322936-82F2-4F6B-A0A3-7E4D00A37DA9}" name="Colonne1" dataDxfId="118" dataCellStyle="Normal 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{A58F1CFF-EB70-4D81-ADE7-4C3EE777913F}" name="Hausses49022916731" displayName="Hausses49022916731" ref="A55:E66" totalsRowShown="0" headerRowDxfId="12" tableBorderDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{A58F1CFF-EB70-4D81-ADE7-4C3EE777913F}" name="Hausses49022916731" displayName="Hausses49022916731" ref="A55:E66" totalsRowShown="0" headerRowDxfId="117" tableBorderDxfId="116">
   <autoFilter ref="A55:E66" xr:uid="{A58F1CFF-EB70-4D81-ADE7-4C3EE777913F}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{499BCA9D-C177-41F8-BAB2-5175AF2BFC36}" name="Position" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{1FFC2203-925B-4B02-A9C7-75E78D774AD9}" name="Code" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{F0D2BA4D-1C1C-4E5A-A859-BF3836BD1687}" name="Marché" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{D2D19A82-C664-4DD1-A30A-100BC3886A0D}" name="Valeur" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{239F057B-8BA0-4A38-803A-9A2C1077A19D}" name="15-janv" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{499BCA9D-C177-41F8-BAB2-5175AF2BFC36}" name="Position" dataDxfId="115"/>
+    <tableColumn id="2" xr3:uid="{1FFC2203-925B-4B02-A9C7-75E78D774AD9}" name="Code" dataDxfId="114"/>
+    <tableColumn id="3" xr3:uid="{F0D2BA4D-1C1C-4E5A-A859-BF3836BD1687}" name="Marché" dataDxfId="113"/>
+    <tableColumn id="4" xr3:uid="{D2D19A82-C664-4DD1-A30A-100BC3886A0D}" name="Valeur" dataDxfId="112"/>
+    <tableColumn id="5" xr3:uid="{239F057B-8BA0-4A38-803A-9A2C1077A19D}" name="15-janv" dataDxfId="111"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{5404D9D9-C096-46CE-B6DD-5EED87505035}" name="Baisses29123016832" displayName="Baisses29123016832" ref="A68:E78" totalsRowShown="0" headerRowDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{5404D9D9-C096-46CE-B6DD-5EED87505035}" name="Baisses29123016832" displayName="Baisses29123016832" ref="A68:E78" totalsRowShown="0" headerRowDxfId="110">
   <autoFilter ref="A68:E78" xr:uid="{5404D9D9-C096-46CE-B6DD-5EED87505035}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{8E429DEE-7701-432C-B092-2B6F81594F0F}" name="Position" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{88039358-F85B-4347-9E38-727E03CED614}" name="Code" dataDxfId="3" dataCellStyle="Normal 2"/>
-    <tableColumn id="3" xr3:uid="{C034F66A-BD2F-44B0-B6AF-2101CB7578F2}" name="Marché" dataDxfId="2" dataCellStyle="Normal 2"/>
-    <tableColumn id="4" xr3:uid="{51440959-11F5-48BB-ADE4-5CFFC531A3A6}" name="Valeur" dataDxfId="1" dataCellStyle="Normal 2"/>
-    <tableColumn id="5" xr3:uid="{714D093F-51B8-4E43-A0D5-29CFB06B4880}" name="Colonne1" dataDxfId="0" dataCellStyle="Normal 2"/>
+    <tableColumn id="1" xr3:uid="{8E429DEE-7701-432C-B092-2B6F81594F0F}" name="Position" dataDxfId="109"/>
+    <tableColumn id="2" xr3:uid="{88039358-F85B-4347-9E38-727E03CED614}" name="Code" dataDxfId="108" dataCellStyle="Normal 2"/>
+    <tableColumn id="3" xr3:uid="{C034F66A-BD2F-44B0-B6AF-2101CB7578F2}" name="Marché" dataDxfId="107" dataCellStyle="Normal 2"/>
+    <tableColumn id="4" xr3:uid="{51440959-11F5-48BB-ADE4-5CFFC531A3A6}" name="Valeur" dataDxfId="106" dataCellStyle="Normal 2"/>
+    <tableColumn id="5" xr3:uid="{714D093F-51B8-4E43-A0D5-29CFB06B4880}" name="Colonne1" dataDxfId="105" dataCellStyle="Normal 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -22260,18 +21704,10 @@
       <c r="A56" s="94">
         <v>1</v>
       </c>
-      <c r="B56" s="71" t="s">
-        <v>94</v>
-      </c>
-      <c r="C56" s="72" t="s">
-        <v>12</v>
-      </c>
-      <c r="D56" s="71" t="s">
-        <v>95</v>
-      </c>
-      <c r="E56" s="95">
-        <v>112.1</v>
-      </c>
+      <c r="B56" s="71"/>
+      <c r="C56" s="72"/>
+      <c r="D56" s="71"/>
+      <c r="E56" s="95"/>
       <c r="F56" s="14">
         <v>112.1</v>
       </c>
@@ -22284,18 +21720,10 @@
       <c r="A57" s="96">
         <v>2</v>
       </c>
-      <c r="B57" s="77" t="s">
-        <v>96</v>
-      </c>
-      <c r="C57" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="D57" s="77" t="s">
-        <v>97</v>
-      </c>
-      <c r="E57" s="95">
-        <v>101.8</v>
-      </c>
+      <c r="B57" s="77"/>
+      <c r="C57" s="24"/>
+      <c r="D57" s="77"/>
+      <c r="E57" s="95"/>
       <c r="F57" s="14">
         <v>101.8</v>
       </c>
@@ -22309,18 +21737,10 @@
       <c r="A58" s="94">
         <v>3</v>
       </c>
-      <c r="B58" s="71" t="s">
-        <v>18</v>
-      </c>
-      <c r="C58" s="72" t="s">
-        <v>12</v>
-      </c>
-      <c r="D58" s="71" t="s">
-        <v>19</v>
-      </c>
-      <c r="E58" s="95">
-        <v>70.86</v>
-      </c>
+      <c r="B58" s="71"/>
+      <c r="C58" s="72"/>
+      <c r="D58" s="71"/>
+      <c r="E58" s="95"/>
       <c r="F58" s="14">
         <v>70.86</v>
       </c>
@@ -22335,18 +21755,10 @@
       <c r="A59" s="96">
         <v>4</v>
       </c>
-      <c r="B59" s="77" t="s">
-        <v>91</v>
-      </c>
-      <c r="C59" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="D59" s="77" t="s">
-        <v>92</v>
-      </c>
-      <c r="E59" s="95">
-        <v>75.78</v>
-      </c>
+      <c r="B59" s="77"/>
+      <c r="C59" s="24"/>
+      <c r="D59" s="77"/>
+      <c r="E59" s="95"/>
       <c r="F59" s="14">
         <v>75.78</v>
       </c>
@@ -22361,18 +21773,10 @@
       <c r="A60" s="94">
         <v>5</v>
       </c>
-      <c r="B60" s="71" t="s">
-        <v>98</v>
-      </c>
-      <c r="C60" s="72" t="s">
-        <v>12</v>
-      </c>
-      <c r="D60" s="71" t="s">
-        <v>99</v>
-      </c>
-      <c r="E60" s="95">
-        <v>270.39999999999998</v>
-      </c>
+      <c r="B60" s="71"/>
+      <c r="C60" s="72"/>
+      <c r="D60" s="71"/>
+      <c r="E60" s="95"/>
       <c r="F60" s="14">
         <v>270.39999999999998</v>
       </c>
@@ -22387,18 +21791,10 @@
       <c r="A61" s="96">
         <v>6</v>
       </c>
-      <c r="B61" s="77" t="s">
-        <v>100</v>
-      </c>
-      <c r="C61" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="D61" s="77" t="s">
-        <v>101</v>
-      </c>
-      <c r="E61" s="95">
-        <v>184.9</v>
-      </c>
+      <c r="B61" s="77"/>
+      <c r="C61" s="24"/>
+      <c r="D61" s="77"/>
+      <c r="E61" s="95"/>
       <c r="F61" s="14">
         <v>184.9</v>
       </c>
@@ -22413,18 +21809,10 @@
       <c r="A62" s="94">
         <v>7</v>
       </c>
-      <c r="B62" s="71" t="s">
-        <v>21</v>
-      </c>
-      <c r="C62" s="72" t="s">
-        <v>12</v>
-      </c>
-      <c r="D62" s="71" t="s">
-        <v>22</v>
-      </c>
-      <c r="E62" s="95">
-        <v>8.125</v>
-      </c>
+      <c r="B62" s="71"/>
+      <c r="C62" s="72"/>
+      <c r="D62" s="71"/>
+      <c r="E62" s="95"/>
       <c r="F62" s="14">
         <v>8.125</v>
       </c>
@@ -22438,18 +21826,10 @@
       <c r="A63" s="96">
         <v>8</v>
       </c>
-      <c r="B63" s="77" t="s">
-        <v>102</v>
-      </c>
-      <c r="C63" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="D63" s="77" t="s">
-        <v>103</v>
-      </c>
-      <c r="E63" s="95">
-        <v>20.2</v>
-      </c>
+      <c r="B63" s="77"/>
+      <c r="C63" s="24"/>
+      <c r="D63" s="77"/>
+      <c r="E63" s="95"/>
       <c r="F63" s="14">
         <v>20.2</v>
       </c>
@@ -22463,18 +21843,10 @@
       <c r="A64" s="94">
         <v>9</v>
       </c>
-      <c r="B64" s="71" t="s">
-        <v>104</v>
-      </c>
-      <c r="C64" s="72" t="s">
-        <v>12</v>
-      </c>
-      <c r="D64" s="71" t="s">
-        <v>105</v>
-      </c>
-      <c r="E64" s="95">
-        <v>360.5</v>
-      </c>
+      <c r="B64" s="71"/>
+      <c r="C64" s="72"/>
+      <c r="D64" s="71"/>
+      <c r="E64" s="95"/>
       <c r="F64" s="14">
         <v>360.5</v>
       </c>
@@ -22488,18 +21860,10 @@
       <c r="A65" s="96">
         <v>10</v>
       </c>
-      <c r="B65" s="77" t="s">
-        <v>106</v>
-      </c>
-      <c r="C65" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="D65" s="77" t="s">
-        <v>107</v>
-      </c>
-      <c r="E65" s="95">
-        <v>215.4</v>
-      </c>
+      <c r="B65" s="77"/>
+      <c r="C65" s="24"/>
+      <c r="D65" s="77"/>
+      <c r="E65" s="95"/>
       <c r="F65" s="14">
         <v>215.4</v>
       </c>
@@ -22566,25 +21930,17 @@
         <v>6</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
     </row>
     <row r="69" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A69" s="70">
         <v>1</v>
       </c>
-      <c r="B69" s="71" t="s">
-        <v>96</v>
-      </c>
-      <c r="C69" s="72" t="s">
-        <v>12</v>
-      </c>
-      <c r="D69" s="71" t="s">
-        <v>97</v>
-      </c>
-      <c r="E69" s="85">
-        <v>101.8</v>
-      </c>
+      <c r="B69" s="71"/>
+      <c r="C69" s="72"/>
+      <c r="D69" s="71"/>
+      <c r="E69" s="85"/>
       <c r="F69" s="14">
         <v>101.8</v>
       </c>
@@ -22597,18 +21953,10 @@
       <c r="A70" s="76">
         <v>2</v>
       </c>
-      <c r="B70" s="77" t="s">
-        <v>100</v>
-      </c>
-      <c r="C70" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="D70" s="77" t="s">
-        <v>101</v>
-      </c>
-      <c r="E70" s="85">
-        <v>184.9</v>
-      </c>
+      <c r="B70" s="77"/>
+      <c r="C70" s="24"/>
+      <c r="D70" s="77"/>
+      <c r="E70" s="85"/>
       <c r="F70" s="14">
         <v>184.9</v>
       </c>
@@ -22623,18 +21971,10 @@
       <c r="A71" s="70">
         <v>3</v>
       </c>
-      <c r="B71" s="71" t="s">
-        <v>21</v>
-      </c>
-      <c r="C71" s="72" t="s">
-        <v>12</v>
-      </c>
-      <c r="D71" s="71" t="s">
-        <v>22</v>
-      </c>
-      <c r="E71" s="85">
-        <v>8.125</v>
-      </c>
+      <c r="B71" s="71"/>
+      <c r="C71" s="72"/>
+      <c r="D71" s="71"/>
+      <c r="E71" s="85"/>
       <c r="F71" s="14">
         <v>8.125</v>
       </c>
@@ -22649,18 +21989,10 @@
       <c r="A72" s="76">
         <v>4</v>
       </c>
-      <c r="B72" s="77" t="s">
-        <v>109</v>
-      </c>
-      <c r="C72" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="D72" s="77" t="s">
-        <v>110</v>
-      </c>
-      <c r="E72" s="85">
-        <v>74</v>
-      </c>
+      <c r="B72" s="77"/>
+      <c r="C72" s="24"/>
+      <c r="D72" s="77"/>
+      <c r="E72" s="85"/>
       <c r="F72" s="14">
         <v>74</v>
       </c>
@@ -22675,18 +22007,10 @@
       <c r="A73" s="70">
         <v>5</v>
       </c>
-      <c r="B73" s="71" t="s">
-        <v>111</v>
-      </c>
-      <c r="C73" s="72" t="s">
-        <v>12</v>
-      </c>
-      <c r="D73" s="71" t="s">
-        <v>112</v>
-      </c>
-      <c r="E73" s="85">
-        <v>51.75</v>
-      </c>
+      <c r="B73" s="71"/>
+      <c r="C73" s="72"/>
+      <c r="D73" s="71"/>
+      <c r="E73" s="85"/>
       <c r="F73" s="14">
         <v>51.75</v>
       </c>
@@ -22701,18 +22025,10 @@
       <c r="A74" s="76">
         <v>6</v>
       </c>
-      <c r="B74" s="77" t="s">
-        <v>113</v>
-      </c>
-      <c r="C74" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="D74" s="77" t="s">
-        <v>114</v>
-      </c>
-      <c r="E74" s="85">
-        <v>39.380000000000003</v>
-      </c>
+      <c r="B74" s="77"/>
+      <c r="C74" s="24"/>
+      <c r="D74" s="77"/>
+      <c r="E74" s="85"/>
       <c r="F74" s="14">
         <v>39.380000000000003</v>
       </c>
@@ -22727,18 +22043,10 @@
       <c r="A75" s="70">
         <v>7</v>
       </c>
-      <c r="B75" s="71" t="s">
-        <v>115</v>
-      </c>
-      <c r="C75" s="72" t="s">
-        <v>12</v>
-      </c>
-      <c r="D75" s="71" t="s">
-        <v>116</v>
-      </c>
-      <c r="E75" s="85">
-        <v>40.92</v>
-      </c>
+      <c r="B75" s="71"/>
+      <c r="C75" s="72"/>
+      <c r="D75" s="71"/>
+      <c r="E75" s="85"/>
       <c r="F75" s="14">
         <v>40.92</v>
       </c>
@@ -22753,18 +22061,10 @@
       <c r="A76" s="76">
         <v>8</v>
       </c>
-      <c r="B76" s="77" t="s">
-        <v>16</v>
-      </c>
-      <c r="C76" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D76" s="77" t="s">
-        <v>17</v>
-      </c>
-      <c r="E76" s="85">
-        <v>5.92</v>
-      </c>
+      <c r="B76" s="77"/>
+      <c r="C76" s="24"/>
+      <c r="D76" s="77"/>
+      <c r="E76" s="85"/>
       <c r="F76" s="14">
         <v>5.92</v>
       </c>
@@ -22779,18 +22079,10 @@
       <c r="A77" s="70">
         <v>9</v>
       </c>
-      <c r="B77" s="71" t="s">
-        <v>117</v>
-      </c>
-      <c r="C77" s="72" t="s">
-        <v>12</v>
-      </c>
-      <c r="D77" s="71" t="s">
-        <v>118</v>
-      </c>
-      <c r="E77" s="85">
-        <v>306.39999999999998</v>
-      </c>
+      <c r="B77" s="71"/>
+      <c r="C77" s="72"/>
+      <c r="D77" s="71"/>
+      <c r="E77" s="85"/>
       <c r="F77" s="14">
         <v>306.39999999999998</v>
       </c>
@@ -22805,18 +22097,10 @@
       <c r="A78" s="86">
         <v>10</v>
       </c>
-      <c r="B78" s="87" t="s">
-        <v>18</v>
-      </c>
-      <c r="C78" s="88" t="s">
-        <v>12</v>
-      </c>
-      <c r="D78" s="87" t="s">
-        <v>19</v>
-      </c>
-      <c r="E78" s="89">
-        <v>70.86</v>
-      </c>
+      <c r="B78" s="87"/>
+      <c r="C78" s="88"/>
+      <c r="D78" s="87"/>
+      <c r="E78" s="89"/>
       <c r="F78" s="14">
         <v>70.86</v>
       </c>
@@ -22848,10 +22132,10 @@
         <v>32</v>
       </c>
       <c r="B81" s="65" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="C81" s="66" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="D81" s="66" t="s">
         <v>3</v>
@@ -23061,13 +22345,13 @@
         <v>32</v>
       </c>
       <c r="B95" s="65" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="C95" s="66" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="D95" s="67" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="E95" s="67" t="s">
         <v>4</v>
@@ -23079,7 +22363,7 @@
         <v>6</v>
       </c>
       <c r="H95" s="6" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="I95" s="60"/>
       <c r="J95" s="61"/>
@@ -23324,7 +22608,7 @@
   <sheetData>
     <row r="1" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="128" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -23336,13 +22620,13 @@
         <v>3</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="H1" s="6" t="s">
         <v>7</v>
@@ -23356,7 +22640,7 @@
       <c r="U1" s="11"/>
       <c r="V1" s="11"/>
       <c r="W1" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.45">
@@ -23364,13 +22648,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C2" s="10" t="s">
         <v>12</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="E2" s="13">
         <v>43.12</v>
@@ -23400,13 +22684,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="C3" s="10" t="s">
         <v>12</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="E3" s="13">
         <v>0.21</v>
@@ -23462,13 +22746,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="E5" s="13">
         <v>12.188000000000001</v>
@@ -23524,13 +22808,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="C7" s="10" t="s">
         <v>12</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="E7" s="13">
         <v>28.52</v>
@@ -23555,13 +22839,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="C8" s="10" t="s">
         <v>12</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="E8" s="13">
         <v>22</v>
@@ -23586,13 +22870,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="C9" s="10" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="E9" s="13">
         <v>0.24199999999999999</v>
@@ -23617,13 +22901,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>12</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="E10" s="13">
         <v>1.88</v>
@@ -23648,13 +22932,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>12</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="E11" s="13">
         <v>158.6</v>
@@ -23713,7 +22997,7 @@
     </row>
     <row r="15" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>1</v>
@@ -23725,13 +23009,13 @@
         <v>3</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>4</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>33</v>
@@ -23743,13 +23027,13 @@
         <v>1</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="C16" s="10" t="s">
         <v>12</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="E16" s="13">
         <v>1.5960000000000001</v>
@@ -23795,13 +23079,13 @@
         <v>3</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="C18" s="10" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="E18" s="13">
         <v>166.7</v>
@@ -23822,13 +23106,13 @@
         <v>4</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="C19" s="10" t="s">
         <v>12</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="E19" s="13">
         <v>1.8560000000000001</v>
@@ -23848,13 +23132,13 @@
         <v>5</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="C20" s="10" t="s">
         <v>12</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="E20" s="13">
         <v>35.74</v>
@@ -23875,13 +23159,13 @@
         <v>6</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="C21" s="10" t="s">
         <v>12</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="E21" s="13">
         <v>2.35</v>
@@ -23901,13 +23185,13 @@
         <v>7</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="C22" s="10" t="s">
         <v>12</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="E22" s="13">
         <v>32.75</v>
@@ -23927,13 +23211,13 @@
         <v>8</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="C23" s="10" t="s">
         <v>12</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="E23" s="13">
         <v>6.4850000000000003</v>
@@ -23953,13 +23237,13 @@
         <v>9</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="C24" s="10" t="s">
         <v>12</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="E24" s="13">
         <v>4.9710000000000001</v>
@@ -23979,13 +23263,13 @@
         <v>10</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="C25" s="10" t="s">
         <v>12</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="E25" s="13">
         <v>46.52</v>
@@ -24042,7 +23326,7 @@
     </row>
     <row r="29" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A29" s="2" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>1</v>
@@ -24054,13 +23338,13 @@
         <v>3</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>4</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="H29" s="6" t="s">
         <v>54</v>
@@ -24071,13 +23355,13 @@
         <v>1</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="C30" s="10" t="s">
         <v>56</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="E30" s="13">
         <v>21</v>
@@ -24096,13 +23380,13 @@
         <v>2</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="C31" s="10" t="s">
         <v>56</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="E31" s="13">
         <v>0.32500000000000001</v>
@@ -24121,13 +23405,13 @@
         <v>3</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="C32" s="10" t="s">
         <v>56</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="E32" s="13">
         <v>1.53</v>
@@ -24146,13 +23430,13 @@
         <v>4</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="C33" s="10" t="s">
         <v>56</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="E33" s="13">
         <v>2E-3</v>
@@ -24171,13 +23455,13 @@
         <v>5</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="C34" s="10" t="s">
         <v>56</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="E34" s="13">
         <v>6.72</v>
@@ -24196,13 +23480,13 @@
         <v>6</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="C35" s="10" t="s">
         <v>56</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="E35" s="13">
         <v>3.88</v>
@@ -24221,13 +23505,13 @@
         <v>7</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="C36" s="10" t="s">
         <v>56</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="E36" s="13">
         <v>6.04</v>
@@ -24246,13 +23530,13 @@
         <v>8</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="C37" s="10" t="s">
         <v>56</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="E37" s="13">
         <v>8.26</v>
@@ -24298,13 +23582,13 @@
         <v>10</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="C39" s="10" t="s">
         <v>56</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="E39" s="13">
         <v>5.0000000000000001E-3</v>
@@ -24344,7 +23628,7 @@
     </row>
     <row r="42" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A42" s="2" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>1</v>
@@ -24356,13 +23640,13 @@
         <v>3</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="F42" s="4" t="s">
         <v>4</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="H42" s="6" t="s">
         <v>76</v>
@@ -24573,7 +23857,7 @@
     </row>
     <row r="55" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A55" s="2" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>1</v>
@@ -24585,13 +23869,13 @@
         <v>3</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="F55" s="129" t="s">
         <v>4</v>
       </c>
       <c r="G55" s="130" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="H55" s="6" t="s">
         <v>93</v>
@@ -24818,7 +24102,7 @@
     </row>
     <row r="68" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A68" s="2" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>1</v>
@@ -24830,16 +24114,16 @@
         <v>3</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="F68" s="129" t="s">
         <v>4</v>
       </c>
       <c r="G68" s="130" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="I68" s="7"/>
     </row>
@@ -24848,13 +24132,13 @@
         <v>1</v>
       </c>
       <c r="B69" s="48" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C69" s="42" t="s">
         <v>12</v>
       </c>
       <c r="D69" s="48" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E69" s="127">
         <v>75.099999999999994</v>
@@ -24929,13 +24213,13 @@
         <v>4</v>
       </c>
       <c r="B72" s="48" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C72" s="42" t="s">
         <v>12</v>
       </c>
       <c r="D72" s="48" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="E72" s="127">
         <v>47.4</v>
@@ -24956,13 +24240,13 @@
         <v>5</v>
       </c>
       <c r="B73" s="48" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="C73" s="42" t="s">
         <v>12</v>
       </c>
       <c r="D73" s="48" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="E73" s="127">
         <v>31.3</v>
@@ -24983,13 +24267,13 @@
         <v>6</v>
       </c>
       <c r="B74" s="48" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="C74" s="42" t="s">
         <v>12</v>
       </c>
       <c r="D74" s="48" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="E74" s="127">
         <v>13.58</v>
@@ -25038,13 +24322,13 @@
         <v>8</v>
       </c>
       <c r="B76" s="48" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="C76" s="42" t="s">
         <v>12</v>
       </c>
       <c r="D76" s="48" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="E76" s="127">
         <v>58.25</v>
@@ -25065,13 +24349,13 @@
         <v>9</v>
       </c>
       <c r="B77" s="48" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C77" s="42" t="s">
         <v>12</v>
       </c>
       <c r="D77" s="48" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E77" s="127">
         <v>19.274999999999999</v>
@@ -25092,13 +24376,13 @@
         <v>10</v>
       </c>
       <c r="B78" s="48" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="C78" s="42" t="s">
         <v>12</v>
       </c>
       <c r="D78" s="48" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="E78" s="127">
         <v>102.5</v>
@@ -25411,443 +24695,429 @@
       <c r="D111" s="54"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B56:B65">
+    <cfRule type="expression" dxfId="104" priority="5" stopIfTrue="1">
+      <formula>IF(AO56&gt;0,TRUE,FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B69:B78">
+    <cfRule type="expression" dxfId="103" priority="3" stopIfTrue="1">
+      <formula>IF(AO69&gt;0,TRUE,FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B81">
-    <cfRule type="expression" dxfId="212" priority="107" stopIfTrue="1">
+    <cfRule type="expression" dxfId="102" priority="107" stopIfTrue="1">
       <formula>IF(AN62&gt;0,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B82:B91">
-    <cfRule type="expression" dxfId="211" priority="66" stopIfTrue="1">
+    <cfRule type="expression" dxfId="101" priority="66" stopIfTrue="1">
       <formula>IF(AL82&gt;0,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B92">
-    <cfRule type="expression" dxfId="210" priority="103" stopIfTrue="1">
+    <cfRule type="expression" dxfId="100" priority="103" stopIfTrue="1">
       <formula>IF(AL91&gt;0,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B95">
-    <cfRule type="expression" dxfId="209" priority="106" stopIfTrue="1">
+    <cfRule type="expression" dxfId="99" priority="106" stopIfTrue="1">
       <formula>IF(AN75&gt;0,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B96:B105">
-    <cfRule type="expression" dxfId="208" priority="64" stopIfTrue="1">
+    <cfRule type="expression" dxfId="98" priority="64" stopIfTrue="1">
       <formula>IF(AO96&gt;0,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B106">
-    <cfRule type="expression" dxfId="207" priority="104" stopIfTrue="1">
+    <cfRule type="expression" dxfId="97" priority="104" stopIfTrue="1">
       <formula>IF(AN104&gt;0,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B107">
-    <cfRule type="expression" dxfId="206" priority="105" stopIfTrue="1">
+    <cfRule type="expression" dxfId="96" priority="105" stopIfTrue="1">
       <formula>IF(AN104&gt;0,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="D56:D65">
+    <cfRule type="expression" dxfId="95" priority="4" stopIfTrue="1">
+      <formula>IF(AQ56&gt;0,TRUE,FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D69:D78">
+    <cfRule type="expression" dxfId="94" priority="2" stopIfTrue="1">
+      <formula>IF(AQ69&gt;0,TRUE,FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="D82:D91">
-    <cfRule type="expression" dxfId="203" priority="65" stopIfTrue="1">
+    <cfRule type="expression" dxfId="93" priority="65" stopIfTrue="1">
       <formula>IF(AN82&gt;0,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D96:D105">
-    <cfRule type="expression" dxfId="202" priority="63" stopIfTrue="1">
+    <cfRule type="expression" dxfId="92" priority="63" stopIfTrue="1">
       <formula>IF(AQ96&gt;0,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F11 F16:F25">
+    <cfRule type="expression" dxfId="91" priority="14" stopIfTrue="1">
+      <formula>IF($U200="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="90" priority="12" stopIfTrue="1">
+      <formula>IF($AN1048554="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="89" priority="13" stopIfTrue="1">
+      <formula>IF($T200="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="88" priority="9" stopIfTrue="1">
+      <formula>IF(#REF!="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="87" priority="10" stopIfTrue="1">
+      <formula>IF($T200="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="86" priority="11" stopIfTrue="1">
+      <formula>IF($U200="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F30:F39">
+    <cfRule type="expression" dxfId="85" priority="39" stopIfTrue="1">
+      <formula>IF($T230="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="84" priority="35" stopIfTrue="1">
+      <formula>IF(#REF!="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="83" priority="36" stopIfTrue="1">
+      <formula>IF($T230="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="82" priority="37" stopIfTrue="1">
+      <formula>IF($U230="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="81" priority="38" stopIfTrue="1">
+      <formula>IF($AN5="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="80" priority="40" stopIfTrue="1">
+      <formula>IF($U230="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F43:F52">
+    <cfRule type="expression" dxfId="79" priority="46" stopIfTrue="1">
+      <formula>IF($U242="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="78" priority="45" stopIfTrue="1">
+      <formula>IF($T242="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="77" priority="44" stopIfTrue="1">
+      <formula>IF($AN17="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="76" priority="41" stopIfTrue="1">
+      <formula>IF(#REF!="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="75" priority="42" stopIfTrue="1">
+      <formula>IF($T242="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="74" priority="43" stopIfTrue="1">
+      <formula>IF($U242="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F56">
+    <cfRule type="expression" dxfId="73" priority="32" stopIfTrue="1">
+      <formula>IF($AN28="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="72" priority="33" stopIfTrue="1">
+      <formula>IF($T254="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="71" priority="34" stopIfTrue="1">
+      <formula>IF($U254="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F56:F67">
+    <cfRule type="expression" dxfId="70" priority="31" stopIfTrue="1">
+      <formula>IF(#REF!="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F57:F67">
+    <cfRule type="expression" dxfId="69" priority="47" stopIfTrue="1">
+      <formula>IF($AK29="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="68" priority="49" stopIfTrue="1">
+      <formula>IF($U255="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="67" priority="48" stopIfTrue="1">
+      <formula>IF($T255="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F69">
+    <cfRule type="expression" dxfId="66" priority="54" stopIfTrue="1">
+      <formula>IF($U268="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="65" priority="53" stopIfTrue="1">
+      <formula>IF($T268="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="64" priority="52" stopIfTrue="1">
+      <formula>IF($AJ43="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="63" priority="50" stopIfTrue="1">
+      <formula>IF($T268="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="62" priority="51" stopIfTrue="1">
+      <formula>IF($U268="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F69:F78">
+    <cfRule type="expression" dxfId="61" priority="1" stopIfTrue="1">
+      <formula>IF(#REF!="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F70:F78">
+    <cfRule type="expression" dxfId="60" priority="57" stopIfTrue="1">
+      <formula>IF($U267="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="59" priority="55" stopIfTrue="1">
+      <formula>IF($AJ42="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="58" priority="56" stopIfTrue="1">
+      <formula>IF($T267="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F82">
-    <cfRule type="expression" dxfId="167" priority="163" stopIfTrue="1">
+    <cfRule type="expression" dxfId="57" priority="161" stopIfTrue="1">
+      <formula>IF($AJ53="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="56" priority="163" stopIfTrue="1">
       <formula>IF($U278="AAA",TRUE,FALSE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="166" priority="161" stopIfTrue="1">
-      <formula>IF($AJ53="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="165" priority="162" stopIfTrue="1">
+    <cfRule type="expression" dxfId="55" priority="162" stopIfTrue="1">
       <formula>IF($T278="AAA",TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F82:F91">
-    <cfRule type="expression" dxfId="164" priority="122" stopIfTrue="1">
+    <cfRule type="expression" dxfId="54" priority="122" stopIfTrue="1">
       <formula>IF(#REF!="AAA",TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F83:F91">
-    <cfRule type="expression" dxfId="163" priority="125" stopIfTrue="1">
+    <cfRule type="expression" dxfId="53" priority="125" stopIfTrue="1">
       <formula>IF($U279="AAA",TRUE,FALSE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="162" priority="123" stopIfTrue="1">
+    <cfRule type="expression" dxfId="52" priority="124" stopIfTrue="1">
+      <formula>IF($T279="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="51" priority="123" stopIfTrue="1">
       <formula>IF($AN55="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="161" priority="124" stopIfTrue="1">
-      <formula>IF($T279="AAA",TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F96:F97">
-    <cfRule type="expression" dxfId="160" priority="131" stopIfTrue="1">
+    <cfRule type="expression" dxfId="50" priority="132" stopIfTrue="1">
+      <formula>IF($U291="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="49" priority="131" stopIfTrue="1">
       <formula>IF($T291="AAA",TRUE,FALSE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="159" priority="132" stopIfTrue="1">
-      <formula>IF($U291="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="158" priority="130" stopIfTrue="1">
+    <cfRule type="expression" dxfId="48" priority="130" stopIfTrue="1">
       <formula>IF($AN65="AAA",TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F96:F106">
-    <cfRule type="expression" dxfId="157" priority="126" stopIfTrue="1">
+    <cfRule type="expression" dxfId="47" priority="126" stopIfTrue="1">
       <formula>IF(#REF!="AAA",TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F98:F106">
-    <cfRule type="expression" dxfId="156" priority="127" stopIfTrue="1">
+    <cfRule type="expression" dxfId="46" priority="128" stopIfTrue="1">
+      <formula>IF($T293="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="45" priority="129" stopIfTrue="1">
+      <formula>IF($U293="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="44" priority="127" stopIfTrue="1">
       <formula>IF($AN68="AAA",TRUE,FALSE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="155" priority="128" stopIfTrue="1">
-      <formula>IF($T293="AAA",TRUE,FALSE)</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G12 G16:G26 G30:G41">
+    <cfRule type="cellIs" dxfId="43" priority="30" stopIfTrue="1" operator="greaterThanOrEqual">
+      <formula>#REF!</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="154" priority="129" stopIfTrue="1">
-      <formula>IF($U293="AAA",TRUE,FALSE)</formula>
+    <cfRule type="cellIs" dxfId="42" priority="29" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G80">
-    <cfRule type="cellIs" dxfId="138" priority="86" stopIfTrue="1" operator="greaterThanOrEqual">
+  <conditionalFormatting sqref="G2:G12 G16:G28">
+    <cfRule type="cellIs" dxfId="41" priority="15" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G30:G41 G2:G12 G16:G26">
+    <cfRule type="cellIs" dxfId="40" priority="28" operator="greaterThan">
       <formula>#REF!</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="137" priority="84" operator="greaterThan">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G43:G54 G30:G41 G56:G67">
+    <cfRule type="cellIs" dxfId="39" priority="24" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G43:G54">
+    <cfRule type="cellIs" dxfId="38" priority="20" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="37" priority="21" operator="greaterThan">
       <formula>#REF!</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="136" priority="83" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="36" priority="22" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="135" priority="85" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="35" priority="23" stopIfTrue="1" operator="greaterThanOrEqual">
+      <formula>#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G53:G54">
+    <cfRule type="cellIs" dxfId="34" priority="6" operator="greaterThan">
+      <formula>#REF!</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="33" priority="7" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="32" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
+      <formula>#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G56:G67">
+    <cfRule type="cellIs" dxfId="31" priority="25" operator="greaterThan">
+      <formula>#REF!</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="30" priority="26" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="29" priority="27" stopIfTrue="1" operator="greaterThanOrEqual">
+      <formula>#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G69:G80">
+    <cfRule type="cellIs" dxfId="28" priority="17" operator="greaterThan">
+      <formula>#REF!</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="27" priority="18" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="26" priority="19" stopIfTrue="1" operator="greaterThanOrEqual">
+      <formula>#REF!</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="25" priority="16" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G82:G92">
-    <cfRule type="cellIs" dxfId="134" priority="97" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="24" priority="96" operator="greaterThan">
+      <formula>#REF!</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="23" priority="95" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="133" priority="96" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="22" priority="98" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>#REF!</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="132" priority="98" stopIfTrue="1" operator="greaterThanOrEqual">
-      <formula>#REF!</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="131" priority="95" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="21" priority="97" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G96:G106">
-    <cfRule type="cellIs" dxfId="130" priority="94" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="20" priority="94" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>#REF!</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="129" priority="93" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="19" priority="93" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="128" priority="92" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="18" priority="92" operator="greaterThan">
       <formula>#REF!</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="127" priority="91" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="17" priority="91" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H81">
-    <cfRule type="cellIs" dxfId="126" priority="72" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="16" priority="72" operator="greaterThan">
       <formula>$H81</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I12 I53 K53 I66 K66">
-    <cfRule type="cellIs" dxfId="125" priority="116" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="15" priority="116" operator="greaterThan">
       <formula>$K12</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I26">
-    <cfRule type="cellIs" dxfId="124" priority="67" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="14" priority="67" operator="greaterThan">
       <formula>$K26</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I75">
-    <cfRule type="cellIs" dxfId="123" priority="117" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="13" priority="117" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I93:I94">
-    <cfRule type="cellIs" dxfId="122" priority="115" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="12" priority="115" operator="greaterThan">
       <formula>$K93</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I107">
-    <cfRule type="cellIs" dxfId="121" priority="114" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="11" priority="114" operator="greaterThan">
       <formula>$K107</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I109">
-    <cfRule type="cellIs" dxfId="120" priority="112" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="10" priority="112" operator="greaterThan">
       <formula>$K109</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J97">
-    <cfRule type="cellIs" dxfId="119" priority="119" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="9" priority="119" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J103">
-    <cfRule type="cellIs" dxfId="118" priority="118" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="8" priority="118" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="cellIs" dxfId="117" priority="70" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="7" priority="70" operator="greaterThan">
       <formula>$K12</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K26">
-    <cfRule type="cellIs" dxfId="116" priority="69" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="69" operator="greaterThan">
       <formula>$K26</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K41">
-    <cfRule type="cellIs" dxfId="115" priority="68" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="68" operator="greaterThan">
       <formula>$K41</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K93:K94">
-    <cfRule type="cellIs" dxfId="114" priority="71" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="4" priority="71" operator="greaterThan">
       <formula>$K93</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K104">
-    <cfRule type="cellIs" dxfId="113" priority="120" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="3" priority="120" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K107">
-    <cfRule type="cellIs" dxfId="112" priority="113" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="113" operator="greaterThan">
       <formula>$I107</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K109">
-    <cfRule type="cellIs" dxfId="111" priority="111" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="111" operator="greaterThan">
       <formula>$I109</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P37:P38">
-    <cfRule type="cellIs" dxfId="110" priority="121" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="121" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B56:B65">
-    <cfRule type="expression" dxfId="109" priority="5" stopIfTrue="1">
-      <formula>IF(AO56&gt;0,TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B69:B78">
-    <cfRule type="expression" dxfId="108" priority="3" stopIfTrue="1">
-      <formula>IF(AO69&gt;0,TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D56:D65">
-    <cfRule type="expression" dxfId="107" priority="4" stopIfTrue="1">
-      <formula>IF(AQ56&gt;0,TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D69:D78">
-    <cfRule type="expression" dxfId="106" priority="2" stopIfTrue="1">
-      <formula>IF(AQ69&gt;0,TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F11 F16:F25">
-    <cfRule type="expression" dxfId="105" priority="9" stopIfTrue="1">
-      <formula>IF(#REF!="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="104" priority="10" stopIfTrue="1">
-      <formula>IF($T200="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="103" priority="11" stopIfTrue="1">
-      <formula>IF($U200="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="102" priority="12" stopIfTrue="1">
-      <formula>IF($AN1048554="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="101" priority="13" stopIfTrue="1">
-      <formula>IF($T200="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="100" priority="14" stopIfTrue="1">
-      <formula>IF($U200="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F30:F39">
-    <cfRule type="expression" dxfId="99" priority="35" stopIfTrue="1">
-      <formula>IF(#REF!="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="98" priority="36" stopIfTrue="1">
-      <formula>IF($T230="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="97" priority="37" stopIfTrue="1">
-      <formula>IF($U230="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="96" priority="38" stopIfTrue="1">
-      <formula>IF($AN5="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="95" priority="39" stopIfTrue="1">
-      <formula>IF($T230="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="94" priority="40" stopIfTrue="1">
-      <formula>IF($U230="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F43:F52">
-    <cfRule type="expression" dxfId="93" priority="41" stopIfTrue="1">
-      <formula>IF(#REF!="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="92" priority="42" stopIfTrue="1">
-      <formula>IF($T242="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="91" priority="43" stopIfTrue="1">
-      <formula>IF($U242="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="90" priority="44" stopIfTrue="1">
-      <formula>IF($AN17="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="89" priority="45" stopIfTrue="1">
-      <formula>IF($T242="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="88" priority="46" stopIfTrue="1">
-      <formula>IF($U242="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F56">
-    <cfRule type="expression" dxfId="87" priority="32" stopIfTrue="1">
-      <formula>IF($AN28="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="86" priority="33" stopIfTrue="1">
-      <formula>IF($T254="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="85" priority="34" stopIfTrue="1">
-      <formula>IF($U254="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F56:F67">
-    <cfRule type="expression" dxfId="84" priority="31" stopIfTrue="1">
-      <formula>IF(#REF!="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F57:F67">
-    <cfRule type="expression" dxfId="83" priority="47" stopIfTrue="1">
-      <formula>IF($AK29="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="82" priority="48" stopIfTrue="1">
-      <formula>IF($T255="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="81" priority="49" stopIfTrue="1">
-      <formula>IF($U255="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F69">
-    <cfRule type="expression" dxfId="80" priority="50" stopIfTrue="1">
-      <formula>IF($T268="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="79" priority="51" stopIfTrue="1">
-      <formula>IF($U268="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="78" priority="52" stopIfTrue="1">
-      <formula>IF($AJ43="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="77" priority="53" stopIfTrue="1">
-      <formula>IF($T268="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="76" priority="54" stopIfTrue="1">
-      <formula>IF($U268="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F69:F78">
-    <cfRule type="expression" dxfId="75" priority="1" stopIfTrue="1">
-      <formula>IF(#REF!="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F70:F78">
-    <cfRule type="expression" dxfId="74" priority="55" stopIfTrue="1">
-      <formula>IF($AJ42="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="73" priority="56" stopIfTrue="1">
-      <formula>IF($T267="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="72" priority="57" stopIfTrue="1">
-      <formula>IF($U267="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G12 G16:G26 G30:G41">
-    <cfRule type="cellIs" dxfId="71" priority="29" stopIfTrue="1" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="70" priority="30" stopIfTrue="1" operator="greaterThanOrEqual">
-      <formula>#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G12 G16:G28">
-    <cfRule type="cellIs" dxfId="69" priority="15" stopIfTrue="1" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G30:G41 G2:G12 G16:G26">
-    <cfRule type="cellIs" dxfId="68" priority="28" operator="greaterThan">
-      <formula>#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G43:G54 G30:G41 G56:G67">
-    <cfRule type="cellIs" dxfId="67" priority="24" stopIfTrue="1" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G43:G54">
-    <cfRule type="cellIs" dxfId="66" priority="20" stopIfTrue="1" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="65" priority="21" operator="greaterThan">
-      <formula>#REF!</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="64" priority="22" stopIfTrue="1" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="63" priority="23" stopIfTrue="1" operator="greaterThanOrEqual">
-      <formula>#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G53:G54">
-    <cfRule type="cellIs" dxfId="62" priority="6" operator="greaterThan">
-      <formula>#REF!</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="61" priority="7" stopIfTrue="1" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
-      <formula>#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G56:G67">
-    <cfRule type="cellIs" dxfId="59" priority="25" operator="greaterThan">
-      <formula>#REF!</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="58" priority="26" stopIfTrue="1" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="57" priority="27" stopIfTrue="1" operator="greaterThanOrEqual">
-      <formula>#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G69:G79">
-    <cfRule type="cellIs" dxfId="56" priority="16" stopIfTrue="1" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="55" priority="17" operator="greaterThan">
-      <formula>#REF!</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="54" priority="18" stopIfTrue="1" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="53" priority="19" stopIfTrue="1" operator="greaterThanOrEqual">
-      <formula>#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Twitter_Donnees.xlsx
+++ b/Twitter_Donnees.xlsx
@@ -8,21 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Bourse\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C379A925-1C94-4466-8D84-700308A296AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{238EF144-5EF1-4F7C-8599-2396079B2FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{CB1B49A7-9C46-47E8-A7CD-9AB6F7C19107}"/>
   </bookViews>
   <sheets>
     <sheet name="Donnees" sheetId="1" r:id="rId1"/>
-    <sheet name="Suivi" sheetId="2" r:id="rId2"/>
+    <sheet name="Suivi" sheetId="3" r:id="rId2"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId3"/>
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Donnees!$A$2:$G$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Suivi!$A$2:$G$11</definedName>
     <definedName name="cours">[1]Cours!$A$2:$H$3000</definedName>
     <definedName name="_xlnm.Criteria" localSheetId="0">Donnees!$O$1</definedName>
+    <definedName name="_xlnm.Criteria" localSheetId="1">Suivi!$O$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -48,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="173">
   <si>
     <t>14/08/2026</t>
   </si>
@@ -365,12 +367,6 @@
     <t>EURAZÉO</t>
   </si>
   <si>
-    <t>IPS</t>
-  </si>
-  <si>
-    <t>IPSOS</t>
-  </si>
-  <si>
     <t>Décote</t>
   </si>
   <si>
@@ -416,169 +412,163 @@
     <t>Colonne1</t>
   </si>
   <si>
-    <t>31-juil</t>
+    <t>SCHNEIDER ELECTRIC</t>
   </si>
   <si>
-    <t>Cours</t>
+    <t>SU</t>
   </si>
   <si>
-    <t>Différence</t>
+    <t>LECTRA</t>
   </si>
   <si>
-    <t>ERA</t>
+    <t>LSS</t>
   </si>
   <si>
-    <t>ERAMET</t>
+    <t>MERSEN</t>
   </si>
   <si>
-    <t>POXEL</t>
+    <t>MRN</t>
   </si>
   <si>
-    <t>WLN</t>
+    <t>SAINT GOBAIN</t>
   </si>
   <si>
-    <t>WORLDLINE</t>
+    <t>SGO</t>
   </si>
   <si>
-    <t>EDEN</t>
+    <t>AIRBUS GROUP</t>
   </si>
   <si>
-    <t>EDENRED</t>
+    <t>AIR</t>
   </si>
   <si>
-    <t>MTU</t>
+    <t>SOPRA STERIA GROUP</t>
   </si>
   <si>
-    <t>MANITOU</t>
+    <t>SOP</t>
   </si>
   <si>
-    <t>VMX</t>
+    <t>SAFRAN</t>
   </si>
   <si>
-    <t>VERIMATRIX</t>
+    <t>SAF</t>
   </si>
   <si>
-    <t>ALCAT</t>
+    <t xml:space="preserve">THALES </t>
   </si>
   <si>
-    <t>CATANA GROUP</t>
+    <t>HO</t>
   </si>
   <si>
-    <t>VIV</t>
+    <t xml:space="preserve">PATRIMOINE COM, </t>
   </si>
   <si>
-    <t xml:space="preserve">VIVENDI </t>
+    <t>PAT</t>
   </si>
   <si>
-    <t>DIM</t>
+    <t>EUTELSAT COMMUNICATION</t>
   </si>
   <si>
-    <t>SARTORIUS STED</t>
+    <t>ETL</t>
   </si>
   <si>
-    <t>ABNX</t>
+    <t>BUREAU VERITAS</t>
   </si>
   <si>
-    <t>ABIONYX PHARMA</t>
+    <t>BVI</t>
   </si>
   <si>
-    <t>DBV</t>
+    <t>ARKEMA</t>
   </si>
   <si>
-    <t>DBV TECHNOLOGIES</t>
+    <t>AKE</t>
   </si>
   <si>
-    <t>EQS</t>
+    <t>INNELEC MULTIMEDIA</t>
   </si>
   <si>
-    <t>EQUASENS</t>
+    <t>ALINN</t>
   </si>
   <si>
-    <t>XFAB</t>
+    <t>PAULIC MEUNERIE</t>
   </si>
   <si>
-    <t>X-FAB SILICON</t>
+    <t>ALPAU</t>
   </si>
   <si>
-    <t>STLAP</t>
+    <t>RIBER</t>
   </si>
   <si>
-    <t>STELLANTIS</t>
+    <t>ALRIB</t>
   </si>
   <si>
-    <t>SPIE</t>
+    <t>IMPLANET</t>
   </si>
   <si>
-    <t>ALATA</t>
+    <t>ALIMP</t>
   </si>
   <si>
-    <t>ATARI</t>
+    <t>INVIBES ADVERTISING</t>
   </si>
   <si>
-    <t>ALROC</t>
+    <t>ALINV</t>
   </si>
   <si>
-    <t>ROCTOOL</t>
+    <t>TME PHARMA</t>
   </si>
   <si>
-    <t>ALTOO</t>
+    <t>ALTME</t>
   </si>
   <si>
-    <t>TOOSLA</t>
+    <t>HERMES INTERNATIONAL</t>
   </si>
   <si>
-    <t>ALSEC</t>
+    <t>RMS</t>
   </si>
   <si>
-    <t>SODITECH</t>
+    <t>ELIOR GROUP</t>
   </si>
   <si>
-    <t>ALGRO</t>
+    <t>ELIOR</t>
   </si>
   <si>
-    <t>GROLLEAU</t>
+    <t>LINEDATA</t>
   </si>
   <si>
-    <t>ALXIL</t>
+    <t>LIN</t>
   </si>
   <si>
-    <t>XILAM ANIMATION</t>
+    <t>BOLLORE</t>
   </si>
   <si>
-    <t>ALICA</t>
+    <t>BOL</t>
   </si>
   <si>
-    <t>ICAP HOLDING</t>
+    <t>UBISOFT</t>
   </si>
   <si>
-    <t>ALNRG</t>
+    <t>UBI</t>
   </si>
   <si>
-    <t>ENERGISME</t>
+    <t>ARAMIS</t>
   </si>
   <si>
-    <t>Colonne8</t>
+    <t>ARAMI</t>
   </si>
   <si>
-    <t>15-janv</t>
+    <t>OVH GROUPE</t>
   </si>
   <si>
-    <t>SWP</t>
+    <t>OVH</t>
   </si>
   <si>
-    <t>SWORD GROUP</t>
+    <t>VITURA</t>
   </si>
   <si>
-    <t>QDT</t>
+    <t>VTR</t>
   </si>
   <si>
-    <t>QUADIENT</t>
-  </si>
-  <si>
-    <t>CAP</t>
-  </si>
-  <si>
-    <t>CAP GEMINI</t>
+    <t>10/8</t>
   </si>
 </sst>
 </file>
@@ -1233,7 +1223,7 @@
     <xf numFmtId="166" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="131">
+  <cellXfs count="128">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1506,13 +1496,6 @@
     <xf numFmtId="2" fontId="5" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="16" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="2" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1520,7 +1503,142 @@
     <cellStyle name="Normal 4" xfId="3" xr:uid="{1BE76CE9-5C3F-452B-84A0-4586D845B2A6}"/>
     <cellStyle name="Pourcentage" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="158">
+  <dxfs count="172">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="12"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <condense val="0"/>
@@ -1554,6 +1672,16 @@
         <extend val="0"/>
         <color indexed="10"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -1668,44 +1796,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <b/>
         <i val="0"/>
         <condense val="0"/>
@@ -1717,22 +1807,6 @@
       <font>
         <b val="0"/>
         <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <condense val="0"/>
         <extend val="0"/>
         <color indexed="10"/>
@@ -1786,6 +1860,50 @@
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -1912,15 +2030,6 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <b/>
         <i val="0"/>
         <condense val="0"/>
@@ -1930,128 +2039,11 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="0"/>
         <i val="0"/>
         <condense val="0"/>
         <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
+        <color indexed="10"/>
       </font>
     </dxf>
     <dxf>
@@ -2476,6 +2468,174 @@
         <extend val="0"/>
         <color indexed="18"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="167" formatCode="000000"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -3315,6 +3475,202 @@
         <left style="thin">
           <color auto="1"/>
         </left>
+        <right style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor indexed="43"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="167" formatCode="000000"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
         <right style="medium">
           <color indexed="64"/>
         </right>
@@ -3567,6 +3923,47 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
         <sz val="12"/>
         <color auto="1"/>
         <name val="Arial"/>
@@ -3598,7 +3995,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
@@ -3607,16 +4004,16 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="8"/>
+        <sz val="11"/>
         <color auto="1"/>
         <name val="Arial"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <numFmt numFmtId="2" formatCode="0.00"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
-          <bgColor indexed="41"/>
+          <bgColor indexed="43"/>
         </patternFill>
       </fill>
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -3624,11 +4021,11 @@
         <left style="thin">
           <color auto="1"/>
         </left>
-        <right style="medium">
-          <color indexed="64"/>
+        <right style="thin">
+          <color auto="1"/>
         </right>
-        <top style="medium">
-          <color indexed="64"/>
+        <top style="thin">
+          <color auto="1"/>
         </top>
         <bottom style="thin">
           <color auto="1"/>
@@ -3700,47 +4097,6 @@
       </fill>
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor indexed="43"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right style="thin">
           <color indexed="64"/>
@@ -3750,39 +4106,6 @@
         <vertical/>
         <horizontal/>
       </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -3836,6 +4159,73 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="167" formatCode="000000"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor indexed="9"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
       <numFmt numFmtId="167" formatCode="000000"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
@@ -3858,7 +4248,7 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color auto="1"/>
         <name val="Arial"/>
         <family val="2"/>
@@ -3917,50 +4307,6 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="167" formatCode="000000"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor indexed="9"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
         <sz val="11"/>
         <color theme="1"/>
         <name val="Calibri"/>
@@ -3975,6 +4321,16 @@
         <bottom/>
         <vertical/>
         <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -20008,18 +20364,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{744BE250-F264-4768-BE22-5662D7F7372D}" name="Hausses28826" displayName="Hausses28826" ref="A29:G40" totalsRowCount="1" headerRowDxfId="157" tableBorderDxfId="156">
-  <autoFilter ref="A29:G39" xr:uid="{744BE250-F264-4768-BE22-5662D7F7372D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{4F0FC2F1-2AFC-46ED-BF74-15C6A2427E2E}" name="Hausses28850" displayName="Hausses28850" ref="A29:G40" totalsRowCount="1" headerRowDxfId="171" tableBorderDxfId="170">
+  <autoFilter ref="A29:G39" xr:uid="{00000000-0009-0000-0100-000057000000}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{C0860192-37DE-4F17-909A-295A14E1C4E9}" name="Position" dataDxfId="155" totalsRowDxfId="154"/>
-    <tableColumn id="2" xr3:uid="{E3572A17-96F7-4B0A-8E34-9B529DD87680}" name="Code" dataDxfId="153" totalsRowDxfId="152" dataCellStyle="Normal 2"/>
-    <tableColumn id="3" xr3:uid="{DC7FB505-4679-4E5F-9F6A-3F01DE92A850}" name="Marché" dataDxfId="151" totalsRowDxfId="150" dataCellStyle="Normal 2"/>
-    <tableColumn id="4" xr3:uid="{3A07F0B0-C50A-4C2D-93EF-1EA166F1D5B2}" name="Valeur" dataDxfId="149" totalsRowDxfId="148" dataCellStyle="Normal 2"/>
-    <tableColumn id="5" xr3:uid="{95915E51-EA38-4FCC-BAE3-D31D066F90F0}" name="Colonne3" dataDxfId="147" dataCellStyle="Normal 2"/>
-    <tableColumn id="6" xr3:uid="{2A6D4D7A-C8DB-429F-BE8E-5AD4EE05E407}" name="RECO" totalsRowLabel="Moyenne" dataDxfId="146" totalsRowDxfId="145" dataCellStyle="Normal 2">
+    <tableColumn id="1" xr3:uid="{DEA1EEF8-7956-41C8-ADDF-15BB20D97522}" name="Position" dataDxfId="168" totalsRowDxfId="169"/>
+    <tableColumn id="2" xr3:uid="{42CFAD8E-9552-4D5D-9664-355BABCBF9F7}" name="Code" dataDxfId="166" totalsRowDxfId="167" dataCellStyle="Normal 2"/>
+    <tableColumn id="3" xr3:uid="{317FEEAE-1E99-4799-BD65-A8D5BE4CA60D}" name="Marché" dataDxfId="164" totalsRowDxfId="165" dataCellStyle="Normal 2"/>
+    <tableColumn id="4" xr3:uid="{C2FBE61F-8825-4877-939B-F47908CE109C}" name="Valeur" dataDxfId="162" totalsRowDxfId="163" dataCellStyle="Normal 2"/>
+    <tableColumn id="5" xr3:uid="{786A58D5-50CD-4020-A6F3-539C76AD8621}" name="RECO" dataDxfId="161" dataCellStyle="Normal 2"/>
+    <tableColumn id="6" xr3:uid="{58C26805-3A9E-43EA-8644-615F7E60E349}" name="COURS" totalsRowLabel="Moyenne" dataDxfId="159" totalsRowDxfId="160" dataCellStyle="Normal 2">
       <calculatedColumnFormula>IFERROR(((VLOOKUP(B30,cours,7,FALSE))),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{A943ECBF-D5A8-4523-8079-6C4FD8A63D85}" name="Différence" totalsRowFunction="custom" dataDxfId="144" totalsRowDxfId="143" dataCellStyle="Normal 4">
+    <tableColumn id="7" xr3:uid="{7045ED3E-B008-4B2E-B1B6-78D66DA958CA}" name="ECART" totalsRowFunction="custom" dataDxfId="157" totalsRowDxfId="158" dataCellStyle="Normal 4">
       <calculatedColumnFormula>(F30/E30-1)</calculatedColumnFormula>
       <totalsRowFormula>AVERAGE(G30:G39)</totalsRowFormula>
     </tableColumn>
@@ -20029,73 +20385,105 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C5996414-920D-414D-8C5B-645CC9C7AB69}" name="Hausses38927" displayName="Hausses38927" ref="A42:G53" totalsRowShown="0" headerRowDxfId="142" tableBorderDxfId="141">
-  <autoFilter ref="A42:G53" xr:uid="{C5996414-920D-414D-8C5B-645CC9C7AB69}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{33F8ABE2-B924-4C60-AA32-9BD429F5A1FC}" name="Hausses38951" displayName="Hausses38951" ref="A42:G53" totalsRowShown="0" headerRowDxfId="156" tableBorderDxfId="155">
+  <autoFilter ref="A42:G53" xr:uid="{00000000-0009-0000-0100-000058000000}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{FC5F0FE5-E484-4444-91D0-E82193591E6B}" name="Position" dataDxfId="140"/>
-    <tableColumn id="2" xr3:uid="{D8A35B94-7C62-4BF2-9D5B-EA9C8A074032}" name="Code" dataDxfId="139" dataCellStyle="Normal 2"/>
-    <tableColumn id="3" xr3:uid="{4A5C029B-DE4E-4957-8EF9-11F667A77972}" name="Marché" dataDxfId="138" dataCellStyle="Normal 2"/>
-    <tableColumn id="4" xr3:uid="{7D250ADA-6B3D-4735-BE65-99738108D11A}" name="Valeur" dataDxfId="137" dataCellStyle="Normal 2"/>
-    <tableColumn id="5" xr3:uid="{F7B3880F-AFCD-4A9E-BF75-A5AA9352095C}" name="Colonne8" dataDxfId="136" dataCellStyle="Normal 2"/>
-    <tableColumn id="6" xr3:uid="{B28A9DE3-ACE1-443B-9BF5-296AA2C7EB82}" name="RECO" dataDxfId="135" dataCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{6C89434B-4D1A-4039-A293-4BB040E7F83F}" name="Différence" dataDxfId="134" dataCellStyle="Normal 4"/>
+    <tableColumn id="1" xr3:uid="{65185694-99B9-4FA7-9779-AC3959D4ACA9}" name="Position" dataDxfId="154"/>
+    <tableColumn id="2" xr3:uid="{13703D39-9406-44AE-9BEA-6828402FB821}" name="Code" dataDxfId="153" dataCellStyle="Normal 2"/>
+    <tableColumn id="3" xr3:uid="{7E95ECD3-FEC9-4E5B-9820-3170FFA54661}" name="Marché" dataDxfId="152" dataCellStyle="Normal 2"/>
+    <tableColumn id="4" xr3:uid="{AE8541C3-51A9-4DA5-BB44-1E451812EC5B}" name="Valeur" dataDxfId="151" dataCellStyle="Normal 2"/>
+    <tableColumn id="5" xr3:uid="{1EC0F571-CDCC-419D-A68A-E41182CA170B}" name="RECO" dataDxfId="150" dataCellStyle="Normal 2"/>
+    <tableColumn id="6" xr3:uid="{AEDE007C-9250-4647-BB28-EBDAB1BC377D}" name="COURS" dataDxfId="149" dataCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{9695F846-59DA-4EAA-BF9F-620AF7634715}" name="ECART" dataDxfId="148" dataCellStyle="Normal 4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{1C43F6EA-7C90-410E-828F-47C3DDAEC980}" name="Hausses18622516529" displayName="Hausses18622516529" ref="A1:G12" totalsRowShown="0" headerRowDxfId="133" tableBorderDxfId="132">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{C4BEEEA5-2E5F-422A-8090-AADD0C1345F0}" name="Decotes9252" displayName="Decotes9252" ref="A81:G92" totalsRowShown="0">
+  <autoFilter ref="A81:G92" xr:uid="{00000000-0009-0000-0100-00005B000000}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{BE54938E-7A14-4A92-8F7F-601A700D7F5D}" name="31-juil" dataDxfId="131"/>
-    <tableColumn id="2" xr3:uid="{FEF859FC-046F-46D3-BFE5-FF67F6EF5908}" name="Code" dataDxfId="130" dataCellStyle="Normal 2"/>
-    <tableColumn id="3" xr3:uid="{0064B851-969D-4FBC-A8A1-799D30FF9E39}" name="Marché" dataDxfId="129" dataCellStyle="Normal 2"/>
-    <tableColumn id="4" xr3:uid="{9C54DC20-A97B-4321-B66D-2895703B8848}" name="Valeur" dataDxfId="128" dataCellStyle="Normal 2"/>
-    <tableColumn id="5" xr3:uid="{56AEDFFC-7DF2-4837-A9E4-C11E35DFB681}" name="Cours" dataDxfId="127" dataCellStyle="Normal 2"/>
-    <tableColumn id="6" xr3:uid="{CD7B1F5D-6EE7-4D23-9F2E-F3A153B4FEF7}" name="RECO" dataDxfId="126" dataCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{F7B37E98-9ABD-4503-A709-1C2138EA3B3A}" name="Différence" dataDxfId="125" dataCellStyle="Normal 4"/>
+    <tableColumn id="1" xr3:uid="{38C92A3D-5868-4B3E-A36B-42C23340D002}" name="Colonne1" dataDxfId="147"/>
+    <tableColumn id="2" xr3:uid="{674C8163-4087-42CF-9CDD-EDD5CB0994E1}" name="Décote" dataDxfId="146"/>
+    <tableColumn id="3" xr3:uid="{15BDCA7F-F49E-4FB0-9B47-447D93DCC9F6}" name="Colonne2" dataDxfId="145"/>
+    <tableColumn id="4" xr3:uid="{9283C4CB-11F0-431B-89C8-62F1403936EE}" name="Valeur" dataDxfId="144"/>
+    <tableColumn id="5" xr3:uid="{1F0F39C5-5BF4-4665-9390-90FA56AEC951}" name="RECO" dataDxfId="143"/>
+    <tableColumn id="6" xr3:uid="{36EAEB05-CCD5-46B4-9CFC-09149024800A}" name="COURS" dataDxfId="142" dataCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{D89CF688-D56E-4FD3-A4F4-362C3C1A92F6}" name="ECART" dataDxfId="141" dataCellStyle="Normal 4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{D92BAC71-B1DC-4BF3-AA7C-9B1962D46808}" name="Baisses18722616630" displayName="Baisses18722616630" ref="A15:E27" totalsRowShown="0" headerRowDxfId="124" tableBorderDxfId="123">
-  <autoFilter ref="A15:E27" xr:uid="{D92BAC71-B1DC-4BF3-AA7C-9B1962D46808}"/>
-  <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{8DD859F8-734F-4CE9-BA57-056BC1E6D343}" name="Position" dataDxfId="122"/>
-    <tableColumn id="2" xr3:uid="{B50A516F-D64E-47C4-99F7-207649AEA279}" name="Code" dataDxfId="121" dataCellStyle="Normal 2"/>
-    <tableColumn id="3" xr3:uid="{6C9523B1-0F3E-49D8-AA4D-569C79CCA593}" name="Marché" dataDxfId="120" dataCellStyle="Normal 2"/>
-    <tableColumn id="4" xr3:uid="{CDAF6207-056D-49A6-B33D-DD8D78E817A2}" name="Valeur" dataDxfId="119" dataCellStyle="Normal 2"/>
-    <tableColumn id="5" xr3:uid="{A9322936-82F2-4F6B-A0A3-7E4D00A37DA9}" name="Colonne1" dataDxfId="118" dataCellStyle="Normal 2"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{9F8587F6-ADCC-4FB8-A814-C2F291EB4B62}" name="Hausses18622516553" displayName="Hausses18622516553" ref="A1:G12" totalsRowShown="0" headerRowDxfId="140" tableBorderDxfId="139">
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{FF69E3F4-23C8-4B00-BBB4-7781C88BEE28}" name="10/8" dataDxfId="138"/>
+    <tableColumn id="2" xr3:uid="{6FC438E8-E5B5-4738-B7F8-370DED7BC285}" name="Code" dataDxfId="137" dataCellStyle="Normal 2"/>
+    <tableColumn id="3" xr3:uid="{56403BB7-A156-42E1-8767-E9F9D9B1BC5B}" name="Marché" dataDxfId="136" dataCellStyle="Normal 2"/>
+    <tableColumn id="4" xr3:uid="{7B5706B9-5DD4-47EC-9A3B-214B9DA78D08}" name="Valeur" dataDxfId="135" dataCellStyle="Normal 2"/>
+    <tableColumn id="5" xr3:uid="{32AA4FB4-C6E8-4266-A706-D871D5D0C3A2}" name="RECO" dataDxfId="134" dataCellStyle="Normal 2"/>
+    <tableColumn id="6" xr3:uid="{9CA07F6F-B96F-4551-8807-5F882F9CEA06}" name="COURS" dataDxfId="133" dataCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{6285446C-2496-4571-B68D-5FBD440782B5}" name="ECART" dataDxfId="132" dataCellStyle="Normal 4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{A58F1CFF-EB70-4D81-ADE7-4C3EE777913F}" name="Hausses49022916731" displayName="Hausses49022916731" ref="A55:E66" totalsRowShown="0" headerRowDxfId="117" tableBorderDxfId="116">
-  <autoFilter ref="A55:E66" xr:uid="{A58F1CFF-EB70-4D81-ADE7-4C3EE777913F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{E0578705-E72D-4863-996B-DF71F27A4A15}" name="Baisses18722616654" displayName="Baisses18722616654" ref="A15:E27" totalsRowShown="0" headerRowDxfId="131" tableBorderDxfId="130">
+  <autoFilter ref="A15:E27" xr:uid="{00000000-0009-0000-0100-0000A5000000}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{499BCA9D-C177-41F8-BAB2-5175AF2BFC36}" name="Position" dataDxfId="115"/>
-    <tableColumn id="2" xr3:uid="{1FFC2203-925B-4B02-A9C7-75E78D774AD9}" name="Code" dataDxfId="114"/>
-    <tableColumn id="3" xr3:uid="{F0D2BA4D-1C1C-4E5A-A859-BF3836BD1687}" name="Marché" dataDxfId="113"/>
-    <tableColumn id="4" xr3:uid="{D2D19A82-C664-4DD1-A30A-100BC3886A0D}" name="Valeur" dataDxfId="112"/>
-    <tableColumn id="5" xr3:uid="{239F057B-8BA0-4A38-803A-9A2C1077A19D}" name="15-janv" dataDxfId="111"/>
+    <tableColumn id="1" xr3:uid="{AA66EF96-6BF4-4DB0-958B-C3EC16774BDF}" name="Position" dataDxfId="129"/>
+    <tableColumn id="2" xr3:uid="{EB61DE09-818C-47EB-A2C0-6845864F6DCD}" name="Code" dataDxfId="128" dataCellStyle="Normal 2"/>
+    <tableColumn id="3" xr3:uid="{EA2FF622-BFFF-4FF0-8E32-B7707B5394BC}" name="Marché" dataDxfId="127" dataCellStyle="Normal 2"/>
+    <tableColumn id="4" xr3:uid="{A2BD23C1-B5D9-4021-9432-CFE41C22CAE0}" name="Valeur" dataDxfId="126" dataCellStyle="Normal 2"/>
+    <tableColumn id="5" xr3:uid="{A68764E5-B780-4ED2-8A4A-C729245E82D6}" name="RECO" dataDxfId="125" dataCellStyle="Normal 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{5404D9D9-C096-46CE-B6DD-5EED87505035}" name="Baisses29123016832" displayName="Baisses29123016832" ref="A68:E78" totalsRowShown="0" headerRowDxfId="110">
-  <autoFilter ref="A68:E78" xr:uid="{5404D9D9-C096-46CE-B6DD-5EED87505035}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{4E269604-F5B3-4876-AB72-A470CD9B844C}" name="Hausses49022916755" displayName="Hausses49022916755" ref="A55:E66" totalsRowShown="0" headerRowDxfId="124" tableBorderDxfId="123">
+  <autoFilter ref="A55:E66" xr:uid="{00000000-0009-0000-0100-0000A6000000}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{8E429DEE-7701-432C-B092-2B6F81594F0F}" name="Position" dataDxfId="109"/>
-    <tableColumn id="2" xr3:uid="{88039358-F85B-4347-9E38-727E03CED614}" name="Code" dataDxfId="108" dataCellStyle="Normal 2"/>
-    <tableColumn id="3" xr3:uid="{C034F66A-BD2F-44B0-B6AF-2101CB7578F2}" name="Marché" dataDxfId="107" dataCellStyle="Normal 2"/>
-    <tableColumn id="4" xr3:uid="{51440959-11F5-48BB-ADE4-5CFFC531A3A6}" name="Valeur" dataDxfId="106" dataCellStyle="Normal 2"/>
-    <tableColumn id="5" xr3:uid="{714D093F-51B8-4E43-A0D5-29CFB06B4880}" name="Colonne1" dataDxfId="105" dataCellStyle="Normal 2"/>
+    <tableColumn id="1" xr3:uid="{A4A7D450-B39D-4786-BD09-8EE9F2B90E4F}" name="Position" dataDxfId="122"/>
+    <tableColumn id="2" xr3:uid="{C6481D4F-8B0D-4BF7-B766-97C21899FAEC}" name="Code" dataDxfId="121"/>
+    <tableColumn id="3" xr3:uid="{4AB0F44F-6FB1-4DF3-8D35-0F5A8F493986}" name="Marché" dataDxfId="120"/>
+    <tableColumn id="4" xr3:uid="{82B42CBB-E06F-4E3B-995B-784A74BF661A}" name="Valeur" dataDxfId="119"/>
+    <tableColumn id="5" xr3:uid="{CF9E2A75-83FE-435F-8FE9-63B80B53A1E0}" name="RECO" dataDxfId="118"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{378C787E-5651-4754-ABFF-09713A4893C9}" name="Baisses29123016856" displayName="Baisses29123016856" ref="A68:E78" totalsRowShown="0" headerRowDxfId="117">
+  <autoFilter ref="A68:E78" xr:uid="{00000000-0009-0000-0100-0000A7000000}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{658F7727-DC51-4AAE-A397-23FFB36EC0B1}" name="Position" dataDxfId="116"/>
+    <tableColumn id="2" xr3:uid="{2AD3241C-DE94-43D4-8789-932ACB9D0BD7}" name="Code" dataDxfId="115" dataCellStyle="Normal 2"/>
+    <tableColumn id="3" xr3:uid="{F1824A3A-CE91-4D5D-9B11-E51D08D77262}" name="Marché" dataDxfId="114" dataCellStyle="Normal 2"/>
+    <tableColumn id="4" xr3:uid="{2A2AFF88-FB8B-459C-B09C-7703E903464D}" name="Valeur" dataDxfId="113" dataCellStyle="Normal 2"/>
+    <tableColumn id="5" xr3:uid="{960A18B7-A303-4390-94BC-F4F690D3B686}" name="RECO" dataDxfId="112" dataCellStyle="Normal 2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{28706E2B-6BC2-4CF9-B5E8-7DF539EC8A99}" name="Etoiles9323216957" displayName="Etoiles9323216957" ref="A95:G106" totalsRowShown="0">
+  <autoFilter ref="A95:G106" xr:uid="{00000000-0009-0000-0100-0000A8000000}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{C3DFB417-71BB-4A0F-A161-A4F197F026D0}" name="Colonne1"/>
+    <tableColumn id="2" xr3:uid="{14F212B0-670E-42AA-A430-9CC05DE3EB29}" name="Etoiles Small" dataDxfId="111"/>
+    <tableColumn id="3" xr3:uid="{3975FA19-A710-459C-BDF4-D10D6A151A9D}" name="Colonne2" dataDxfId="110"/>
+    <tableColumn id="4" xr3:uid="{AC00B8B5-DBFE-4400-A7B3-1B5FEE8E25AE}" name="Colonne3" dataDxfId="109"/>
+    <tableColumn id="5" xr3:uid="{653A818F-3EE7-4217-835D-29B33CB031AE}" name="RECO" dataDxfId="108"/>
+    <tableColumn id="6" xr3:uid="{A762B138-3B4E-42EC-ABF3-32B1699BE75D}" name="COURS" dataDxfId="107" dataCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{C038CB98-7C97-4F3B-A7D7-9956AC4F99DD}" name="ECART" dataDxfId="106" dataCellStyle="Normal 4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -22132,10 +22520,10 @@
         <v>32</v>
       </c>
       <c r="B81" s="65" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C81" s="66" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D81" s="66" t="s">
         <v>3</v>
@@ -22345,13 +22733,13 @@
         <v>32</v>
       </c>
       <c r="B95" s="65" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C95" s="66" t="s">
+        <v>106</v>
+      </c>
+      <c r="D95" s="67" t="s">
         <v>108</v>
-      </c>
-      <c r="D95" s="67" t="s">
-        <v>110</v>
       </c>
       <c r="E95" s="67" t="s">
         <v>4</v>
@@ -22363,7 +22751,7 @@
         <v>6</v>
       </c>
       <c r="H95" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I95" s="60"/>
       <c r="J95" s="61"/>
@@ -22593,22 +22981,24 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{952C8468-8889-4A1C-8D9C-0E0505F70003}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A576667A-0295-40B8-870D-C2CC5ED7BB45}">
+  <sheetPr codeName="Feuil12"/>
   <dimension ref="A1:W111"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="12.15234375" customWidth="1"/>
-    <col min="2" max="2" width="13.07421875" customWidth="1"/>
+    <col min="2" max="2" width="13.07421875" style="16" customWidth="1"/>
     <col min="3" max="3" width="10.4609375" customWidth="1"/>
     <col min="4" max="4" width="27.07421875" customWidth="1"/>
     <col min="5" max="5" width="12.69140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.3046875" customWidth="1"/>
+    <col min="8" max="8" width="11.07421875" style="16"/>
+    <col min="9" max="9" width="6.3046875" style="7" customWidth="1"/>
     <col min="11" max="11" width="6.765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="128" t="s">
-        <v>122</v>
+      <c r="A1" s="8" t="s">
+        <v>172</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -22620,18 +23010,17 @@
         <v>3</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>123</v>
+        <v>4</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>124</v>
+        <v>6</v>
       </c>
       <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7"/>
       <c r="P1" s="9"/>
       <c r="Q1" s="10"/>
       <c r="R1" s="10"/>
@@ -22640,7 +23029,7 @@
       <c r="U1" s="11"/>
       <c r="V1" s="11"/>
       <c r="W1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.45">
@@ -22648,26 +23037,25 @@
         <v>1</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>125</v>
+        <v>171</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>126</v>
+        <v>170</v>
       </c>
       <c r="E2" s="13">
-        <v>43.12</v>
+        <v>5.5</v>
       </c>
       <c r="F2" s="14">
-        <f t="shared" ref="F2:F11" si="0">IFERROR(((VLOOKUP(B2,cours,7,FALSE))),"")</f>
-        <v>46.08</v>
+        <f>IFERROR(((VLOOKUP(B2,cours,7,FALSE))),"")</f>
+        <v>4.5999999999999996</v>
       </c>
       <c r="G2" s="15">
-        <f t="shared" ref="G2:G11" si="1">(F2/E2-1)</f>
-        <v>6.8645640074211478E-2</v>
-      </c>
-      <c r="H2" s="16"/>
+        <f>(F2/E2-1)</f>
+        <v>-0.16363636363636369</v>
+      </c>
       <c r="I2" s="17"/>
       <c r="J2" s="17"/>
       <c r="K2" s="18"/>
@@ -22676,7 +23064,8 @@
       <c r="U2" s="11"/>
       <c r="V2" s="11"/>
       <c r="W2" s="20">
-        <v>46248</v>
+        <f ca="1">TODAY()</f>
+        <v>46249</v>
       </c>
     </row>
     <row r="3" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.45">
@@ -22684,24 +23073,24 @@
         <v>2</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>127</v>
+        <v>169</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>12</v>
+        <v>111</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>127</v>
+        <v>168</v>
       </c>
       <c r="E3" s="13">
-        <v>0.21</v>
+        <v>16.18</v>
       </c>
       <c r="F3" s="14">
-        <f t="shared" si="0"/>
-        <v>0.20300000000000001</v>
+        <f>IFERROR(((VLOOKUP(B3,cours,7,FALSE))),"")</f>
+        <v>16.93</v>
       </c>
       <c r="G3" s="15">
-        <f t="shared" si="1"/>
-        <v>-3.3333333333333215E-2</v>
+        <f>(F3/E3-1)</f>
+        <v>4.6353522867737862E-2</v>
       </c>
       <c r="H3" s="7"/>
       <c r="I3" s="17"/>
@@ -22715,24 +23104,24 @@
         <v>3</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E4" s="13">
-        <v>69</v>
+        <v>5.82</v>
       </c>
       <c r="F4" s="14">
-        <f t="shared" si="0"/>
-        <v>70.86</v>
+        <f>IFERROR(((VLOOKUP(B4,cours,7,FALSE))),"")</f>
+        <v>5.92</v>
       </c>
       <c r="G4" s="15">
-        <f t="shared" si="1"/>
-        <v>2.6956521739130324E-2</v>
+        <f>(F4/E4-1)</f>
+        <v>1.7182130584192379E-2</v>
       </c>
       <c r="H4" s="7"/>
       <c r="I4" s="17"/>
@@ -22746,24 +23135,24 @@
         <v>4</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>113</v>
+        <v>12</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="E5" s="13">
-        <v>12.188000000000001</v>
+        <v>23</v>
       </c>
       <c r="F5" s="14">
-        <f t="shared" si="0"/>
-        <v>12.762</v>
+        <f>IFERROR(((VLOOKUP(B5,cours,7,FALSE))),"")</f>
+        <v>23.65</v>
       </c>
       <c r="G5" s="15">
-        <f t="shared" si="1"/>
-        <v>4.7095503774204017E-2</v>
+        <f>(F5/E5-1)</f>
+        <v>2.8260869565217339E-2</v>
       </c>
       <c r="H5" s="7"/>
       <c r="I5" s="17"/>
@@ -22777,24 +23166,24 @@
         <v>5</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>25</v>
+        <v>101</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>26</v>
+        <v>102</v>
       </c>
       <c r="E6" s="13">
-        <v>92.9</v>
+        <v>75.849999999999994</v>
       </c>
       <c r="F6" s="14">
-        <f t="shared" si="0"/>
-        <v>99.4</v>
+        <f>IFERROR(((VLOOKUP(B6,cours,7,FALSE))),"")</f>
+        <v>74</v>
       </c>
       <c r="G6" s="15">
-        <f t="shared" si="1"/>
-        <v>6.9967707212055918E-2</v>
+        <f>(F6/E6-1)</f>
+        <v>-2.4390243902438935E-2</v>
       </c>
       <c r="H6" s="7"/>
       <c r="I6" s="17"/>
@@ -22808,24 +23197,24 @@
         <v>6</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C7" s="10" t="s">
         <v>12</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E7" s="13">
-        <v>28.52</v>
+        <v>363.2</v>
       </c>
       <c r="F7" s="14">
-        <f t="shared" si="0"/>
-        <v>28.58</v>
+        <f>IFERROR(((VLOOKUP(B7,cours,7,FALSE))),"")</f>
+        <v>360.5</v>
       </c>
       <c r="G7" s="15">
-        <f t="shared" si="1"/>
-        <v>2.1037868162692153E-3</v>
+        <f>(F7/E7-1)</f>
+        <v>-7.4339207048458311E-3</v>
       </c>
       <c r="H7" s="7"/>
       <c r="I7" s="17"/>
@@ -22839,24 +23228,24 @@
         <v>7</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="C8" s="10" t="s">
         <v>12</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>133</v>
+        <v>24</v>
       </c>
       <c r="E8" s="13">
-        <v>22</v>
+        <v>24.75</v>
       </c>
       <c r="F8" s="14">
-        <f t="shared" si="0"/>
-        <v>22.05</v>
+        <f>IFERROR(((VLOOKUP(B8,cours,7,FALSE))),"")</f>
+        <v>25.6</v>
       </c>
       <c r="G8" s="15">
-        <f t="shared" si="1"/>
-        <v>2.2727272727272041E-3</v>
+        <f>(F8/E8-1)</f>
+        <v>3.4343434343434343E-2</v>
       </c>
       <c r="H8" s="7"/>
       <c r="I8" s="17"/>
@@ -22870,24 +23259,24 @@
         <v>8</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>134</v>
+        <v>27</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>135</v>
+        <v>28</v>
       </c>
       <c r="E9" s="13">
-        <v>0.24199999999999999</v>
+        <v>203</v>
       </c>
       <c r="F9" s="14">
-        <f t="shared" si="0"/>
-        <v>0.28999999999999998</v>
+        <f>IFERROR(((VLOOKUP(B9,cours,7,FALSE))),"")</f>
+        <v>206.4</v>
       </c>
       <c r="G9" s="15">
-        <f t="shared" si="1"/>
-        <v>0.19834710743801653</v>
+        <f>(F9/E9-1)</f>
+        <v>1.6748768472906406E-2</v>
       </c>
       <c r="H9" s="7"/>
       <c r="I9" s="17"/>
@@ -22901,24 +23290,24 @@
         <v>9</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>136</v>
+        <v>167</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>12</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>137</v>
+        <v>166</v>
       </c>
       <c r="E10" s="13">
-        <v>1.88</v>
+        <v>4.25</v>
       </c>
       <c r="F10" s="14">
-        <f t="shared" si="0"/>
-        <v>1.8779999999999999</v>
+        <f>IFERROR(((VLOOKUP(B10,cours,7,FALSE))),"")</f>
+        <v>4.3099999999999996</v>
       </c>
       <c r="G10" s="15">
-        <f t="shared" si="1"/>
-        <v>-1.0638297872340718E-3</v>
+        <f>(F10/E10-1)</f>
+        <v>1.4117647058823346E-2</v>
       </c>
       <c r="H10" s="7"/>
       <c r="I10" s="17"/>
@@ -22932,24 +23321,24 @@
         <v>10</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>117</v>
+        <v>143</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>12</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>118</v>
+        <v>142</v>
       </c>
       <c r="E11" s="13">
-        <v>158.6</v>
+        <v>61.85</v>
       </c>
       <c r="F11" s="14">
-        <f t="shared" si="0"/>
-        <v>158.9</v>
+        <f>IFERROR(((VLOOKUP(B11,cours,7,FALSE))),"")</f>
+        <v>62.2</v>
       </c>
       <c r="G11" s="15">
-        <f t="shared" si="1"/>
-        <v>1.8915510718791051E-3</v>
+        <f>(F11/E11-1)</f>
+        <v>5.6588520614389015E-3</v>
       </c>
       <c r="H11" s="7"/>
       <c r="I11" s="23"/>
@@ -22969,35 +23358,37 @@
       </c>
       <c r="G12" s="27">
         <f>AVERAGE(G2:G11)</f>
-        <v>3.8288338227792651E-2</v>
+        <v>-3.2795303289897882E-3</v>
       </c>
       <c r="H12" s="28" t="s">
         <v>30</v>
       </c>
       <c r="I12" s="29">
+        <f>COUNTIF(G2:G11,"&gt;0")</f>
         <v>7</v>
       </c>
       <c r="J12" s="30" t="s">
         <v>31</v>
       </c>
       <c r="K12" s="31">
+        <f>COUNTIF(G2:G11,"&lt;0")</f>
         <v>3</v>
       </c>
       <c r="L12" s="19"/>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.4">
-      <c r="B13" s="16"/>
       <c r="F13" s="7"/>
       <c r="H13" s="7"/>
+      <c r="I13"/>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.4">
-      <c r="B14" s="16"/>
       <c r="F14" s="7"/>
       <c r="H14" s="7"/>
+      <c r="I14"/>
     </row>
     <row r="15" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>1</v>
@@ -23009,94 +23400,95 @@
         <v>3</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>121</v>
+        <v>4</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>124</v>
+        <v>6</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="I15" s="7"/>
     </row>
     <row r="16" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A16" s="12">
         <v>1</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>138</v>
+        <v>36</v>
       </c>
       <c r="C16" s="10" t="s">
         <v>12</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>139</v>
+        <v>37</v>
       </c>
       <c r="E16" s="13">
-        <v>1.5960000000000001</v>
+        <v>5.37</v>
       </c>
       <c r="F16" s="14">
-        <f t="shared" ref="F16:F25" si="2">IFERROR(((VLOOKUP(B16,cours,7,FALSE))),"")</f>
-        <v>1.694</v>
+        <f>IFERROR(((VLOOKUP(B16,cours,7,FALSE))),"")</f>
+        <v>5.4349999999999996</v>
       </c>
       <c r="G16" s="15">
-        <f t="shared" ref="G16:G25" si="3">(F16/E16-1)</f>
-        <v>6.1403508771929793E-2</v>
+        <f>(F16/E16-1)</f>
+        <v>1.2104283054003684E-2</v>
       </c>
       <c r="H16" s="32"/>
+      <c r="I16"/>
     </row>
     <row r="17" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A17" s="21">
         <v>2</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="E17" s="13">
-        <v>163</v>
+        <v>30.8</v>
       </c>
       <c r="F17" s="14">
-        <f t="shared" si="2"/>
-        <v>168.6</v>
+        <f>IFERROR(((VLOOKUP(B17,cours,7,FALSE))),"")</f>
+        <v>29.56</v>
       </c>
       <c r="G17" s="15">
-        <f t="shared" si="3"/>
-        <v>3.4355828220858919E-2</v>
+        <f>(F17/E17-1)</f>
+        <v>-4.0259740259740329E-2</v>
       </c>
       <c r="H17" s="7"/>
+      <c r="I17"/>
     </row>
     <row r="18" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A18" s="12">
         <v>3</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="C18" s="10" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="E18" s="13">
-        <v>166.7</v>
+        <v>5.2439999999999998</v>
       </c>
       <c r="F18" s="14">
-        <f t="shared" si="2"/>
-        <v>185.5</v>
+        <f>IFERROR(((VLOOKUP(B18,cours,7,FALSE))),"")</f>
+        <v>5.45</v>
       </c>
       <c r="G18" s="15">
-        <f t="shared" si="3"/>
-        <v>0.11277744451109784</v>
+        <f>(F18/E18-1)</f>
+        <v>3.9282990083905567E-2</v>
       </c>
       <c r="H18" s="7"/>
       <c r="I18" s="17"/>
@@ -23106,50 +23498,51 @@
         <v>4</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>142</v>
+        <v>46</v>
       </c>
       <c r="C19" s="10" t="s">
         <v>12</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>143</v>
+        <v>47</v>
       </c>
       <c r="E19" s="13">
-        <v>1.8560000000000001</v>
+        <v>6.62</v>
       </c>
       <c r="F19" s="14">
-        <f t="shared" si="2"/>
-        <v>2</v>
+        <f>IFERROR(((VLOOKUP(B19,cours,7,FALSE))),"")</f>
+        <v>6.58</v>
       </c>
       <c r="G19" s="15">
-        <f t="shared" si="3"/>
-        <v>7.7586206896551602E-2</v>
+        <f>(F19/E19-1)</f>
+        <v>-6.0422960725076136E-3</v>
       </c>
       <c r="H19" s="7"/>
+      <c r="I19"/>
     </row>
     <row r="20" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A20" s="12">
         <v>5</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="C20" s="10" t="s">
         <v>12</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="E20" s="13">
-        <v>35.74</v>
+        <v>7.0049999999999999</v>
       </c>
       <c r="F20" s="14">
-        <f t="shared" si="2"/>
-        <v>39.380000000000003</v>
+        <f>IFERROR(((VLOOKUP(B20,cours,7,FALSE))),"")</f>
+        <v>7.4649999999999999</v>
       </c>
       <c r="G20" s="15">
-        <f t="shared" si="3"/>
-        <v>0.10184667039731399</v>
+        <f>(F20/E20-1)</f>
+        <v>6.5667380442540946E-2</v>
       </c>
       <c r="H20" s="7"/>
       <c r="I20" s="17"/>
@@ -23159,130 +23552,135 @@
         <v>6</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="C21" s="10" t="s">
         <v>12</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="E21" s="13">
-        <v>2.35</v>
+        <v>3.7719999999999998</v>
       </c>
       <c r="F21" s="14">
-        <f t="shared" si="2"/>
-        <v>2.3660000000000001</v>
+        <f>IFERROR(((VLOOKUP(B21,cours,7,FALSE))),"")</f>
+        <v>3.8679999999999999</v>
       </c>
       <c r="G21" s="15">
-        <f t="shared" si="3"/>
-        <v>6.8085106382977933E-3</v>
+        <f>(F21/E21-1)</f>
+        <v>2.5450689289501671E-2</v>
       </c>
       <c r="H21" s="7"/>
+      <c r="I21"/>
     </row>
     <row r="22" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A22" s="12">
         <v>7</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>146</v>
+        <v>52</v>
       </c>
       <c r="C22" s="10" t="s">
         <v>12</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>147</v>
+        <v>53</v>
       </c>
       <c r="E22" s="13">
-        <v>32.75</v>
+        <v>344</v>
       </c>
       <c r="F22" s="14">
-        <f t="shared" si="2"/>
-        <v>34.25</v>
+        <f>IFERROR(((VLOOKUP(B22,cours,7,FALSE))),"")</f>
+        <v>343</v>
       </c>
       <c r="G22" s="15">
-        <f t="shared" si="3"/>
-        <v>4.5801526717557328E-2</v>
+        <f>(F22/E22-1)</f>
+        <v>-2.9069767441860517E-3</v>
       </c>
       <c r="H22" s="7"/>
+      <c r="I22"/>
     </row>
     <row r="23" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A23" s="21">
         <v>8</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="E23" s="13">
-        <v>6.4850000000000003</v>
+        <v>43.1</v>
       </c>
       <c r="F23" s="14">
-        <f t="shared" si="2"/>
-        <v>6.665</v>
+        <f>IFERROR(((VLOOKUP(B23,cours,7,FALSE))),"")</f>
+        <v>43.6</v>
       </c>
       <c r="G23" s="15">
-        <f t="shared" si="3"/>
-        <v>2.775636083269073E-2</v>
+        <f>(F23/E23-1)</f>
+        <v>1.1600928074245953E-2</v>
       </c>
       <c r="H23" s="7"/>
+      <c r="I23"/>
     </row>
     <row r="24" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A24" s="12">
         <v>9</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="C24" s="10" t="s">
         <v>12</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="E24" s="13">
-        <v>4.9710000000000001</v>
+        <v>2.0659999999999998</v>
       </c>
       <c r="F24" s="14">
-        <f t="shared" si="2"/>
-        <v>4.6100000000000003</v>
+        <f>IFERROR(((VLOOKUP(B24,cours,7,FALSE))),"")</f>
+        <v>2.15</v>
       </c>
       <c r="G24" s="15">
-        <f t="shared" si="3"/>
-        <v>-7.2621202977268151E-2</v>
+        <f>(F24/E24-1)</f>
+        <v>4.0658276863504428E-2</v>
       </c>
       <c r="H24" s="7"/>
+      <c r="I24"/>
     </row>
     <row r="25" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A25" s="21">
         <v>10</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C25" s="10" t="s">
         <v>12</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E25" s="13">
-        <v>46.52</v>
+        <v>1644.5</v>
       </c>
       <c r="F25" s="14">
-        <f t="shared" si="2"/>
-        <v>47.9</v>
+        <f>IFERROR(((VLOOKUP(B25,cours,7,FALSE))),"")</f>
+        <v>1576</v>
       </c>
       <c r="G25" s="15">
-        <f t="shared" si="3"/>
-        <v>2.9664660361134798E-2</v>
+        <f>(F25/E25-1)</f>
+        <v>-4.1653998175737339E-2</v>
       </c>
       <c r="H25" s="7"/>
+      <c r="I25"/>
     </row>
     <row r="26" spans="1:11" ht="15.9" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A26" s="21"/>
@@ -23295,18 +23693,20 @@
       </c>
       <c r="G26" s="34">
         <f>AVERAGE(G16:G25)</f>
-        <v>4.2537951437016462E-2</v>
+        <v>1.0390153655553092E-2</v>
       </c>
       <c r="H26" s="28" t="s">
         <v>30</v>
       </c>
       <c r="I26" s="29">
+        <f>COUNTIF(G16:G25,"&gt;0")</f>
         <v>6</v>
       </c>
       <c r="J26" s="30" t="s">
         <v>31</v>
       </c>
       <c r="K26" s="31">
+        <f>COUNTIF(G16:G25,"&lt;0")</f>
         <v>4</v>
       </c>
     </row>
@@ -23317,16 +23717,15 @@
       <c r="D27" s="37"/>
       <c r="F27" s="7"/>
       <c r="H27" s="7"/>
+      <c r="I27"/>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="B28" s="16"/>
       <c r="F28" s="7"/>
       <c r="H28" s="7"/>
-      <c r="I28" s="7"/>
     </row>
     <row r="29" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A29" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>1</v>
@@ -23338,217 +23737,231 @@
         <v>3</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>110</v>
+        <v>4</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>124</v>
+        <v>6</v>
       </c>
       <c r="H29" s="6" t="s">
         <v>54</v>
       </c>
+      <c r="I29"/>
     </row>
     <row r="30" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A30" s="12">
         <v>1</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>153</v>
+        <v>113</v>
       </c>
       <c r="C30" s="10" t="s">
         <v>56</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>154</v>
+        <v>114</v>
       </c>
       <c r="E30" s="13">
-        <v>21</v>
+        <v>0.51900000000000002</v>
       </c>
       <c r="F30" s="14">
-        <f t="shared" ref="F30:F39" si="4">IFERROR(((VLOOKUP(B30,cours,7,FALSE))),"")</f>
-        <v>21.594999999999999</v>
+        <f>IFERROR(((VLOOKUP(B30,cours,7,FALSE))),"")</f>
+        <v>0.78</v>
       </c>
       <c r="G30" s="15">
-        <f t="shared" ref="G30:G39" si="5">(F30/E30-1)</f>
-        <v>2.8333333333333321E-2</v>
-      </c>
+        <f>(F30/E30-1)</f>
+        <v>0.50289017341040454</v>
+      </c>
+      <c r="H30"/>
+      <c r="I30"/>
     </row>
     <row r="31" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A31" s="21">
         <v>2</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>115</v>
+        <v>155</v>
       </c>
       <c r="C31" s="10" t="s">
         <v>56</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>116</v>
+        <v>154</v>
       </c>
       <c r="E31" s="13">
-        <v>0.32500000000000001</v>
+        <v>6.3E-2</v>
       </c>
       <c r="F31" s="14">
-        <f t="shared" si="4"/>
-        <v>0.78</v>
+        <f>IFERROR(((VLOOKUP(B31,cours,7,FALSE))),"")</f>
+        <v>6.4000000000000001E-2</v>
       </c>
       <c r="G31" s="15">
-        <f t="shared" si="5"/>
-        <v>1.4</v>
-      </c>
+        <f>(F31/E31-1)</f>
+        <v>1.5873015873015817E-2</v>
+      </c>
+      <c r="H31"/>
+      <c r="I31"/>
     </row>
     <row r="32" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A32" s="12">
         <v>3</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C32" s="10" t="s">
         <v>56</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E32" s="13">
-        <v>1.53</v>
-      </c>
-      <c r="F32" s="14">
-        <f t="shared" si="4"/>
-        <v>1.6</v>
-      </c>
-      <c r="G32" s="15">
-        <f t="shared" si="5"/>
-        <v>4.5751633986928164E-2</v>
-      </c>
+        <v>1.155</v>
+      </c>
+      <c r="F32" s="14" t="str">
+        <f>IFERROR(((VLOOKUP(B32,cours,7,FALSE))),"")</f>
+        <v/>
+      </c>
+      <c r="G32" s="15"/>
+      <c r="H32"/>
+      <c r="I32"/>
     </row>
     <row r="33" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A33" s="21">
         <v>4</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="C33" s="10" t="s">
         <v>56</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="E33" s="13">
-        <v>2E-3</v>
+        <v>0.17899999999999999</v>
       </c>
       <c r="F33" s="14">
-        <f t="shared" si="4"/>
-        <v>1E-3</v>
+        <f>IFERROR(((VLOOKUP(B33,cours,7,FALSE))),"")</f>
+        <v>0.18</v>
       </c>
       <c r="G33" s="15">
-        <f t="shared" si="5"/>
-        <v>-0.5</v>
-      </c>
+        <f>(F33/E33-1)</f>
+        <v>5.5865921787709993E-3</v>
+      </c>
+      <c r="H33"/>
+      <c r="I33"/>
     </row>
     <row r="34" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A34" s="12">
         <v>5</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>159</v>
+        <v>65</v>
       </c>
       <c r="C34" s="10" t="s">
         <v>56</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>160</v>
+        <v>66</v>
       </c>
       <c r="E34" s="13">
-        <v>6.72</v>
+        <v>28.7</v>
       </c>
       <c r="F34" s="14">
-        <f t="shared" si="4"/>
-        <v>6.44</v>
+        <f>IFERROR(((VLOOKUP(B34,cours,7,FALSE))),"")</f>
+        <v>27.86</v>
       </c>
       <c r="G34" s="15">
-        <f t="shared" si="5"/>
-        <v>-4.1666666666666519E-2</v>
-      </c>
+        <f>(F34/E34-1)</f>
+        <v>-2.9268292682926855E-2</v>
+      </c>
+      <c r="H34"/>
+      <c r="I34"/>
     </row>
     <row r="35" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A35" s="21">
         <v>6</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>161</v>
+        <v>68</v>
       </c>
       <c r="C35" s="10" t="s">
         <v>56</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>162</v>
+        <v>69</v>
       </c>
       <c r="E35" s="13">
-        <v>3.88</v>
+        <v>21.4</v>
       </c>
       <c r="F35" s="14">
-        <f t="shared" si="4"/>
-        <v>3.6</v>
+        <f>IFERROR(((VLOOKUP(B35,cours,7,FALSE))),"")</f>
+        <v>22.4</v>
       </c>
       <c r="G35" s="15">
-        <f t="shared" si="5"/>
-        <v>-7.2164948453608213E-2</v>
-      </c>
+        <f>(F35/E35-1)</f>
+        <v>4.6728971962616717E-2</v>
+      </c>
+      <c r="H35"/>
+      <c r="I35"/>
     </row>
     <row r="36" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A36" s="12">
         <v>7</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="C36" s="10" t="s">
         <v>56</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="E36" s="13">
-        <v>6.04</v>
+        <v>9.7799999999999994</v>
       </c>
       <c r="F36" s="14">
-        <f t="shared" si="4"/>
-        <v>5.22</v>
+        <f>IFERROR(((VLOOKUP(B36,cours,7,FALSE))),"")</f>
+        <v>9.7200000000000006</v>
       </c>
       <c r="G36" s="15">
-        <f t="shared" si="5"/>
-        <v>-0.13576158940397354</v>
-      </c>
+        <f>(F36/E36-1)</f>
+        <v>-6.1349693251532278E-3</v>
+      </c>
+      <c r="H36"/>
+      <c r="I36"/>
     </row>
     <row r="37" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A37" s="21">
         <v>8</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>165</v>
+        <v>63</v>
       </c>
       <c r="C37" s="10" t="s">
         <v>56</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>166</v>
+        <v>64</v>
       </c>
       <c r="E37" s="13">
-        <v>8.26</v>
+        <v>2E-3</v>
       </c>
       <c r="F37" s="14">
-        <f t="shared" si="4"/>
-        <v>8.32</v>
+        <f>IFERROR(((VLOOKUP(B37,cours,7,FALSE))),"")</f>
+        <v>2E-3</v>
       </c>
       <c r="G37" s="15">
-        <f t="shared" si="5"/>
-        <v>7.2639225181598821E-3</v>
-      </c>
+        <f>(F37/E37-1)</f>
+        <v>0</v>
+      </c>
+      <c r="H37"/>
+      <c r="I37"/>
       <c r="P37" s="38"/>
     </row>
     <row r="38" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
@@ -23556,25 +23969,27 @@
         <v>9</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>72</v>
+        <v>147</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>73</v>
+        <v>146</v>
       </c>
       <c r="E38" s="13">
-        <v>2.8</v>
+        <v>1.44</v>
       </c>
       <c r="F38" s="14">
-        <f t="shared" si="4"/>
-        <v>3.09</v>
+        <f>IFERROR(((VLOOKUP(B38,cours,7,FALSE))),"")</f>
+        <v>1.43</v>
       </c>
       <c r="G38" s="15">
-        <f t="shared" si="5"/>
-        <v>0.10357142857142865</v>
-      </c>
+        <f>(F38/E38-1)</f>
+        <v>-6.9444444444444198E-3</v>
+      </c>
+      <c r="H38"/>
+      <c r="I38"/>
       <c r="P38" s="38"/>
     </row>
     <row r="39" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
@@ -23582,25 +23997,27 @@
         <v>10</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>167</v>
+        <v>145</v>
       </c>
       <c r="C39" s="10" t="s">
         <v>56</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>168</v>
+        <v>144</v>
       </c>
       <c r="E39" s="13">
-        <v>5.0000000000000001E-3</v>
+        <v>3.11</v>
       </c>
       <c r="F39" s="14">
-        <f t="shared" si="4"/>
-        <v>4.0000000000000001E-3</v>
+        <f>IFERROR(((VLOOKUP(B39,cours,7,FALSE))),"")</f>
+        <v>2.82</v>
       </c>
       <c r="G39" s="15">
-        <f t="shared" si="5"/>
-        <v>-0.19999999999999996</v>
-      </c>
+        <f>(F39/E39-1)</f>
+        <v>-9.3247588424437367E-2</v>
+      </c>
+      <c r="H39"/>
+      <c r="I39"/>
     </row>
     <row r="40" spans="1:16" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A40" s="21"/>
@@ -23612,11 +24029,13 @@
       </c>
       <c r="G40" s="41">
         <f>AVERAGE(G30:G39)</f>
-        <v>6.3532711388560176E-2</v>
+        <v>4.8387050949760688E-2</v>
       </c>
       <c r="H40">
+        <f>COUNTIF(G30:G39,"&lt;0")</f>
         <v>4</v>
       </c>
+      <c r="I40"/>
     </row>
     <row r="41" spans="1:16" ht="15.45" x14ac:dyDescent="0.4">
       <c r="B41" s="39"/>
@@ -23624,11 +24043,13 @@
       <c r="D41" s="43"/>
       <c r="F41" s="44"/>
       <c r="G41" s="45"/>
+      <c r="H41"/>
+      <c r="I41"/>
       <c r="K41" s="31"/>
     </row>
     <row r="42" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A42" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>1</v>
@@ -23640,187 +24061,288 @@
         <v>3</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>169</v>
+        <v>4</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>124</v>
+        <v>6</v>
       </c>
       <c r="H42" s="6" t="s">
         <v>76</v>
       </c>
+      <c r="I42"/>
     </row>
     <row r="43" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A43" s="12">
         <v>1</v>
       </c>
-      <c r="B43" s="10"/>
-      <c r="C43" s="10"/>
-      <c r="D43" s="11"/>
-      <c r="E43" s="13"/>
-      <c r="F43" s="14" t="str">
-        <f t="shared" ref="F43:F52" si="6">IFERROR(((VLOOKUP(B43,cours,7,FALSE))),"")</f>
-        <v/>
-      </c>
-      <c r="G43" s="15" t="e">
-        <f t="shared" ref="G43:G52" si="7">(F43/E43-1)</f>
-        <v>#VALUE!</v>
-      </c>
+      <c r="B43" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="C43" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D43" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="E43" s="13">
+        <v>43.9</v>
+      </c>
+      <c r="F43" s="14">
+        <f>IFERROR(((VLOOKUP(B43,cours,7,FALSE))),"")</f>
+        <v>44.9</v>
+      </c>
+      <c r="G43" s="15">
+        <f>(F43/E43-1)</f>
+        <v>2.277904328018221E-2</v>
+      </c>
+      <c r="H43"/>
+      <c r="I43"/>
     </row>
     <row r="44" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A44" s="21">
         <v>2</v>
       </c>
-      <c r="B44" s="10"/>
-      <c r="C44" s="10"/>
-      <c r="D44" s="11"/>
-      <c r="E44" s="13"/>
-      <c r="F44" s="14" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="G44" s="15" t="e">
-        <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
+      <c r="B44" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="C44" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D44" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="E44" s="13">
+        <v>61.85</v>
+      </c>
+      <c r="F44" s="14">
+        <f>IFERROR(((VLOOKUP(B44,cours,7,FALSE))),"")</f>
+        <v>62.2</v>
+      </c>
+      <c r="G44" s="15">
+        <f>(F44/E44-1)</f>
+        <v>5.6588520614389015E-3</v>
+      </c>
+      <c r="H44"/>
+      <c r="I44"/>
     </row>
     <row r="45" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A45" s="12">
         <v>3</v>
       </c>
-      <c r="B45" s="10"/>
-      <c r="C45" s="10"/>
-      <c r="D45" s="11"/>
-      <c r="E45" s="13"/>
-      <c r="F45" s="14" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="G45" s="15" t="e">
-        <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
+      <c r="B45" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="C45" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D45" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="E45" s="13">
+        <v>23</v>
+      </c>
+      <c r="F45" s="14">
+        <f>IFERROR(((VLOOKUP(B45,cours,7,FALSE))),"")</f>
+        <v>23.65</v>
+      </c>
+      <c r="G45" s="15">
+        <f>(F45/E45-1)</f>
+        <v>2.8260869565217339E-2</v>
+      </c>
+      <c r="H45"/>
+      <c r="I45"/>
     </row>
     <row r="46" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A46" s="21">
         <v>4</v>
       </c>
-      <c r="B46" s="10"/>
-      <c r="C46" s="10"/>
-      <c r="D46" s="11"/>
-      <c r="E46" s="13"/>
-      <c r="F46" s="14" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="G46" s="15" t="e">
-        <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
+      <c r="B46" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C46" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D46" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="E46" s="13">
+        <v>203</v>
+      </c>
+      <c r="F46" s="14">
+        <f>IFERROR(((VLOOKUP(B46,cours,7,FALSE))),"")</f>
+        <v>206.4</v>
+      </c>
+      <c r="G46" s="15">
+        <f>(F46/E46-1)</f>
+        <v>1.6748768472906406E-2</v>
+      </c>
+      <c r="H46"/>
+      <c r="I46"/>
     </row>
     <row r="47" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A47" s="12">
         <v>5</v>
       </c>
-      <c r="B47" s="10"/>
-      <c r="C47" s="10"/>
-      <c r="D47" s="11"/>
-      <c r="E47" s="13"/>
-      <c r="F47" s="14" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="G47" s="15" t="e">
-        <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
+      <c r="B47" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="C47" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D47" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="E47" s="13">
+        <v>28.4</v>
+      </c>
+      <c r="F47" s="14">
+        <f>IFERROR(((VLOOKUP(B47,cours,7,FALSE))),"")</f>
+        <v>27.57</v>
+      </c>
+      <c r="G47" s="15">
+        <f>(F47/E47-1)</f>
+        <v>-2.9225352112675962E-2</v>
+      </c>
+      <c r="H47"/>
+      <c r="I47"/>
     </row>
     <row r="48" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A48" s="21">
         <v>6</v>
       </c>
-      <c r="B48" s="10"/>
-      <c r="C48" s="10"/>
-      <c r="D48" s="11"/>
-      <c r="E48" s="13"/>
-      <c r="F48" s="14" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="G48" s="15" t="e">
-        <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
+      <c r="B48" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C48" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D48" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E48" s="13">
+        <v>24.75</v>
+      </c>
+      <c r="F48" s="14">
+        <f>IFERROR(((VLOOKUP(B48,cours,7,FALSE))),"")</f>
+        <v>25.6</v>
+      </c>
+      <c r="G48" s="15">
+        <f>(F48/E48-1)</f>
+        <v>3.4343434343434343E-2</v>
+      </c>
+      <c r="H48"/>
+      <c r="I48"/>
     </row>
     <row r="49" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A49" s="12">
         <v>7</v>
       </c>
-      <c r="B49" s="10"/>
-      <c r="C49" s="10"/>
-      <c r="D49" s="11"/>
-      <c r="E49" s="13"/>
-      <c r="F49" s="14" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="G49" s="15" t="e">
-        <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
+      <c r="B49" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="C49" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D49" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="E49" s="13">
+        <v>73.3</v>
+      </c>
+      <c r="F49" s="14">
+        <f>IFERROR(((VLOOKUP(B49,cours,7,FALSE))),"")</f>
+        <v>73.099999999999994</v>
+      </c>
+      <c r="G49" s="15">
+        <f>(F49/E49-1)</f>
+        <v>-2.7285129604366354E-3</v>
+      </c>
+      <c r="H49"/>
+      <c r="I49"/>
     </row>
     <row r="50" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A50" s="21">
         <v>8</v>
       </c>
-      <c r="B50" s="10"/>
-      <c r="C50" s="10"/>
-      <c r="D50" s="11"/>
-      <c r="E50" s="13"/>
-      <c r="F50" s="14" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="G50" s="15" t="e">
-        <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
+      <c r="B50" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="C50" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D50" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="E50" s="13">
+        <v>2.06</v>
+      </c>
+      <c r="F50" s="14">
+        <f>IFERROR(((VLOOKUP(B50,cours,7,FALSE))),"")</f>
+        <v>2.145</v>
+      </c>
+      <c r="G50" s="15">
+        <f>(F50/E50-1)</f>
+        <v>4.1262135922329968E-2</v>
+      </c>
+      <c r="H50"/>
+      <c r="I50"/>
     </row>
     <row r="51" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A51" s="12">
         <v>9</v>
       </c>
-      <c r="B51" s="10"/>
-      <c r="C51" s="10"/>
-      <c r="D51" s="11"/>
-      <c r="E51" s="13"/>
-      <c r="F51" s="14" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="G51" s="15" t="e">
-        <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
+      <c r="B51" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="C51" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D51" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="E51" s="13">
+        <v>163</v>
+      </c>
+      <c r="F51" s="14">
+        <f>IFERROR(((VLOOKUP(B51,cours,7,FALSE))),"")</f>
+        <v>158.9</v>
+      </c>
+      <c r="G51" s="15">
+        <f>(F51/E51-1)</f>
+        <v>-2.51533742331288E-2</v>
+      </c>
+      <c r="H51"/>
+      <c r="I51"/>
     </row>
     <row r="52" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A52" s="21">
         <v>10</v>
       </c>
-      <c r="B52" s="10"/>
-      <c r="C52" s="10"/>
-      <c r="D52" s="11"/>
-      <c r="E52" s="13"/>
-      <c r="F52" s="14" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="G52" s="15" t="e">
-        <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
+      <c r="B52" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="C52" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D52" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="E52" s="13">
+        <v>26.7</v>
+      </c>
+      <c r="F52" s="14">
+        <f>IFERROR(((VLOOKUP(B52,cours,7,FALSE))),"")</f>
+        <v>26.6</v>
+      </c>
+      <c r="G52" s="15">
+        <f>(F52/E52-1)</f>
+        <v>-3.7453183520598232E-3</v>
+      </c>
+      <c r="H52"/>
+      <c r="I52"/>
     </row>
     <row r="53" spans="1:11" ht="15.9" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A53" s="21"/>
@@ -23830,20 +24352,22 @@
       <c r="F53" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="G53" s="46" t="e">
+      <c r="G53" s="46">
         <f>AVERAGE(G43:G52)</f>
-        <v>#VALUE!</v>
+        <v>8.8200545987207942E-3</v>
       </c>
       <c r="H53" s="28" t="s">
         <v>30</v>
       </c>
       <c r="I53" s="29">
+        <f>COUNTIF(G43:G52,"&gt;0")</f>
         <v>6</v>
       </c>
       <c r="J53" s="30" t="s">
         <v>31</v>
       </c>
       <c r="K53" s="31">
+        <f>COUNTIF(G43:G52,"&lt;0")</f>
         <v>4</v>
       </c>
     </row>
@@ -23854,10 +24378,11 @@
       <c r="F54" s="44"/>
       <c r="G54" s="47"/>
       <c r="H54" s="7"/>
+      <c r="I54"/>
     </row>
     <row r="55" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A55" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>1</v>
@@ -23869,203 +24394,290 @@
         <v>3</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="F55" s="129" t="s">
         <v>4</v>
       </c>
-      <c r="G55" s="130" t="s">
-        <v>124</v>
+      <c r="F55" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G55" s="5" t="s">
+        <v>6</v>
       </c>
       <c r="H55" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="I55" s="7"/>
     </row>
     <row r="56" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A56" s="12">
         <v>1</v>
       </c>
-      <c r="B56" s="48"/>
-      <c r="C56" s="42"/>
-      <c r="D56" s="48"/>
-      <c r="E56" s="127"/>
-      <c r="F56" s="14" t="str">
-        <f t="shared" ref="F56:F65" si="8">IFERROR(((VLOOKUP(B56,cours,7,0))),"")</f>
-        <v/>
-      </c>
-      <c r="G56" s="49" t="e">
-        <f t="shared" ref="G56:G65" si="9">(F56/E56-1)</f>
-        <v>#VALUE!</v>
+      <c r="B56" s="48" t="s">
+        <v>94</v>
+      </c>
+      <c r="C56" s="42" t="s">
+        <v>12</v>
+      </c>
+      <c r="D56" s="48" t="s">
+        <v>95</v>
+      </c>
+      <c r="E56" s="127">
+        <v>112.8</v>
+      </c>
+      <c r="F56" s="14">
+        <f>IFERROR(((VLOOKUP(B56,cours,7,0))),"")</f>
+        <v>112.1</v>
+      </c>
+      <c r="G56" s="49">
+        <f>(F56/E56-1)</f>
+        <v>-6.2056737588652711E-3</v>
       </c>
       <c r="H56" s="7"/>
-      <c r="I56" s="7"/>
     </row>
     <row r="57" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A57" s="21">
         <v>2</v>
       </c>
-      <c r="B57" s="48"/>
-      <c r="C57" s="42"/>
-      <c r="D57" s="48"/>
-      <c r="E57" s="127"/>
-      <c r="F57" s="14" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="G57" s="49" t="e">
-        <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+      <c r="B57" s="48" t="s">
+        <v>135</v>
+      </c>
+      <c r="C57" s="42" t="s">
+        <v>12</v>
+      </c>
+      <c r="D57" s="48" t="s">
+        <v>134</v>
+      </c>
+      <c r="E57" s="127">
+        <v>267.39999999999998</v>
+      </c>
+      <c r="F57" s="14">
+        <f>IFERROR(((VLOOKUP(B57,cours,7,0))),"")</f>
+        <v>270.39999999999998</v>
+      </c>
+      <c r="G57" s="49">
+        <f>(F57/E57-1)</f>
+        <v>1.1219147344801783E-2</v>
       </c>
       <c r="H57" s="7"/>
+      <c r="I57"/>
     </row>
     <row r="58" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A58" s="12">
         <v>3</v>
       </c>
-      <c r="B58" s="48"/>
-      <c r="C58" s="42"/>
-      <c r="D58" s="48"/>
-      <c r="E58" s="127"/>
-      <c r="F58" s="14" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="G58" s="49" t="e">
-        <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+      <c r="B58" s="48" t="s">
+        <v>103</v>
+      </c>
+      <c r="C58" s="42" t="s">
+        <v>12</v>
+      </c>
+      <c r="D58" s="48" t="s">
+        <v>104</v>
+      </c>
+      <c r="E58" s="127">
+        <v>52.9</v>
+      </c>
+      <c r="F58" s="14">
+        <f>IFERROR(((VLOOKUP(B58,cours,7,0))),"")</f>
+        <v>51.75</v>
+      </c>
+      <c r="G58" s="49">
+        <f>(F58/E58-1)</f>
+        <v>-2.1739130434782594E-2</v>
       </c>
       <c r="H58" s="7"/>
+      <c r="I58"/>
       <c r="K58" s="50"/>
     </row>
     <row r="59" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A59" s="21">
         <v>4</v>
       </c>
-      <c r="B59" s="48"/>
-      <c r="C59" s="42"/>
-      <c r="D59" s="48"/>
-      <c r="E59" s="127"/>
-      <c r="F59" s="14" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="G59" s="49" t="e">
-        <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+      <c r="B59" s="48" t="s">
+        <v>96</v>
+      </c>
+      <c r="C59" s="42" t="s">
+        <v>12</v>
+      </c>
+      <c r="D59" s="48" t="s">
+        <v>97</v>
+      </c>
+      <c r="E59" s="127">
+        <v>98.6</v>
+      </c>
+      <c r="F59" s="14">
+        <f>IFERROR(((VLOOKUP(B59,cours,7,0))),"")</f>
+        <v>101.8</v>
+      </c>
+      <c r="G59" s="49">
+        <f>(F59/E59-1)</f>
+        <v>3.2454361054766734E-2</v>
       </c>
       <c r="H59" s="7"/>
+      <c r="I59"/>
       <c r="K59" s="50"/>
     </row>
     <row r="60" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A60" s="12">
         <v>5</v>
       </c>
-      <c r="B60" s="48"/>
-      <c r="C60" s="42"/>
-      <c r="D60" s="48"/>
-      <c r="E60" s="127"/>
-      <c r="F60" s="14" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="G60" s="49" t="e">
-        <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+      <c r="B60" s="48" t="s">
+        <v>133</v>
+      </c>
+      <c r="C60" s="42" t="s">
+        <v>12</v>
+      </c>
+      <c r="D60" s="48" t="s">
+        <v>132</v>
+      </c>
+      <c r="E60" s="127">
+        <v>363.2</v>
+      </c>
+      <c r="F60" s="14">
+        <f>IFERROR(((VLOOKUP(B60,cours,7,0))),"")</f>
+        <v>360.5</v>
+      </c>
+      <c r="G60" s="49">
+        <f>(F60/E60-1)</f>
+        <v>-7.4339207048458311E-3</v>
       </c>
       <c r="H60" s="7"/>
+      <c r="I60"/>
       <c r="K60" s="50"/>
     </row>
     <row r="61" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A61" s="21">
         <v>6</v>
       </c>
-      <c r="B61" s="48"/>
-      <c r="C61" s="42"/>
-      <c r="D61" s="48"/>
-      <c r="E61" s="127"/>
-      <c r="F61" s="14" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="G61" s="49" t="e">
-        <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+      <c r="B61" s="48" t="s">
+        <v>91</v>
+      </c>
+      <c r="C61" s="42" t="s">
+        <v>12</v>
+      </c>
+      <c r="D61" s="48" t="s">
+        <v>92</v>
+      </c>
+      <c r="E61" s="127">
+        <v>75.540000000000006</v>
+      </c>
+      <c r="F61" s="14">
+        <f>IFERROR(((VLOOKUP(B61,cours,7,0))),"")</f>
+        <v>75.78</v>
+      </c>
+      <c r="G61" s="49">
+        <f>(F61/E61-1)</f>
+        <v>3.1771247021445959E-3</v>
       </c>
       <c r="H61" s="7"/>
+      <c r="I61"/>
       <c r="K61" s="50"/>
     </row>
     <row r="62" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A62" s="12">
         <v>7</v>
       </c>
-      <c r="B62" s="48"/>
-      <c r="C62" s="42"/>
-      <c r="D62" s="48"/>
-      <c r="E62" s="127"/>
-      <c r="F62" s="14" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="G62" s="49" t="e">
-        <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+      <c r="B62" s="48" t="s">
+        <v>131</v>
+      </c>
+      <c r="C62" s="42" t="s">
+        <v>12</v>
+      </c>
+      <c r="D62" s="48" t="s">
+        <v>130</v>
+      </c>
+      <c r="E62" s="127">
+        <v>185</v>
+      </c>
+      <c r="F62" s="14">
+        <f>IFERROR(((VLOOKUP(B62,cours,7,0))),"")</f>
+        <v>184.9</v>
+      </c>
+      <c r="G62" s="49">
+        <f>(F62/E62-1)</f>
+        <v>-5.4054054054053502E-4</v>
       </c>
       <c r="H62" s="7"/>
+      <c r="I62"/>
     </row>
     <row r="63" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A63" s="21">
         <v>8</v>
       </c>
-      <c r="B63" s="48"/>
-      <c r="C63" s="42"/>
-      <c r="D63" s="48"/>
-      <c r="E63" s="127"/>
-      <c r="F63" s="14" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="G63" s="49" t="e">
-        <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+      <c r="B63" s="48" t="s">
+        <v>129</v>
+      </c>
+      <c r="C63" s="42" t="s">
+        <v>12</v>
+      </c>
+      <c r="D63" s="48" t="s">
+        <v>128</v>
+      </c>
+      <c r="E63" s="127">
+        <v>214.65</v>
+      </c>
+      <c r="F63" s="14">
+        <f>IFERROR(((VLOOKUP(B63,cours,7,0))),"")</f>
+        <v>215.4</v>
+      </c>
+      <c r="G63" s="49">
+        <f>(F63/E63-1)</f>
+        <v>3.4940600978337066E-3</v>
       </c>
       <c r="H63" s="7"/>
+      <c r="I63"/>
     </row>
     <row r="64" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A64" s="12">
         <v>9</v>
       </c>
-      <c r="B64" s="48"/>
-      <c r="C64" s="42"/>
-      <c r="D64" s="48"/>
-      <c r="E64" s="127"/>
-      <c r="F64" s="14" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="G64" s="49" t="e">
-        <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+      <c r="B64" s="48" t="s">
+        <v>101</v>
+      </c>
+      <c r="C64" s="42" t="s">
+        <v>12</v>
+      </c>
+      <c r="D64" s="48" t="s">
+        <v>102</v>
+      </c>
+      <c r="E64" s="127">
+        <v>75.849999999999994</v>
+      </c>
+      <c r="F64" s="14">
+        <f>IFERROR(((VLOOKUP(B64,cours,7,0))),"")</f>
+        <v>74</v>
+      </c>
+      <c r="G64" s="49">
+        <f>(F64/E64-1)</f>
+        <v>-2.4390243902438935E-2</v>
       </c>
       <c r="H64" s="7"/>
+      <c r="I64"/>
     </row>
     <row r="65" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A65" s="21">
         <v>10</v>
       </c>
-      <c r="B65" s="48"/>
-      <c r="C65" s="42"/>
-      <c r="D65" s="48"/>
-      <c r="E65" s="127"/>
-      <c r="F65" s="14" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="G65" s="49" t="e">
-        <f t="shared" si="9"/>
-        <v>#VALUE!</v>
+      <c r="B65" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="C65" s="42" t="s">
+        <v>12</v>
+      </c>
+      <c r="D65" s="48" t="s">
+        <v>99</v>
+      </c>
+      <c r="E65" s="127">
+        <v>19.93</v>
+      </c>
+      <c r="F65" s="14">
+        <f>IFERROR(((VLOOKUP(B65,cours,7,0))),"")</f>
+        <v>20.2</v>
+      </c>
+      <c r="G65" s="49">
+        <f>(F65/E65-1)</f>
+        <v>1.3547415955845521E-2</v>
       </c>
       <c r="H65" s="7"/>
+      <c r="I65"/>
     </row>
     <row r="66" spans="1:11" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A66" s="21"/>
@@ -24075,20 +24687,22 @@
       <c r="F66" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="G66" s="46" t="e">
+      <c r="G66" s="46">
         <f>AVERAGE(G56:G65)</f>
-        <v>#VALUE!</v>
+        <v>3.5825998139191737E-4</v>
       </c>
       <c r="H66" s="52" t="s">
         <v>30</v>
       </c>
       <c r="I66" s="7">
+        <f>COUNTIF(G56:G65,"&gt;0")</f>
         <v>5</v>
       </c>
       <c r="J66" s="52" t="s">
         <v>31</v>
       </c>
       <c r="K66" s="31">
+        <f>COUNTIF(G56:G65,"&lt;0")</f>
         <v>5</v>
       </c>
     </row>
@@ -24099,10 +24713,11 @@
       <c r="F67" s="53"/>
       <c r="G67" s="47"/>
       <c r="H67" s="7"/>
+      <c r="I67"/>
     </row>
     <row r="68" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A68" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>1</v>
@@ -24114,71 +24729,70 @@
         <v>3</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="F68" s="129" t="s">
         <v>4</v>
       </c>
-      <c r="G68" s="130" t="s">
-        <v>124</v>
+      <c r="F68" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G68" s="5" t="s">
+        <v>6</v>
       </c>
       <c r="H68" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="I68" s="7"/>
     </row>
     <row r="69" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A69" s="12">
         <v>1</v>
       </c>
       <c r="B69" s="48" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C69" s="42" t="s">
         <v>12</v>
       </c>
       <c r="D69" s="48" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="E69" s="127">
-        <v>75.099999999999994</v>
+        <v>112.8</v>
       </c>
       <c r="F69" s="14">
         <f>IFERROR(((VLOOKUP(B69,cours,7,FALSE))),"")</f>
-        <v>74</v>
+        <v>112.1</v>
       </c>
       <c r="G69" s="49">
-        <f t="shared" ref="G69:G78" si="10">(F69/E69-1)</f>
-        <v>-1.464713715046595E-2</v>
+        <f>(F69/E69-1)</f>
+        <v>-6.2056737588652711E-3</v>
       </c>
       <c r="H69" s="7"/>
-      <c r="I69" s="7"/>
     </row>
     <row r="70" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A70" s="21">
         <v>2</v>
       </c>
       <c r="B70" s="48" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="C70" s="42" t="s">
         <v>12</v>
       </c>
       <c r="D70" s="48" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="E70" s="127">
-        <v>109.66</v>
+        <v>52.9</v>
       </c>
       <c r="F70" s="14">
-        <f t="shared" ref="F70:F78" si="11">IFERROR(((VLOOKUP(B70,cours,7,0))),"")</f>
-        <v>112.1</v>
+        <f>IFERROR(((VLOOKUP(B70,cours,7,0))),"")</f>
+        <v>51.75</v>
       </c>
       <c r="G70" s="49">
-        <f t="shared" si="10"/>
-        <v>2.2250592741200004E-2</v>
+        <f>(F70/E70-1)</f>
+        <v>-2.1739130434782594E-2</v>
       </c>
       <c r="H70" s="7"/>
+      <c r="I70"/>
       <c r="J70" s="43"/>
     </row>
     <row r="71" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
@@ -24195,17 +24809,18 @@
         <v>97</v>
       </c>
       <c r="E71" s="127">
-        <v>92.62</v>
+        <v>98.6</v>
       </c>
       <c r="F71" s="14">
-        <f t="shared" si="11"/>
+        <f>IFERROR(((VLOOKUP(B71,cours,7,0))),"")</f>
         <v>101.8</v>
       </c>
       <c r="G71" s="49">
-        <f t="shared" si="10"/>
-        <v>9.9114662060030057E-2</v>
+        <f>(F71/E71-1)</f>
+        <v>3.2454361054766734E-2</v>
       </c>
       <c r="H71" s="7"/>
+      <c r="I71"/>
       <c r="J71" s="43"/>
     </row>
     <row r="72" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
@@ -24213,26 +24828,27 @@
         <v>4</v>
       </c>
       <c r="B72" s="48" t="s">
-        <v>103</v>
+        <v>129</v>
       </c>
       <c r="C72" s="42" t="s">
         <v>12</v>
       </c>
       <c r="D72" s="48" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="E72" s="127">
-        <v>47.4</v>
+        <v>214.65</v>
       </c>
       <c r="F72" s="14">
-        <f t="shared" si="11"/>
-        <v>51.75</v>
+        <f>IFERROR(((VLOOKUP(B72,cours,7,0))),"")</f>
+        <v>215.4</v>
       </c>
       <c r="G72" s="49">
-        <f t="shared" si="10"/>
-        <v>9.1772151898734222E-2</v>
+        <f>(F72/E72-1)</f>
+        <v>3.4940600978337066E-3</v>
       </c>
       <c r="H72" s="7"/>
+      <c r="I72"/>
       <c r="J72" s="54"/>
     </row>
     <row r="73" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
@@ -24240,26 +24856,27 @@
         <v>5</v>
       </c>
       <c r="B73" s="48" t="s">
-        <v>171</v>
+        <v>101</v>
       </c>
       <c r="C73" s="42" t="s">
         <v>12</v>
       </c>
       <c r="D73" s="48" t="s">
-        <v>172</v>
+        <v>102</v>
       </c>
       <c r="E73" s="127">
-        <v>31.3</v>
+        <v>75.849999999999994</v>
       </c>
       <c r="F73" s="14">
-        <f t="shared" si="11"/>
-        <v>31.2</v>
+        <f>IFERROR(((VLOOKUP(B73,cours,7,0))),"")</f>
+        <v>74</v>
       </c>
       <c r="G73" s="49">
-        <f t="shared" si="10"/>
-        <v>-3.1948881789137795E-3</v>
+        <f>(F73/E73-1)</f>
+        <v>-2.4390243902438935E-2</v>
       </c>
       <c r="H73" s="7"/>
+      <c r="I73"/>
       <c r="J73" s="54"/>
     </row>
     <row r="74" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
@@ -24267,26 +24884,27 @@
         <v>6</v>
       </c>
       <c r="B74" s="48" t="s">
-        <v>173</v>
+        <v>117</v>
       </c>
       <c r="C74" s="42" t="s">
         <v>12</v>
       </c>
       <c r="D74" s="48" t="s">
-        <v>174</v>
+        <v>118</v>
       </c>
       <c r="E74" s="127">
-        <v>13.58</v>
+        <v>58.95</v>
       </c>
       <c r="F74" s="14">
-        <f t="shared" si="11"/>
-        <v>12.34</v>
+        <f>IFERROR(((VLOOKUP(B74,cours,7,0))),"")</f>
+        <v>58.6</v>
       </c>
       <c r="G74" s="49">
-        <f t="shared" si="10"/>
-        <v>-9.1310751104565546E-2</v>
+        <f>(F74/E74-1)</f>
+        <v>-5.9372349448685302E-3</v>
       </c>
       <c r="H74" s="7"/>
+      <c r="I74"/>
       <c r="J74" s="54"/>
     </row>
     <row r="75" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
@@ -24294,24 +24912,24 @@
         <v>7</v>
       </c>
       <c r="B75" s="48" t="s">
-        <v>91</v>
+        <v>127</v>
       </c>
       <c r="C75" s="42" t="s">
         <v>12</v>
       </c>
       <c r="D75" s="48" t="s">
-        <v>92</v>
+        <v>126</v>
       </c>
       <c r="E75" s="127">
-        <v>76.42</v>
+        <v>84.58</v>
       </c>
       <c r="F75" s="14">
-        <f t="shared" si="11"/>
-        <v>75.78</v>
+        <f>IFERROR(((VLOOKUP(B75,cours,7,0))),"")</f>
+        <v>83.94</v>
       </c>
       <c r="G75" s="49">
-        <f t="shared" si="10"/>
-        <v>-8.3747710023553967E-3</v>
+        <f>(F75/E75-1)</f>
+        <v>-7.5668006620950301E-3</v>
       </c>
       <c r="H75" s="7"/>
       <c r="I75" s="38"/>
@@ -24322,26 +24940,27 @@
         <v>8</v>
       </c>
       <c r="B76" s="48" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="C76" s="42" t="s">
         <v>12</v>
       </c>
       <c r="D76" s="48" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E76" s="127">
-        <v>58.25</v>
+        <v>41.22</v>
       </c>
       <c r="F76" s="14">
-        <f t="shared" si="11"/>
-        <v>58.6</v>
+        <f>IFERROR(((VLOOKUP(B76,cours,7,0))),"")</f>
+        <v>40.92</v>
       </c>
       <c r="G76" s="49">
-        <f t="shared" si="10"/>
-        <v>6.0085836909871126E-3</v>
+        <f>(F76/E76-1)</f>
+        <v>-7.2780203784570396E-3</v>
       </c>
       <c r="H76" s="7"/>
+      <c r="I76"/>
       <c r="J76" s="43"/>
     </row>
     <row r="77" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
@@ -24349,26 +24968,27 @@
         <v>9</v>
       </c>
       <c r="B77" s="48" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="C77" s="42" t="s">
         <v>12</v>
       </c>
       <c r="D77" s="48" t="s">
-        <v>99</v>
+        <v>122</v>
       </c>
       <c r="E77" s="127">
-        <v>19.274999999999999</v>
+        <v>23</v>
       </c>
       <c r="F77" s="14">
-        <f t="shared" si="11"/>
-        <v>20.2</v>
+        <f>IFERROR(((VLOOKUP(B77,cours,7,0))),"")</f>
+        <v>23.65</v>
       </c>
       <c r="G77" s="49">
-        <f t="shared" si="10"/>
-        <v>4.7989623865110298E-2</v>
+        <f>(F77/E77-1)</f>
+        <v>2.8260869565217339E-2</v>
       </c>
       <c r="H77" s="7"/>
+      <c r="I77"/>
       <c r="J77" s="43"/>
     </row>
     <row r="78" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
@@ -24376,142 +24996,233 @@
         <v>10</v>
       </c>
       <c r="B78" s="48" t="s">
-        <v>175</v>
+        <v>121</v>
       </c>
       <c r="C78" s="42" t="s">
         <v>12</v>
       </c>
       <c r="D78" s="48" t="s">
-        <v>176</v>
+        <v>120</v>
       </c>
       <c r="E78" s="127">
-        <v>102.5</v>
+        <v>302.25</v>
       </c>
       <c r="F78" s="14">
-        <f t="shared" si="11"/>
-        <v>108.3</v>
+        <f>IFERROR(((VLOOKUP(B78,cours,7,0))),"")</f>
+        <v>306.39999999999998</v>
       </c>
       <c r="G78" s="49">
-        <f t="shared" si="10"/>
-        <v>5.6585365853658587E-2</v>
+        <f>(F78/E78-1)</f>
+        <v>1.3730355665839467E-2</v>
       </c>
       <c r="H78" s="7"/>
+      <c r="I78"/>
       <c r="J78" s="43"/>
     </row>
     <row r="79" spans="1:11" ht="15.45" x14ac:dyDescent="0.4">
-      <c r="B79" s="16"/>
       <c r="F79" s="55" t="s">
         <v>29</v>
       </c>
       <c r="G79" s="46">
         <f>AVERAGE(G69:G78)</f>
-        <v>2.0619343267341959E-2</v>
+        <v>4.822542302149846E-4</v>
       </c>
       <c r="H79" s="7"/>
+      <c r="I79"/>
     </row>
     <row r="80" spans="1:11" ht="15.45" x14ac:dyDescent="0.4">
-      <c r="B80" s="16"/>
       <c r="F80" s="44"/>
       <c r="G80" s="56"/>
       <c r="H80" s="7"/>
+      <c r="I80"/>
     </row>
     <row r="81" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B81" s="57"/>
-      <c r="D81" s="2"/>
-      <c r="E81" s="3"/>
-      <c r="F81" s="4"/>
-      <c r="G81" s="5"/>
-      <c r="H81" s="31"/>
+      <c r="A81" t="s">
+        <v>119</v>
+      </c>
+      <c r="B81" s="57" t="s">
+        <v>105</v>
+      </c>
+      <c r="C81" t="s">
+        <v>106</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F81" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G81" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H81" s="31">
+        <f>COUNTIF($G$70:$G$79,"&lt;0")</f>
+        <v>5</v>
+      </c>
+      <c r="I81"/>
     </row>
     <row r="82" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A82" s="12"/>
+      <c r="A82" s="12">
+        <v>1</v>
+      </c>
       <c r="B82" s="48"/>
       <c r="C82" s="42"/>
       <c r="D82" s="48"/>
       <c r="E82" s="127"/>
-      <c r="F82" s="14"/>
+      <c r="F82" s="14" t="str">
+        <f>IFERROR(((VLOOKUP(B82,cours,7,0))),"")</f>
+        <v/>
+      </c>
       <c r="G82" s="49"/>
+      <c r="H82"/>
+      <c r="I82"/>
     </row>
     <row r="83" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A83" s="21"/>
+      <c r="A83" s="21">
+        <v>2</v>
+      </c>
       <c r="B83" s="48"/>
       <c r="C83" s="42"/>
       <c r="D83" s="48"/>
       <c r="E83" s="127"/>
-      <c r="F83" s="14"/>
+      <c r="F83" s="14" t="str">
+        <f>IFERROR(((VLOOKUP(B83,cours,7,0))),"")</f>
+        <v/>
+      </c>
       <c r="G83" s="49"/>
+      <c r="H83"/>
+      <c r="I83"/>
     </row>
     <row r="84" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A84" s="12"/>
+      <c r="A84" s="12">
+        <v>3</v>
+      </c>
       <c r="B84" s="48"/>
       <c r="C84" s="42"/>
       <c r="D84" s="48"/>
       <c r="E84" s="127"/>
-      <c r="F84" s="14"/>
+      <c r="F84" s="14" t="str">
+        <f>IFERROR(((VLOOKUP(B84,cours,7,0))),"")</f>
+        <v/>
+      </c>
       <c r="G84" s="49"/>
+      <c r="H84"/>
+      <c r="I84"/>
     </row>
     <row r="85" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A85" s="21"/>
+      <c r="A85" s="21">
+        <v>4</v>
+      </c>
       <c r="B85" s="48"/>
       <c r="C85" s="58"/>
       <c r="D85" s="48"/>
       <c r="E85" s="127"/>
-      <c r="F85" s="14"/>
+      <c r="F85" s="14" t="str">
+        <f>IFERROR(((VLOOKUP(B85,cours,7,0))),"")</f>
+        <v/>
+      </c>
       <c r="G85" s="49"/>
+      <c r="H85"/>
+      <c r="I85"/>
     </row>
     <row r="86" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A86" s="12"/>
+      <c r="A86" s="12">
+        <v>5</v>
+      </c>
       <c r="B86" s="48"/>
       <c r="C86" s="58"/>
       <c r="D86" s="48"/>
       <c r="E86" s="127"/>
-      <c r="F86" s="14"/>
+      <c r="F86" s="14" t="str">
+        <f>IFERROR(((VLOOKUP(B86,cours,7,0))),"")</f>
+        <v/>
+      </c>
       <c r="G86" s="49"/>
+      <c r="H86"/>
+      <c r="I86"/>
     </row>
     <row r="87" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A87" s="21"/>
+      <c r="A87" s="21">
+        <v>6</v>
+      </c>
       <c r="B87" s="48"/>
       <c r="C87" s="58"/>
       <c r="D87" s="48"/>
       <c r="E87" s="127"/>
-      <c r="F87" s="14"/>
+      <c r="F87" s="14" t="str">
+        <f>IFERROR(((VLOOKUP(B87,cours,7,0))),"")</f>
+        <v/>
+      </c>
       <c r="G87" s="49"/>
+      <c r="H87"/>
+      <c r="I87"/>
     </row>
     <row r="88" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A88" s="12"/>
+      <c r="A88" s="12">
+        <v>7</v>
+      </c>
       <c r="B88" s="48"/>
       <c r="C88" s="42"/>
       <c r="D88" s="48"/>
       <c r="E88" s="127"/>
-      <c r="F88" s="14"/>
+      <c r="F88" s="14" t="str">
+        <f>IFERROR(((VLOOKUP(B88,cours,7,0))),"")</f>
+        <v/>
+      </c>
       <c r="G88" s="49"/>
+      <c r="H88"/>
+      <c r="I88"/>
     </row>
     <row r="89" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A89" s="21"/>
+      <c r="A89" s="21">
+        <v>8</v>
+      </c>
       <c r="B89" s="48"/>
       <c r="C89" s="58"/>
       <c r="D89" s="48"/>
       <c r="E89" s="127"/>
-      <c r="F89" s="14"/>
+      <c r="F89" s="14" t="str">
+        <f>IFERROR(((VLOOKUP(B89,cours,7,0))),"")</f>
+        <v/>
+      </c>
       <c r="G89" s="49"/>
+      <c r="H89"/>
+      <c r="I89"/>
     </row>
     <row r="90" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A90" s="12"/>
+      <c r="A90" s="12">
+        <v>9</v>
+      </c>
       <c r="B90" s="48"/>
       <c r="C90" s="42"/>
       <c r="D90" s="48"/>
       <c r="E90" s="127"/>
-      <c r="F90" s="14"/>
+      <c r="F90" s="14" t="str">
+        <f>IFERROR(((VLOOKUP(B90,cours,7,0))),"")</f>
+        <v/>
+      </c>
       <c r="G90" s="49"/>
+      <c r="H90"/>
+      <c r="I90"/>
     </row>
     <row r="91" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A91" s="21"/>
+      <c r="A91" s="21">
+        <v>10</v>
+      </c>
       <c r="B91" s="48"/>
       <c r="C91" s="42"/>
       <c r="D91" s="48"/>
       <c r="E91" s="127"/>
-      <c r="F91" s="14"/>
+      <c r="F91" s="14" t="str">
+        <f>IFERROR(((VLOOKUP(B91,cours,7,0))),"")</f>
+        <v/>
+      </c>
       <c r="G91" s="49"/>
+      <c r="H91"/>
+      <c r="I91"/>
     </row>
     <row r="92" spans="1:12" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A92" s="21"/>
@@ -24519,615 +25230,731 @@
       <c r="C92" s="42"/>
       <c r="D92" s="43"/>
       <c r="E92" s="127"/>
-      <c r="F92" s="55"/>
+      <c r="F92" s="55" t="s">
+        <v>29</v>
+      </c>
       <c r="G92" s="46"/>
+      <c r="H92"/>
+      <c r="I92"/>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="B93" s="16"/>
       <c r="F93" s="7"/>
-      <c r="H93" s="52"/>
-      <c r="I93" s="7"/>
-      <c r="J93" s="52"/>
-      <c r="K93" s="31"/>
+      <c r="H93" s="52" t="s">
+        <v>30</v>
+      </c>
+      <c r="I93" s="7">
+        <f>COUNTIF(G83:G92,"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="J93" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="K93" s="31">
+        <f>COUNTIF(G83:G92,"&lt;0")</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="B94" s="16"/>
       <c r="F94" s="7"/>
       <c r="H94" s="52"/>
-      <c r="I94" s="7"/>
       <c r="J94" s="52"/>
       <c r="K94" s="31"/>
     </row>
     <row r="95" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B95" s="57"/>
-      <c r="D95" s="59"/>
-      <c r="E95" s="3"/>
-      <c r="F95" s="4"/>
-      <c r="G95" s="5"/>
-      <c r="H95" s="6"/>
+      <c r="A95" t="s">
+        <v>119</v>
+      </c>
+      <c r="B95" s="57" t="s">
+        <v>107</v>
+      </c>
+      <c r="C95" t="s">
+        <v>106</v>
+      </c>
+      <c r="D95" s="59" t="s">
+        <v>108</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F95" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G95" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H95" s="6" t="s">
+        <v>109</v>
+      </c>
       <c r="I95" s="60"/>
       <c r="J95" s="61"/>
       <c r="L95" s="62"/>
     </row>
     <row r="96" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A96" s="12"/>
+      <c r="A96" s="12">
+        <v>1</v>
+      </c>
       <c r="B96" s="48"/>
       <c r="C96" s="42"/>
       <c r="D96" s="48"/>
       <c r="E96" s="13"/>
-      <c r="F96" s="14"/>
+      <c r="F96" s="14" t="str">
+        <f>IFERROR(((VLOOKUP(B96,cours,7,0))),"")</f>
+        <v/>
+      </c>
       <c r="G96" s="49"/>
       <c r="H96" s="7"/>
-      <c r="I96" s="7"/>
     </row>
     <row r="97" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A97" s="21"/>
+      <c r="A97" s="21">
+        <v>2</v>
+      </c>
       <c r="B97" s="48"/>
       <c r="C97" s="42"/>
       <c r="D97" s="48"/>
       <c r="E97" s="13"/>
-      <c r="F97" s="14"/>
+      <c r="F97" s="14" t="str">
+        <f>IFERROR(((VLOOKUP(B97,cours,7,0))),"")</f>
+        <v/>
+      </c>
       <c r="G97" s="49"/>
       <c r="H97" s="7"/>
+      <c r="I97"/>
       <c r="J97" s="38"/>
     </row>
     <row r="98" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A98" s="12"/>
+      <c r="A98" s="12">
+        <v>3</v>
+      </c>
       <c r="B98" s="48"/>
       <c r="C98" s="42"/>
       <c r="D98" s="48"/>
       <c r="E98" s="13"/>
-      <c r="F98" s="14"/>
+      <c r="F98" s="14" t="str">
+        <f>IFERROR(((VLOOKUP(B98,cours,7,0))),"")</f>
+        <v/>
+      </c>
       <c r="G98" s="49"/>
       <c r="H98" s="7"/>
+      <c r="I98"/>
     </row>
     <row r="99" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A99" s="21"/>
+      <c r="A99" s="21">
+        <v>4</v>
+      </c>
       <c r="B99" s="48"/>
       <c r="C99" s="42"/>
       <c r="D99" s="48"/>
       <c r="E99" s="13"/>
-      <c r="F99" s="14"/>
+      <c r="F99" s="14" t="str">
+        <f>IFERROR(((VLOOKUP(B99,cours,7,0))),"")</f>
+        <v/>
+      </c>
       <c r="G99" s="49"/>
       <c r="H99" s="7"/>
+      <c r="I99"/>
     </row>
     <row r="100" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A100" s="12"/>
+      <c r="A100" s="12">
+        <v>5</v>
+      </c>
       <c r="B100" s="48"/>
       <c r="C100" s="42"/>
       <c r="D100" s="48"/>
       <c r="E100" s="13"/>
-      <c r="F100" s="14"/>
+      <c r="F100" s="14" t="str">
+        <f>IFERROR(((VLOOKUP(B100,cours,7,0))),"")</f>
+        <v/>
+      </c>
       <c r="G100" s="49"/>
       <c r="H100" s="7"/>
+      <c r="I100"/>
       <c r="L100" s="62"/>
     </row>
     <row r="101" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A101" s="21"/>
+      <c r="A101" s="21">
+        <v>6</v>
+      </c>
       <c r="B101" s="48"/>
       <c r="C101" s="42"/>
       <c r="D101" s="48"/>
       <c r="E101" s="13"/>
-      <c r="F101" s="14"/>
+      <c r="F101" s="14" t="str">
+        <f>IFERROR(((VLOOKUP(B101,cours,7,0))),"")</f>
+        <v/>
+      </c>
       <c r="G101" s="49"/>
       <c r="H101" s="7"/>
+      <c r="I101"/>
       <c r="L101" s="62"/>
     </row>
     <row r="102" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A102" s="12"/>
+      <c r="A102" s="12">
+        <v>7</v>
+      </c>
       <c r="B102" s="48"/>
       <c r="C102" s="42"/>
       <c r="D102" s="48"/>
       <c r="E102" s="13"/>
-      <c r="F102" s="14"/>
+      <c r="F102" s="14" t="str">
+        <f>IFERROR(((VLOOKUP(B102,cours,7,0))),"")</f>
+        <v/>
+      </c>
       <c r="G102" s="49"/>
       <c r="H102" s="7"/>
+      <c r="I102"/>
     </row>
     <row r="103" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A103" s="21"/>
+      <c r="A103" s="21">
+        <v>8</v>
+      </c>
       <c r="B103" s="48"/>
       <c r="C103" s="42"/>
       <c r="D103" s="48"/>
       <c r="E103" s="13"/>
-      <c r="F103" s="14"/>
+      <c r="F103" s="14" t="str">
+        <f>IFERROR(((VLOOKUP(B103,cours,7,0))),"")</f>
+        <v/>
+      </c>
       <c r="G103" s="49"/>
       <c r="H103" s="7"/>
+      <c r="I103"/>
       <c r="J103" s="38"/>
     </row>
     <row r="104" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A104" s="12"/>
+      <c r="A104" s="12">
+        <v>9</v>
+      </c>
       <c r="B104" s="48"/>
       <c r="C104" s="42"/>
       <c r="D104" s="48"/>
       <c r="E104" s="13"/>
-      <c r="F104" s="14"/>
+      <c r="F104" s="14" t="str">
+        <f>IFERROR(((VLOOKUP(B104,cours,7,0))),"")</f>
+        <v/>
+      </c>
       <c r="G104" s="49"/>
       <c r="H104" s="7"/>
+      <c r="I104"/>
       <c r="K104" s="38"/>
     </row>
     <row r="105" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A105" s="21"/>
+      <c r="A105" s="21">
+        <v>10</v>
+      </c>
       <c r="B105" s="48"/>
       <c r="C105" s="42"/>
       <c r="D105" s="48"/>
       <c r="E105" s="13"/>
-      <c r="F105" s="14"/>
+      <c r="F105" s="14" t="str">
+        <f>IFERROR(((VLOOKUP(B105,cours,7,0))),"")</f>
+        <v/>
+      </c>
       <c r="G105" s="49"/>
       <c r="H105" s="7"/>
+      <c r="I105"/>
     </row>
     <row r="106" spans="1:12" ht="15.45" x14ac:dyDescent="0.4">
       <c r="B106" s="57"/>
       <c r="C106" s="42"/>
       <c r="D106" s="43"/>
       <c r="E106" s="127"/>
-      <c r="F106" s="63"/>
+      <c r="F106" s="63" t="s">
+        <v>29</v>
+      </c>
       <c r="G106" s="46"/>
       <c r="H106" s="7"/>
+      <c r="I106"/>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B107" s="57"/>
       <c r="C107" s="42"/>
       <c r="D107" s="43"/>
       <c r="E107" s="43"/>
-      <c r="H107" s="52"/>
-      <c r="I107" s="7"/>
-      <c r="J107" s="52"/>
-      <c r="K107" s="7"/>
+      <c r="H107" s="52" t="s">
+        <v>30</v>
+      </c>
+      <c r="I107" s="7">
+        <f>COUNTIF(G97:G106,"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="J107" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="K107" s="7">
+        <f>COUNTIF(G97:G106,"&lt;0")</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="B108" s="16"/>
       <c r="D108" s="43"/>
+      <c r="H108"/>
+      <c r="I108"/>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="B109" s="16"/>
       <c r="D109" s="54"/>
-      <c r="H109" s="52"/>
-      <c r="I109" s="7"/>
-      <c r="J109" s="52"/>
-      <c r="K109" s="7"/>
+      <c r="H109" s="52" t="s">
+        <v>30</v>
+      </c>
+      <c r="I109" s="7">
+        <f>SUM(I1:I107)</f>
+        <v>24</v>
+      </c>
+      <c r="J109" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="K109" s="7">
+        <f>SUM(K1:K107)</f>
+        <v>16</v>
+      </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="B110" s="16"/>
       <c r="D110" s="54"/>
+      <c r="H110"/>
+      <c r="I110"/>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="B111" s="16"/>
       <c r="D111" s="54"/>
+      <c r="H111"/>
+      <c r="I111"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B56:B65">
-    <cfRule type="expression" dxfId="104" priority="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="105" priority="5" stopIfTrue="1">
       <formula>IF(AO56&gt;0,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B69:B78">
-    <cfRule type="expression" dxfId="103" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="104" priority="3" stopIfTrue="1">
       <formula>IF(AO69&gt;0,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B81">
-    <cfRule type="expression" dxfId="102" priority="107" stopIfTrue="1">
+    <cfRule type="expression" dxfId="103" priority="50" stopIfTrue="1">
       <formula>IF(AN62&gt;0,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B82:B91">
-    <cfRule type="expression" dxfId="101" priority="66" stopIfTrue="1">
+    <cfRule type="expression" dxfId="102" priority="9" stopIfTrue="1">
       <formula>IF(AL82&gt;0,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B92">
-    <cfRule type="expression" dxfId="100" priority="103" stopIfTrue="1">
+    <cfRule type="expression" dxfId="101" priority="46" stopIfTrue="1">
       <formula>IF(AL91&gt;0,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B95">
-    <cfRule type="expression" dxfId="99" priority="106" stopIfTrue="1">
+    <cfRule type="expression" dxfId="100" priority="49" stopIfTrue="1">
       <formula>IF(AN75&gt;0,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B96:B105">
-    <cfRule type="expression" dxfId="98" priority="64" stopIfTrue="1">
+    <cfRule type="expression" dxfId="99" priority="7" stopIfTrue="1">
       <formula>IF(AO96&gt;0,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B106">
-    <cfRule type="expression" dxfId="97" priority="104" stopIfTrue="1">
+    <cfRule type="expression" dxfId="98" priority="47" stopIfTrue="1">
       <formula>IF(AN104&gt;0,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B107">
-    <cfRule type="expression" dxfId="96" priority="105" stopIfTrue="1">
+    <cfRule type="expression" dxfId="97" priority="48" stopIfTrue="1">
       <formula>IF(AN104&gt;0,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D56:D65">
-    <cfRule type="expression" dxfId="95" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="96" priority="4" stopIfTrue="1">
       <formula>IF(AQ56&gt;0,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D69:D78">
-    <cfRule type="expression" dxfId="94" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="95" priority="2" stopIfTrue="1">
       <formula>IF(AQ69&gt;0,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D82:D91">
-    <cfRule type="expression" dxfId="93" priority="65" stopIfTrue="1">
+    <cfRule type="expression" dxfId="94" priority="8" stopIfTrue="1">
       <formula>IF(AN82&gt;0,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D96:D105">
-    <cfRule type="expression" dxfId="92" priority="63" stopIfTrue="1">
+    <cfRule type="expression" dxfId="93" priority="6" stopIfTrue="1">
       <formula>IF(AQ96&gt;0,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F11 F16:F25">
-    <cfRule type="expression" dxfId="91" priority="14" stopIfTrue="1">
+    <cfRule type="expression" dxfId="92" priority="19" stopIfTrue="1">
+      <formula>IF(#REF!="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="91" priority="20" stopIfTrue="1">
+      <formula>IF($T200="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="90" priority="21" stopIfTrue="1">
       <formula>IF($U200="AAA",TRUE,FALSE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="90" priority="12" stopIfTrue="1">
+    <cfRule type="expression" dxfId="89" priority="22" stopIfTrue="1">
       <formula>IF($AN1048554="AAA",TRUE,FALSE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="89" priority="13" stopIfTrue="1">
+    <cfRule type="expression" dxfId="88" priority="23" stopIfTrue="1">
       <formula>IF($T200="AAA",TRUE,FALSE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="88" priority="9" stopIfTrue="1">
-      <formula>IF(#REF!="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="87" priority="10" stopIfTrue="1">
-      <formula>IF($T200="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="86" priority="11" stopIfTrue="1">
+    <cfRule type="expression" dxfId="87" priority="24" stopIfTrue="1">
       <formula>IF($U200="AAA",TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F30:F39">
-    <cfRule type="expression" dxfId="85" priority="39" stopIfTrue="1">
+    <cfRule type="expression" dxfId="86" priority="80" stopIfTrue="1">
+      <formula>IF(#REF!="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="85" priority="81" stopIfTrue="1">
       <formula>IF($T230="AAA",TRUE,FALSE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="84" priority="35" stopIfTrue="1">
-      <formula>IF(#REF!="AAA",TRUE,FALSE)</formula>
+    <cfRule type="expression" dxfId="84" priority="82" stopIfTrue="1">
+      <formula>IF($U230="AAA",TRUE,FALSE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="83" priority="36" stopIfTrue="1">
+    <cfRule type="expression" dxfId="83" priority="83" stopIfTrue="1">
+      <formula>IF($AN5="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="82" priority="84" stopIfTrue="1">
       <formula>IF($T230="AAA",TRUE,FALSE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="82" priority="37" stopIfTrue="1">
-      <formula>IF($U230="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="81" priority="38" stopIfTrue="1">
-      <formula>IF($AN5="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="80" priority="40" stopIfTrue="1">
+    <cfRule type="expression" dxfId="81" priority="85" stopIfTrue="1">
       <formula>IF($U230="AAA",TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F43:F52">
-    <cfRule type="expression" dxfId="79" priority="46" stopIfTrue="1">
+    <cfRule type="expression" dxfId="80" priority="86" stopIfTrue="1">
+      <formula>IF(#REF!="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="79" priority="87" stopIfTrue="1">
+      <formula>IF($T242="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="78" priority="88" stopIfTrue="1">
       <formula>IF($U242="AAA",TRUE,FALSE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="78" priority="45" stopIfTrue="1">
+    <cfRule type="expression" dxfId="77" priority="89" stopIfTrue="1">
+      <formula>IF($AN17="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="76" priority="90" stopIfTrue="1">
       <formula>IF($T242="AAA",TRUE,FALSE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="77" priority="44" stopIfTrue="1">
-      <formula>IF($AN17="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="76" priority="41" stopIfTrue="1">
-      <formula>IF(#REF!="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="75" priority="42" stopIfTrue="1">
-      <formula>IF($T242="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="74" priority="43" stopIfTrue="1">
+    <cfRule type="expression" dxfId="75" priority="91" stopIfTrue="1">
       <formula>IF($U242="AAA",TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F56">
-    <cfRule type="expression" dxfId="73" priority="32" stopIfTrue="1">
+    <cfRule type="expression" dxfId="74" priority="76" stopIfTrue="1">
+      <formula>IF(#REF!="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="73" priority="77" stopIfTrue="1">
       <formula>IF($AN28="AAA",TRUE,FALSE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="72" priority="33" stopIfTrue="1">
+    <cfRule type="expression" dxfId="72" priority="78" stopIfTrue="1">
       <formula>IF($T254="AAA",TRUE,FALSE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="71" priority="34" stopIfTrue="1">
+    <cfRule type="expression" dxfId="71" priority="79" stopIfTrue="1">
       <formula>IF($U254="AAA",TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F56:F67">
-    <cfRule type="expression" dxfId="70" priority="31" stopIfTrue="1">
+  <conditionalFormatting sqref="F69:F78">
+    <cfRule type="expression" dxfId="70" priority="1" stopIfTrue="1">
       <formula>IF(#REF!="AAA",TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F57:F67">
-    <cfRule type="expression" dxfId="69" priority="47" stopIfTrue="1">
-      <formula>IF($AK29="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="68" priority="49" stopIfTrue="1">
-      <formula>IF($U255="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="67" priority="48" stopIfTrue="1">
-      <formula>IF($T255="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F69">
-    <cfRule type="expression" dxfId="66" priority="54" stopIfTrue="1">
-      <formula>IF($U268="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="65" priority="53" stopIfTrue="1">
-      <formula>IF($T268="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="64" priority="52" stopIfTrue="1">
-      <formula>IF($AJ43="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="63" priority="50" stopIfTrue="1">
-      <formula>IF($T268="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="62" priority="51" stopIfTrue="1">
-      <formula>IF($U268="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F69:F78">
-    <cfRule type="expression" dxfId="61" priority="1" stopIfTrue="1">
-      <formula>IF(#REF!="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F70:F78">
-    <cfRule type="expression" dxfId="60" priority="57" stopIfTrue="1">
-      <formula>IF($U267="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="59" priority="55" stopIfTrue="1">
-      <formula>IF($AJ42="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="58" priority="56" stopIfTrue="1">
-      <formula>IF($T267="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F82">
-    <cfRule type="expression" dxfId="57" priority="161" stopIfTrue="1">
-      <formula>IF($AJ53="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="56" priority="163" stopIfTrue="1">
-      <formula>IF($U278="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="55" priority="162" stopIfTrue="1">
-      <formula>IF($T278="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F82:F91">
-    <cfRule type="expression" dxfId="54" priority="122" stopIfTrue="1">
+    <cfRule type="expression" dxfId="69" priority="65" stopIfTrue="1">
       <formula>IF(#REF!="AAA",TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F83:F91">
-    <cfRule type="expression" dxfId="53" priority="125" stopIfTrue="1">
-      <formula>IF($U279="AAA",TRUE,FALSE)</formula>
+    <cfRule type="expression" dxfId="68" priority="66" stopIfTrue="1">
+      <formula>IF($AN55="AAA",TRUE,FALSE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="52" priority="124" stopIfTrue="1">
+    <cfRule type="expression" dxfId="67" priority="67" stopIfTrue="1">
       <formula>IF($T279="AAA",TRUE,FALSE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="51" priority="123" stopIfTrue="1">
-      <formula>IF($AN55="AAA",TRUE,FALSE)</formula>
+    <cfRule type="expression" dxfId="66" priority="68" stopIfTrue="1">
+      <formula>IF($U279="AAA",TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F96:F97">
-    <cfRule type="expression" dxfId="50" priority="132" stopIfTrue="1">
-      <formula>IF($U291="AAA",TRUE,FALSE)</formula>
+    <cfRule type="expression" dxfId="65" priority="73" stopIfTrue="1">
+      <formula>IF($AN65="AAA",TRUE,FALSE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="49" priority="131" stopIfTrue="1">
+    <cfRule type="expression" dxfId="64" priority="74" stopIfTrue="1">
       <formula>IF($T291="AAA",TRUE,FALSE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="48" priority="130" stopIfTrue="1">
-      <formula>IF($AN65="AAA",TRUE,FALSE)</formula>
+    <cfRule type="expression" dxfId="63" priority="75" stopIfTrue="1">
+      <formula>IF($U291="AAA",TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F96:F106">
-    <cfRule type="expression" dxfId="47" priority="126" stopIfTrue="1">
+    <cfRule type="expression" dxfId="62" priority="69" stopIfTrue="1">
       <formula>IF(#REF!="AAA",TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F98:F106">
-    <cfRule type="expression" dxfId="46" priority="128" stopIfTrue="1">
+    <cfRule type="expression" dxfId="61" priority="70" stopIfTrue="1">
+      <formula>IF($AN68="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="60" priority="71" stopIfTrue="1">
       <formula>IF($T293="AAA",TRUE,FALSE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="45" priority="129" stopIfTrue="1">
+    <cfRule type="expression" dxfId="59" priority="72" stopIfTrue="1">
       <formula>IF($U293="AAA",TRUE,FALSE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="44" priority="127" stopIfTrue="1">
-      <formula>IF($AN68="AAA",TRUE,FALSE)</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G16:G26 G30:G41 G2:G12">
+    <cfRule type="cellIs" dxfId="58" priority="52" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="57" priority="53" stopIfTrue="1" operator="greaterThanOrEqual">
+      <formula>#REF!</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G12 G16:G26 G30:G41">
-    <cfRule type="cellIs" dxfId="43" priority="30" stopIfTrue="1" operator="greaterThanOrEqual">
-      <formula>#REF!</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="29" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="G16:G28 G2:G12">
+    <cfRule type="cellIs" dxfId="56" priority="25" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G12 G16:G28">
-    <cfRule type="cellIs" dxfId="41" priority="15" stopIfTrue="1" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G30:G41 G2:G12 G16:G26">
-    <cfRule type="cellIs" dxfId="40" priority="28" operator="greaterThan">
+  <conditionalFormatting sqref="G30:G41 G16:G26 G2:G12">
+    <cfRule type="cellIs" dxfId="55" priority="51" operator="greaterThan">
       <formula>#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G43:G54 G30:G41 G56:G67">
-    <cfRule type="cellIs" dxfId="39" priority="24" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="54" priority="42" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G43:G54">
-    <cfRule type="cellIs" dxfId="38" priority="20" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="53" priority="30" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="21" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="52" priority="31" operator="greaterThan">
       <formula>#REF!</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="36" priority="22" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="51" priority="32" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="35" priority="23" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="50" priority="33" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G53:G54">
-    <cfRule type="cellIs" dxfId="34" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="49" priority="16" operator="greaterThan">
       <formula>#REF!</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="7" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="48" priority="17" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="32" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="47" priority="18" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G56:G67">
-    <cfRule type="cellIs" dxfId="31" priority="25" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="46" priority="43" operator="greaterThan">
       <formula>#REF!</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="26" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="45" priority="44" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="29" priority="27" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="44" priority="45" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G69:G80">
-    <cfRule type="cellIs" dxfId="28" priority="17" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="43" priority="26" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="42" priority="27" operator="greaterThan">
       <formula>#REF!</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="18" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="41" priority="28" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="19" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="40" priority="29" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>#REF!</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="16" stopIfTrue="1" operator="lessThan">
-      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G82:G92">
-    <cfRule type="cellIs" dxfId="24" priority="96" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="39" priority="38" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="38" priority="39" operator="greaterThan">
       <formula>#REF!</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="95" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="37" priority="40" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="98" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="36" priority="41" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>#REF!</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="97" stopIfTrue="1" operator="lessThan">
-      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G96:G106">
-    <cfRule type="cellIs" dxfId="20" priority="94" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="35" priority="34" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="34" priority="35" operator="greaterThan">
       <formula>#REF!</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="93" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="33" priority="36" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="92" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="32" priority="37" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>#REF!</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="91" stopIfTrue="1" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H81">
-    <cfRule type="cellIs" dxfId="16" priority="72" operator="greaterThan">
-      <formula>$H81</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I12 I53 K53 I66 K66">
-    <cfRule type="cellIs" dxfId="15" priority="116" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="31" priority="59" operator="greaterThan">
       <formula>$K12</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I26">
-    <cfRule type="cellIs" dxfId="14" priority="67" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="30" priority="10" operator="greaterThan">
       <formula>$K26</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I75">
-    <cfRule type="cellIs" dxfId="13" priority="117" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="29" priority="60" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I93:I94">
-    <cfRule type="cellIs" dxfId="12" priority="115" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="28" priority="58" operator="greaterThan">
       <formula>$K93</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I107">
-    <cfRule type="cellIs" dxfId="11" priority="114" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="27" priority="57" operator="greaterThan">
       <formula>$K107</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I109">
-    <cfRule type="cellIs" dxfId="10" priority="112" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="26" priority="55" operator="greaterThan">
       <formula>$K109</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J97">
-    <cfRule type="cellIs" dxfId="9" priority="119" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="25" priority="62" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J103">
-    <cfRule type="cellIs" dxfId="8" priority="118" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="24" priority="61" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="cellIs" dxfId="7" priority="70" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="23" priority="13" operator="greaterThan">
       <formula>$K12</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K26">
-    <cfRule type="cellIs" dxfId="6" priority="69" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="22" priority="12" operator="greaterThan">
       <formula>$K26</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K41">
-    <cfRule type="cellIs" dxfId="5" priority="68" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="21" priority="11" operator="greaterThan">
       <formula>$K41</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="H81">
+    <cfRule type="cellIs" dxfId="20" priority="15" operator="greaterThan">
+      <formula>$H81</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="K93:K94">
-    <cfRule type="cellIs" dxfId="4" priority="71" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="19" priority="14" operator="greaterThan">
       <formula>$K93</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K104">
-    <cfRule type="cellIs" dxfId="3" priority="120" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="18" priority="63" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K107">
-    <cfRule type="cellIs" dxfId="2" priority="113" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="17" priority="56" operator="greaterThan">
       <formula>$I107</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K109">
-    <cfRule type="cellIs" dxfId="1" priority="111" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="16" priority="54" operator="greaterThan">
       <formula>$I109</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P37:P38">
-    <cfRule type="cellIs" dxfId="0" priority="121" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="15" priority="64" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="F57:F67">
+    <cfRule type="expression" dxfId="14" priority="92" stopIfTrue="1">
+      <formula>IF(#REF!="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="13" priority="93" stopIfTrue="1">
+      <formula>IF($AK29="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="12" priority="94" stopIfTrue="1">
+      <formula>IF($T255="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="11" priority="95" stopIfTrue="1">
+      <formula>IF($U255="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F69">
+    <cfRule type="expression" dxfId="10" priority="96" stopIfTrue="1">
+      <formula>IF($T268="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="9" priority="97" stopIfTrue="1">
+      <formula>IF($U268="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="98" stopIfTrue="1">
+      <formula>IF($AJ43="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="7" priority="99" stopIfTrue="1">
+      <formula>IF($T268="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="6" priority="100" stopIfTrue="1">
+      <formula>IF($U268="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F70:F78">
+    <cfRule type="expression" dxfId="5" priority="101" stopIfTrue="1">
+      <formula>IF($AJ42="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="102" stopIfTrue="1">
+      <formula>IF($T267="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="3" priority="103" stopIfTrue="1">
+      <formula>IF($U267="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F82">
+    <cfRule type="expression" dxfId="2" priority="104" stopIfTrue="1">
+      <formula>IF($AJ53="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="105" stopIfTrue="1">
+      <formula>IF($T278="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="106" stopIfTrue="1">
+      <formula>IF($U278="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="6">
-    <tablePart r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+  <tableParts count="8">
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
     <tablePart r:id="rId4"/>
     <tablePart r:id="rId5"/>
     <tablePart r:id="rId6"/>
+    <tablePart r:id="rId7"/>
+    <tablePart r:id="rId8"/>
+    <tablePart r:id="rId9"/>
   </tableParts>
 </worksheet>
 </file>
--- a/Twitter_Donnees.xlsx
+++ b/Twitter_Donnees.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Bourse\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3C432EA-27E2-4A59-9ADB-512FD41BA7D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{304BB556-A4B7-404E-8823-569BEE1DF702}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{F0554941-820F-4636-9443-571F98099751}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="160">
   <si>
     <t>14/08/2026</t>
   </si>
@@ -1176,7 +1176,7 @@
     <xf numFmtId="166" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="131">
+  <cellXfs count="128">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1337,7 +1337,7 @@
     <xf numFmtId="16" fontId="2" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1350,18 +1350,18 @@
     <xf numFmtId="10" fontId="6" fillId="8" borderId="22" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="167" fontId="5" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="5" fillId="7" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1369,7 +1369,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="16" fontId="2" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1385,29 +1385,26 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="2" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="29" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="5" fillId="7" borderId="30" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="5" fillId="5" borderId="32" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="31" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="5" fillId="5" borderId="32" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="5" fillId="4" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="33" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="2" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="5" fillId="5" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="5" fillId="6" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
     <xf numFmtId="167" fontId="5" fillId="5" borderId="32" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="6" borderId="32" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="32" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
     <xf numFmtId="16" fontId="2" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1436,7 +1433,7 @@
     <xf numFmtId="10" fontId="6" fillId="8" borderId="39" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="32" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="8" fillId="8" borderId="40" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1457,14 +1454,412 @@
     <cellStyle name="Normal 4" xfId="3" xr:uid="{1392998E-B22D-467D-85CD-A138D4CE51BA}"/>
     <cellStyle name="Pourcentage" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="212">
+  <dxfs count="105">
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b/>
         <i val="0"/>
         <condense val="0"/>
         <extend val="0"/>
-        <color indexed="12"/>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color auto="1"/>
       </font>
     </dxf>
     <dxf>
@@ -1591,1378 +1986,6 @@
         <condense val="0"/>
         <extend val="0"/>
         <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
       </font>
     </dxf>
     <dxf>
@@ -19426,8 +18449,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="112" t="s">
-        <v>0</v>
+      <c r="A1" s="1">
+        <v>46255</v>
       </c>
       <c r="B1" s="93" t="s">
         <v>1</v>
@@ -19438,13 +18461,13 @@
       <c r="D1" s="94" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="113" t="s">
+      <c r="E1" s="110" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="114" t="s">
+      <c r="F1" s="111" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="115" t="s">
+      <c r="G1" s="112" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="7" t="s">
@@ -19465,13 +18488,13 @@
       <c r="A2" s="96">
         <v>1</v>
       </c>
-      <c r="B2" s="105" t="s">
+      <c r="B2" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="105" t="s">
+      <c r="C2" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="106" t="s">
+      <c r="D2" s="15" t="s">
         <v>10</v>
       </c>
       <c r="E2" s="16">
@@ -19480,7 +18503,7 @@
       <c r="F2" s="77">
         <v>0.34799999999999998</v>
       </c>
-      <c r="G2" s="116">
+      <c r="G2" s="113">
         <v>0</v>
       </c>
       <c r="I2" s="20"/>
@@ -19496,13 +18519,13 @@
       <c r="A3" s="98">
         <v>2</v>
       </c>
-      <c r="B3" s="105" t="s">
+      <c r="B3" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="105" t="s">
+      <c r="C3" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="106" t="s">
+      <c r="D3" s="15" t="s">
         <v>13</v>
       </c>
       <c r="E3" s="16">
@@ -19511,7 +18534,7 @@
       <c r="F3" s="77">
         <v>14.42</v>
       </c>
-      <c r="G3" s="116">
+      <c r="G3" s="113">
         <v>0</v>
       </c>
       <c r="H3" s="8"/>
@@ -19525,13 +18548,13 @@
       <c r="A4" s="96">
         <v>3</v>
       </c>
-      <c r="B4" s="105" t="s">
+      <c r="B4" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="105" t="s">
+      <c r="C4" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="106" t="s">
+      <c r="D4" s="15" t="s">
         <v>15</v>
       </c>
       <c r="E4" s="16">
@@ -19540,7 +18563,7 @@
       <c r="F4" s="77">
         <v>75.95</v>
       </c>
-      <c r="G4" s="116">
+      <c r="G4" s="113">
         <v>0</v>
       </c>
       <c r="H4" s="8"/>
@@ -19554,13 +18577,13 @@
       <c r="A5" s="98">
         <v>4</v>
       </c>
-      <c r="B5" s="105" t="s">
+      <c r="B5" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="105" t="s">
+      <c r="C5" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="106" t="s">
+      <c r="D5" s="15" t="s">
         <v>17</v>
       </c>
       <c r="E5" s="16">
@@ -19569,7 +18592,7 @@
       <c r="F5" s="77">
         <v>71.739999999999995</v>
       </c>
-      <c r="G5" s="116">
+      <c r="G5" s="113">
         <v>0</v>
       </c>
       <c r="H5" s="8"/>
@@ -19583,13 +18606,13 @@
       <c r="A6" s="96">
         <v>5</v>
       </c>
-      <c r="B6" s="105" t="s">
+      <c r="B6" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="105" t="s">
+      <c r="C6" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="106" t="s">
+      <c r="D6" s="15" t="s">
         <v>19</v>
       </c>
       <c r="E6" s="16">
@@ -19598,7 +18621,7 @@
       <c r="F6" s="77">
         <v>29.24</v>
       </c>
-      <c r="G6" s="116">
+      <c r="G6" s="113">
         <v>0</v>
       </c>
       <c r="H6" s="8"/>
@@ -19612,13 +18635,13 @@
       <c r="A7" s="98">
         <v>6</v>
       </c>
-      <c r="B7" s="105" t="s">
+      <c r="B7" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="105" t="s">
+      <c r="C7" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="106" t="s">
+      <c r="D7" s="15" t="s">
         <v>21</v>
       </c>
       <c r="E7" s="16">
@@ -19627,7 +18650,7 @@
       <c r="F7" s="77">
         <v>76.05</v>
       </c>
-      <c r="G7" s="116">
+      <c r="G7" s="113">
         <v>0</v>
       </c>
       <c r="H7" s="8"/>
@@ -19641,13 +18664,13 @@
       <c r="A8" s="96">
         <v>7</v>
       </c>
-      <c r="B8" s="105" t="s">
+      <c r="B8" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="105" t="s">
+      <c r="C8" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="106" t="s">
+      <c r="D8" s="15" t="s">
         <v>23</v>
       </c>
       <c r="E8" s="16">
@@ -19656,7 +18679,7 @@
       <c r="F8" s="77">
         <v>0.115</v>
       </c>
-      <c r="G8" s="116">
+      <c r="G8" s="113">
         <v>0</v>
       </c>
       <c r="H8" s="8"/>
@@ -19670,13 +18693,13 @@
       <c r="A9" s="98">
         <v>8</v>
       </c>
-      <c r="B9" s="105" t="s">
+      <c r="B9" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="105" t="s">
+      <c r="C9" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="106" t="s">
+      <c r="D9" s="15" t="s">
         <v>25</v>
       </c>
       <c r="E9" s="16">
@@ -19685,7 +18708,7 @@
       <c r="F9" s="77">
         <v>15.5</v>
       </c>
-      <c r="G9" s="116">
+      <c r="G9" s="113">
         <v>0</v>
       </c>
       <c r="H9" s="8"/>
@@ -19699,13 +18722,13 @@
       <c r="A10" s="96">
         <v>9</v>
       </c>
-      <c r="B10" s="105" t="s">
+      <c r="B10" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="105" t="s">
+      <c r="C10" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="106" t="s">
+      <c r="D10" s="15" t="s">
         <v>27</v>
       </c>
       <c r="E10" s="16">
@@ -19714,7 +18737,7 @@
       <c r="F10" s="77">
         <v>0.8</v>
       </c>
-      <c r="G10" s="116">
+      <c r="G10" s="113">
         <v>0</v>
       </c>
       <c r="H10" s="8"/>
@@ -19728,13 +18751,13 @@
       <c r="A11" s="98">
         <v>10</v>
       </c>
-      <c r="B11" s="105" t="s">
+      <c r="B11" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="105" t="s">
+      <c r="C11" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="106" t="s">
+      <c r="D11" s="15" t="s">
         <v>29</v>
       </c>
       <c r="E11" s="16">
@@ -19743,7 +18766,7 @@
       <c r="F11" s="77">
         <v>163.19999999999999</v>
       </c>
-      <c r="G11" s="116">
+      <c r="G11" s="113">
         <v>0</v>
       </c>
       <c r="H11" s="8"/>
@@ -19758,8 +18781,8 @@
       <c r="B12" s="100"/>
       <c r="C12" s="101"/>
       <c r="D12" s="102"/>
-      <c r="E12" s="117"/>
-      <c r="F12" s="118" t="s">
+      <c r="E12" s="114"/>
+      <c r="F12" s="115" t="s">
         <v>30</v>
       </c>
       <c r="G12" s="39">
@@ -19819,13 +18842,13 @@
       <c r="A16" s="96">
         <v>1</v>
       </c>
-      <c r="B16" s="105" t="s">
+      <c r="B16" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="C16" s="105" t="s">
+      <c r="C16" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="D16" s="106" t="s">
+      <c r="D16" s="15" t="s">
         <v>35</v>
       </c>
       <c r="E16" s="36">
@@ -19844,13 +18867,13 @@
       <c r="A17" s="98">
         <v>2</v>
       </c>
-      <c r="B17" s="105" t="s">
+      <c r="B17" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="105" t="s">
+      <c r="C17" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="106" t="s">
+      <c r="D17" s="15" t="s">
         <v>37</v>
       </c>
       <c r="E17" s="36">
@@ -19869,13 +18892,13 @@
       <c r="A18" s="96">
         <v>3</v>
       </c>
-      <c r="B18" s="105" t="s">
+      <c r="B18" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="105" t="s">
+      <c r="C18" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="D18" s="106" t="s">
+      <c r="D18" s="15" t="s">
         <v>39</v>
       </c>
       <c r="E18" s="36">
@@ -19894,13 +18917,13 @@
       <c r="A19" s="98">
         <v>4</v>
       </c>
-      <c r="B19" s="105" t="s">
+      <c r="B19" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="C19" s="105" t="s">
+      <c r="C19" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="D19" s="106" t="s">
+      <c r="D19" s="15" t="s">
         <v>41</v>
       </c>
       <c r="E19" s="36">
@@ -19919,13 +18942,13 @@
       <c r="A20" s="96">
         <v>5</v>
       </c>
-      <c r="B20" s="105" t="s">
+      <c r="B20" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C20" s="105" t="s">
+      <c r="C20" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="D20" s="106" t="s">
+      <c r="D20" s="15" t="s">
         <v>43</v>
       </c>
       <c r="E20" s="36">
@@ -19944,13 +18967,13 @@
       <c r="A21" s="98">
         <v>6</v>
       </c>
-      <c r="B21" s="105" t="s">
+      <c r="B21" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="C21" s="105" t="s">
+      <c r="C21" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="D21" s="106" t="s">
+      <c r="D21" s="15" t="s">
         <v>45</v>
       </c>
       <c r="E21" s="36">
@@ -19969,13 +18992,13 @@
       <c r="A22" s="96">
         <v>7</v>
       </c>
-      <c r="B22" s="105" t="s">
+      <c r="B22" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="C22" s="105" t="s">
+      <c r="C22" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="D22" s="106" t="s">
+      <c r="D22" s="15" t="s">
         <v>47</v>
       </c>
       <c r="E22" s="36">
@@ -19994,13 +19017,13 @@
       <c r="A23" s="98">
         <v>8</v>
       </c>
-      <c r="B23" s="105" t="s">
+      <c r="B23" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="C23" s="105" t="s">
+      <c r="C23" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="D23" s="106" t="s">
+      <c r="D23" s="15" t="s">
         <v>49</v>
       </c>
       <c r="E23" s="36">
@@ -20019,13 +19042,13 @@
       <c r="A24" s="96">
         <v>9</v>
       </c>
-      <c r="B24" s="105" t="s">
+      <c r="B24" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="C24" s="105" t="s">
+      <c r="C24" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="D24" s="106" t="s">
+      <c r="D24" s="15" t="s">
         <v>51</v>
       </c>
       <c r="E24" s="36">
@@ -20044,13 +19067,13 @@
       <c r="A25" s="98">
         <v>10</v>
       </c>
-      <c r="B25" s="105" t="s">
+      <c r="B25" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="C25" s="105" t="s">
+      <c r="C25" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="D25" s="106" t="s">
+      <c r="D25" s="15" t="s">
         <v>53</v>
       </c>
       <c r="E25" s="36">
@@ -20067,9 +19090,9 @@
     </row>
     <row r="26" spans="1:11" ht="15.9" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A26" s="96"/>
-      <c r="B26" s="105"/>
+      <c r="B26" s="14"/>
       <c r="C26" s="76"/>
-      <c r="D26" s="107"/>
+      <c r="D26" s="105"/>
       <c r="E26" s="36"/>
       <c r="F26" s="38" t="s">
         <v>30</v>
@@ -20091,11 +19114,11 @@
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A27" s="108"/>
-      <c r="B27" s="109"/>
+      <c r="A27" s="106"/>
+      <c r="B27" s="107"/>
       <c r="C27" s="100"/>
-      <c r="D27" s="110"/>
-      <c r="E27" s="111"/>
+      <c r="D27" s="108"/>
+      <c r="E27" s="109"/>
       <c r="F27" s="8"/>
       <c r="H27" s="8"/>
       <c r="I27"/>
@@ -20117,13 +19140,13 @@
       <c r="D29" s="94" t="s">
         <v>3</v>
       </c>
-      <c r="E29" s="113" t="s">
+      <c r="E29" s="110" t="s">
         <v>4</v>
       </c>
-      <c r="F29" s="114" t="s">
+      <c r="F29" s="111" t="s">
         <v>5</v>
       </c>
-      <c r="G29" s="115" t="s">
+      <c r="G29" s="112" t="s">
         <v>6</v>
       </c>
       <c r="H29" s="7" t="s">
@@ -20135,13 +19158,13 @@
       <c r="A30" s="96">
         <v>1</v>
       </c>
-      <c r="B30" s="105" t="s">
+      <c r="B30" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="C30" s="105" t="s">
+      <c r="C30" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="D30" s="106" t="s">
+      <c r="D30" s="15" t="s">
         <v>57</v>
       </c>
       <c r="E30" s="16">
@@ -20150,7 +19173,7 @@
       <c r="F30" s="77">
         <v>11.4</v>
       </c>
-      <c r="G30" s="116">
+      <c r="G30" s="113">
         <v>0</v>
       </c>
       <c r="H30"/>
@@ -20160,13 +19183,13 @@
       <c r="A31" s="98">
         <v>2</v>
       </c>
-      <c r="B31" s="105" t="s">
+      <c r="B31" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="C31" s="105" t="s">
+      <c r="C31" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="D31" s="106" t="s">
+      <c r="D31" s="15" t="s">
         <v>59</v>
       </c>
       <c r="E31" s="16">
@@ -20175,7 +19198,7 @@
       <c r="F31" s="77">
         <v>21.75</v>
       </c>
-      <c r="G31" s="116">
+      <c r="G31" s="113">
         <v>0</v>
       </c>
       <c r="H31"/>
@@ -20185,13 +19208,13 @@
       <c r="A32" s="96">
         <v>3</v>
       </c>
-      <c r="B32" s="105" t="s">
+      <c r="B32" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="C32" s="105" t="s">
+      <c r="C32" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="D32" s="106" t="s">
+      <c r="D32" s="15" t="s">
         <v>61</v>
       </c>
       <c r="E32" s="16">
@@ -20200,7 +19223,7 @@
       <c r="F32" s="77">
         <v>8.8999999999999996E-2</v>
       </c>
-      <c r="G32" s="116">
+      <c r="G32" s="113">
         <v>0</v>
       </c>
       <c r="H32"/>
@@ -20210,13 +19233,13 @@
       <c r="A33" s="98">
         <v>4</v>
       </c>
-      <c r="B33" s="105" t="s">
+      <c r="B33" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="C33" s="105" t="s">
+      <c r="C33" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="D33" s="106" t="s">
+      <c r="D33" s="15" t="s">
         <v>63</v>
       </c>
       <c r="E33" s="16">
@@ -20225,7 +19248,7 @@
       <c r="F33" s="77">
         <v>0.38</v>
       </c>
-      <c r="G33" s="116">
+      <c r="G33" s="113">
         <v>0</v>
       </c>
       <c r="H33"/>
@@ -20235,13 +19258,13 @@
       <c r="A34" s="96">
         <v>5</v>
       </c>
-      <c r="B34" s="105" t="s">
+      <c r="B34" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="C34" s="105" t="s">
+      <c r="C34" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="D34" s="106" t="s">
+      <c r="D34" s="15" t="s">
         <v>65</v>
       </c>
       <c r="E34" s="16">
@@ -20250,7 +19273,7 @@
       <c r="F34" s="77">
         <v>1.79</v>
       </c>
-      <c r="G34" s="116">
+      <c r="G34" s="113">
         <v>0</v>
       </c>
       <c r="H34"/>
@@ -20260,13 +19283,13 @@
       <c r="A35" s="98">
         <v>6</v>
       </c>
-      <c r="B35" s="105" t="s">
+      <c r="B35" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="C35" s="105" t="s">
+      <c r="C35" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="D35" s="106" t="s">
+      <c r="D35" s="15" t="s">
         <v>67</v>
       </c>
       <c r="E35" s="16">
@@ -20275,7 +19298,7 @@
       <c r="F35" s="77">
         <v>3</v>
       </c>
-      <c r="G35" s="116">
+      <c r="G35" s="113">
         <v>0</v>
       </c>
       <c r="H35"/>
@@ -20285,13 +19308,13 @@
       <c r="A36" s="96">
         <v>7</v>
       </c>
-      <c r="B36" s="105" t="s">
+      <c r="B36" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="C36" s="105" t="s">
+      <c r="C36" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="D36" s="106" t="s">
+      <c r="D36" s="15" t="s">
         <v>69</v>
       </c>
       <c r="E36" s="16">
@@ -20300,7 +19323,7 @@
       <c r="F36" s="77">
         <v>0.13600000000000001</v>
       </c>
-      <c r="G36" s="116">
+      <c r="G36" s="113">
         <v>0</v>
       </c>
       <c r="H36"/>
@@ -20310,13 +19333,13 @@
       <c r="A37" s="98">
         <v>8</v>
       </c>
-      <c r="B37" s="105" t="s">
+      <c r="B37" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="C37" s="105" t="s">
+      <c r="C37" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="D37" s="106" t="s">
+      <c r="D37" s="15" t="s">
         <v>72</v>
       </c>
       <c r="E37" s="16">
@@ -20325,7 +19348,7 @@
       <c r="F37" s="77">
         <v>3.19</v>
       </c>
-      <c r="G37" s="116">
+      <c r="G37" s="113">
         <v>0</v>
       </c>
       <c r="H37"/>
@@ -20336,13 +19359,13 @@
       <c r="A38" s="96">
         <v>9</v>
       </c>
-      <c r="B38" s="105" t="s">
+      <c r="B38" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="C38" s="105" t="s">
+      <c r="C38" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="D38" s="106" t="s">
+      <c r="D38" s="15" t="s">
         <v>74</v>
       </c>
       <c r="E38" s="16">
@@ -20351,7 +19374,7 @@
       <c r="F38" s="77">
         <v>0.58799999999999997</v>
       </c>
-      <c r="G38" s="116">
+      <c r="G38" s="113">
         <v>0</v>
       </c>
       <c r="H38"/>
@@ -20362,13 +19385,13 @@
       <c r="A39" s="98">
         <v>10</v>
       </c>
-      <c r="B39" s="105" t="s">
+      <c r="B39" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="C39" s="105" t="s">
+      <c r="C39" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="D39" s="106" t="s">
+      <c r="D39" s="15" t="s">
         <v>76</v>
       </c>
       <c r="E39" s="16">
@@ -20377,22 +19400,22 @@
       <c r="F39" s="77">
         <v>0.158</v>
       </c>
-      <c r="G39" s="116">
+      <c r="G39" s="113">
         <v>0</v>
       </c>
       <c r="H39"/>
       <c r="I39"/>
     </row>
     <row r="40" spans="1:16" ht="15.9" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="125"/>
-      <c r="B40" s="126"/>
-      <c r="C40" s="127"/>
-      <c r="D40" s="128"/>
-      <c r="E40" s="129"/>
-      <c r="F40" s="118" t="s">
+      <c r="A40" s="122"/>
+      <c r="B40" s="123"/>
+      <c r="C40" s="124"/>
+      <c r="D40" s="125"/>
+      <c r="E40" s="126"/>
+      <c r="F40" s="115" t="s">
         <v>30</v>
       </c>
-      <c r="G40" s="130">
+      <c r="G40" s="127">
         <v>0</v>
       </c>
       <c r="H40">
@@ -20423,13 +19446,13 @@
       <c r="D42" s="94" t="s">
         <v>3</v>
       </c>
-      <c r="E42" s="113" t="s">
+      <c r="E42" s="110" t="s">
         <v>4</v>
       </c>
-      <c r="F42" s="114" t="s">
+      <c r="F42" s="111" t="s">
         <v>5</v>
       </c>
-      <c r="G42" s="121" t="s">
+      <c r="G42" s="118" t="s">
         <v>6</v>
       </c>
       <c r="H42" s="7" t="s">
@@ -20441,12 +19464,12 @@
       <c r="A43" s="96">
         <v>1</v>
       </c>
-      <c r="B43" s="105"/>
-      <c r="C43" s="105"/>
-      <c r="D43" s="106"/>
+      <c r="B43" s="14"/>
+      <c r="C43" s="14"/>
+      <c r="D43" s="15"/>
       <c r="E43" s="16"/>
       <c r="F43" s="77"/>
-      <c r="G43" s="122"/>
+      <c r="G43" s="119"/>
       <c r="H43"/>
       <c r="I43"/>
     </row>
@@ -20454,12 +19477,12 @@
       <c r="A44" s="98">
         <v>2</v>
       </c>
-      <c r="B44" s="105"/>
-      <c r="C44" s="105"/>
-      <c r="D44" s="106"/>
+      <c r="B44" s="14"/>
+      <c r="C44" s="14"/>
+      <c r="D44" s="15"/>
       <c r="E44" s="16"/>
       <c r="F44" s="77"/>
-      <c r="G44" s="122"/>
+      <c r="G44" s="119"/>
       <c r="H44"/>
       <c r="I44"/>
     </row>
@@ -20467,12 +19490,12 @@
       <c r="A45" s="96">
         <v>3</v>
       </c>
-      <c r="B45" s="105"/>
-      <c r="C45" s="105"/>
-      <c r="D45" s="106"/>
+      <c r="B45" s="14"/>
+      <c r="C45" s="14"/>
+      <c r="D45" s="15"/>
       <c r="E45" s="16"/>
       <c r="F45" s="77"/>
-      <c r="G45" s="122"/>
+      <c r="G45" s="119"/>
       <c r="H45"/>
       <c r="I45"/>
     </row>
@@ -20480,12 +19503,12 @@
       <c r="A46" s="98">
         <v>4</v>
       </c>
-      <c r="B46" s="105"/>
-      <c r="C46" s="105"/>
-      <c r="D46" s="106"/>
+      <c r="B46" s="14"/>
+      <c r="C46" s="14"/>
+      <c r="D46" s="15"/>
       <c r="E46" s="16"/>
       <c r="F46" s="77"/>
-      <c r="G46" s="122"/>
+      <c r="G46" s="119"/>
       <c r="H46"/>
       <c r="I46"/>
     </row>
@@ -20493,12 +19516,12 @@
       <c r="A47" s="96">
         <v>5</v>
       </c>
-      <c r="B47" s="105"/>
-      <c r="C47" s="105"/>
-      <c r="D47" s="106"/>
+      <c r="B47" s="14"/>
+      <c r="C47" s="14"/>
+      <c r="D47" s="15"/>
       <c r="E47" s="16"/>
       <c r="F47" s="77"/>
-      <c r="G47" s="122"/>
+      <c r="G47" s="119"/>
       <c r="H47"/>
       <c r="I47"/>
     </row>
@@ -20506,12 +19529,12 @@
       <c r="A48" s="98">
         <v>6</v>
       </c>
-      <c r="B48" s="105"/>
-      <c r="C48" s="105"/>
-      <c r="D48" s="106"/>
+      <c r="B48" s="14"/>
+      <c r="C48" s="14"/>
+      <c r="D48" s="15"/>
       <c r="E48" s="16"/>
       <c r="F48" s="77"/>
-      <c r="G48" s="122"/>
+      <c r="G48" s="119"/>
       <c r="H48"/>
       <c r="I48"/>
     </row>
@@ -20519,12 +19542,12 @@
       <c r="A49" s="96">
         <v>7</v>
       </c>
-      <c r="B49" s="105"/>
-      <c r="C49" s="105"/>
-      <c r="D49" s="106"/>
+      <c r="B49" s="14"/>
+      <c r="C49" s="14"/>
+      <c r="D49" s="15"/>
       <c r="E49" s="16"/>
       <c r="F49" s="77"/>
-      <c r="G49" s="122"/>
+      <c r="G49" s="119"/>
       <c r="H49"/>
       <c r="I49"/>
     </row>
@@ -20532,12 +19555,12 @@
       <c r="A50" s="98">
         <v>8</v>
       </c>
-      <c r="B50" s="105"/>
-      <c r="C50" s="105"/>
-      <c r="D50" s="106"/>
+      <c r="B50" s="14"/>
+      <c r="C50" s="14"/>
+      <c r="D50" s="15"/>
       <c r="E50" s="16"/>
       <c r="F50" s="77"/>
-      <c r="G50" s="122"/>
+      <c r="G50" s="119"/>
       <c r="H50"/>
       <c r="I50"/>
     </row>
@@ -20545,12 +19568,12 @@
       <c r="A51" s="96">
         <v>9</v>
       </c>
-      <c r="B51" s="105"/>
-      <c r="C51" s="105"/>
-      <c r="D51" s="106"/>
+      <c r="B51" s="14"/>
+      <c r="C51" s="14"/>
+      <c r="D51" s="15"/>
       <c r="E51" s="16"/>
       <c r="F51" s="77"/>
-      <c r="G51" s="122"/>
+      <c r="G51" s="119"/>
       <c r="H51"/>
       <c r="I51"/>
     </row>
@@ -20558,12 +19581,12 @@
       <c r="A52" s="98">
         <v>10</v>
       </c>
-      <c r="B52" s="105"/>
-      <c r="C52" s="105"/>
-      <c r="D52" s="106"/>
+      <c r="B52" s="14"/>
+      <c r="C52" s="14"/>
+      <c r="D52" s="15"/>
       <c r="E52" s="16"/>
       <c r="F52" s="77"/>
-      <c r="G52" s="122"/>
+      <c r="G52" s="119"/>
       <c r="H52"/>
       <c r="I52"/>
     </row>
@@ -20572,11 +19595,11 @@
       <c r="B53" s="100"/>
       <c r="C53" s="101"/>
       <c r="D53" s="102"/>
-      <c r="E53" s="123"/>
-      <c r="F53" s="120" t="s">
+      <c r="E53" s="120"/>
+      <c r="F53" s="117" t="s">
         <v>30</v>
       </c>
-      <c r="G53" s="124">
+      <c r="G53" s="121">
         <v>0</v>
       </c>
       <c r="H53" s="31" t="s">
@@ -21165,7 +20188,7 @@
         <v>4</v>
       </c>
       <c r="B85" s="80"/>
-      <c r="C85" s="119"/>
+      <c r="C85" s="116"/>
       <c r="D85" s="80"/>
       <c r="E85" s="16"/>
       <c r="F85" s="77"/>
@@ -21178,7 +20201,7 @@
         <v>5</v>
       </c>
       <c r="B86" s="75"/>
-      <c r="C86" s="119"/>
+      <c r="C86" s="116"/>
       <c r="D86" s="75"/>
       <c r="E86" s="16"/>
       <c r="F86" s="77"/>
@@ -21191,7 +20214,7 @@
         <v>6</v>
       </c>
       <c r="B87" s="80"/>
-      <c r="C87" s="119"/>
+      <c r="C87" s="116"/>
       <c r="D87" s="80"/>
       <c r="E87" s="16"/>
       <c r="F87" s="77"/>
@@ -21217,7 +20240,7 @@
         <v>8</v>
       </c>
       <c r="B89" s="80"/>
-      <c r="C89" s="119"/>
+      <c r="C89" s="116"/>
       <c r="D89" s="80"/>
       <c r="E89" s="16"/>
       <c r="F89" s="77"/>
@@ -21257,7 +20280,7 @@
       <c r="C92" s="83"/>
       <c r="D92" s="54"/>
       <c r="E92" s="84"/>
-      <c r="F92" s="120" t="s">
+      <c r="F92" s="117" t="s">
         <v>30</v>
       </c>
       <c r="G92" s="50" t="e">
@@ -23681,76 +22704,73 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B56:B65">
-    <cfRule type="expression" dxfId="105" priority="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="104" priority="5" stopIfTrue="1">
       <formula>IF(AO56&gt;0,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B69:B78">
-    <cfRule type="expression" dxfId="104" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="103" priority="3" stopIfTrue="1">
       <formula>IF(AO69&gt;0,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B81">
-    <cfRule type="expression" dxfId="103" priority="50" stopIfTrue="1">
+    <cfRule type="expression" dxfId="102" priority="50" stopIfTrue="1">
       <formula>IF(AN62&gt;0,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B82:B91">
-    <cfRule type="expression" dxfId="102" priority="9" stopIfTrue="1">
+    <cfRule type="expression" dxfId="101" priority="9" stopIfTrue="1">
       <formula>IF(AL82&gt;0,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B92">
-    <cfRule type="expression" dxfId="101" priority="46" stopIfTrue="1">
+    <cfRule type="expression" dxfId="100" priority="46" stopIfTrue="1">
       <formula>IF(AL91&gt;0,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B95">
-    <cfRule type="expression" dxfId="100" priority="49" stopIfTrue="1">
+    <cfRule type="expression" dxfId="99" priority="49" stopIfTrue="1">
       <formula>IF(AN75&gt;0,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B96:B105">
-    <cfRule type="expression" dxfId="99" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="98" priority="7" stopIfTrue="1">
       <formula>IF(AO96&gt;0,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B106">
-    <cfRule type="expression" dxfId="98" priority="47" stopIfTrue="1">
+    <cfRule type="expression" dxfId="97" priority="47" stopIfTrue="1">
       <formula>IF(AN104&gt;0,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B107">
-    <cfRule type="expression" dxfId="97" priority="48" stopIfTrue="1">
+    <cfRule type="expression" dxfId="96" priority="48" stopIfTrue="1">
       <formula>IF(AN104&gt;0,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D56:D65">
-    <cfRule type="expression" dxfId="96" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="95" priority="4" stopIfTrue="1">
       <formula>IF(AQ56&gt;0,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D69:D78">
-    <cfRule type="expression" dxfId="95" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="94" priority="2" stopIfTrue="1">
       <formula>IF(AQ69&gt;0,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D82:D91">
-    <cfRule type="expression" dxfId="94" priority="8" stopIfTrue="1">
+    <cfRule type="expression" dxfId="93" priority="8" stopIfTrue="1">
       <formula>IF(AN82&gt;0,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D96:D105">
-    <cfRule type="expression" dxfId="93" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="92" priority="6" stopIfTrue="1">
       <formula>IF(AQ96&gt;0,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F11 F16:F25">
-    <cfRule type="expression" dxfId="92" priority="19" stopIfTrue="1">
+    <cfRule type="expression" dxfId="91" priority="19" stopIfTrue="1">
       <formula>IF(#REF!="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="91" priority="20" stopIfTrue="1">
-      <formula>IF($T200="AAA",TRUE,FALSE)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="90" priority="21" stopIfTrue="1">
       <formula>IF($U200="AAA",TRUE,FALSE)</formula>
@@ -23764,33 +22784,33 @@
     <cfRule type="expression" dxfId="87" priority="24" stopIfTrue="1">
       <formula>IF($U200="AAA",TRUE,FALSE)</formula>
     </cfRule>
+    <cfRule type="expression" dxfId="86" priority="20" stopIfTrue="1">
+      <formula>IF($T200="AAA",TRUE,FALSE)</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F30:F39">
-    <cfRule type="expression" dxfId="86" priority="80" stopIfTrue="1">
-      <formula>IF(#REF!="AAA",TRUE,FALSE)</formula>
+    <cfRule type="expression" dxfId="85" priority="85" stopIfTrue="1">
+      <formula>IF($U230="AAA",TRUE,FALSE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="85" priority="81" stopIfTrue="1">
+    <cfRule type="expression" dxfId="84" priority="84" stopIfTrue="1">
       <formula>IF($T230="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="84" priority="82" stopIfTrue="1">
-      <formula>IF($U230="AAA",TRUE,FALSE)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="83" priority="83" stopIfTrue="1">
       <formula>IF($AN5="AAA",TRUE,FALSE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="82" priority="84" stopIfTrue="1">
+    <cfRule type="expression" dxfId="82" priority="82" stopIfTrue="1">
+      <formula>IF($U230="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="81" priority="81" stopIfTrue="1">
       <formula>IF($T230="AAA",TRUE,FALSE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="81" priority="85" stopIfTrue="1">
-      <formula>IF($U230="AAA",TRUE,FALSE)</formula>
+    <cfRule type="expression" dxfId="80" priority="80" stopIfTrue="1">
+      <formula>IF(#REF!="AAA",TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F43:F52">
-    <cfRule type="expression" dxfId="80" priority="86" stopIfTrue="1">
+    <cfRule type="expression" dxfId="79" priority="86" stopIfTrue="1">
       <formula>IF(#REF!="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="79" priority="87" stopIfTrue="1">
-      <formula>IF($T242="AAA",TRUE,FALSE)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="78" priority="88" stopIfTrue="1">
       <formula>IF($U242="AAA",TRUE,FALSE)</formula>
@@ -23804,306 +22824,308 @@
     <cfRule type="expression" dxfId="75" priority="91" stopIfTrue="1">
       <formula>IF($U242="AAA",TRUE,FALSE)</formula>
     </cfRule>
+    <cfRule type="expression" dxfId="74" priority="87" stopIfTrue="1">
+      <formula>IF($T242="AAA",TRUE,FALSE)</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F56">
-    <cfRule type="expression" dxfId="74" priority="76" stopIfTrue="1">
-      <formula>IF(#REF!="AAA",TRUE,FALSE)</formula>
+    <cfRule type="expression" dxfId="73" priority="78" stopIfTrue="1">
+      <formula>IF($T254="AAA",TRUE,FALSE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="73" priority="77" stopIfTrue="1">
+    <cfRule type="expression" dxfId="72" priority="77" stopIfTrue="1">
       <formula>IF($AN28="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="72" priority="78" stopIfTrue="1">
-      <formula>IF($T254="AAA",TRUE,FALSE)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="71" priority="79" stopIfTrue="1">
       <formula>IF($U254="AAA",TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F69:F78">
-    <cfRule type="expression" dxfId="70" priority="1" stopIfTrue="1">
+  <conditionalFormatting sqref="F56:F67">
+    <cfRule type="expression" dxfId="70" priority="76" stopIfTrue="1">
       <formula>IF(#REF!="AAA",TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="F57:F67">
+    <cfRule type="expression" dxfId="69" priority="95" stopIfTrue="1">
+      <formula>IF($U255="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="68" priority="93" stopIfTrue="1">
+      <formula>IF($AK29="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="67" priority="94" stopIfTrue="1">
+      <formula>IF($T255="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F69">
+    <cfRule type="expression" dxfId="66" priority="97" stopIfTrue="1">
+      <formula>IF($U268="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="65" priority="96" stopIfTrue="1">
+      <formula>IF($T268="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="64" priority="98" stopIfTrue="1">
+      <formula>IF($AJ43="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="63" priority="99" stopIfTrue="1">
+      <formula>IF($T268="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="62" priority="100" stopIfTrue="1">
+      <formula>IF($U268="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F69:F78">
+    <cfRule type="expression" dxfId="61" priority="1" stopIfTrue="1">
+      <formula>IF(#REF!="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F70:F78">
+    <cfRule type="expression" dxfId="60" priority="103" stopIfTrue="1">
+      <formula>IF($U267="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="59" priority="102" stopIfTrue="1">
+      <formula>IF($T267="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="58" priority="101" stopIfTrue="1">
+      <formula>IF($AJ42="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F82">
+    <cfRule type="expression" dxfId="57" priority="106" stopIfTrue="1">
+      <formula>IF($U278="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="56" priority="104" stopIfTrue="1">
+      <formula>IF($AJ53="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="55" priority="105" stopIfTrue="1">
+      <formula>IF($T278="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F82:F91">
-    <cfRule type="expression" dxfId="69" priority="65" stopIfTrue="1">
+    <cfRule type="expression" dxfId="54" priority="65" stopIfTrue="1">
       <formula>IF(#REF!="AAA",TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F83:F91">
-    <cfRule type="expression" dxfId="68" priority="66" stopIfTrue="1">
+    <cfRule type="expression" dxfId="53" priority="68" stopIfTrue="1">
+      <formula>IF($U279="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="52" priority="66" stopIfTrue="1">
       <formula>IF($AN55="AAA",TRUE,FALSE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="67" priority="67" stopIfTrue="1">
+    <cfRule type="expression" dxfId="51" priority="67" stopIfTrue="1">
       <formula>IF($T279="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="66" priority="68" stopIfTrue="1">
-      <formula>IF($U279="AAA",TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F96:F97">
-    <cfRule type="expression" dxfId="65" priority="73" stopIfTrue="1">
-      <formula>IF($AN65="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="64" priority="74" stopIfTrue="1">
+    <cfRule type="expression" dxfId="50" priority="74" stopIfTrue="1">
       <formula>IF($T291="AAA",TRUE,FALSE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="63" priority="75" stopIfTrue="1">
+    <cfRule type="expression" dxfId="49" priority="75" stopIfTrue="1">
       <formula>IF($U291="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="48" priority="73" stopIfTrue="1">
+      <formula>IF($AN65="AAA",TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F96:F106">
-    <cfRule type="expression" dxfId="62" priority="69" stopIfTrue="1">
+    <cfRule type="expression" dxfId="47" priority="69" stopIfTrue="1">
       <formula>IF(#REF!="AAA",TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F98:F106">
-    <cfRule type="expression" dxfId="61" priority="70" stopIfTrue="1">
+    <cfRule type="expression" dxfId="46" priority="70" stopIfTrue="1">
       <formula>IF($AN68="AAA",TRUE,FALSE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="60" priority="71" stopIfTrue="1">
+    <cfRule type="expression" dxfId="45" priority="71" stopIfTrue="1">
       <formula>IF($T293="AAA",TRUE,FALSE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="59" priority="72" stopIfTrue="1">
+    <cfRule type="expression" dxfId="44" priority="72" stopIfTrue="1">
       <formula>IF($U293="AAA",TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G16:G26 G2:G12 G30:G41">
-    <cfRule type="cellIs" dxfId="58" priority="52" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="G2:G12 G16:G26 G30:G41">
+    <cfRule type="cellIs" dxfId="43" priority="53" stopIfTrue="1" operator="greaterThanOrEqual">
+      <formula>#REF!</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="42" priority="52" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="57" priority="53" stopIfTrue="1" operator="greaterThanOrEqual">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G12 G16:G28">
+    <cfRule type="cellIs" dxfId="41" priority="25" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G30:G41 G2:G12 G16:G26">
+    <cfRule type="cellIs" dxfId="40" priority="51" operator="greaterThan">
       <formula>#REF!</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G16:G28 G2:G12">
-    <cfRule type="cellIs" dxfId="56" priority="25" stopIfTrue="1" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G16:G26 G2:G12 G30:G41">
-    <cfRule type="cellIs" dxfId="55" priority="51" operator="greaterThan">
-      <formula>#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G43:G54 G56:G67 G30:G41">
-    <cfRule type="cellIs" dxfId="54" priority="42" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="G43:G54 G30:G41 G56:G67">
+    <cfRule type="cellIs" dxfId="39" priority="42" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G43:G54">
-    <cfRule type="cellIs" dxfId="53" priority="30" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="38" priority="30" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="52" priority="31" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="37" priority="33" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>#REF!</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="51" priority="32" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="36" priority="32" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="50" priority="33" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="35" priority="31" operator="greaterThan">
       <formula>#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G53:G54">
-    <cfRule type="cellIs" dxfId="49" priority="16" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="34" priority="16" operator="greaterThan">
       <formula>#REF!</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="48" priority="17" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="33" priority="18" stopIfTrue="1" operator="greaterThanOrEqual">
+      <formula>#REF!</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="32" priority="17" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="47" priority="18" stopIfTrue="1" operator="greaterThanOrEqual">
-      <formula>#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G56:G67">
-    <cfRule type="cellIs" dxfId="46" priority="43" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="31" priority="45" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>#REF!</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="45" priority="44" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="30" priority="43" operator="greaterThan">
+      <formula>#REF!</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="29" priority="44" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="44" priority="45" stopIfTrue="1" operator="greaterThanOrEqual">
-      <formula>#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G69:G80">
-    <cfRule type="cellIs" dxfId="43" priority="26" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="28" priority="29" stopIfTrue="1" operator="greaterThanOrEqual">
+      <formula>#REF!</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="27" priority="27" operator="greaterThan">
+      <formula>#REF!</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="26" priority="26" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="27" operator="greaterThan">
-      <formula>#REF!</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="41" priority="28" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="25" priority="28" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="29" stopIfTrue="1" operator="greaterThanOrEqual">
-      <formula>#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G82:G92">
-    <cfRule type="cellIs" dxfId="39" priority="38" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="24" priority="40" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="38" priority="39" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="23" priority="39" operator="greaterThan">
       <formula>#REF!</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="40" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="22" priority="41" stopIfTrue="1" operator="greaterThanOrEqual">
+      <formula>#REF!</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="21" priority="38" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="36" priority="41" stopIfTrue="1" operator="greaterThanOrEqual">
-      <formula>#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G96:G106">
-    <cfRule type="cellIs" dxfId="35" priority="34" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="20" priority="37" stopIfTrue="1" operator="greaterThanOrEqual">
+      <formula>#REF!</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="19" priority="36" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="35" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="18" priority="35" operator="greaterThan">
       <formula>#REF!</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="36" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="17" priority="34" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="32" priority="37" stopIfTrue="1" operator="greaterThanOrEqual">
-      <formula>#REF!</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H81">
+    <cfRule type="cellIs" dxfId="16" priority="15" operator="greaterThan">
+      <formula>$H81</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I12 I53 K53 I66 K66">
-    <cfRule type="cellIs" dxfId="31" priority="59" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="15" priority="59" operator="greaterThan">
       <formula>$K12</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I26">
-    <cfRule type="cellIs" dxfId="30" priority="10" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="14" priority="10" operator="greaterThan">
       <formula>$K26</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I75">
-    <cfRule type="cellIs" dxfId="29" priority="60" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="13" priority="60" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I93:I94">
-    <cfRule type="cellIs" dxfId="28" priority="58" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="12" priority="58" operator="greaterThan">
       <formula>$K93</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I107">
-    <cfRule type="cellIs" dxfId="27" priority="57" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="11" priority="57" operator="greaterThan">
       <formula>$K107</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I109">
-    <cfRule type="cellIs" dxfId="26" priority="55" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="10" priority="55" operator="greaterThan">
       <formula>$K109</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J97">
-    <cfRule type="cellIs" dxfId="25" priority="62" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="9" priority="62" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J103">
-    <cfRule type="cellIs" dxfId="24" priority="61" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="8" priority="61" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="cellIs" dxfId="23" priority="13" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="7" priority="13" operator="greaterThan">
       <formula>$K12</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K26">
-    <cfRule type="cellIs" dxfId="22" priority="12" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="12" operator="greaterThan">
       <formula>$K26</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K41">
-    <cfRule type="cellIs" dxfId="21" priority="11" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="11" operator="greaterThan">
       <formula>$K41</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H81">
-    <cfRule type="cellIs" dxfId="20" priority="15" operator="greaterThan">
-      <formula>$H81</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="K93:K94">
-    <cfRule type="cellIs" dxfId="19" priority="14" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="4" priority="14" operator="greaterThan">
       <formula>$K93</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K104">
-    <cfRule type="cellIs" dxfId="18" priority="63" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="3" priority="63" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K107">
-    <cfRule type="cellIs" dxfId="17" priority="56" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="56" operator="greaterThan">
       <formula>$I107</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K109">
-    <cfRule type="cellIs" dxfId="16" priority="54" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="54" operator="greaterThan">
       <formula>$I109</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P37:P38">
-    <cfRule type="cellIs" dxfId="15" priority="64" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="64" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F57:F67">
-    <cfRule type="expression" dxfId="14" priority="92" stopIfTrue="1">
-      <formula>IF(#REF!="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="13" priority="93" stopIfTrue="1">
-      <formula>IF($AK29="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="12" priority="94" stopIfTrue="1">
-      <formula>IF($T255="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="11" priority="95" stopIfTrue="1">
-      <formula>IF($U255="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F69">
-    <cfRule type="expression" dxfId="10" priority="96" stopIfTrue="1">
-      <formula>IF($T268="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="9" priority="97" stopIfTrue="1">
-      <formula>IF($U268="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="8" priority="98" stopIfTrue="1">
-      <formula>IF($AJ43="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="7" priority="99" stopIfTrue="1">
-      <formula>IF($T268="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="6" priority="100" stopIfTrue="1">
-      <formula>IF($U268="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F70:F78">
-    <cfRule type="expression" dxfId="5" priority="101" stopIfTrue="1">
-      <formula>IF($AJ42="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="102" stopIfTrue="1">
-      <formula>IF($T267="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="3" priority="103" stopIfTrue="1">
-      <formula>IF($U267="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F82">
-    <cfRule type="expression" dxfId="2" priority="104" stopIfTrue="1">
-      <formula>IF($AJ53="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="105" stopIfTrue="1">
-      <formula>IF($T278="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="0" priority="106" stopIfTrue="1">
-      <formula>IF($U278="AAA",TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Twitter_Donnees.xlsx
+++ b/Twitter_Donnees.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Bourse\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4F429416-0EC9-49A1-90B2-3FFF5941422E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDE97C68-D717-401F-B5F4-13D0882D2076}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{A7B67D64-2DDB-46B6-9CAD-5E62F326C346}"/>
   </bookViews>
@@ -1152,7 +1152,7 @@
     <xf numFmtId="166" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="131">
+  <cellXfs count="129">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1313,7 +1313,7 @@
     <xf numFmtId="16" fontId="2" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1326,18 +1326,18 @@
     <xf numFmtId="10" fontId="6" fillId="8" borderId="22" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="167" fontId="5" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="5" fillId="7" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1345,7 +1345,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="16" fontId="2" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1361,28 +1361,26 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="2" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="29" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="5" fillId="7" borderId="30" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="5" fillId="5" borderId="32" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="31" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="5" fillId="5" borderId="32" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="5" fillId="4" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="33" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="2" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="5" fillId="5" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="5" fillId="6" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
     <xf numFmtId="167" fontId="5" fillId="5" borderId="32" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="6" borderId="32" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="32" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="2" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1412,7 +1410,7 @@
     <xf numFmtId="10" fontId="6" fillId="8" borderId="39" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="32" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="8" fillId="8" borderId="40" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1433,9 +1431,203 @@
     <cellStyle name="Normal 4" xfId="3" xr:uid="{970C258E-AAE1-4AD6-8E1A-24DB03BEBBD2}"/>
     <cellStyle name="Pourcentage" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="215">
+  <dxfs count="105">
     <dxf>
       <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -1450,7 +1642,201 @@
         <i val="0"/>
         <condense val="0"/>
         <extend val="0"/>
-        <color indexed="12"/>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color auto="1"/>
       </font>
     </dxf>
     <dxf>
@@ -1577,1398 +1963,6 @@
         <condense val="0"/>
         <extend val="0"/>
         <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="18"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
       </font>
     </dxf>
     <dxf>
@@ -19432,8 +18426,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="112">
-        <v>46121</v>
+      <c r="A1" s="110">
+        <v>46269</v>
       </c>
       <c r="B1" s="93" t="s">
         <v>0</v>
@@ -19444,13 +18438,13 @@
       <c r="D1" s="94" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="113" t="s">
+      <c r="E1" s="111" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="114" t="s">
+      <c r="F1" s="112" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="115" t="s">
+      <c r="G1" s="113" t="s">
         <v>5</v>
       </c>
       <c r="H1" s="7" t="s">
@@ -19471,13 +18465,13 @@
       <c r="A2" s="96">
         <v>1</v>
       </c>
-      <c r="B2" s="105" t="s">
+      <c r="B2" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="105" t="s">
+      <c r="C2" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="106" t="s">
+      <c r="D2" s="15" t="s">
         <v>9</v>
       </c>
       <c r="E2" s="16">
@@ -19486,7 +18480,7 @@
       <c r="F2" s="77">
         <v>128.30000000000001</v>
       </c>
-      <c r="G2" s="116">
+      <c r="G2" s="114">
         <v>0</v>
       </c>
       <c r="I2" s="20"/>
@@ -19502,13 +18496,13 @@
       <c r="A3" s="98">
         <v>2</v>
       </c>
-      <c r="B3" s="105" t="s">
+      <c r="B3" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="105" t="s">
+      <c r="C3" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="106" t="s">
+      <c r="D3" s="15" t="s">
         <v>11</v>
       </c>
       <c r="E3" s="16">
@@ -19517,7 +18511,7 @@
       <c r="F3" s="77">
         <v>90.5</v>
       </c>
-      <c r="G3" s="116">
+      <c r="G3" s="114">
         <v>0</v>
       </c>
       <c r="H3" s="8"/>
@@ -19531,13 +18525,13 @@
       <c r="A4" s="96">
         <v>3</v>
       </c>
-      <c r="B4" s="105" t="s">
+      <c r="B4" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="105" t="s">
+      <c r="C4" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="106" t="s">
+      <c r="D4" s="15" t="s">
         <v>13</v>
       </c>
       <c r="E4" s="16">
@@ -19546,7 +18540,7 @@
       <c r="F4" s="77">
         <v>44.805</v>
       </c>
-      <c r="G4" s="116">
+      <c r="G4" s="114">
         <v>0</v>
       </c>
       <c r="H4" s="8"/>
@@ -19560,13 +18554,13 @@
       <c r="A5" s="98">
         <v>4</v>
       </c>
-      <c r="B5" s="105" t="s">
+      <c r="B5" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="105" t="s">
+      <c r="C5" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="106" t="s">
+      <c r="D5" s="15" t="s">
         <v>14</v>
       </c>
       <c r="E5" s="16">
@@ -19575,7 +18569,7 @@
       <c r="F5" s="77">
         <v>12.65</v>
       </c>
-      <c r="G5" s="116">
+      <c r="G5" s="114">
         <v>0</v>
       </c>
       <c r="H5" s="8"/>
@@ -19589,13 +18583,13 @@
       <c r="A6" s="96">
         <v>5</v>
       </c>
-      <c r="B6" s="105" t="s">
+      <c r="B6" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="105" t="s">
+      <c r="C6" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="106" t="s">
+      <c r="D6" s="15" t="s">
         <v>17</v>
       </c>
       <c r="E6" s="16">
@@ -19604,7 +18598,7 @@
       <c r="F6" s="77">
         <v>216.2</v>
       </c>
-      <c r="G6" s="116">
+      <c r="G6" s="114">
         <v>0</v>
       </c>
       <c r="H6" s="8"/>
@@ -19618,13 +18612,13 @@
       <c r="A7" s="98">
         <v>6</v>
       </c>
-      <c r="B7" s="105" t="s">
+      <c r="B7" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="105" t="s">
+      <c r="C7" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="106" t="s">
+      <c r="D7" s="15" t="s">
         <v>19</v>
       </c>
       <c r="E7" s="16">
@@ -19633,7 +18627,7 @@
       <c r="F7" s="77">
         <v>19.82</v>
       </c>
-      <c r="G7" s="116">
+      <c r="G7" s="114">
         <v>0</v>
       </c>
       <c r="H7" s="8"/>
@@ -19647,13 +18641,13 @@
       <c r="A8" s="96">
         <v>7</v>
       </c>
-      <c r="B8" s="105" t="s">
+      <c r="B8" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="105" t="s">
+      <c r="C8" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="106" t="s">
+      <c r="D8" s="15" t="s">
         <v>21</v>
       </c>
       <c r="E8" s="16">
@@ -19662,7 +18656,7 @@
       <c r="F8" s="77">
         <v>0.96</v>
       </c>
-      <c r="G8" s="116">
+      <c r="G8" s="114">
         <v>0</v>
       </c>
       <c r="H8" s="8"/>
@@ -19676,13 +18670,13 @@
       <c r="A9" s="98">
         <v>8</v>
       </c>
-      <c r="B9" s="105" t="s">
+      <c r="B9" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="105" t="s">
+      <c r="C9" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="106" t="s">
+      <c r="D9" s="15" t="s">
         <v>23</v>
       </c>
       <c r="E9" s="16">
@@ -19691,7 +18685,7 @@
       <c r="F9" s="77">
         <v>9.2100000000000009</v>
       </c>
-      <c r="G9" s="116">
+      <c r="G9" s="114">
         <v>0</v>
       </c>
       <c r="H9" s="8"/>
@@ -19705,13 +18699,13 @@
       <c r="A10" s="96">
         <v>9</v>
       </c>
-      <c r="B10" s="105" t="s">
+      <c r="B10" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="105" t="s">
+      <c r="C10" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="106" t="s">
+      <c r="D10" s="15" t="s">
         <v>25</v>
       </c>
       <c r="E10" s="16">
@@ -19720,7 +18714,7 @@
       <c r="F10" s="77">
         <v>16.405000000000001</v>
       </c>
-      <c r="G10" s="116">
+      <c r="G10" s="114">
         <v>0</v>
       </c>
       <c r="H10" s="8"/>
@@ -19734,13 +18728,13 @@
       <c r="A11" s="98">
         <v>10</v>
       </c>
-      <c r="B11" s="105" t="s">
+      <c r="B11" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="105" t="s">
+      <c r="C11" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="106" t="s">
+      <c r="D11" s="15" t="s">
         <v>27</v>
       </c>
       <c r="E11" s="16">
@@ -19749,7 +18743,7 @@
       <c r="F11" s="77">
         <v>18.64</v>
       </c>
-      <c r="G11" s="116">
+      <c r="G11" s="114">
         <v>0</v>
       </c>
       <c r="H11" s="8"/>
@@ -19764,8 +18758,8 @@
       <c r="B12" s="100"/>
       <c r="C12" s="101"/>
       <c r="D12" s="102"/>
-      <c r="E12" s="117"/>
-      <c r="F12" s="118" t="s">
+      <c r="E12" s="115"/>
+      <c r="F12" s="116" t="s">
         <v>28</v>
       </c>
       <c r="G12" s="39">
@@ -19825,13 +18819,13 @@
       <c r="A16" s="96">
         <v>1</v>
       </c>
-      <c r="B16" s="105" t="s">
+      <c r="B16" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="105" t="s">
+      <c r="C16" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="D16" s="106" t="s">
+      <c r="D16" s="15" t="s">
         <v>34</v>
       </c>
       <c r="E16" s="36">
@@ -19850,13 +18844,13 @@
       <c r="A17" s="98">
         <v>2</v>
       </c>
-      <c r="B17" s="105" t="s">
+      <c r="B17" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="105" t="s">
+      <c r="C17" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="D17" s="106" t="s">
+      <c r="D17" s="15" t="s">
         <v>36</v>
       </c>
       <c r="E17" s="36">
@@ -19875,13 +18869,13 @@
       <c r="A18" s="96">
         <v>3</v>
       </c>
-      <c r="B18" s="105" t="s">
+      <c r="B18" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="C18" s="105" t="s">
+      <c r="C18" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="D18" s="106" t="s">
+      <c r="D18" s="15" t="s">
         <v>38</v>
       </c>
       <c r="E18" s="36">
@@ -19900,13 +18894,13 @@
       <c r="A19" s="98">
         <v>4</v>
       </c>
-      <c r="B19" s="105" t="s">
+      <c r="B19" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="C19" s="105" t="s">
+      <c r="C19" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="D19" s="106" t="s">
+      <c r="D19" s="15" t="s">
         <v>40</v>
       </c>
       <c r="E19" s="36">
@@ -19925,13 +18919,13 @@
       <c r="A20" s="96">
         <v>5</v>
       </c>
-      <c r="B20" s="105" t="s">
+      <c r="B20" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="C20" s="105" t="s">
+      <c r="C20" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="D20" s="106" t="s">
+      <c r="D20" s="15" t="s">
         <v>42</v>
       </c>
       <c r="E20" s="36">
@@ -19950,13 +18944,13 @@
       <c r="A21" s="98">
         <v>6</v>
       </c>
-      <c r="B21" s="105" t="s">
+      <c r="B21" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C21" s="105" t="s">
+      <c r="C21" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="D21" s="106" t="s">
+      <c r="D21" s="15" t="s">
         <v>44</v>
       </c>
       <c r="E21" s="36">
@@ -19975,13 +18969,13 @@
       <c r="A22" s="96">
         <v>7</v>
       </c>
-      <c r="B22" s="105" t="s">
+      <c r="B22" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="C22" s="105" t="s">
+      <c r="C22" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="D22" s="106" t="s">
+      <c r="D22" s="15" t="s">
         <v>46</v>
       </c>
       <c r="E22" s="36">
@@ -20000,13 +18994,13 @@
       <c r="A23" s="98">
         <v>8</v>
       </c>
-      <c r="B23" s="105" t="s">
+      <c r="B23" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="C23" s="105" t="s">
+      <c r="C23" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="D23" s="106" t="s">
+      <c r="D23" s="15" t="s">
         <v>48</v>
       </c>
       <c r="E23" s="36">
@@ -20025,13 +19019,13 @@
       <c r="A24" s="96">
         <v>9</v>
       </c>
-      <c r="B24" s="105" t="s">
+      <c r="B24" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="C24" s="105" t="s">
+      <c r="C24" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="D24" s="106" t="s">
+      <c r="D24" s="15" t="s">
         <v>50</v>
       </c>
       <c r="E24" s="36">
@@ -20050,13 +19044,13 @@
       <c r="A25" s="98">
         <v>10</v>
       </c>
-      <c r="B25" s="105" t="s">
+      <c r="B25" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="C25" s="105" t="s">
+      <c r="C25" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="D25" s="106" t="s">
+      <c r="D25" s="15" t="s">
         <v>52</v>
       </c>
       <c r="E25" s="36">
@@ -20073,9 +19067,9 @@
     </row>
     <row r="26" spans="1:11" ht="15.9" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A26" s="96"/>
-      <c r="B26" s="105"/>
+      <c r="B26" s="14"/>
       <c r="C26" s="76"/>
-      <c r="D26" s="107"/>
+      <c r="D26" s="105"/>
       <c r="E26" s="36"/>
       <c r="F26" s="38" t="s">
         <v>28</v>
@@ -20097,11 +19091,11 @@
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A27" s="108"/>
-      <c r="B27" s="109"/>
+      <c r="A27" s="106"/>
+      <c r="B27" s="107"/>
       <c r="C27" s="100"/>
-      <c r="D27" s="110"/>
-      <c r="E27" s="111"/>
+      <c r="D27" s="108"/>
+      <c r="E27" s="109"/>
       <c r="F27" s="8"/>
       <c r="H27" s="8"/>
       <c r="I27"/>
@@ -20123,13 +19117,13 @@
       <c r="D29" s="94" t="s">
         <v>2</v>
       </c>
-      <c r="E29" s="113" t="s">
+      <c r="E29" s="111" t="s">
         <v>3</v>
       </c>
-      <c r="F29" s="114" t="s">
+      <c r="F29" s="112" t="s">
         <v>4</v>
       </c>
-      <c r="G29" s="115" t="s">
+      <c r="G29" s="113" t="s">
         <v>5</v>
       </c>
       <c r="H29" s="7" t="s">
@@ -20141,13 +19135,13 @@
       <c r="A30" s="96">
         <v>1</v>
       </c>
-      <c r="B30" s="105" t="s">
+      <c r="B30" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="C30" s="105" t="s">
+      <c r="C30" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="D30" s="106" t="s">
+      <c r="D30" s="15" t="s">
         <v>56</v>
       </c>
       <c r="E30" s="16">
@@ -20156,7 +19150,7 @@
       <c r="F30" s="77">
         <v>3.95</v>
       </c>
-      <c r="G30" s="116">
+      <c r="G30" s="114">
         <v>0</v>
       </c>
       <c r="H30"/>
@@ -20166,13 +19160,13 @@
       <c r="A31" s="98">
         <v>2</v>
       </c>
-      <c r="B31" s="105" t="s">
+      <c r="B31" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="C31" s="105" t="s">
+      <c r="C31" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="D31" s="106" t="s">
+      <c r="D31" s="15" t="s">
         <v>58</v>
       </c>
       <c r="E31" s="16">
@@ -20181,7 +19175,7 @@
       <c r="F31" s="77">
         <v>28.76</v>
       </c>
-      <c r="G31" s="116">
+      <c r="G31" s="114">
         <v>0</v>
       </c>
       <c r="H31"/>
@@ -20191,13 +19185,13 @@
       <c r="A32" s="96">
         <v>3</v>
       </c>
-      <c r="B32" s="105" t="s">
+      <c r="B32" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="C32" s="105" t="s">
+      <c r="C32" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="D32" s="106" t="s">
+      <c r="D32" s="15" t="s">
         <v>60</v>
       </c>
       <c r="E32" s="16">
@@ -20206,7 +19200,7 @@
       <c r="F32" s="77">
         <v>0.28799999999999998</v>
       </c>
-      <c r="G32" s="116">
+      <c r="G32" s="114">
         <v>0</v>
       </c>
       <c r="H32"/>
@@ -20216,13 +19210,13 @@
       <c r="A33" s="98">
         <v>4</v>
       </c>
-      <c r="B33" s="105" t="s">
+      <c r="B33" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="C33" s="105" t="s">
+      <c r="C33" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="D33" s="106" t="s">
+      <c r="D33" s="15" t="s">
         <v>63</v>
       </c>
       <c r="E33" s="16">
@@ -20231,7 +19225,7 @@
       <c r="F33" s="77">
         <v>19.600000000000001</v>
       </c>
-      <c r="G33" s="116">
+      <c r="G33" s="114">
         <v>0</v>
       </c>
       <c r="H33"/>
@@ -20241,13 +19235,13 @@
       <c r="A34" s="96">
         <v>5</v>
       </c>
-      <c r="B34" s="105" t="s">
+      <c r="B34" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="C34" s="105" t="s">
+      <c r="C34" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="D34" s="106" t="s">
+      <c r="D34" s="15" t="s">
         <v>65</v>
       </c>
       <c r="E34" s="16">
@@ -20256,7 +19250,7 @@
       <c r="F34" s="77">
         <v>1.095</v>
       </c>
-      <c r="G34" s="116">
+      <c r="G34" s="114">
         <v>0</v>
       </c>
       <c r="H34"/>
@@ -20266,13 +19260,13 @@
       <c r="A35" s="98">
         <v>6</v>
       </c>
-      <c r="B35" s="105" t="s">
+      <c r="B35" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="C35" s="105" t="s">
+      <c r="C35" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="D35" s="106" t="s">
+      <c r="D35" s="15" t="s">
         <v>67</v>
       </c>
       <c r="E35" s="16">
@@ -20281,7 +19275,7 @@
       <c r="F35" s="77">
         <v>4.92</v>
       </c>
-      <c r="G35" s="116">
+      <c r="G35" s="114">
         <v>0</v>
       </c>
       <c r="H35"/>
@@ -20291,13 +19285,13 @@
       <c r="A36" s="96">
         <v>7</v>
       </c>
-      <c r="B36" s="105" t="s">
+      <c r="B36" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="C36" s="105" t="s">
+      <c r="C36" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="D36" s="106" t="s">
+      <c r="D36" s="15" t="s">
         <v>69</v>
       </c>
       <c r="E36" s="16">
@@ -20306,7 +19300,7 @@
       <c r="F36" s="77">
         <v>32.5</v>
       </c>
-      <c r="G36" s="116">
+      <c r="G36" s="114">
         <v>0</v>
       </c>
       <c r="H36"/>
@@ -20316,13 +19310,13 @@
       <c r="A37" s="98">
         <v>8</v>
       </c>
-      <c r="B37" s="105" t="s">
+      <c r="B37" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="C37" s="105" t="s">
+      <c r="C37" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="D37" s="106" t="s">
+      <c r="D37" s="15" t="s">
         <v>71</v>
       </c>
       <c r="E37" s="16">
@@ -20331,7 +19325,7 @@
       <c r="F37" s="77">
         <v>0.46600000000000003</v>
       </c>
-      <c r="G37" s="116">
+      <c r="G37" s="114">
         <v>0</v>
       </c>
       <c r="H37"/>
@@ -20342,13 +19336,13 @@
       <c r="A38" s="96">
         <v>9</v>
       </c>
-      <c r="B38" s="105" t="s">
+      <c r="B38" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="C38" s="105" t="s">
+      <c r="C38" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="D38" s="106" t="s">
+      <c r="D38" s="15" t="s">
         <v>73</v>
       </c>
       <c r="E38" s="16">
@@ -20357,7 +19351,7 @@
       <c r="F38" s="77">
         <v>117.5</v>
       </c>
-      <c r="G38" s="116">
+      <c r="G38" s="114">
         <v>0</v>
       </c>
       <c r="H38"/>
@@ -20368,13 +19362,13 @@
       <c r="A39" s="98">
         <v>10</v>
       </c>
-      <c r="B39" s="105" t="s">
+      <c r="B39" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="C39" s="105" t="s">
+      <c r="C39" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="D39" s="106" t="s">
+      <c r="D39" s="15" t="s">
         <v>75</v>
       </c>
       <c r="E39" s="16">
@@ -20383,22 +19377,22 @@
       <c r="F39" s="77">
         <v>5.14</v>
       </c>
-      <c r="G39" s="116">
+      <c r="G39" s="114">
         <v>0</v>
       </c>
       <c r="H39"/>
       <c r="I39"/>
     </row>
     <row r="40" spans="1:16" ht="16.3" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A40" s="125"/>
-      <c r="B40" s="126"/>
-      <c r="C40" s="127"/>
-      <c r="D40" s="128"/>
-      <c r="E40" s="129"/>
-      <c r="F40" s="118" t="s">
+      <c r="A40" s="123"/>
+      <c r="B40" s="124"/>
+      <c r="C40" s="125"/>
+      <c r="D40" s="126"/>
+      <c r="E40" s="127"/>
+      <c r="F40" s="116" t="s">
         <v>28</v>
       </c>
-      <c r="G40" s="130">
+      <c r="G40" s="128">
         <v>0</v>
       </c>
       <c r="H40" s="31" t="s">
@@ -20437,13 +19431,13 @@
       <c r="D42" s="94" t="s">
         <v>2</v>
       </c>
-      <c r="E42" s="113" t="s">
+      <c r="E42" s="111" t="s">
         <v>3</v>
       </c>
-      <c r="F42" s="114" t="s">
+      <c r="F42" s="112" t="s">
         <v>4</v>
       </c>
-      <c r="G42" s="121" t="s">
+      <c r="G42" s="119" t="s">
         <v>5</v>
       </c>
       <c r="H42" s="7" t="s">
@@ -20455,12 +19449,12 @@
       <c r="A43" s="96">
         <v>1</v>
       </c>
-      <c r="B43" s="105"/>
-      <c r="C43" s="105"/>
-      <c r="D43" s="106"/>
+      <c r="B43" s="14"/>
+      <c r="C43" s="14"/>
+      <c r="D43" s="15"/>
       <c r="E43" s="16"/>
       <c r="F43" s="77"/>
-      <c r="G43" s="122" t="e">
+      <c r="G43" s="120" t="e">
         <v>#VALUE!</v>
       </c>
       <c r="H43"/>
@@ -20470,12 +19464,12 @@
       <c r="A44" s="98">
         <v>2</v>
       </c>
-      <c r="B44" s="105"/>
-      <c r="C44" s="105"/>
-      <c r="D44" s="106"/>
+      <c r="B44" s="14"/>
+      <c r="C44" s="14"/>
+      <c r="D44" s="15"/>
       <c r="E44" s="16"/>
       <c r="F44" s="77"/>
-      <c r="G44" s="122" t="e">
+      <c r="G44" s="120" t="e">
         <v>#VALUE!</v>
       </c>
       <c r="H44"/>
@@ -20485,12 +19479,12 @@
       <c r="A45" s="96">
         <v>3</v>
       </c>
-      <c r="B45" s="105"/>
-      <c r="C45" s="105"/>
-      <c r="D45" s="106"/>
+      <c r="B45" s="14"/>
+      <c r="C45" s="14"/>
+      <c r="D45" s="15"/>
       <c r="E45" s="16"/>
       <c r="F45" s="77"/>
-      <c r="G45" s="122" t="e">
+      <c r="G45" s="120" t="e">
         <v>#VALUE!</v>
       </c>
       <c r="H45"/>
@@ -20500,12 +19494,12 @@
       <c r="A46" s="98">
         <v>4</v>
       </c>
-      <c r="B46" s="105"/>
-      <c r="C46" s="105"/>
-      <c r="D46" s="106"/>
+      <c r="B46" s="14"/>
+      <c r="C46" s="14"/>
+      <c r="D46" s="15"/>
       <c r="E46" s="16"/>
       <c r="F46" s="77"/>
-      <c r="G46" s="122" t="e">
+      <c r="G46" s="120" t="e">
         <v>#VALUE!</v>
       </c>
       <c r="H46"/>
@@ -20515,12 +19509,12 @@
       <c r="A47" s="96">
         <v>5</v>
       </c>
-      <c r="B47" s="105"/>
-      <c r="C47" s="105"/>
-      <c r="D47" s="106"/>
+      <c r="B47" s="14"/>
+      <c r="C47" s="14"/>
+      <c r="D47" s="15"/>
       <c r="E47" s="16"/>
       <c r="F47" s="77"/>
-      <c r="G47" s="122" t="e">
+      <c r="G47" s="120" t="e">
         <v>#VALUE!</v>
       </c>
       <c r="H47"/>
@@ -20530,12 +19524,12 @@
       <c r="A48" s="98">
         <v>6</v>
       </c>
-      <c r="B48" s="105"/>
-      <c r="C48" s="105"/>
-      <c r="D48" s="106"/>
+      <c r="B48" s="14"/>
+      <c r="C48" s="14"/>
+      <c r="D48" s="15"/>
       <c r="E48" s="16"/>
       <c r="F48" s="77"/>
-      <c r="G48" s="122" t="e">
+      <c r="G48" s="120" t="e">
         <v>#VALUE!</v>
       </c>
       <c r="H48"/>
@@ -20545,12 +19539,12 @@
       <c r="A49" s="96">
         <v>7</v>
       </c>
-      <c r="B49" s="105"/>
-      <c r="C49" s="105"/>
-      <c r="D49" s="106"/>
+      <c r="B49" s="14"/>
+      <c r="C49" s="14"/>
+      <c r="D49" s="15"/>
       <c r="E49" s="16"/>
       <c r="F49" s="77"/>
-      <c r="G49" s="122" t="e">
+      <c r="G49" s="120" t="e">
         <v>#VALUE!</v>
       </c>
       <c r="H49"/>
@@ -20560,12 +19554,12 @@
       <c r="A50" s="98">
         <v>8</v>
       </c>
-      <c r="B50" s="105"/>
-      <c r="C50" s="105"/>
-      <c r="D50" s="106"/>
+      <c r="B50" s="14"/>
+      <c r="C50" s="14"/>
+      <c r="D50" s="15"/>
       <c r="E50" s="16"/>
       <c r="F50" s="77"/>
-      <c r="G50" s="122" t="e">
+      <c r="G50" s="120" t="e">
         <v>#VALUE!</v>
       </c>
       <c r="H50"/>
@@ -20575,12 +19569,12 @@
       <c r="A51" s="96">
         <v>9</v>
       </c>
-      <c r="B51" s="105"/>
-      <c r="C51" s="105"/>
-      <c r="D51" s="106"/>
+      <c r="B51" s="14"/>
+      <c r="C51" s="14"/>
+      <c r="D51" s="15"/>
       <c r="E51" s="16"/>
       <c r="F51" s="77"/>
-      <c r="G51" s="122" t="e">
+      <c r="G51" s="120" t="e">
         <v>#VALUE!</v>
       </c>
       <c r="H51"/>
@@ -20590,12 +19584,12 @@
       <c r="A52" s="98">
         <v>10</v>
       </c>
-      <c r="B52" s="105"/>
-      <c r="C52" s="105"/>
-      <c r="D52" s="106"/>
+      <c r="B52" s="14"/>
+      <c r="C52" s="14"/>
+      <c r="D52" s="15"/>
       <c r="E52" s="16"/>
       <c r="F52" s="77"/>
-      <c r="G52" s="122" t="e">
+      <c r="G52" s="120" t="e">
         <v>#VALUE!</v>
       </c>
       <c r="H52"/>
@@ -20606,11 +19600,11 @@
       <c r="B53" s="100"/>
       <c r="C53" s="101"/>
       <c r="D53" s="102"/>
-      <c r="E53" s="123"/>
-      <c r="F53" s="120" t="s">
+      <c r="E53" s="121"/>
+      <c r="F53" s="118" t="s">
         <v>28</v>
       </c>
-      <c r="G53" s="124" t="e">
+      <c r="G53" s="122" t="e">
         <v>#VALUE!</v>
       </c>
       <c r="H53" s="31" t="s">
@@ -20668,9 +19662,7 @@
       <c r="B56" s="75"/>
       <c r="C56" s="76"/>
       <c r="D56" s="75"/>
-      <c r="E56" s="97">
-        <v>16.405000000000001</v>
-      </c>
+      <c r="E56" s="97"/>
       <c r="F56" s="17"/>
       <c r="G56" s="53" t="e">
         <v>#VALUE!</v>
@@ -20684,9 +19676,7 @@
       <c r="B57" s="80"/>
       <c r="C57" s="26"/>
       <c r="D57" s="80"/>
-      <c r="E57" s="97">
-        <v>9.9320000000000004</v>
-      </c>
+      <c r="E57" s="97"/>
       <c r="F57" s="17"/>
       <c r="G57" s="53" t="e">
         <v>#VALUE!</v>
@@ -20701,9 +19691,7 @@
       <c r="B58" s="75"/>
       <c r="C58" s="76"/>
       <c r="D58" s="75"/>
-      <c r="E58" s="97">
-        <v>21.15</v>
-      </c>
+      <c r="E58" s="97"/>
       <c r="F58" s="17"/>
       <c r="G58" s="53" t="e">
         <v>#VALUE!</v>
@@ -20719,9 +19707,7 @@
       <c r="B59" s="80"/>
       <c r="C59" s="26"/>
       <c r="D59" s="80"/>
-      <c r="E59" s="97">
-        <v>35.159999999999997</v>
-      </c>
+      <c r="E59" s="97"/>
       <c r="F59" s="17"/>
       <c r="G59" s="53" t="e">
         <v>#VALUE!</v>
@@ -20737,9 +19723,7 @@
       <c r="B60" s="75"/>
       <c r="C60" s="76"/>
       <c r="D60" s="75"/>
-      <c r="E60" s="97">
-        <v>2.56</v>
-      </c>
+      <c r="E60" s="97"/>
       <c r="F60" s="17"/>
       <c r="G60" s="53" t="e">
         <v>#VALUE!</v>
@@ -20755,9 +19739,7 @@
       <c r="B61" s="80"/>
       <c r="C61" s="26"/>
       <c r="D61" s="80"/>
-      <c r="E61" s="97">
-        <v>30.45</v>
-      </c>
+      <c r="E61" s="97"/>
       <c r="F61" s="17"/>
       <c r="G61" s="53" t="e">
         <v>#VALUE!</v>
@@ -20773,9 +19755,7 @@
       <c r="B62" s="75"/>
       <c r="C62" s="76"/>
       <c r="D62" s="75"/>
-      <c r="E62" s="97">
-        <v>15.71</v>
-      </c>
+      <c r="E62" s="97"/>
       <c r="F62" s="17"/>
       <c r="G62" s="53" t="e">
         <v>#VALUE!</v>
@@ -20790,9 +19770,7 @@
       <c r="B63" s="80"/>
       <c r="C63" s="26"/>
       <c r="D63" s="80"/>
-      <c r="E63" s="97">
-        <v>46.9</v>
-      </c>
+      <c r="E63" s="97"/>
       <c r="F63" s="17"/>
       <c r="G63" s="53" t="e">
         <v>#VALUE!</v>
@@ -21231,7 +20209,7 @@
         <v>4</v>
       </c>
       <c r="B85" s="80"/>
-      <c r="C85" s="119"/>
+      <c r="C85" s="117"/>
       <c r="D85" s="80"/>
       <c r="E85" s="16"/>
       <c r="F85" s="77"/>
@@ -21246,7 +20224,7 @@
         <v>5</v>
       </c>
       <c r="B86" s="75"/>
-      <c r="C86" s="119"/>
+      <c r="C86" s="117"/>
       <c r="D86" s="75"/>
       <c r="E86" s="16"/>
       <c r="F86" s="77"/>
@@ -21261,7 +20239,7 @@
         <v>6</v>
       </c>
       <c r="B87" s="80"/>
-      <c r="C87" s="119"/>
+      <c r="C87" s="117"/>
       <c r="D87" s="80"/>
       <c r="E87" s="16"/>
       <c r="F87" s="77"/>
@@ -21291,7 +20269,7 @@
         <v>8</v>
       </c>
       <c r="B89" s="80"/>
-      <c r="C89" s="119"/>
+      <c r="C89" s="117"/>
       <c r="D89" s="80"/>
       <c r="E89" s="16"/>
       <c r="F89" s="77"/>
@@ -21337,7 +20315,7 @@
       <c r="C92" s="83"/>
       <c r="D92" s="54"/>
       <c r="E92" s="84"/>
-      <c r="F92" s="120" t="s">
+      <c r="F92" s="118" t="s">
         <v>28</v>
       </c>
       <c r="G92" s="50" t="e">
@@ -23788,434 +22766,428 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B56:B65">
-    <cfRule type="expression" dxfId="106" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="104" priority="6" stopIfTrue="1">
       <formula>IF(AO56&gt;0,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B69:B78">
-    <cfRule type="expression" dxfId="105" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="103" priority="4" stopIfTrue="1">
       <formula>IF(AO69&gt;0,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B81">
-    <cfRule type="expression" dxfId="104" priority="51" stopIfTrue="1">
+    <cfRule type="expression" dxfId="102" priority="51" stopIfTrue="1">
       <formula>IF(AN62&gt;0,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B82:B91">
-    <cfRule type="expression" dxfId="103" priority="10" stopIfTrue="1">
+    <cfRule type="expression" dxfId="101" priority="10" stopIfTrue="1">
       <formula>IF(AL82&gt;0,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B92">
-    <cfRule type="expression" dxfId="102" priority="47" stopIfTrue="1">
+    <cfRule type="expression" dxfId="100" priority="47" stopIfTrue="1">
       <formula>IF(AL91&gt;0,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B95">
-    <cfRule type="expression" dxfId="101" priority="50" stopIfTrue="1">
+    <cfRule type="expression" dxfId="99" priority="50" stopIfTrue="1">
       <formula>IF(AN75&gt;0,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B96:B105">
-    <cfRule type="expression" dxfId="100" priority="8" stopIfTrue="1">
+    <cfRule type="expression" dxfId="98" priority="8" stopIfTrue="1">
       <formula>IF(AO96&gt;0,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B106">
-    <cfRule type="expression" dxfId="99" priority="48" stopIfTrue="1">
+    <cfRule type="expression" dxfId="97" priority="48" stopIfTrue="1">
       <formula>IF(AN104&gt;0,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B107">
-    <cfRule type="expression" dxfId="98" priority="49" stopIfTrue="1">
+    <cfRule type="expression" dxfId="96" priority="49" stopIfTrue="1">
       <formula>IF(AN104&gt;0,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D56:D65">
-    <cfRule type="expression" dxfId="97" priority="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="95" priority="5" stopIfTrue="1">
       <formula>IF(AQ56&gt;0,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D69:D78">
-    <cfRule type="expression" dxfId="96" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="94" priority="3" stopIfTrue="1">
       <formula>IF(AQ69&gt;0,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D82:D91">
-    <cfRule type="expression" dxfId="95" priority="9" stopIfTrue="1">
+    <cfRule type="expression" dxfId="93" priority="9" stopIfTrue="1">
       <formula>IF(AN82&gt;0,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D96:D105">
-    <cfRule type="expression" dxfId="94" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="92" priority="7" stopIfTrue="1">
       <formula>IF(AQ96&gt;0,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F11 F16:F25">
-    <cfRule type="expression" dxfId="93" priority="20" stopIfTrue="1">
+    <cfRule type="expression" dxfId="91" priority="20" stopIfTrue="1">
       <formula>IF(#REF!="AAA",TRUE,FALSE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="92" priority="21" stopIfTrue="1">
+    <cfRule type="expression" dxfId="90" priority="21" stopIfTrue="1">
       <formula>IF($T200="AAA",TRUE,FALSE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="91" priority="22" stopIfTrue="1">
+    <cfRule type="expression" dxfId="89" priority="22" stopIfTrue="1">
       <formula>IF($U200="AAA",TRUE,FALSE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="90" priority="23" stopIfTrue="1">
+    <cfRule type="expression" dxfId="88" priority="23" stopIfTrue="1">
       <formula>IF($AN1048554="AAA",TRUE,FALSE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="89" priority="24" stopIfTrue="1">
+    <cfRule type="expression" dxfId="87" priority="24" stopIfTrue="1">
       <formula>IF($T200="AAA",TRUE,FALSE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="88" priority="25" stopIfTrue="1">
+    <cfRule type="expression" dxfId="86" priority="25" stopIfTrue="1">
       <formula>IF($U200="AAA",TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F30:F39">
-    <cfRule type="expression" dxfId="87" priority="81" stopIfTrue="1">
+    <cfRule type="expression" dxfId="85" priority="82" stopIfTrue="1">
+      <formula>IF($T230="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="84" priority="81" stopIfTrue="1">
       <formula>IF(#REF!="AAA",TRUE,FALSE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="86" priority="82" stopIfTrue="1">
-      <formula>IF($T230="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="85" priority="83" stopIfTrue="1">
+    <cfRule type="expression" dxfId="83" priority="83" stopIfTrue="1">
       <formula>IF($U230="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="84" priority="84" stopIfTrue="1">
-      <formula>IF($AN5="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="83" priority="85" stopIfTrue="1">
-      <formula>IF($T230="AAA",TRUE,FALSE)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="82" priority="86" stopIfTrue="1">
       <formula>IF($U230="AAA",TRUE,FALSE)</formula>
     </cfRule>
+    <cfRule type="expression" dxfId="81" priority="85" stopIfTrue="1">
+      <formula>IF($T230="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="80" priority="84" stopIfTrue="1">
+      <formula>IF($AN5="AAA",TRUE,FALSE)</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F43:F52">
-    <cfRule type="expression" dxfId="81" priority="87" stopIfTrue="1">
-      <formula>IF(#REF!="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="80" priority="88" stopIfTrue="1">
+    <cfRule type="expression" dxfId="79" priority="91" stopIfTrue="1">
       <formula>IF($T242="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="79" priority="89" stopIfTrue="1">
-      <formula>IF($U242="AAA",TRUE,FALSE)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="78" priority="90" stopIfTrue="1">
       <formula>IF($AN17="AAA",TRUE,FALSE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="77" priority="91" stopIfTrue="1">
+    <cfRule type="expression" dxfId="77" priority="89" stopIfTrue="1">
+      <formula>IF($U242="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="76" priority="88" stopIfTrue="1">
       <formula>IF($T242="AAA",TRUE,FALSE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="76" priority="92" stopIfTrue="1">
+    <cfRule type="expression" dxfId="75" priority="87" stopIfTrue="1">
+      <formula>IF(#REF!="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="74" priority="92" stopIfTrue="1">
       <formula>IF($U242="AAA",TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F56">
-    <cfRule type="expression" dxfId="75" priority="77" stopIfTrue="1">
+    <cfRule type="expression" dxfId="73" priority="80" stopIfTrue="1">
+      <formula>IF($U254="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="72" priority="79" stopIfTrue="1">
+      <formula>IF($T254="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="71" priority="78" stopIfTrue="1">
+      <formula>IF($AN28="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F56:F67">
+    <cfRule type="expression" dxfId="70" priority="77" stopIfTrue="1">
       <formula>IF(#REF!="AAA",TRUE,FALSE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="74" priority="78" stopIfTrue="1">
-      <formula>IF($AN28="AAA",TRUE,FALSE)</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F57:F67">
+    <cfRule type="expression" dxfId="69" priority="94" stopIfTrue="1">
+      <formula>IF($AK29="AAA",TRUE,FALSE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="73" priority="79" stopIfTrue="1">
-      <formula>IF($T254="AAA",TRUE,FALSE)</formula>
+    <cfRule type="expression" dxfId="68" priority="95" stopIfTrue="1">
+      <formula>IF($T255="AAA",TRUE,FALSE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="72" priority="80" stopIfTrue="1">
-      <formula>IF($U254="AAA",TRUE,FALSE)</formula>
+    <cfRule type="expression" dxfId="67" priority="96" stopIfTrue="1">
+      <formula>IF($U255="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F69">
+    <cfRule type="expression" dxfId="66" priority="98" stopIfTrue="1">
+      <formula>IF($U268="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="65" priority="97" stopIfTrue="1">
+      <formula>IF($T268="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="64" priority="99" stopIfTrue="1">
+      <formula>IF($AJ43="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="63" priority="100" stopIfTrue="1">
+      <formula>IF($T268="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="62" priority="101" stopIfTrue="1">
+      <formula>IF($U268="AAA",TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F69:F78">
-    <cfRule type="expression" dxfId="71" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="61" priority="2" stopIfTrue="1">
       <formula>IF(#REF!="AAA",TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="F70:F78">
+    <cfRule type="expression" dxfId="60" priority="102" stopIfTrue="1">
+      <formula>IF($AJ42="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="59" priority="103" stopIfTrue="1">
+      <formula>IF($T267="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="58" priority="104" stopIfTrue="1">
+      <formula>IF($U267="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F82">
+    <cfRule type="expression" dxfId="57" priority="105" stopIfTrue="1">
+      <formula>IF($AJ53="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="56" priority="106" stopIfTrue="1">
+      <formula>IF($T278="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="55" priority="107" stopIfTrue="1">
+      <formula>IF($U278="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F82:F91">
-    <cfRule type="expression" dxfId="70" priority="66" stopIfTrue="1">
+    <cfRule type="expression" dxfId="54" priority="66" stopIfTrue="1">
       <formula>IF(#REF!="AAA",TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F83:F91">
-    <cfRule type="expression" dxfId="69" priority="67" stopIfTrue="1">
+    <cfRule type="expression" dxfId="53" priority="67" stopIfTrue="1">
       <formula>IF($AN55="AAA",TRUE,FALSE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="68" priority="68" stopIfTrue="1">
+    <cfRule type="expression" dxfId="52" priority="69" stopIfTrue="1">
+      <formula>IF($U279="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="51" priority="68" stopIfTrue="1">
       <formula>IF($T279="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="67" priority="69" stopIfTrue="1">
-      <formula>IF($U279="AAA",TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F96:F97">
-    <cfRule type="expression" dxfId="66" priority="74" stopIfTrue="1">
-      <formula>IF($AN65="AAA",TRUE,FALSE)</formula>
+    <cfRule type="expression" dxfId="50" priority="76" stopIfTrue="1">
+      <formula>IF($U291="AAA",TRUE,FALSE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="65" priority="75" stopIfTrue="1">
+    <cfRule type="expression" dxfId="49" priority="75" stopIfTrue="1">
       <formula>IF($T291="AAA",TRUE,FALSE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="64" priority="76" stopIfTrue="1">
-      <formula>IF($U291="AAA",TRUE,FALSE)</formula>
+    <cfRule type="expression" dxfId="48" priority="74" stopIfTrue="1">
+      <formula>IF($AN65="AAA",TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F96:F106">
-    <cfRule type="expression" dxfId="63" priority="70" stopIfTrue="1">
+    <cfRule type="expression" dxfId="47" priority="70" stopIfTrue="1">
       <formula>IF(#REF!="AAA",TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F98:F106">
-    <cfRule type="expression" dxfId="62" priority="71" stopIfTrue="1">
+    <cfRule type="expression" dxfId="46" priority="73" stopIfTrue="1">
+      <formula>IF($U293="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="45" priority="72" stopIfTrue="1">
+      <formula>IF($T293="AAA",TRUE,FALSE)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="44" priority="71" stopIfTrue="1">
       <formula>IF($AN68="AAA",TRUE,FALSE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="61" priority="72" stopIfTrue="1">
-      <formula>IF($T293="AAA",TRUE,FALSE)</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G12 G16:G26 G30:G41">
+    <cfRule type="cellIs" dxfId="43" priority="54" stopIfTrue="1" operator="greaterThanOrEqual">
+      <formula>#REF!</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="60" priority="73" stopIfTrue="1">
-      <formula>IF($U293="AAA",TRUE,FALSE)</formula>
+    <cfRule type="cellIs" dxfId="42" priority="53" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G16:G26 G2:G12 G30:G41">
-    <cfRule type="cellIs" dxfId="59" priority="53" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="G2:G12 G16:G28">
+    <cfRule type="cellIs" dxfId="41" priority="26" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="58" priority="54" stopIfTrue="1" operator="greaterThanOrEqual">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G30:G41 G2:G12 G16:G26">
+    <cfRule type="cellIs" dxfId="40" priority="52" operator="greaterThan">
       <formula>#REF!</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G16:G28 G2:G12">
-    <cfRule type="cellIs" dxfId="57" priority="26" stopIfTrue="1" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G16:G26 G2:G12 G30:G41">
-    <cfRule type="cellIs" dxfId="56" priority="52" operator="greaterThan">
-      <formula>#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G43:G54 G56:G67 G30:G41">
-    <cfRule type="cellIs" dxfId="55" priority="43" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="G43:G54 G30:G41 G56:G67">
+    <cfRule type="cellIs" dxfId="39" priority="43" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G43:G54">
-    <cfRule type="cellIs" dxfId="54" priority="31" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="38" priority="34" stopIfTrue="1" operator="greaterThanOrEqual">
+      <formula>#REF!</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="37" priority="33" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="53" priority="32" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="36" priority="32" operator="greaterThan">
       <formula>#REF!</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="52" priority="33" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="35" priority="31" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="51" priority="34" stopIfTrue="1" operator="greaterThanOrEqual">
-      <formula>#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G53:G54">
-    <cfRule type="cellIs" dxfId="50" priority="17" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="34" priority="19" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>#REF!</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="49" priority="18" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="33" priority="18" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="48" priority="19" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="32" priority="17" operator="greaterThan">
       <formula>#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G56:G67">
-    <cfRule type="cellIs" dxfId="47" priority="44" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="31" priority="45" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="30" priority="46" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>#REF!</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="45" stopIfTrue="1" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="45" priority="46" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="29" priority="44" operator="greaterThan">
       <formula>#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G69:G80">
-    <cfRule type="cellIs" dxfId="44" priority="27" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="28" priority="30" stopIfTrue="1" operator="greaterThanOrEqual">
+      <formula>#REF!</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="27" priority="29" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="43" priority="28" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="26" priority="28" operator="greaterThan">
       <formula>#REF!</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="29" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="25" priority="27" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="41" priority="30" stopIfTrue="1" operator="greaterThanOrEqual">
-      <formula>#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G82:G92">
-    <cfRule type="cellIs" dxfId="40" priority="39" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="24" priority="41" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="39" priority="40" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="23" priority="39" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="22" priority="42" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>#REF!</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="38" priority="41" stopIfTrue="1" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="42" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="21" priority="40" operator="greaterThan">
       <formula>#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G96:G106">
-    <cfRule type="cellIs" dxfId="36" priority="35" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="20" priority="38" stopIfTrue="1" operator="greaterThanOrEqual">
+      <formula>#REF!</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="19" priority="37" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="35" priority="36" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="18" priority="36" operator="greaterThan">
       <formula>#REF!</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="37" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="17" priority="35" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="38" stopIfTrue="1" operator="greaterThanOrEqual">
-      <formula>#REF!</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H81">
+    <cfRule type="cellIs" dxfId="16" priority="16" operator="greaterThan">
+      <formula>$H81</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I12 I53 K53 I66 K66">
-    <cfRule type="cellIs" dxfId="32" priority="60" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="15" priority="60" operator="greaterThan">
       <formula>$K12</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I26">
-    <cfRule type="cellIs" dxfId="31" priority="11" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="14" priority="11" operator="greaterThan">
       <formula>$K26</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="I40 K40:K41">
+    <cfRule type="cellIs" dxfId="13" priority="1" operator="greaterThan">
+      <formula>$K40</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="I75">
-    <cfRule type="cellIs" dxfId="30" priority="61" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="12" priority="61" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I93:I94">
-    <cfRule type="cellIs" dxfId="29" priority="59" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="11" priority="59" operator="greaterThan">
       <formula>$K93</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I107">
-    <cfRule type="cellIs" dxfId="28" priority="58" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="10" priority="58" operator="greaterThan">
       <formula>$K107</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I109">
-    <cfRule type="cellIs" dxfId="27" priority="56" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="9" priority="56" operator="greaterThan">
       <formula>$K109</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J97">
-    <cfRule type="cellIs" dxfId="26" priority="63" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="8" priority="63" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J103">
-    <cfRule type="cellIs" dxfId="25" priority="62" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="7" priority="62" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="cellIs" dxfId="24" priority="14" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="14" operator="greaterThan">
       <formula>$K12</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K26">
-    <cfRule type="cellIs" dxfId="23" priority="13" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="13" operator="greaterThan">
       <formula>$K26</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K41">
-    <cfRule type="cellIs" dxfId="22" priority="12" operator="greaterThan">
-      <formula>$K41</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H81">
-    <cfRule type="cellIs" dxfId="21" priority="16" operator="greaterThan">
-      <formula>$H81</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="K93:K94">
-    <cfRule type="cellIs" dxfId="20" priority="15" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="4" priority="15" operator="greaterThan">
       <formula>$K93</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K104">
-    <cfRule type="cellIs" dxfId="19" priority="64" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="3" priority="64" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K107">
-    <cfRule type="cellIs" dxfId="18" priority="57" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="57" operator="greaterThan">
       <formula>$I107</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K109">
-    <cfRule type="cellIs" dxfId="17" priority="55" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="55" operator="greaterThan">
       <formula>$I109</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P37:P38">
-    <cfRule type="cellIs" dxfId="16" priority="65" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="65" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F57:F67">
-    <cfRule type="expression" dxfId="15" priority="93" stopIfTrue="1">
-      <formula>IF(#REF!="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="14" priority="94" stopIfTrue="1">
-      <formula>IF($AK29="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="13" priority="95" stopIfTrue="1">
-      <formula>IF($T255="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="12" priority="96" stopIfTrue="1">
-      <formula>IF($U255="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F69">
-    <cfRule type="expression" dxfId="11" priority="97" stopIfTrue="1">
-      <formula>IF($T268="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="10" priority="98" stopIfTrue="1">
-      <formula>IF($U268="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="9" priority="99" stopIfTrue="1">
-      <formula>IF($AJ43="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="8" priority="100" stopIfTrue="1">
-      <formula>IF($T268="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="7" priority="101" stopIfTrue="1">
-      <formula>IF($U268="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F70:F78">
-    <cfRule type="expression" dxfId="6" priority="102" stopIfTrue="1">
-      <formula>IF($AJ42="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="5" priority="103" stopIfTrue="1">
-      <formula>IF($T267="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="104" stopIfTrue="1">
-      <formula>IF($U267="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F82">
-    <cfRule type="expression" dxfId="3" priority="105" stopIfTrue="1">
-      <formula>IF($AJ53="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="2" priority="106" stopIfTrue="1">
-      <formula>IF($T278="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="107" stopIfTrue="1">
-      <formula>IF($U278="AAA",TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I40 K40">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
-      <formula>$K40</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
